--- a/GBDS JUNE FILES 2026/INVENTORY COUNT SHEET - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/INVENTORY COUNT SHEET - JUNE 2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C37AD6-E1A2-4DB3-BEA5-7BB062115617}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{738CC4FC-89ED-484C-B54D-E631CEE9E033}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
@@ -10734,13 +10734,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -13673,13 +13673,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>

--- a/GBDS JUNE FILES 2026/INVENTORY COUNT SHEET - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/INVENTORY COUNT SHEET - JUNE 2026.xlsx
@@ -5,23 +5,23 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS\GBDS JUNE FILES 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{738CC4FC-89ED-484C-B54D-E631CEE9E033}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B0C753E-0D1D-4017-9A93-30A07130E4A3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
-    <sheet name="06-03-2026" sheetId="55" r:id="rId2"/>
-    <sheet name="06-03-2026 (2)" sheetId="56" r:id="rId3"/>
-    <sheet name="06-03-2026 (3)" sheetId="57" r:id="rId4"/>
+    <sheet name="06-01-2026" sheetId="57" r:id="rId2"/>
+    <sheet name="06-02-2026" sheetId="55" r:id="rId3"/>
+    <sheet name="06-04-2026" sheetId="56" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'06-03-2026'!$A$1:$W$59</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'06-03-2026 (2)'!$A$1:$W$59</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'06-03-2026 (3)'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'06-01-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'06-02-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'06-04-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="74">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -254,6 +254,12 @@
   </si>
   <si>
     <t xml:space="preserve">DATE: </t>
+  </si>
+  <si>
+    <t>DATE: 06/01/2026</t>
+  </si>
+  <si>
+    <t>DATE: 06/02/2026</t>
   </si>
   <si>
     <t>DATE: 06/03/2026</t>
@@ -4874,6 +4880,3152 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{904A2011-2D80-4AE1-96EB-73435B2D09C4}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="105" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="105"/>
+      <c r="K1" s="105"/>
+      <c r="L1" s="105"/>
+      <c r="M1" s="105"/>
+      <c r="N1" s="105"/>
+      <c r="O1" s="105"/>
+      <c r="P1" s="105"/>
+      <c r="Q1" s="105"/>
+      <c r="R1" s="105"/>
+      <c r="S1" s="105"/>
+      <c r="T1" s="105"/>
+      <c r="U1" s="105"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="106" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="106"/>
+      <c r="E4" s="106"/>
+      <c r="F4" s="106"/>
+      <c r="G4" s="106"/>
+      <c r="H4" s="106"/>
+      <c r="I4" s="106"/>
+      <c r="J4" s="107"/>
+      <c r="K4" s="108"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="109" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="115" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="98" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="113" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="114"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="97"/>
+      <c r="Q5" s="97"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="110"/>
+      <c r="U5" s="116"/>
+      <c r="V5" s="99"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="97"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="97"/>
+      <c r="Q6" s="97"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="52">
+        <v>30</v>
+      </c>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
+      <c r="J7" s="53"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
+      <c r="L7" s="55"/>
+      <c r="M7" s="56">
+        <v>2</v>
+      </c>
+      <c r="N7" s="57">
+        <v>22</v>
+      </c>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="53">
+        <v>1</v>
+      </c>
+      <c r="R7" s="54"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="58">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>31</v>
+      </c>
+      <c r="U7" s="58">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>847</v>
+      </c>
+      <c r="V7" s="58">
+        <f>U7/24</f>
+        <v>35.291666666666664</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="59">
+        <f>30+3+63</f>
+        <v>96</v>
+      </c>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="63"/>
+      <c r="N8" s="64"/>
+      <c r="O8" s="65"/>
+      <c r="P8" s="66"/>
+      <c r="Q8" s="66">
+        <v>2</v>
+      </c>
+      <c r="R8" s="67"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="68">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="69">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>2352</v>
+      </c>
+      <c r="V8" s="69">
+        <f>U8/24</f>
+        <v>98</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="70">
+        <f>145+4</f>
+        <v>149</v>
+      </c>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="73">
+        <v>2</v>
+      </c>
+      <c r="N9" s="74"/>
+      <c r="O9" s="70">
+        <v>1</v>
+      </c>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71"/>
+      <c r="R9" s="72"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="76">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>3648</v>
+      </c>
+      <c r="V9" s="76">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>152</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="70">
+        <v>35</v>
+      </c>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="74"/>
+      <c r="O10" s="70"/>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71"/>
+      <c r="R10" s="72"/>
+      <c r="S10" s="55"/>
+      <c r="T10" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="58">
+        <f t="shared" si="2"/>
+        <v>840</v>
+      </c>
+      <c r="V10" s="58">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="70">
+        <v>10</v>
+      </c>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
+      <c r="L11" s="55"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="55"/>
+      <c r="T11" s="58">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U11" s="58">
+        <f t="shared" si="2"/>
+        <v>242</v>
+      </c>
+      <c r="V11" s="58">
+        <f t="shared" si="3"/>
+        <v>10.083333333333334</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="59">
+        <f>250+504+1440+576+5+360</f>
+        <v>3135</v>
+      </c>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="63">
+        <v>18</v>
+      </c>
+      <c r="N12" s="64"/>
+      <c r="O12" s="65">
+        <v>12</v>
+      </c>
+      <c r="P12" s="66"/>
+      <c r="Q12" s="66">
+        <v>15</v>
+      </c>
+      <c r="R12" s="67"/>
+      <c r="S12" s="62"/>
+      <c r="T12" s="69">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U12" s="69">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>76320</v>
+      </c>
+      <c r="V12" s="69">
+        <f>U12/24</f>
+        <v>3180</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="70">
+        <v>3</v>
+      </c>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
+      <c r="I13" s="70"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="55"/>
+      <c r="T13" s="76">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="U13" s="76">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>88</v>
+      </c>
+      <c r="V13" s="76">
+        <f>U13/24</f>
+        <v>3.6666666666666665</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="70">
+        <v>4</v>
+      </c>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="55"/>
+      <c r="T14" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="75">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>96</v>
+      </c>
+      <c r="V14" s="75">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>4</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="70">
+        <v>1</v>
+      </c>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="55"/>
+      <c r="T15" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="75">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="V15" s="75">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="55"/>
+      <c r="T16" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="70">
+        <v>3</v>
+      </c>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70"/>
+      <c r="I17" s="70"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V17" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="55"/>
+      <c r="T18" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="70">
+        <v>3</v>
+      </c>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70">
+        <f>24+20</f>
+        <v>44</v>
+      </c>
+      <c r="I19" s="70"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="55"/>
+      <c r="T19" s="58">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="U19" s="75">
+        <f t="shared" si="4"/>
+        <v>116</v>
+      </c>
+      <c r="V19" s="75">
+        <f t="shared" si="5"/>
+        <v>4.833333333333333</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="70">
+        <v>6</v>
+      </c>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="74"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="55"/>
+      <c r="T20" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="75">
+        <f t="shared" si="4"/>
+        <v>144</v>
+      </c>
+      <c r="V20" s="75">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="70">
+        <v>1</v>
+      </c>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70">
+        <f>24*2</f>
+        <v>48</v>
+      </c>
+      <c r="I21" s="70"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="58">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="U21" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V21" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="70">
+        <v>1</v>
+      </c>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70">
+        <v>20</v>
+      </c>
+      <c r="I22" s="70"/>
+      <c r="J22" s="71"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="55"/>
+      <c r="T22" s="58">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U22" s="75">
+        <f t="shared" si="4"/>
+        <v>44</v>
+      </c>
+      <c r="V22" s="75">
+        <f t="shared" si="5"/>
+        <v>1.8333333333333333</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
+      <c r="I23" s="70"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="74"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="55"/>
+      <c r="T23" s="58">
+        <f t="shared" si="0"/>
+        <v>907</v>
+      </c>
+      <c r="U23" s="75">
+        <f t="shared" si="4"/>
+        <v>907</v>
+      </c>
+      <c r="V23" s="75">
+        <f t="shared" si="5"/>
+        <v>37.791666666666664</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="70">
+        <v>6</v>
+      </c>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70">
+        <f>24*3</f>
+        <v>72</v>
+      </c>
+      <c r="I24" s="70"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="55"/>
+      <c r="T24" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U24" s="75">
+        <f t="shared" si="4"/>
+        <v>216</v>
+      </c>
+      <c r="V24" s="75">
+        <f t="shared" si="5"/>
+        <v>9</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="70">
+        <f>64+63+21</f>
+        <v>148</v>
+      </c>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70">
+        <v>1</v>
+      </c>
+      <c r="J25" s="71"/>
+      <c r="K25" s="72"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="73">
+        <v>1</v>
+      </c>
+      <c r="N25" s="74"/>
+      <c r="O25" s="70">
+        <v>1</v>
+      </c>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71">
+        <v>2</v>
+      </c>
+      <c r="R25" s="72"/>
+      <c r="S25" s="55"/>
+      <c r="T25" s="58">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="U25" s="75">
+        <f t="shared" si="4"/>
+        <v>3649</v>
+      </c>
+      <c r="V25" s="75">
+        <f t="shared" si="5"/>
+        <v>152.04166666666666</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="74"/>
+      <c r="O26" s="70"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="71"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="55"/>
+      <c r="T26" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="70">
+        <v>2</v>
+      </c>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="70"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="55"/>
+      <c r="T27" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V27" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="70">
+        <f>64+45</f>
+        <v>109</v>
+      </c>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="73">
+        <v>10</v>
+      </c>
+      <c r="N28" s="74"/>
+      <c r="O28" s="70">
+        <v>2</v>
+      </c>
+      <c r="P28" s="71"/>
+      <c r="Q28" s="71">
+        <v>3</v>
+      </c>
+      <c r="R28" s="72"/>
+      <c r="S28" s="55"/>
+      <c r="T28" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="75">
+        <f t="shared" si="4"/>
+        <v>2976</v>
+      </c>
+      <c r="V28" s="75">
+        <f t="shared" si="5"/>
+        <v>124</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="70">
+        <v>62</v>
+      </c>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70">
+        <v>5</v>
+      </c>
+      <c r="J29" s="71"/>
+      <c r="K29" s="72"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="73"/>
+      <c r="N29" s="74"/>
+      <c r="O29" s="70">
+        <v>1</v>
+      </c>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71"/>
+      <c r="R29" s="72"/>
+      <c r="S29" s="55"/>
+      <c r="T29" s="58">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U29" s="75">
+        <f t="shared" si="4"/>
+        <v>1517</v>
+      </c>
+      <c r="V29" s="75">
+        <f t="shared" si="5"/>
+        <v>63.208333333333336</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="70">
+        <v>15</v>
+      </c>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="74"/>
+      <c r="O30" s="70"/>
+      <c r="P30" s="71"/>
+      <c r="Q30" s="71"/>
+      <c r="R30" s="72"/>
+      <c r="S30" s="55"/>
+      <c r="T30" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="75">
+        <f t="shared" si="4"/>
+        <v>360</v>
+      </c>
+      <c r="V30" s="75">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="70"/>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="70">
+        <f>5+1</f>
+        <v>6</v>
+      </c>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="74"/>
+      <c r="O32" s="70"/>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="55"/>
+      <c r="T32" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="75">
+        <f t="shared" si="4"/>
+        <v>144</v>
+      </c>
+      <c r="V32" s="75">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="70">
+        <v>2</v>
+      </c>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="70"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="73"/>
+      <c r="N33" s="74"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="55"/>
+      <c r="T33" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V33" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="70">
+        <v>69</v>
+      </c>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
+      <c r="J34" s="71"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
+      <c r="L34" s="55"/>
+      <c r="M34" s="73">
+        <v>12</v>
+      </c>
+      <c r="N34" s="74"/>
+      <c r="O34" s="70">
+        <v>1</v>
+      </c>
+      <c r="P34" s="71">
+        <v>12</v>
+      </c>
+      <c r="Q34" s="71">
+        <v>8</v>
+      </c>
+      <c r="R34" s="72"/>
+      <c r="S34" s="55"/>
+      <c r="T34" s="58">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="U34" s="75">
+        <f t="shared" si="4"/>
+        <v>2174</v>
+      </c>
+      <c r="V34" s="75">
+        <f t="shared" si="5"/>
+        <v>90.583333333333329</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="72"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="74"/>
+      <c r="O35" s="70"/>
+      <c r="P35" s="71"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="72"/>
+      <c r="S35" s="55"/>
+      <c r="T35" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="70">
+        <v>1</v>
+      </c>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="73"/>
+      <c r="N36" s="74"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="71"/>
+      <c r="Q36" s="71"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="55"/>
+      <c r="T36" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="75">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="V36" s="75">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="59">
+        <f>540+324+3564+99</f>
+        <v>4527</v>
+      </c>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59"/>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>2</v>
+      </c>
+      <c r="K37" s="61">
+        <v>3</v>
+      </c>
+      <c r="L37" s="62"/>
+      <c r="M37" s="63">
+        <v>13</v>
+      </c>
+      <c r="N37" s="64">
+        <v>1</v>
+      </c>
+      <c r="O37" s="65">
+        <v>40</v>
+      </c>
+      <c r="P37" s="66"/>
+      <c r="Q37" s="66">
+        <v>28</v>
+      </c>
+      <c r="R37" s="67"/>
+      <c r="S37" s="62"/>
+      <c r="T37" s="77">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="U37" s="77">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>27656</v>
+      </c>
+      <c r="V37" s="77">
+        <f>U37/6</f>
+        <v>4609.333333333333</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="73"/>
+      <c r="N38" s="74"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="71"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="55"/>
+      <c r="T38" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="75">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="75">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="74"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="71"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="95"/>
+      <c r="T39" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U39" s="75">
+        <f>C39*24+M39*24+O39*24+Q39*24+T39</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="75">
+        <f>U39/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="59">
+        <f>64+28</f>
+        <v>92</v>
+      </c>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
+      <c r="L40" s="62"/>
+      <c r="M40" s="63">
+        <v>1</v>
+      </c>
+      <c r="N40" s="64"/>
+      <c r="O40" s="65">
+        <v>1</v>
+      </c>
+      <c r="P40" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q40" s="66"/>
+      <c r="R40" s="67"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="77">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="U40" s="77">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>2288</v>
+      </c>
+      <c r="V40" s="77">
+        <f>U40/24</f>
+        <v>95.333333333333329</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="82">
+        <f>192+49</f>
+        <v>241</v>
+      </c>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="85"/>
+      <c r="M41" s="86">
+        <v>10</v>
+      </c>
+      <c r="N41" s="87"/>
+      <c r="O41" s="82">
+        <v>12</v>
+      </c>
+      <c r="P41" s="83"/>
+      <c r="Q41" s="83">
+        <v>26</v>
+      </c>
+      <c r="R41" s="84"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="88">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>3468</v>
+      </c>
+      <c r="V41" s="88">
+        <f>U41/12</f>
+        <v>289</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="71"/>
+      <c r="K42" s="72"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="73"/>
+      <c r="N42" s="74"/>
+      <c r="O42" s="70"/>
+      <c r="P42" s="71"/>
+      <c r="Q42" s="71"/>
+      <c r="R42" s="72"/>
+      <c r="S42" s="55"/>
+      <c r="T42" s="75"/>
+      <c r="U42" s="75"/>
+      <c r="V42" s="75"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="65">
+        <f>4860+4104+4968+1836+8424+5508+3024+5832</f>
+        <v>38556</v>
+      </c>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65"/>
+      <c r="I43" s="65">
+        <v>7</v>
+      </c>
+      <c r="J43" s="66">
+        <f>8*6+1</f>
+        <v>49</v>
+      </c>
+      <c r="K43" s="67">
+        <f>69*6+7</f>
+        <v>421</v>
+      </c>
+      <c r="L43" s="62"/>
+      <c r="M43" s="63">
+        <v>580</v>
+      </c>
+      <c r="N43" s="64"/>
+      <c r="O43" s="65">
+        <v>363</v>
+      </c>
+      <c r="P43" s="66"/>
+      <c r="Q43" s="66">
+        <v>547</v>
+      </c>
+      <c r="R43" s="67"/>
+      <c r="S43" s="62"/>
+      <c r="T43" s="77">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>477</v>
+      </c>
+      <c r="U43" s="77">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>240753</v>
+      </c>
+      <c r="V43" s="77">
+        <f>U43/6</f>
+        <v>40125.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="70"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="71"/>
+      <c r="K44" s="72"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="73"/>
+      <c r="N44" s="74"/>
+      <c r="O44" s="70"/>
+      <c r="P44" s="71"/>
+      <c r="Q44" s="71"/>
+      <c r="R44" s="72"/>
+      <c r="S44" s="55"/>
+      <c r="T44" s="75"/>
+      <c r="U44" s="75"/>
+      <c r="V44" s="75"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="70"/>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="70"/>
+      <c r="I45" s="70"/>
+      <c r="J45" s="71"/>
+      <c r="K45" s="72"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="73"/>
+      <c r="N45" s="74"/>
+      <c r="O45" s="70"/>
+      <c r="P45" s="71"/>
+      <c r="Q45" s="71">
+        <v>1</v>
+      </c>
+      <c r="R45" s="72"/>
+      <c r="S45" s="55"/>
+      <c r="T45" s="75">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="75">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>24</v>
+      </c>
+      <c r="V45" s="75">
+        <f>U45/24</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="73"/>
+      <c r="N46" s="74"/>
+      <c r="O46" s="70"/>
+      <c r="P46" s="71"/>
+      <c r="Q46" s="71"/>
+      <c r="R46" s="72"/>
+      <c r="S46" s="55"/>
+      <c r="T46" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="75">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="75">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="65">
+        <f>432+106+2160+74+22</f>
+        <v>2794</v>
+      </c>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65">
+        <v>2</v>
+      </c>
+      <c r="I47" s="65"/>
+      <c r="J47" s="66"/>
+      <c r="K47" s="67">
+        <v>4</v>
+      </c>
+      <c r="L47" s="62"/>
+      <c r="M47" s="63"/>
+      <c r="N47" s="64"/>
+      <c r="O47" s="65">
+        <v>5</v>
+      </c>
+      <c r="P47" s="66">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="66">
+        <v>9</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
+      <c r="S47" s="62"/>
+      <c r="T47" s="77">
+        <f t="shared" si="7"/>
+        <v>13</v>
+      </c>
+      <c r="U47" s="77">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>16861</v>
+      </c>
+      <c r="V47" s="77">
+        <f>U47/6</f>
+        <v>2810.1666666666665</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
+      <c r="I48" s="70"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="72"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="73"/>
+      <c r="N48" s="74"/>
+      <c r="O48" s="70"/>
+      <c r="P48" s="71"/>
+      <c r="Q48" s="71"/>
+      <c r="R48" s="72"/>
+      <c r="S48" s="55"/>
+      <c r="T48" s="75">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="U48" s="75">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="V48" s="75">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="70">
+        <v>2</v>
+      </c>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="70"/>
+      <c r="I49" s="70"/>
+      <c r="J49" s="71"/>
+      <c r="K49" s="72"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="74"/>
+      <c r="O49" s="70"/>
+      <c r="P49" s="71"/>
+      <c r="Q49" s="71"/>
+      <c r="R49" s="72"/>
+      <c r="S49" s="55"/>
+      <c r="T49" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="75">
+        <f t="shared" si="8"/>
+        <v>48</v>
+      </c>
+      <c r="V49" s="75">
+        <f t="shared" si="9"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="70"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="70"/>
+      <c r="F50" s="70"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
+      <c r="J50" s="71"/>
+      <c r="K50" s="72"/>
+      <c r="L50" s="55"/>
+      <c r="M50" s="73"/>
+      <c r="N50" s="74"/>
+      <c r="O50" s="70"/>
+      <c r="P50" s="71"/>
+      <c r="Q50" s="71"/>
+      <c r="R50" s="72"/>
+      <c r="S50" s="55"/>
+      <c r="T50" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="65"/>
+      <c r="I51" s="65"/>
+      <c r="J51" s="66"/>
+      <c r="K51" s="67"/>
+      <c r="L51" s="62"/>
+      <c r="M51" s="63"/>
+      <c r="N51" s="64"/>
+      <c r="O51" s="65"/>
+      <c r="P51" s="66"/>
+      <c r="Q51" s="66"/>
+      <c r="R51" s="67"/>
+      <c r="S51" s="62"/>
+      <c r="T51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="77">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>204</v>
+      </c>
+      <c r="V51" s="77">
+        <f>U51/6</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="70">
+        <v>1</v>
+      </c>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="70"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="71"/>
+      <c r="K52" s="72"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="73"/>
+      <c r="N52" s="74"/>
+      <c r="O52" s="70"/>
+      <c r="P52" s="71"/>
+      <c r="Q52" s="71"/>
+      <c r="R52" s="72"/>
+      <c r="S52" s="55"/>
+      <c r="T52" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="75">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>24</v>
+      </c>
+      <c r="V52" s="75">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="70">
+        <v>10</v>
+      </c>
+      <c r="D53" s="70"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="70"/>
+      <c r="H53" s="70"/>
+      <c r="I53" s="70"/>
+      <c r="J53" s="71"/>
+      <c r="K53" s="72"/>
+      <c r="L53" s="55"/>
+      <c r="M53" s="73"/>
+      <c r="N53" s="74"/>
+      <c r="O53" s="70"/>
+      <c r="P53" s="71"/>
+      <c r="Q53" s="71"/>
+      <c r="R53" s="72"/>
+      <c r="S53" s="55"/>
+      <c r="T53" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="75">
+        <f t="shared" si="10"/>
+        <v>240</v>
+      </c>
+      <c r="V53" s="75">
+        <f t="shared" si="9"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="71"/>
+      <c r="K54" s="72"/>
+      <c r="L54" s="55"/>
+      <c r="M54" s="73"/>
+      <c r="N54" s="74"/>
+      <c r="O54" s="70"/>
+      <c r="P54" s="71"/>
+      <c r="Q54" s="71"/>
+      <c r="R54" s="72"/>
+      <c r="S54" s="55"/>
+      <c r="T54" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="70"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="70"/>
+      <c r="I55" s="70"/>
+      <c r="J55" s="71"/>
+      <c r="K55" s="72"/>
+      <c r="L55" s="55"/>
+      <c r="M55" s="73"/>
+      <c r="N55" s="74"/>
+      <c r="O55" s="70"/>
+      <c r="P55" s="71"/>
+      <c r="Q55" s="71"/>
+      <c r="R55" s="72"/>
+      <c r="S55" s="55"/>
+      <c r="T55" s="75"/>
+      <c r="U55" s="75"/>
+      <c r="V55" s="75"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="70"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="70"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="71"/>
+      <c r="K56" s="72"/>
+      <c r="L56" s="55"/>
+      <c r="M56" s="73"/>
+      <c r="N56" s="74"/>
+      <c r="O56" s="70"/>
+      <c r="P56" s="71"/>
+      <c r="Q56" s="71"/>
+      <c r="R56" s="72"/>
+      <c r="S56" s="55"/>
+      <c r="T56" s="75"/>
+      <c r="U56" s="75"/>
+      <c r="V56" s="75"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="70"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="70"/>
+      <c r="I57" s="70"/>
+      <c r="J57" s="71"/>
+      <c r="K57" s="72"/>
+      <c r="L57" s="55"/>
+      <c r="M57" s="73"/>
+      <c r="N57" s="74"/>
+      <c r="O57" s="70"/>
+      <c r="P57" s="71"/>
+      <c r="Q57" s="71"/>
+      <c r="R57" s="72"/>
+      <c r="S57" s="55"/>
+      <c r="T57" s="75"/>
+      <c r="U57" s="75"/>
+      <c r="V57" s="75"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>50154</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>1133</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>19</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>51</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>457</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>649</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>23</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>440</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>28</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>642</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>3</v>
+      </c>
+      <c r="S58" s="55"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>1714</v>
+      </c>
+      <c r="U58" s="90">
+        <f>SUM(U7:U57)</f>
+        <v>388558</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>52018.666666666664</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="102" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="103"/>
+      <c r="E60" s="103"/>
+      <c r="F60" s="103"/>
+      <c r="G60" s="103"/>
+      <c r="H60" s="103"/>
+      <c r="I60" s="103"/>
+      <c r="J60" s="103"/>
+      <c r="K60" s="104"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DC4BC4A-16CE-4134-A359-B3B72FCD191D}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -4931,7 +8083,7 @@
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -5105,34 +8257,46 @@
       <c r="B7" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="52"/>
+      <c r="C7" s="52">
+        <v>20</v>
+      </c>
       <c r="D7" s="52"/>
       <c r="E7" s="52"/>
       <c r="F7" s="52"/>
       <c r="G7" s="52"/>
       <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
-      <c r="J7" s="53"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
+      <c r="J7" s="53">
+        <v>6</v>
+      </c>
       <c r="K7" s="54"/>
       <c r="L7" s="55"/>
-      <c r="M7" s="56"/>
+      <c r="M7" s="56">
+        <v>2</v>
+      </c>
       <c r="N7" s="57"/>
-      <c r="O7" s="52"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
       <c r="P7" s="53"/>
-      <c r="Q7" s="53"/>
+      <c r="Q7" s="53">
+        <v>11</v>
+      </c>
       <c r="R7" s="54"/>
       <c r="S7" s="55"/>
       <c r="T7" s="58">
         <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U7" s="58">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>825</v>
       </c>
       <c r="V7" s="58">
         <f>U7/24</f>
-        <v>0</v>
+        <v>34.375</v>
       </c>
       <c r="W7" s="50"/>
       <c r="AF7" s="12"/>
@@ -5167,7 +8331,10 @@
       <c r="B8" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="59"/>
+      <c r="C8" s="59">
+        <f>30+63+3</f>
+        <v>96</v>
+      </c>
       <c r="D8" s="59"/>
       <c r="E8" s="59"/>
       <c r="F8" s="59"/>
@@ -5181,7 +8348,9 @@
       <c r="N8" s="64"/>
       <c r="O8" s="65"/>
       <c r="P8" s="66"/>
-      <c r="Q8" s="66"/>
+      <c r="Q8" s="66">
+        <v>2</v>
+      </c>
       <c r="R8" s="67"/>
       <c r="S8" s="62"/>
       <c r="T8" s="68">
@@ -5190,11 +8359,11 @@
       </c>
       <c r="U8" s="69">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
+        <v>2352</v>
       </c>
       <c r="V8" s="69">
         <f>U8/24</f>
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="W8" s="50"/>
       <c r="AF8" s="12"/>
@@ -5229,7 +8398,10 @@
       <c r="B9" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="70"/>
+      <c r="C9" s="70">
+        <f>54+90</f>
+        <v>144</v>
+      </c>
       <c r="D9" s="70"/>
       <c r="E9" s="70"/>
       <c r="F9" s="70"/>
@@ -5243,7 +8415,9 @@
       <c r="N9" s="74"/>
       <c r="O9" s="70"/>
       <c r="P9" s="71"/>
-      <c r="Q9" s="71"/>
+      <c r="Q9" s="71">
+        <v>5</v>
+      </c>
       <c r="R9" s="72"/>
       <c r="S9" s="55"/>
       <c r="T9" s="75">
@@ -5252,11 +8426,11 @@
       </c>
       <c r="U9" s="76">
         <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
-        <v>0</v>
+        <v>3576</v>
       </c>
       <c r="V9" s="76">
         <f t="shared" ref="V9:V11" si="3">U9/24</f>
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="W9" s="50"/>
       <c r="AF9" s="12"/>
@@ -5291,7 +8465,9 @@
       <c r="B10" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="70"/>
+      <c r="C10" s="70">
+        <v>33</v>
+      </c>
       <c r="D10" s="70"/>
       <c r="E10" s="70"/>
       <c r="F10" s="70"/>
@@ -5305,7 +8481,9 @@
       <c r="N10" s="74"/>
       <c r="O10" s="70"/>
       <c r="P10" s="71"/>
-      <c r="Q10" s="71"/>
+      <c r="Q10" s="71">
+        <v>2</v>
+      </c>
       <c r="R10" s="72"/>
       <c r="S10" s="55"/>
       <c r="T10" s="58">
@@ -5314,11 +8492,11 @@
       </c>
       <c r="U10" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>840</v>
       </c>
       <c r="V10" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="W10" s="50"/>
       <c r="AF10" s="12"/>
@@ -5353,34 +8531,40 @@
       <c r="B11" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="70"/>
+      <c r="C11" s="70">
+        <v>5</v>
+      </c>
       <c r="D11" s="70"/>
       <c r="E11" s="70"/>
       <c r="F11" s="70"/>
       <c r="G11" s="70"/>
       <c r="H11" s="70"/>
       <c r="I11" s="70"/>
-      <c r="J11" s="71"/>
+      <c r="J11" s="71">
+        <v>2</v>
+      </c>
       <c r="K11" s="72"/>
       <c r="L11" s="55"/>
       <c r="M11" s="73"/>
       <c r="N11" s="74"/>
       <c r="O11" s="70"/>
       <c r="P11" s="71"/>
-      <c r="Q11" s="71"/>
+      <c r="Q11" s="71">
+        <v>5</v>
+      </c>
       <c r="R11" s="72"/>
       <c r="S11" s="55"/>
       <c r="T11" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U11" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="V11" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>10.083333333333334</v>
       </c>
       <c r="AF11" s="12"/>
       <c r="AG11" s="12"/>
@@ -5413,7 +8597,10 @@
       <c r="B12" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="59"/>
+      <c r="C12" s="59">
+        <f>34+144+72+504+1440+576+360</f>
+        <v>3130</v>
+      </c>
       <c r="D12" s="59"/>
       <c r="E12" s="59"/>
       <c r="F12" s="59"/>
@@ -5423,24 +8610,34 @@
       <c r="J12" s="60"/>
       <c r="K12" s="61"/>
       <c r="L12" s="62"/>
-      <c r="M12" s="63"/>
-      <c r="N12" s="64"/>
-      <c r="O12" s="65"/>
-      <c r="P12" s="66"/>
-      <c r="Q12" s="66"/>
+      <c r="M12" s="63">
+        <v>11</v>
+      </c>
+      <c r="N12" s="64">
+        <v>12</v>
+      </c>
+      <c r="O12" s="65">
+        <v>13</v>
+      </c>
+      <c r="P12" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q12" s="66">
+        <v>5</v>
+      </c>
       <c r="R12" s="67"/>
       <c r="S12" s="62"/>
       <c r="T12" s="69">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U12" s="69">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
+        <v>75840</v>
       </c>
       <c r="V12" s="69">
         <f>U12/24</f>
-        <v>0</v>
+        <v>3160</v>
       </c>
       <c r="W12" s="9"/>
       <c r="X12" s="9"/>
@@ -5482,12 +8679,16 @@
       <c r="B13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="70"/>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
       <c r="D13" s="70"/>
       <c r="E13" s="70"/>
       <c r="F13" s="70"/>
       <c r="G13" s="70"/>
-      <c r="H13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
       <c r="I13" s="70"/>
       <c r="J13" s="71"/>
       <c r="K13" s="72"/>
@@ -5496,20 +8697,22 @@
       <c r="N13" s="74"/>
       <c r="O13" s="70"/>
       <c r="P13" s="71"/>
-      <c r="Q13" s="71"/>
+      <c r="Q13" s="71">
+        <v>1</v>
+      </c>
       <c r="R13" s="72"/>
       <c r="S13" s="55"/>
       <c r="T13" s="76">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="U13" s="76">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="V13" s="76">
         <f>U13/24</f>
-        <v>0</v>
+        <v>3.6666666666666665</v>
       </c>
       <c r="AF13" s="12"/>
       <c r="AG13" s="12"/>
@@ -5543,7 +8746,9 @@
       <c r="B14" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="70"/>
+      <c r="C14" s="70">
+        <v>4</v>
+      </c>
       <c r="D14" s="70"/>
       <c r="E14" s="70"/>
       <c r="F14" s="70"/>
@@ -5566,11 +8771,11 @@
       </c>
       <c r="U14" s="75">
         <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V14" s="75">
         <f t="shared" ref="V14:V36" si="5">U14/24</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF14" s="12"/>
       <c r="AG14" s="12"/>
@@ -5618,7 +8823,9 @@
       <c r="N15" s="74"/>
       <c r="O15" s="70"/>
       <c r="P15" s="71"/>
-      <c r="Q15" s="71"/>
+      <c r="Q15" s="71">
+        <v>1</v>
+      </c>
       <c r="R15" s="72"/>
       <c r="S15" s="55"/>
       <c r="T15" s="58">
@@ -5627,11 +8834,11 @@
       </c>
       <c r="U15" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V15" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF15" s="12"/>
       <c r="AG15" s="12"/>
@@ -5731,7 +8938,10 @@
       <c r="E17" s="70"/>
       <c r="F17" s="70"/>
       <c r="G17" s="70"/>
-      <c r="H17" s="70"/>
+      <c r="H17" s="70">
+        <f>24*3</f>
+        <v>72</v>
+      </c>
       <c r="I17" s="70"/>
       <c r="J17" s="71"/>
       <c r="K17" s="72"/>
@@ -5745,15 +8955,15 @@
       <c r="S17" s="55"/>
       <c r="T17" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U17" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V17" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF17" s="12"/>
       <c r="AG17" s="12"/>
@@ -5847,12 +9057,17 @@
       <c r="B19" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="70"/>
+      <c r="C19" s="70">
+        <v>2</v>
+      </c>
       <c r="D19" s="70"/>
       <c r="E19" s="70"/>
       <c r="F19" s="70"/>
       <c r="G19" s="70"/>
-      <c r="H19" s="70"/>
+      <c r="H19" s="70">
+        <f>24+20</f>
+        <v>44</v>
+      </c>
       <c r="I19" s="70"/>
       <c r="J19" s="71"/>
       <c r="K19" s="72"/>
@@ -5861,20 +9076,22 @@
       <c r="N19" s="74"/>
       <c r="O19" s="70"/>
       <c r="P19" s="71"/>
-      <c r="Q19" s="71"/>
+      <c r="Q19" s="71">
+        <v>1</v>
+      </c>
       <c r="R19" s="72"/>
       <c r="S19" s="55"/>
       <c r="T19" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="U19" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="V19" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="AF19" s="12"/>
       <c r="AG19" s="12"/>
@@ -5908,7 +9125,9 @@
       <c r="B20" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="70"/>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
       <c r="D20" s="70"/>
       <c r="E20" s="70"/>
       <c r="F20" s="70"/>
@@ -5922,7 +9141,9 @@
       <c r="N20" s="74"/>
       <c r="O20" s="70"/>
       <c r="P20" s="71"/>
-      <c r="Q20" s="71"/>
+      <c r="Q20" s="71">
+        <v>1</v>
+      </c>
       <c r="R20" s="72"/>
       <c r="S20" s="55"/>
       <c r="T20" s="58">
@@ -5931,11 +9152,11 @@
       </c>
       <c r="U20" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="V20" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AF20" s="12"/>
       <c r="AG20" s="12"/>
@@ -5974,7 +9195,10 @@
       <c r="E21" s="70"/>
       <c r="F21" s="70"/>
       <c r="G21" s="70"/>
-      <c r="H21" s="70"/>
+      <c r="H21" s="70">
+        <f>24*2</f>
+        <v>48</v>
+      </c>
       <c r="I21" s="70"/>
       <c r="J21" s="71"/>
       <c r="K21" s="72"/>
@@ -5983,20 +9207,22 @@
       <c r="N21" s="74"/>
       <c r="O21" s="70"/>
       <c r="P21" s="71"/>
-      <c r="Q21" s="71"/>
+      <c r="Q21" s="71">
+        <v>1</v>
+      </c>
       <c r="R21" s="72"/>
       <c r="S21" s="55"/>
       <c r="T21" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="U21" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V21" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF21" s="12"/>
       <c r="AG21" s="12"/>
@@ -6035,7 +9261,9 @@
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
       <c r="G22" s="70"/>
-      <c r="H22" s="70"/>
+      <c r="H22" s="70">
+        <v>20</v>
+      </c>
       <c r="I22" s="70"/>
       <c r="J22" s="71"/>
       <c r="K22" s="72"/>
@@ -6044,20 +9272,22 @@
       <c r="N22" s="74"/>
       <c r="O22" s="70"/>
       <c r="P22" s="71"/>
-      <c r="Q22" s="71"/>
+      <c r="Q22" s="71">
+        <v>1</v>
+      </c>
       <c r="R22" s="72"/>
       <c r="S22" s="55"/>
       <c r="T22" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U22" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="V22" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1.8333333333333333</v>
       </c>
       <c r="W22" s="9"/>
       <c r="X22" s="9"/>
@@ -6105,7 +9335,10 @@
       <c r="E23" s="70"/>
       <c r="F23" s="70"/>
       <c r="G23" s="70"/>
-      <c r="H23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
       <c r="I23" s="70"/>
       <c r="J23" s="71"/>
       <c r="K23" s="72"/>
@@ -6119,15 +9352,15 @@
       <c r="S23" s="55"/>
       <c r="T23" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="U23" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="V23" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>37.791666666666664</v>
       </c>
       <c r="W23" s="9"/>
       <c r="X23" s="9"/>
@@ -6170,12 +9403,17 @@
       <c r="B24" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="70"/>
+      <c r="C24" s="70">
+        <v>5</v>
+      </c>
       <c r="D24" s="70"/>
       <c r="E24" s="70"/>
       <c r="F24" s="70"/>
       <c r="G24" s="70"/>
-      <c r="H24" s="70"/>
+      <c r="H24" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
       <c r="I24" s="70"/>
       <c r="J24" s="71"/>
       <c r="K24" s="72"/>
@@ -6184,20 +9422,22 @@
       <c r="N24" s="74"/>
       <c r="O24" s="70"/>
       <c r="P24" s="71"/>
-      <c r="Q24" s="71"/>
+      <c r="Q24" s="71">
+        <v>1</v>
+      </c>
       <c r="R24" s="72"/>
       <c r="S24" s="55"/>
       <c r="T24" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U24" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="V24" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AF24" s="12"/>
       <c r="AG24" s="12"/>
@@ -6231,34 +9471,43 @@
       <c r="B25" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="70"/>
+      <c r="C25" s="70">
+        <f>63+63+21</f>
+        <v>147</v>
+      </c>
       <c r="D25" s="70"/>
       <c r="E25" s="70"/>
       <c r="F25" s="70"/>
       <c r="G25" s="70"/>
       <c r="H25" s="70"/>
-      <c r="I25" s="70"/>
+      <c r="I25" s="70">
+        <v>1</v>
+      </c>
       <c r="J25" s="71"/>
       <c r="K25" s="72"/>
       <c r="L25" s="55"/>
-      <c r="M25" s="73"/>
+      <c r="M25" s="73">
+        <v>1</v>
+      </c>
       <c r="N25" s="74"/>
-      <c r="O25" s="70"/>
+      <c r="O25" s="70">
+        <v>1</v>
+      </c>
       <c r="P25" s="71"/>
       <c r="Q25" s="71"/>
       <c r="R25" s="72"/>
       <c r="S25" s="55"/>
       <c r="T25" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3577</v>
       </c>
       <c r="V25" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>149.04166666666666</v>
       </c>
       <c r="AY25" s="14" t="e">
         <f>#REF!-AY24</f>
@@ -6334,7 +9583,9 @@
       <c r="N27" s="74"/>
       <c r="O27" s="70"/>
       <c r="P27" s="71"/>
-      <c r="Q27" s="71"/>
+      <c r="Q27" s="71">
+        <v>2</v>
+      </c>
       <c r="R27" s="72"/>
       <c r="S27" s="55"/>
       <c r="T27" s="58">
@@ -6343,11 +9594,11 @@
       </c>
       <c r="U27" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V27" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W27" s="9"/>
       <c r="X27" s="9"/>
@@ -6367,7 +9618,10 @@
       <c r="B28" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="70"/>
+      <c r="C28" s="70">
+        <f>63+34</f>
+        <v>97</v>
+      </c>
       <c r="D28" s="70"/>
       <c r="E28" s="70"/>
       <c r="F28" s="70"/>
@@ -6377,11 +9631,17 @@
       <c r="J28" s="71"/>
       <c r="K28" s="72"/>
       <c r="L28" s="55"/>
-      <c r="M28" s="73"/>
+      <c r="M28" s="73">
+        <v>1</v>
+      </c>
       <c r="N28" s="74"/>
-      <c r="O28" s="70"/>
+      <c r="O28" s="70">
+        <v>2</v>
+      </c>
       <c r="P28" s="71"/>
-      <c r="Q28" s="71"/>
+      <c r="Q28" s="71">
+        <v>10</v>
+      </c>
       <c r="R28" s="72"/>
       <c r="S28" s="55"/>
       <c r="T28" s="58">
@@ -6390,11 +9650,11 @@
       </c>
       <c r="U28" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2640</v>
       </c>
       <c r="V28" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="W28" s="9"/>
       <c r="X28" s="9"/>
@@ -6414,34 +9674,44 @@
       <c r="B29" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="70"/>
+      <c r="C29" s="70">
+        <v>51</v>
+      </c>
       <c r="D29" s="70"/>
       <c r="E29" s="70"/>
       <c r="F29" s="70"/>
       <c r="G29" s="70"/>
       <c r="H29" s="70"/>
-      <c r="I29" s="70"/>
+      <c r="I29" s="70">
+        <v>5</v>
+      </c>
       <c r="J29" s="71"/>
       <c r="K29" s="72"/>
       <c r="L29" s="55"/>
-      <c r="M29" s="73"/>
+      <c r="M29" s="73">
+        <v>1</v>
+      </c>
       <c r="N29" s="74"/>
-      <c r="O29" s="70"/>
+      <c r="O29" s="70">
+        <v>1</v>
+      </c>
       <c r="P29" s="71"/>
-      <c r="Q29" s="71"/>
+      <c r="Q29" s="71">
+        <v>10</v>
+      </c>
       <c r="R29" s="72"/>
       <c r="S29" s="55"/>
       <c r="T29" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U29" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1517</v>
       </c>
       <c r="V29" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>63.208333333333336</v>
       </c>
     </row>
     <row r="30" spans="1:54" x14ac:dyDescent="0.25">
@@ -6452,7 +9722,10 @@
       <c r="B30" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="70"/>
+      <c r="C30" s="70">
+        <f>10+3</f>
+        <v>13</v>
+      </c>
       <c r="D30" s="70"/>
       <c r="E30" s="70"/>
       <c r="F30" s="70"/>
@@ -6466,7 +9739,9 @@
       <c r="N30" s="74"/>
       <c r="O30" s="70"/>
       <c r="P30" s="71"/>
-      <c r="Q30" s="71"/>
+      <c r="Q30" s="71">
+        <v>2</v>
+      </c>
       <c r="R30" s="72"/>
       <c r="S30" s="55"/>
       <c r="T30" s="58">
@@ -6475,11 +9750,11 @@
       </c>
       <c r="U30" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="V30" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
@@ -6528,7 +9803,9 @@
       <c r="B32" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="C32" s="70"/>
+      <c r="C32" s="70">
+        <v>4</v>
+      </c>
       <c r="D32" s="70"/>
       <c r="E32" s="70"/>
       <c r="F32" s="70"/>
@@ -6542,7 +9819,9 @@
       <c r="N32" s="74"/>
       <c r="O32" s="70"/>
       <c r="P32" s="71"/>
-      <c r="Q32" s="71"/>
+      <c r="Q32" s="71">
+        <v>2</v>
+      </c>
       <c r="R32" s="72"/>
       <c r="S32" s="55"/>
       <c r="T32" s="58">
@@ -6551,11 +9830,11 @@
       </c>
       <c r="U32" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="V32" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.25">
@@ -6580,7 +9859,9 @@
       <c r="N33" s="74"/>
       <c r="O33" s="70"/>
       <c r="P33" s="71"/>
-      <c r="Q33" s="71"/>
+      <c r="Q33" s="71">
+        <v>2</v>
+      </c>
       <c r="R33" s="72"/>
       <c r="S33" s="55"/>
       <c r="T33" s="58">
@@ -6589,11 +9870,11 @@
       </c>
       <c r="U33" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V33" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.25">
@@ -6604,34 +9885,48 @@
       <c r="B34" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="70"/>
+      <c r="C34" s="70">
+        <v>69</v>
+      </c>
       <c r="D34" s="70"/>
       <c r="E34" s="70"/>
       <c r="F34" s="70"/>
       <c r="G34" s="70"/>
       <c r="H34" s="70"/>
-      <c r="I34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
       <c r="J34" s="71"/>
-      <c r="K34" s="72"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
       <c r="L34" s="55"/>
-      <c r="M34" s="73"/>
+      <c r="M34" s="73">
+        <v>2</v>
+      </c>
       <c r="N34" s="74"/>
-      <c r="O34" s="70"/>
-      <c r="P34" s="71"/>
-      <c r="Q34" s="71"/>
+      <c r="O34" s="70">
+        <v>1</v>
+      </c>
+      <c r="P34" s="71">
+        <v>12</v>
+      </c>
+      <c r="Q34" s="71">
+        <v>7</v>
+      </c>
       <c r="R34" s="72"/>
       <c r="S34" s="55"/>
       <c r="T34" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="U34" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1910</v>
       </c>
       <c r="V34" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>79.583333333333329</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -6694,7 +9989,9 @@
       <c r="N36" s="74"/>
       <c r="O36" s="70"/>
       <c r="P36" s="71"/>
-      <c r="Q36" s="71"/>
+      <c r="Q36" s="71">
+        <v>1</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="55"/>
       <c r="T36" s="58">
@@ -6703,11 +10000,11 @@
       </c>
       <c r="U36" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V36" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -6718,34 +10015,49 @@
       <c r="B37" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="59"/>
+      <c r="C37" s="59">
+        <f>540+3456+64+324</f>
+        <v>4384</v>
+      </c>
       <c r="D37" s="59"/>
       <c r="E37" s="59"/>
       <c r="F37" s="59"/>
       <c r="G37" s="59"/>
       <c r="H37" s="59"/>
-      <c r="I37" s="59"/>
-      <c r="J37" s="60"/>
-      <c r="K37" s="61"/>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>2</v>
+      </c>
+      <c r="K37" s="61">
+        <v>3</v>
+      </c>
       <c r="L37" s="62"/>
-      <c r="M37" s="63"/>
+      <c r="M37" s="63">
+        <v>20</v>
+      </c>
       <c r="N37" s="64"/>
-      <c r="O37" s="65"/>
+      <c r="O37" s="65">
+        <v>24</v>
+      </c>
       <c r="P37" s="66"/>
-      <c r="Q37" s="66"/>
+      <c r="Q37" s="66">
+        <v>102</v>
+      </c>
       <c r="R37" s="67"/>
       <c r="S37" s="62"/>
       <c r="T37" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U37" s="77">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
+        <v>27187</v>
       </c>
       <c r="V37" s="77">
         <f>U37/6</f>
-        <v>0</v>
+        <v>4531.166666666667</v>
       </c>
       <c r="W37" s="50"/>
     </row>
@@ -6833,7 +10145,10 @@
       <c r="B40" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="59"/>
+      <c r="C40" s="59">
+        <f>63+28</f>
+        <v>91</v>
+      </c>
       <c r="D40" s="59"/>
       <c r="E40" s="59"/>
       <c r="F40" s="59"/>
@@ -6841,26 +10156,36 @@
       <c r="H40" s="59"/>
       <c r="I40" s="59"/>
       <c r="J40" s="60"/>
-      <c r="K40" s="61"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
       <c r="L40" s="62"/>
-      <c r="M40" s="63"/>
+      <c r="M40" s="63">
+        <v>1</v>
+      </c>
       <c r="N40" s="64"/>
-      <c r="O40" s="65"/>
-      <c r="P40" s="66"/>
-      <c r="Q40" s="66"/>
+      <c r="O40" s="65">
+        <v>1</v>
+      </c>
+      <c r="P40" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q40" s="66">
+        <v>1</v>
+      </c>
       <c r="R40" s="67"/>
       <c r="S40" s="62"/>
       <c r="T40" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="U40" s="77">
         <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
+        <v>2288</v>
       </c>
       <c r="V40" s="77">
         <f>U40/24</f>
-        <v>0</v>
+        <v>95.333333333333329</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -6871,7 +10196,10 @@
       <c r="B41" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="82"/>
+      <c r="C41" s="82">
+        <f>192+39</f>
+        <v>231</v>
+      </c>
       <c r="D41" s="82"/>
       <c r="E41" s="82"/>
       <c r="F41" s="82"/>
@@ -6881,11 +10209,17 @@
       <c r="J41" s="83"/>
       <c r="K41" s="84"/>
       <c r="L41" s="85"/>
-      <c r="M41" s="86"/>
+      <c r="M41" s="86">
+        <v>10</v>
+      </c>
       <c r="N41" s="87"/>
-      <c r="O41" s="82"/>
+      <c r="O41" s="82">
+        <v>6</v>
+      </c>
       <c r="P41" s="83"/>
-      <c r="Q41" s="83"/>
+      <c r="Q41" s="83">
+        <v>20</v>
+      </c>
       <c r="R41" s="84"/>
       <c r="S41" s="85"/>
       <c r="T41" s="88">
@@ -6894,11 +10228,11 @@
       </c>
       <c r="U41" s="88">
         <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
+        <v>3204</v>
       </c>
       <c r="V41" s="88">
         <f>U41/12</f>
-        <v>0</v>
+        <v>267</v>
       </c>
     </row>
     <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -6938,34 +10272,51 @@
       <c r="B43" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="65"/>
+      <c r="C43" s="65">
+        <f>7776+4212+3024+8424+5508+3024+5832</f>
+        <v>37800</v>
+      </c>
       <c r="D43" s="65"/>
       <c r="E43" s="65"/>
       <c r="F43" s="65"/>
       <c r="G43" s="65"/>
       <c r="H43" s="65"/>
-      <c r="I43" s="65"/>
-      <c r="J43" s="66"/>
-      <c r="K43" s="67"/>
+      <c r="I43" s="65">
+        <v>7</v>
+      </c>
+      <c r="J43" s="66">
+        <f>6*9+1</f>
+        <v>55</v>
+      </c>
+      <c r="K43" s="67">
+        <f>69*6+7</f>
+        <v>421</v>
+      </c>
       <c r="L43" s="62"/>
-      <c r="M43" s="63"/>
+      <c r="M43" s="63">
+        <v>334</v>
+      </c>
       <c r="N43" s="64"/>
-      <c r="O43" s="65"/>
+      <c r="O43" s="65">
+        <v>411</v>
+      </c>
       <c r="P43" s="66"/>
-      <c r="Q43" s="66"/>
+      <c r="Q43" s="66">
+        <v>348</v>
+      </c>
       <c r="R43" s="67"/>
       <c r="S43" s="62"/>
       <c r="T43" s="77">
         <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
+        <v>483</v>
       </c>
       <c r="U43" s="77">
         <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
+        <v>233841</v>
       </c>
       <c r="V43" s="77">
         <f>U43/6</f>
-        <v>0</v>
+        <v>38973.5</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -7019,7 +10370,9 @@
       <c r="N45" s="74"/>
       <c r="O45" s="70"/>
       <c r="P45" s="71"/>
-      <c r="Q45" s="71"/>
+      <c r="Q45" s="71">
+        <v>1</v>
+      </c>
       <c r="R45" s="72"/>
       <c r="S45" s="55"/>
       <c r="T45" s="75">
@@ -7028,11 +10381,11 @@
       </c>
       <c r="U45" s="75">
         <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V45" s="75">
         <f>U45/24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.25">
@@ -7081,34 +10434,49 @@
       <c r="B47" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C47" s="65"/>
+      <c r="C47" s="65">
+        <f>432+106+22+2160+71</f>
+        <v>2791</v>
+      </c>
       <c r="D47" s="65"/>
       <c r="E47" s="65"/>
       <c r="F47" s="65"/>
       <c r="G47" s="65"/>
-      <c r="H47" s="65"/>
+      <c r="H47" s="65">
+        <v>2</v>
+      </c>
       <c r="I47" s="65"/>
       <c r="J47" s="66"/>
-      <c r="K47" s="67"/>
+      <c r="K47" s="67">
+        <v>4</v>
+      </c>
       <c r="L47" s="62"/>
       <c r="M47" s="63"/>
       <c r="N47" s="64"/>
-      <c r="O47" s="65"/>
-      <c r="P47" s="66"/>
-      <c r="Q47" s="66"/>
-      <c r="R47" s="67"/>
+      <c r="O47" s="65">
+        <v>5</v>
+      </c>
+      <c r="P47" s="66">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="66">
+        <v>12</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
       <c r="S47" s="62"/>
       <c r="T47" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="U47" s="77">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
+        <v>16861</v>
       </c>
       <c r="V47" s="77">
         <f>U47/6</f>
-        <v>0</v>
+        <v>2810.1666666666665</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -7119,7 +10487,9 @@
       <c r="B48" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="C48" s="70"/>
+      <c r="C48" s="70">
+        <v>1</v>
+      </c>
       <c r="D48" s="70"/>
       <c r="E48" s="70"/>
       <c r="F48" s="70"/>
@@ -7142,11 +10512,11 @@
       </c>
       <c r="U48" s="75">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V48" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
@@ -7157,7 +10527,9 @@
       <c r="B49" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="C49" s="70"/>
+      <c r="C49" s="70">
+        <v>1</v>
+      </c>
       <c r="D49" s="70"/>
       <c r="E49" s="70"/>
       <c r="F49" s="70"/>
@@ -7171,7 +10543,9 @@
       <c r="N49" s="74"/>
       <c r="O49" s="70"/>
       <c r="P49" s="71"/>
-      <c r="Q49" s="71"/>
+      <c r="Q49" s="71">
+        <v>1</v>
+      </c>
       <c r="R49" s="72"/>
       <c r="S49" s="55"/>
       <c r="T49" s="75">
@@ -7180,11 +10554,11 @@
       </c>
       <c r="U49" s="75">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V49" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.25">
@@ -7233,7 +10607,9 @@
       <c r="B51" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C51" s="65"/>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
       <c r="D51" s="65"/>
       <c r="E51" s="65"/>
       <c r="F51" s="65"/>
@@ -7256,11 +10632,11 @@
       </c>
       <c r="U51" s="77">
         <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V51" s="77">
         <f>U51/6</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -7285,7 +10661,9 @@
       <c r="N52" s="74"/>
       <c r="O52" s="70"/>
       <c r="P52" s="71"/>
-      <c r="Q52" s="71"/>
+      <c r="Q52" s="71">
+        <v>1</v>
+      </c>
       <c r="R52" s="72"/>
       <c r="S52" s="55"/>
       <c r="T52" s="75">
@@ -7294,11 +10672,11 @@
       </c>
       <c r="U52" s="75">
         <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V52" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.25">
@@ -7309,7 +10687,9 @@
       <c r="B53" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="70"/>
+      <c r="C53" s="70">
+        <v>9</v>
+      </c>
       <c r="D53" s="70"/>
       <c r="E53" s="70"/>
       <c r="F53" s="70"/>
@@ -7323,7 +10703,9 @@
       <c r="N53" s="74"/>
       <c r="O53" s="70"/>
       <c r="P53" s="71"/>
-      <c r="Q53" s="71"/>
+      <c r="Q53" s="71">
+        <v>1</v>
+      </c>
       <c r="R53" s="72"/>
       <c r="S53" s="55"/>
       <c r="T53" s="75">
@@ -7332,11 +10714,11 @@
       </c>
       <c r="U53" s="75">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="V53" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -7462,7 +10844,7 @@
       </c>
       <c r="C58" s="2">
         <f>SUM(C7:C57)</f>
-        <v>0</v>
+        <v>49169</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -7476,56 +10858,56 @@
       </c>
       <c r="H58" s="2">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1181</v>
       </c>
       <c r="I58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="K58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>449</v>
       </c>
       <c r="M58" s="5">
         <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
+        <v>383</v>
       </c>
       <c r="N58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>466</v>
       </c>
       <c r="P58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Q58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="R58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S58" s="55"/>
       <c r="T58" s="4">
         <f>SUM(T7:T57)</f>
-        <v>0</v>
+        <v>1769</v>
       </c>
       <c r="U58" s="90">
         <f>SUM(U7:U57)</f>
-        <v>0</v>
+        <v>379667</v>
       </c>
       <c r="V58" s="4">
         <f>SUM(V7:V57)</f>
-        <v>0</v>
+        <v>50714.583333333336</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -7812,7 +11194,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E38FC253-41DB-4918-B98F-2A65359497C9}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -7827,7 +11209,7 @@
     <col min="8" max="8" width="6.7109375" style="9" customWidth="1"/>
     <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
-    <col min="11" max="11" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
     <col min="13" max="13" width="10" style="9" customWidth="1"/>
     <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
@@ -7870,7 +11252,7 @@
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -8044,34 +11426,46 @@
       <c r="B7" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="52"/>
+      <c r="C7" s="52">
+        <v>20</v>
+      </c>
       <c r="D7" s="52"/>
       <c r="E7" s="52"/>
       <c r="F7" s="52"/>
       <c r="G7" s="52"/>
       <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
       <c r="J7" s="53"/>
-      <c r="K7" s="54"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
       <c r="L7" s="55"/>
-      <c r="M7" s="56"/>
+      <c r="M7" s="56">
+        <v>1</v>
+      </c>
       <c r="N7" s="57"/>
-      <c r="O7" s="52"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
       <c r="P7" s="53"/>
-      <c r="Q7" s="53"/>
+      <c r="Q7" s="53">
+        <v>1</v>
+      </c>
       <c r="R7" s="54"/>
       <c r="S7" s="55"/>
       <c r="T7" s="58">
         <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U7" s="58">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>561</v>
       </c>
       <c r="V7" s="58">
         <f>U7/24</f>
-        <v>0</v>
+        <v>23.375</v>
       </c>
       <c r="W7" s="50"/>
       <c r="AF7" s="12"/>
@@ -8106,7 +11500,10 @@
       <c r="B8" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="59"/>
+      <c r="C8" s="59">
+        <f>61+33</f>
+        <v>94</v>
+      </c>
       <c r="D8" s="59"/>
       <c r="E8" s="59"/>
       <c r="F8" s="59"/>
@@ -8116,11 +11513,15 @@
       <c r="J8" s="60"/>
       <c r="K8" s="61"/>
       <c r="L8" s="62"/>
-      <c r="M8" s="63"/>
+      <c r="M8" s="63">
+        <v>2</v>
+      </c>
       <c r="N8" s="64"/>
       <c r="O8" s="65"/>
       <c r="P8" s="66"/>
-      <c r="Q8" s="66"/>
+      <c r="Q8" s="66">
+        <v>2</v>
+      </c>
       <c r="R8" s="67"/>
       <c r="S8" s="62"/>
       <c r="T8" s="68">
@@ -8129,11 +11530,11 @@
       </c>
       <c r="U8" s="69">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
+        <v>2352</v>
       </c>
       <c r="V8" s="69">
         <f>U8/24</f>
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="W8" s="50"/>
       <c r="AF8" s="12"/>
@@ -8168,7 +11569,10 @@
       <c r="B9" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="70"/>
+      <c r="C9" s="70">
+        <f>90+53</f>
+        <v>143</v>
+      </c>
       <c r="D9" s="70"/>
       <c r="E9" s="70"/>
       <c r="F9" s="70"/>
@@ -8178,7 +11582,9 @@
       <c r="J9" s="71"/>
       <c r="K9" s="72"/>
       <c r="L9" s="55"/>
-      <c r="M9" s="73"/>
+      <c r="M9" s="73">
+        <v>1</v>
+      </c>
       <c r="N9" s="74"/>
       <c r="O9" s="70"/>
       <c r="P9" s="71"/>
@@ -8191,11 +11597,11 @@
       </c>
       <c r="U9" s="76">
         <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
-        <v>0</v>
+        <v>3456</v>
       </c>
       <c r="V9" s="76">
         <f t="shared" ref="V9:V11" si="3">U9/24</f>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="W9" s="50"/>
       <c r="AF9" s="12"/>
@@ -8230,7 +11636,9 @@
       <c r="B10" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="70"/>
+      <c r="C10" s="70">
+        <v>32</v>
+      </c>
       <c r="D10" s="70"/>
       <c r="E10" s="70"/>
       <c r="F10" s="70"/>
@@ -8240,7 +11648,9 @@
       <c r="J10" s="71"/>
       <c r="K10" s="72"/>
       <c r="L10" s="55"/>
-      <c r="M10" s="73"/>
+      <c r="M10" s="73">
+        <v>1</v>
+      </c>
       <c r="N10" s="74"/>
       <c r="O10" s="70"/>
       <c r="P10" s="71"/>
@@ -8253,11 +11663,11 @@
       </c>
       <c r="U10" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="V10" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="W10" s="50"/>
       <c r="AF10" s="12"/>
@@ -8292,7 +11702,9 @@
       <c r="B11" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="70"/>
+      <c r="C11" s="70">
+        <v>5</v>
+      </c>
       <c r="D11" s="70"/>
       <c r="E11" s="70"/>
       <c r="F11" s="70"/>
@@ -8300,7 +11712,9 @@
       <c r="H11" s="70"/>
       <c r="I11" s="70"/>
       <c r="J11" s="71"/>
-      <c r="K11" s="72"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
       <c r="L11" s="55"/>
       <c r="M11" s="73"/>
       <c r="N11" s="74"/>
@@ -8311,15 +11725,15 @@
       <c r="S11" s="55"/>
       <c r="T11" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U11" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="V11" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>5.083333333333333</v>
       </c>
       <c r="AF11" s="12"/>
       <c r="AG11" s="12"/>
@@ -8352,7 +11766,10 @@
       <c r="B12" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="59"/>
+      <c r="C12" s="59">
+        <f>720+34+288+576+47+1440</f>
+        <v>3105</v>
+      </c>
       <c r="D12" s="59"/>
       <c r="E12" s="59"/>
       <c r="F12" s="59"/>
@@ -8362,24 +11779,32 @@
       <c r="J12" s="60"/>
       <c r="K12" s="61"/>
       <c r="L12" s="62"/>
-      <c r="M12" s="63"/>
+      <c r="M12" s="63">
+        <v>26</v>
+      </c>
       <c r="N12" s="64"/>
-      <c r="O12" s="65"/>
-      <c r="P12" s="66"/>
-      <c r="Q12" s="66"/>
+      <c r="O12" s="65">
+        <v>10</v>
+      </c>
+      <c r="P12" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q12" s="66">
+        <v>4</v>
+      </c>
       <c r="R12" s="67"/>
       <c r="S12" s="62"/>
       <c r="T12" s="69">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="U12" s="69">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
+        <v>75492</v>
       </c>
       <c r="V12" s="69">
         <f>U12/24</f>
-        <v>0</v>
+        <v>3145.5</v>
       </c>
       <c r="W12" s="9"/>
       <c r="X12" s="9"/>
@@ -8421,12 +11846,16 @@
       <c r="B13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="70"/>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
       <c r="D13" s="70"/>
       <c r="E13" s="70"/>
       <c r="F13" s="70"/>
       <c r="G13" s="70"/>
-      <c r="H13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
       <c r="I13" s="70"/>
       <c r="J13" s="71"/>
       <c r="K13" s="72"/>
@@ -8440,15 +11869,15 @@
       <c r="S13" s="55"/>
       <c r="T13" s="76">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="U13" s="76">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="V13" s="76">
         <f>U13/24</f>
-        <v>0</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="AF13" s="12"/>
       <c r="AG13" s="12"/>
@@ -8482,7 +11911,9 @@
       <c r="B14" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="70"/>
+      <c r="C14" s="70">
+        <v>4</v>
+      </c>
       <c r="D14" s="70"/>
       <c r="E14" s="70"/>
       <c r="F14" s="70"/>
@@ -8505,11 +11936,11 @@
       </c>
       <c r="U14" s="75">
         <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V14" s="75">
         <f t="shared" ref="V14:V36" si="5">U14/24</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF14" s="12"/>
       <c r="AG14" s="12"/>
@@ -8670,7 +12101,10 @@
       <c r="E17" s="70"/>
       <c r="F17" s="70"/>
       <c r="G17" s="70"/>
-      <c r="H17" s="70"/>
+      <c r="H17" s="70">
+        <f>24*3</f>
+        <v>72</v>
+      </c>
       <c r="I17" s="70"/>
       <c r="J17" s="71"/>
       <c r="K17" s="72"/>
@@ -8684,15 +12118,15 @@
       <c r="S17" s="55"/>
       <c r="T17" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U17" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V17" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF17" s="12"/>
       <c r="AG17" s="12"/>
@@ -8786,12 +12220,17 @@
       <c r="B19" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="70"/>
+      <c r="C19" s="70">
+        <v>2</v>
+      </c>
       <c r="D19" s="70"/>
       <c r="E19" s="70"/>
       <c r="F19" s="70"/>
       <c r="G19" s="70"/>
-      <c r="H19" s="70"/>
+      <c r="H19" s="70">
+        <f>24+20</f>
+        <v>44</v>
+      </c>
       <c r="I19" s="70"/>
       <c r="J19" s="71"/>
       <c r="K19" s="72"/>
@@ -8805,15 +12244,15 @@
       <c r="S19" s="55"/>
       <c r="T19" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="U19" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="V19" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3.8333333333333335</v>
       </c>
       <c r="AF19" s="12"/>
       <c r="AG19" s="12"/>
@@ -8847,7 +12286,9 @@
       <c r="B20" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="70"/>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
       <c r="D20" s="70"/>
       <c r="E20" s="70"/>
       <c r="F20" s="70"/>
@@ -8870,11 +12311,11 @@
       </c>
       <c r="U20" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V20" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF20" s="12"/>
       <c r="AG20" s="12"/>
@@ -8913,7 +12354,10 @@
       <c r="E21" s="70"/>
       <c r="F21" s="70"/>
       <c r="G21" s="70"/>
-      <c r="H21" s="70"/>
+      <c r="H21" s="70">
+        <f>2*24</f>
+        <v>48</v>
+      </c>
       <c r="I21" s="70"/>
       <c r="J21" s="71"/>
       <c r="K21" s="72"/>
@@ -8927,15 +12371,15 @@
       <c r="S21" s="55"/>
       <c r="T21" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="U21" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V21" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF21" s="12"/>
       <c r="AG21" s="12"/>
@@ -8975,7 +12419,9 @@
       <c r="F22" s="70"/>
       <c r="G22" s="70"/>
       <c r="H22" s="70"/>
-      <c r="I22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
       <c r="J22" s="71"/>
       <c r="K22" s="72"/>
       <c r="L22" s="55"/>
@@ -8988,15 +12434,15 @@
       <c r="S22" s="55"/>
       <c r="T22" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U22" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V22" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="W22" s="9"/>
       <c r="X22" s="9"/>
@@ -9044,7 +12490,10 @@
       <c r="E23" s="70"/>
       <c r="F23" s="70"/>
       <c r="G23" s="70"/>
-      <c r="H23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
       <c r="I23" s="70"/>
       <c r="J23" s="71"/>
       <c r="K23" s="72"/>
@@ -9058,15 +12507,15 @@
       <c r="S23" s="55"/>
       <c r="T23" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="U23" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="V23" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>37.791666666666664</v>
       </c>
       <c r="W23" s="9"/>
       <c r="X23" s="9"/>
@@ -9109,12 +12558,17 @@
       <c r="B24" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="70"/>
+      <c r="C24" s="70">
+        <v>5</v>
+      </c>
       <c r="D24" s="70"/>
       <c r="E24" s="70"/>
       <c r="F24" s="70"/>
       <c r="G24" s="70"/>
-      <c r="H24" s="70"/>
+      <c r="H24" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
       <c r="I24" s="70"/>
       <c r="J24" s="71"/>
       <c r="K24" s="72"/>
@@ -9128,15 +12582,15 @@
       <c r="S24" s="55"/>
       <c r="T24" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U24" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="V24" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AF24" s="12"/>
       <c r="AG24" s="12"/>
@@ -9170,34 +12624,43 @@
       <c r="B25" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="70"/>
+      <c r="C25" s="70">
+        <f>126+19</f>
+        <v>145</v>
+      </c>
       <c r="D25" s="70"/>
       <c r="E25" s="70"/>
       <c r="F25" s="70"/>
       <c r="G25" s="70"/>
       <c r="H25" s="70"/>
       <c r="I25" s="70"/>
-      <c r="J25" s="71"/>
+      <c r="J25" s="71">
+        <v>1</v>
+      </c>
       <c r="K25" s="72"/>
       <c r="L25" s="55"/>
-      <c r="M25" s="73"/>
+      <c r="M25" s="73">
+        <v>3</v>
+      </c>
       <c r="N25" s="74"/>
-      <c r="O25" s="70"/>
+      <c r="O25" s="70">
+        <v>1</v>
+      </c>
       <c r="P25" s="71"/>
       <c r="Q25" s="71"/>
       <c r="R25" s="72"/>
       <c r="S25" s="55"/>
       <c r="T25" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3577</v>
       </c>
       <c r="V25" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>149.04166666666666</v>
       </c>
       <c r="AY25" s="14" t="e">
         <f>#REF!-AY24</f>
@@ -9306,7 +12769,10 @@
       <c r="B28" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="70"/>
+      <c r="C28" s="70">
+        <f>31+63</f>
+        <v>94</v>
+      </c>
       <c r="D28" s="70"/>
       <c r="E28" s="70"/>
       <c r="F28" s="70"/>
@@ -9316,9 +12782,13 @@
       <c r="J28" s="71"/>
       <c r="K28" s="72"/>
       <c r="L28" s="55"/>
-      <c r="M28" s="73"/>
+      <c r="M28" s="73">
+        <v>4</v>
+      </c>
       <c r="N28" s="74"/>
-      <c r="O28" s="70"/>
+      <c r="O28" s="70">
+        <v>2</v>
+      </c>
       <c r="P28" s="71"/>
       <c r="Q28" s="71"/>
       <c r="R28" s="72"/>
@@ -9329,11 +12799,11 @@
       </c>
       <c r="U28" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="V28" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W28" s="9"/>
       <c r="X28" s="9"/>
@@ -9353,34 +12823,42 @@
       <c r="B29" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="70"/>
+      <c r="C29" s="70">
+        <v>51</v>
+      </c>
       <c r="D29" s="70"/>
       <c r="E29" s="70"/>
       <c r="F29" s="70"/>
       <c r="G29" s="70"/>
       <c r="H29" s="70"/>
-      <c r="I29" s="70"/>
+      <c r="I29" s="70">
+        <v>5</v>
+      </c>
       <c r="J29" s="71"/>
       <c r="K29" s="72"/>
       <c r="L29" s="55"/>
-      <c r="M29" s="73"/>
+      <c r="M29" s="73">
+        <v>1</v>
+      </c>
       <c r="N29" s="74"/>
-      <c r="O29" s="70"/>
+      <c r="O29" s="70">
+        <v>1</v>
+      </c>
       <c r="P29" s="71"/>
       <c r="Q29" s="71"/>
       <c r="R29" s="72"/>
       <c r="S29" s="55"/>
       <c r="T29" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U29" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1277</v>
       </c>
       <c r="V29" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>53.208333333333336</v>
       </c>
     </row>
     <row r="30" spans="1:54" x14ac:dyDescent="0.25">
@@ -9391,7 +12869,9 @@
       <c r="B30" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="70"/>
+      <c r="C30" s="70">
+        <v>13</v>
+      </c>
       <c r="D30" s="70"/>
       <c r="E30" s="70"/>
       <c r="F30" s="70"/>
@@ -9414,11 +12894,11 @@
       </c>
       <c r="U30" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="V30" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
@@ -9467,7 +12947,9 @@
       <c r="B32" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="C32" s="70"/>
+      <c r="C32" s="70">
+        <v>4</v>
+      </c>
       <c r="D32" s="70"/>
       <c r="E32" s="70"/>
       <c r="F32" s="70"/>
@@ -9490,11 +12972,11 @@
       </c>
       <c r="U32" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V32" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.25">
@@ -9543,34 +13025,48 @@
       <c r="B34" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="70"/>
+      <c r="C34" s="70">
+        <v>66</v>
+      </c>
       <c r="D34" s="70"/>
       <c r="E34" s="70"/>
       <c r="F34" s="70"/>
       <c r="G34" s="70"/>
       <c r="H34" s="70"/>
-      <c r="I34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
       <c r="J34" s="71"/>
-      <c r="K34" s="72"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
       <c r="L34" s="55"/>
-      <c r="M34" s="73"/>
+      <c r="M34" s="73">
+        <v>3</v>
+      </c>
       <c r="N34" s="74"/>
-      <c r="O34" s="70"/>
-      <c r="P34" s="71"/>
-      <c r="Q34" s="71"/>
+      <c r="O34" s="70">
+        <v>1</v>
+      </c>
+      <c r="P34" s="71">
+        <v>12</v>
+      </c>
+      <c r="Q34" s="71">
+        <v>7</v>
+      </c>
       <c r="R34" s="72"/>
       <c r="S34" s="55"/>
       <c r="T34" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="U34" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="V34" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>77.583333333333329</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -9657,34 +13153,49 @@
       <c r="B37" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="59"/>
+      <c r="C37" s="59">
+        <f>864+3456+54</f>
+        <v>4374</v>
+      </c>
       <c r="D37" s="59"/>
       <c r="E37" s="59"/>
       <c r="F37" s="59"/>
       <c r="G37" s="59"/>
       <c r="H37" s="59"/>
-      <c r="I37" s="59"/>
-      <c r="J37" s="60"/>
-      <c r="K37" s="61"/>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>2</v>
+      </c>
+      <c r="K37" s="61">
+        <v>3</v>
+      </c>
       <c r="L37" s="62"/>
-      <c r="M37" s="63"/>
+      <c r="M37" s="63">
+        <v>19</v>
+      </c>
       <c r="N37" s="64"/>
-      <c r="O37" s="65"/>
+      <c r="O37" s="65">
+        <v>23</v>
+      </c>
       <c r="P37" s="66"/>
-      <c r="Q37" s="66"/>
+      <c r="Q37" s="66">
+        <v>28</v>
+      </c>
       <c r="R37" s="67"/>
       <c r="S37" s="62"/>
       <c r="T37" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U37" s="77">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
+        <v>26671</v>
       </c>
       <c r="V37" s="77">
         <f>U37/6</f>
-        <v>0</v>
+        <v>4445.166666666667</v>
       </c>
       <c r="W37" s="50"/>
     </row>
@@ -9772,7 +13283,10 @@
       <c r="B40" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="59"/>
+      <c r="C40" s="59">
+        <f>63+26</f>
+        <v>89</v>
+      </c>
       <c r="D40" s="59"/>
       <c r="E40" s="59"/>
       <c r="F40" s="59"/>
@@ -9780,26 +13294,34 @@
       <c r="H40" s="59"/>
       <c r="I40" s="59"/>
       <c r="J40" s="60"/>
-      <c r="K40" s="61"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
       <c r="L40" s="62"/>
-      <c r="M40" s="63"/>
+      <c r="M40" s="63">
+        <v>3</v>
+      </c>
       <c r="N40" s="64"/>
-      <c r="O40" s="65"/>
-      <c r="P40" s="66"/>
+      <c r="O40" s="65">
+        <v>1</v>
+      </c>
+      <c r="P40" s="66">
+        <v>12</v>
+      </c>
       <c r="Q40" s="66"/>
       <c r="R40" s="67"/>
       <c r="S40" s="62"/>
       <c r="T40" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="U40" s="77">
         <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
+        <v>2264</v>
       </c>
       <c r="V40" s="77">
         <f>U40/24</f>
-        <v>0</v>
+        <v>94.333333333333329</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -9810,7 +13332,10 @@
       <c r="B41" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="82"/>
+      <c r="C41" s="82">
+        <f>192+34</f>
+        <v>226</v>
+      </c>
       <c r="D41" s="82"/>
       <c r="E41" s="82"/>
       <c r="F41" s="82"/>
@@ -9820,9 +13345,13 @@
       <c r="J41" s="83"/>
       <c r="K41" s="84"/>
       <c r="L41" s="85"/>
-      <c r="M41" s="86"/>
+      <c r="M41" s="86">
+        <v>13</v>
+      </c>
       <c r="N41" s="87"/>
-      <c r="O41" s="82"/>
+      <c r="O41" s="82">
+        <v>6</v>
+      </c>
       <c r="P41" s="83"/>
       <c r="Q41" s="83"/>
       <c r="R41" s="84"/>
@@ -9833,11 +13362,11 @@
       </c>
       <c r="U41" s="88">
         <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
+        <v>2940</v>
       </c>
       <c r="V41" s="88">
         <f>U41/12</f>
-        <v>0</v>
+        <v>245</v>
       </c>
     </row>
     <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -9877,34 +13406,52 @@
       <c r="B43" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="65"/>
+      <c r="C43" s="65">
+        <f>7776+3456+3024+8424+5508+3024+5832</f>
+        <v>37044</v>
+      </c>
       <c r="D43" s="65"/>
       <c r="E43" s="65"/>
       <c r="F43" s="65"/>
       <c r="G43" s="65"/>
       <c r="H43" s="65"/>
-      <c r="I43" s="65"/>
-      <c r="J43" s="66"/>
-      <c r="K43" s="67"/>
+      <c r="I43" s="65">
+        <f>7</f>
+        <v>7</v>
+      </c>
+      <c r="J43" s="66">
+        <f>6*9+1</f>
+        <v>55</v>
+      </c>
+      <c r="K43" s="67">
+        <f>69*6+7</f>
+        <v>421</v>
+      </c>
       <c r="L43" s="62"/>
-      <c r="M43" s="63"/>
+      <c r="M43" s="63">
+        <v>469</v>
+      </c>
       <c r="N43" s="64"/>
-      <c r="O43" s="65"/>
+      <c r="O43" s="65">
+        <v>398</v>
+      </c>
       <c r="P43" s="66"/>
-      <c r="Q43" s="66"/>
+      <c r="Q43" s="66">
+        <v>2</v>
+      </c>
       <c r="R43" s="67"/>
       <c r="S43" s="62"/>
       <c r="T43" s="77">
         <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
+        <v>483</v>
       </c>
       <c r="U43" s="77">
         <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
+        <v>227961</v>
       </c>
       <c r="V43" s="77">
         <f>U43/6</f>
-        <v>0</v>
+        <v>37993.5</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -10020,34 +13567,51 @@
       <c r="B47" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C47" s="65"/>
+      <c r="C47" s="65">
+        <f>14+432+106+2160+71</f>
+        <v>2783</v>
+      </c>
       <c r="D47" s="65"/>
       <c r="E47" s="65"/>
       <c r="F47" s="65"/>
       <c r="G47" s="65"/>
-      <c r="H47" s="65"/>
+      <c r="H47" s="65">
+        <v>2</v>
+      </c>
       <c r="I47" s="65"/>
       <c r="J47" s="66"/>
-      <c r="K47" s="67"/>
+      <c r="K47" s="67">
+        <v>4</v>
+      </c>
       <c r="L47" s="62"/>
-      <c r="M47" s="63"/>
+      <c r="M47" s="63">
+        <v>8</v>
+      </c>
       <c r="N47" s="64"/>
-      <c r="O47" s="65"/>
-      <c r="P47" s="66"/>
-      <c r="Q47" s="66"/>
-      <c r="R47" s="67"/>
+      <c r="O47" s="65">
+        <v>5</v>
+      </c>
+      <c r="P47" s="66">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="66">
+        <v>2</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
       <c r="S47" s="62"/>
       <c r="T47" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="U47" s="77">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
+        <v>16801</v>
       </c>
       <c r="V47" s="77">
         <f>U47/6</f>
-        <v>0</v>
+        <v>2800.1666666666665</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -10063,7 +13627,9 @@
       <c r="E48" s="70"/>
       <c r="F48" s="70"/>
       <c r="G48" s="70"/>
-      <c r="H48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
       <c r="I48" s="70"/>
       <c r="J48" s="71"/>
       <c r="K48" s="72"/>
@@ -10077,15 +13643,15 @@
       <c r="S48" s="55"/>
       <c r="T48" s="75">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U48" s="75">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V48" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
@@ -10096,7 +13662,9 @@
       <c r="B49" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="C49" s="70"/>
+      <c r="C49" s="70">
+        <v>1</v>
+      </c>
       <c r="D49" s="70"/>
       <c r="E49" s="70"/>
       <c r="F49" s="70"/>
@@ -10119,11 +13687,11 @@
       </c>
       <c r="U49" s="75">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V49" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.25">
@@ -10172,7 +13740,9 @@
       <c r="B51" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C51" s="65"/>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
       <c r="D51" s="65"/>
       <c r="E51" s="65"/>
       <c r="F51" s="65"/>
@@ -10195,11 +13765,11 @@
       </c>
       <c r="U51" s="77">
         <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V51" s="77">
         <f>U51/6</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -10248,7 +13818,9 @@
       <c r="B53" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="70"/>
+      <c r="C53" s="70">
+        <v>9</v>
+      </c>
       <c r="D53" s="70"/>
       <c r="E53" s="70"/>
       <c r="F53" s="70"/>
@@ -10271,11 +13843,11 @@
       </c>
       <c r="U53" s="75">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="V53" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -10401,7 +13973,7 @@
       </c>
       <c r="C58" s="2">
         <f>SUM(C7:C57)</f>
-        <v>0</v>
+        <v>48350</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -10415,23 +13987,23 @@
       </c>
       <c r="H58" s="2">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1185</v>
       </c>
       <c r="I58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="K58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>457</v>
       </c>
       <c r="M58" s="5">
         <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
+        <v>554</v>
       </c>
       <c r="N58" s="5">
         <f t="shared" si="12"/>
@@ -10439,2971 +14011,32 @@
       </c>
       <c r="O58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>449</v>
       </c>
       <c r="P58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Q58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="R58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S58" s="55"/>
       <c r="T58" s="4">
         <f>SUM(T7:T57)</f>
-        <v>0</v>
+        <v>1781</v>
       </c>
       <c r="U58" s="90">
         <f>SUM(U7:U57)</f>
-        <v>0</v>
+        <v>371015</v>
       </c>
       <c r="V58" s="4">
         <f>SUM(V7:V57)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="30" t="s">
-        <v>37</v>
-      </c>
-      <c r="C60" s="102" t="s">
-        <v>41</v>
-      </c>
-      <c r="D60" s="103"/>
-      <c r="E60" s="103"/>
-      <c r="F60" s="103"/>
-      <c r="G60" s="103"/>
-      <c r="H60" s="103"/>
-      <c r="I60" s="103"/>
-      <c r="J60" s="103"/>
-      <c r="K60" s="104"/>
-      <c r="U60" s="24" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B61" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="C61" s="19"/>
-      <c r="D61" s="19"/>
-      <c r="E61" s="19"/>
-      <c r="F61" s="19"/>
-      <c r="G61" s="19"/>
-      <c r="H61" s="19"/>
-      <c r="I61" s="19"/>
-      <c r="J61" s="45"/>
-      <c r="K61" s="20"/>
-      <c r="U61" s="7"/>
-    </row>
-    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B62" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="C62" s="1"/>
-      <c r="D62" s="1"/>
-      <c r="E62" s="1"/>
-      <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
-      <c r="I62" s="1"/>
-      <c r="J62" s="44"/>
-      <c r="K62" s="21"/>
-      <c r="U62" s="3"/>
-    </row>
-    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="C63" s="22"/>
-      <c r="D63" s="22"/>
-      <c r="E63" s="22"/>
-      <c r="F63" s="22"/>
-      <c r="G63" s="22"/>
-      <c r="H63" s="22"/>
-      <c r="I63" s="22"/>
-      <c r="J63" s="46"/>
-      <c r="K63" s="23"/>
-      <c r="U63" s="8"/>
-    </row>
-    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B65" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="C65" s="19"/>
-      <c r="D65" s="19"/>
-      <c r="E65" s="19"/>
-      <c r="F65" s="19"/>
-      <c r="G65" s="19"/>
-      <c r="H65" s="19"/>
-      <c r="I65" s="19"/>
-      <c r="J65" s="45"/>
-      <c r="K65" s="20"/>
-      <c r="U65" s="7"/>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B66" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="C66" s="1"/>
-      <c r="D66" s="1"/>
-      <c r="E66" s="1"/>
-      <c r="F66" s="1"/>
-      <c r="G66" s="1"/>
-      <c r="H66" s="1"/>
-      <c r="I66" s="1"/>
-      <c r="J66" s="44"/>
-      <c r="K66" s="21"/>
-      <c r="U66" s="3"/>
-    </row>
-    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B67" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="C67" s="22"/>
-      <c r="D67" s="22"/>
-      <c r="E67" s="22"/>
-      <c r="F67" s="22"/>
-      <c r="G67" s="22"/>
-      <c r="H67" s="22"/>
-      <c r="I67" s="22"/>
-      <c r="J67" s="46"/>
-      <c r="K67" s="23"/>
-      <c r="U67" s="8"/>
-    </row>
-    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B69" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="C69" s="19"/>
-      <c r="D69" s="19"/>
-      <c r="E69" s="19"/>
-      <c r="F69" s="19"/>
-      <c r="G69" s="19"/>
-      <c r="H69" s="19"/>
-      <c r="I69" s="19"/>
-      <c r="J69" s="45"/>
-      <c r="K69" s="20"/>
-      <c r="U69" s="7"/>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B70" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="C70" s="1"/>
-      <c r="D70" s="1"/>
-      <c r="E70" s="1"/>
-      <c r="F70" s="1"/>
-      <c r="G70" s="1"/>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
-      <c r="J70" s="44"/>
-      <c r="K70" s="21"/>
-      <c r="U70" s="3"/>
-    </row>
-    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="C71" s="22"/>
-      <c r="D71" s="22"/>
-      <c r="E71" s="22"/>
-      <c r="F71" s="22"/>
-      <c r="G71" s="22"/>
-      <c r="H71" s="22"/>
-      <c r="I71" s="22"/>
-      <c r="J71" s="46"/>
-      <c r="K71" s="23"/>
-      <c r="U71" s="8"/>
-    </row>
-    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B73" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="C73" s="19"/>
-      <c r="D73" s="19"/>
-      <c r="E73" s="19"/>
-      <c r="F73" s="19"/>
-      <c r="G73" s="19"/>
-      <c r="H73" s="19"/>
-      <c r="I73" s="19"/>
-      <c r="J73" s="45"/>
-      <c r="K73" s="20"/>
-      <c r="U73" s="7"/>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B74" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="C74" s="1"/>
-      <c r="D74" s="1"/>
-      <c r="E74" s="1"/>
-      <c r="F74" s="1"/>
-      <c r="G74" s="1"/>
-      <c r="H74" s="1"/>
-      <c r="I74" s="1"/>
-      <c r="J74" s="44"/>
-      <c r="K74" s="21"/>
-      <c r="U74" s="3"/>
-    </row>
-    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B75" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="C75" s="22"/>
-      <c r="D75" s="22"/>
-      <c r="E75" s="22"/>
-      <c r="F75" s="22"/>
-      <c r="G75" s="22"/>
-      <c r="H75" s="22"/>
-      <c r="I75" s="22"/>
-      <c r="J75" s="46"/>
-      <c r="K75" s="23"/>
-      <c r="U75" s="8"/>
-    </row>
-    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B77" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="C77" s="19"/>
-      <c r="D77" s="19"/>
-      <c r="E77" s="19"/>
-      <c r="F77" s="19"/>
-      <c r="G77" s="19"/>
-      <c r="H77" s="19"/>
-      <c r="I77" s="19"/>
-      <c r="J77" s="45"/>
-      <c r="K77" s="20"/>
-      <c r="U77" s="7"/>
-    </row>
-    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B78" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="C78" s="1"/>
-      <c r="D78" s="1"/>
-      <c r="E78" s="1"/>
-      <c r="F78" s="1"/>
-      <c r="G78" s="1"/>
-      <c r="H78" s="1"/>
-      <c r="I78" s="1"/>
-      <c r="J78" s="44"/>
-      <c r="K78" s="21"/>
-      <c r="U78" s="3"/>
-    </row>
-    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B79" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="C79" s="22"/>
-      <c r="D79" s="22"/>
-      <c r="E79" s="22"/>
-      <c r="F79" s="22"/>
-      <c r="G79" s="22"/>
-      <c r="H79" s="22"/>
-      <c r="I79" s="22"/>
-      <c r="J79" s="46"/>
-      <c r="K79" s="23"/>
-      <c r="U79" s="8"/>
-    </row>
-    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B81" s="30" t="s">
-        <v>49</v>
-      </c>
-      <c r="C81" s="17"/>
-      <c r="D81" s="17"/>
-      <c r="E81" s="17"/>
-      <c r="F81" s="17"/>
-      <c r="G81" s="17"/>
-      <c r="H81" s="17"/>
-      <c r="I81" s="17"/>
-      <c r="J81" s="47"/>
-      <c r="K81" s="18"/>
-      <c r="U81" s="16"/>
-    </row>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="C60:K60"/>
-    <mergeCell ref="I1:U1"/>
-    <mergeCell ref="C4:K4"/>
-    <mergeCell ref="T4:T5"/>
-    <mergeCell ref="U4:U5"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
-  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
-  <colBreaks count="1" manualBreakCount="1">
-    <brk id="24" max="80" man="1"/>
-  </colBreaks>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{904A2011-2D80-4AE1-96EB-73435B2D09C4}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:BB81"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
-    <col min="3" max="6" width="10" style="9" customWidth="1"/>
-    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
-    <col min="8" max="8" width="6.7109375" style="9" customWidth="1"/>
-    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
-    <col min="11" max="11" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
-    <col min="13" max="13" width="10" style="9" customWidth="1"/>
-    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10" style="9" customWidth="1"/>
-    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
-    <col min="17" max="17" width="10" style="9" customWidth="1"/>
-    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
-    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
-    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
-    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
-    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
-    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
-    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
-    <col min="55" max="16384" width="9.140625" style="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="I1" s="105" t="s">
-        <v>43</v>
-      </c>
-      <c r="J1" s="105"/>
-      <c r="K1" s="105"/>
-      <c r="L1" s="105"/>
-      <c r="M1" s="105"/>
-      <c r="N1" s="105"/>
-      <c r="O1" s="105"/>
-      <c r="P1" s="105"/>
-      <c r="Q1" s="105"/>
-      <c r="R1" s="105"/>
-      <c r="S1" s="105"/>
-      <c r="T1" s="105"/>
-      <c r="U1" s="105"/>
-    </row>
-    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="B2" s="28" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B4" s="41" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" s="106" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" s="106"/>
-      <c r="E4" s="106"/>
-      <c r="F4" s="106"/>
-      <c r="G4" s="106"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="107"/>
-      <c r="K4" s="108"/>
-      <c r="M4" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="N4" s="48" t="s">
-        <v>61</v>
-      </c>
-      <c r="O4" s="35" t="s">
-        <v>39</v>
-      </c>
-      <c r="P4" s="48" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q4" s="36" t="s">
-        <v>40</v>
-      </c>
-      <c r="R4" s="48" t="s">
-        <v>61</v>
-      </c>
-      <c r="S4" s="9"/>
-      <c r="T4" s="109" t="s">
-        <v>68</v>
-      </c>
-      <c r="U4" s="115" t="s">
-        <v>67</v>
-      </c>
-      <c r="V4" s="98" t="s">
-        <v>66</v>
-      </c>
-      <c r="AF4" s="11"/>
-      <c r="AG4" s="11"/>
-      <c r="AH4" s="11"/>
-      <c r="AI4" s="11"/>
-      <c r="AJ4" s="11"/>
-      <c r="AK4" s="11"/>
-      <c r="AL4" s="11"/>
-      <c r="AM4" s="11"/>
-      <c r="AN4" s="11"/>
-      <c r="AO4" s="11"/>
-      <c r="AP4" s="11"/>
-      <c r="AQ4" s="11"/>
-      <c r="AR4" s="11"/>
-      <c r="AS4" s="11"/>
-      <c r="AT4" s="11"/>
-      <c r="AU4" s="11"/>
-      <c r="AV4" s="11"/>
-      <c r="AW4" s="11"/>
-      <c r="AX4" s="11"/>
-      <c r="AY4" s="11"/>
-      <c r="AZ4" s="11"/>
-      <c r="BA4" s="11"/>
-      <c r="BB4" s="11"/>
-    </row>
-    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="37"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40" t="s">
-        <v>64</v>
-      </c>
-      <c r="I5" s="40" t="s">
-        <v>60</v>
-      </c>
-      <c r="J5" s="113" t="s">
-        <v>65</v>
-      </c>
-      <c r="K5" s="114"/>
-      <c r="M5" s="37"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="40"/>
-      <c r="P5" s="97"/>
-      <c r="Q5" s="97"/>
-      <c r="R5" s="38"/>
-      <c r="S5" s="9"/>
-      <c r="T5" s="110"/>
-      <c r="U5" s="116"/>
-      <c r="V5" s="99"/>
-      <c r="AF5" s="11"/>
-      <c r="AG5" s="11"/>
-      <c r="AH5" s="11"/>
-      <c r="AI5" s="11"/>
-      <c r="AJ5" s="11"/>
-      <c r="AK5" s="11"/>
-      <c r="AL5" s="11"/>
-      <c r="AM5" s="11"/>
-      <c r="AN5" s="11"/>
-      <c r="AO5" s="11"/>
-      <c r="AP5" s="11"/>
-      <c r="AQ5" s="11"/>
-      <c r="AR5" s="11"/>
-      <c r="AS5" s="11"/>
-      <c r="AT5" s="11"/>
-      <c r="AU5" s="11"/>
-      <c r="AV5" s="11"/>
-      <c r="AW5" s="11"/>
-      <c r="AX5" s="11"/>
-      <c r="AY5" s="11"/>
-      <c r="AZ5" s="11"/>
-      <c r="BA5" s="11"/>
-      <c r="BB5" s="11"/>
-    </row>
-    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="37"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="97"/>
-      <c r="K6" s="38"/>
-      <c r="M6" s="37"/>
-      <c r="N6" s="49"/>
-      <c r="O6" s="40"/>
-      <c r="P6" s="97"/>
-      <c r="Q6" s="97"/>
-      <c r="R6" s="38"/>
-      <c r="S6" s="9"/>
-      <c r="T6" s="39"/>
-      <c r="U6" s="39"/>
-      <c r="V6" s="39"/>
-      <c r="AF6" s="11"/>
-      <c r="AG6" s="11"/>
-      <c r="AH6" s="11"/>
-      <c r="AI6" s="11"/>
-      <c r="AJ6" s="11"/>
-      <c r="AK6" s="11"/>
-      <c r="AL6" s="11"/>
-      <c r="AM6" s="11"/>
-      <c r="AN6" s="11"/>
-      <c r="AO6" s="11"/>
-      <c r="AP6" s="11"/>
-      <c r="AQ6" s="11"/>
-      <c r="AR6" s="11"/>
-      <c r="AS6" s="11"/>
-      <c r="AT6" s="11"/>
-      <c r="AU6" s="11"/>
-      <c r="AV6" s="11"/>
-      <c r="AW6" s="11"/>
-      <c r="AX6" s="11"/>
-      <c r="AY6" s="11"/>
-      <c r="AZ6" s="11"/>
-      <c r="BA6" s="11"/>
-      <c r="BB6" s="11"/>
-    </row>
-    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A7" s="27">
-        <v>1</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="52"/>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="52"/>
-      <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
-      <c r="J7" s="53"/>
-      <c r="K7" s="54"/>
-      <c r="L7" s="55"/>
-      <c r="M7" s="56"/>
-      <c r="N7" s="57"/>
-      <c r="O7" s="52"/>
-      <c r="P7" s="53"/>
-      <c r="Q7" s="53"/>
-      <c r="R7" s="54"/>
-      <c r="S7" s="55"/>
-      <c r="T7" s="58">
-        <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
-      </c>
-      <c r="U7" s="58">
-        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
-      </c>
-      <c r="V7" s="58">
-        <f>U7/24</f>
-        <v>0</v>
-      </c>
-      <c r="W7" s="50"/>
-      <c r="AF7" s="12"/>
-      <c r="AG7" s="12"/>
-      <c r="AH7" s="12"/>
-      <c r="AI7" s="12"/>
-      <c r="AJ7" s="12"/>
-      <c r="AK7" s="12"/>
-      <c r="AL7" s="12"/>
-      <c r="AM7" s="12"/>
-      <c r="AN7" s="12"/>
-      <c r="AO7" s="12"/>
-      <c r="AP7" s="12"/>
-      <c r="AQ7" s="12"/>
-      <c r="AR7" s="12"/>
-      <c r="AS7" s="12"/>
-      <c r="AT7" s="12"/>
-      <c r="AU7" s="12"/>
-      <c r="AV7" s="12"/>
-      <c r="AW7" s="12"/>
-      <c r="AX7" s="12"/>
-      <c r="AY7" s="12"/>
-      <c r="AZ7" s="12"/>
-      <c r="BA7" s="12"/>
-      <c r="BB7" s="12"/>
-    </row>
-    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27">
-        <f>A7+1</f>
-        <v>2</v>
-      </c>
-      <c r="B8" s="42" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="59"/>
-      <c r="D8" s="59"/>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="59"/>
-      <c r="I8" s="59"/>
-      <c r="J8" s="60"/>
-      <c r="K8" s="61"/>
-      <c r="L8" s="62"/>
-      <c r="M8" s="63"/>
-      <c r="N8" s="64"/>
-      <c r="O8" s="65"/>
-      <c r="P8" s="66"/>
-      <c r="Q8" s="66"/>
-      <c r="R8" s="67"/>
-      <c r="S8" s="62"/>
-      <c r="T8" s="68">
-        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
-        <v>0</v>
-      </c>
-      <c r="U8" s="69">
-        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
-      </c>
-      <c r="V8" s="69">
-        <f>U8/24</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="50"/>
-      <c r="AF8" s="12"/>
-      <c r="AG8" s="12"/>
-      <c r="AH8" s="12"/>
-      <c r="AI8" s="12"/>
-      <c r="AJ8" s="12"/>
-      <c r="AK8" s="12"/>
-      <c r="AL8" s="12"/>
-      <c r="AM8" s="12"/>
-      <c r="AN8" s="12"/>
-      <c r="AO8" s="12"/>
-      <c r="AP8" s="12"/>
-      <c r="AQ8" s="12"/>
-      <c r="AR8" s="12"/>
-      <c r="AS8" s="12"/>
-      <c r="AT8" s="12"/>
-      <c r="AU8" s="12"/>
-      <c r="AV8" s="12"/>
-      <c r="AW8" s="12"/>
-      <c r="AX8" s="12"/>
-      <c r="AY8" s="12"/>
-      <c r="AZ8" s="12"/>
-      <c r="BA8" s="12"/>
-      <c r="BB8" s="12"/>
-    </row>
-    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A9" s="27">
-        <f t="shared" ref="A9:A57" si="1">A8+1</f>
-        <v>3</v>
-      </c>
-      <c r="B9" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="70"/>
-      <c r="D9" s="70"/>
-      <c r="E9" s="70"/>
-      <c r="F9" s="70"/>
-      <c r="G9" s="70"/>
-      <c r="H9" s="70"/>
-      <c r="I9" s="70"/>
-      <c r="J9" s="71"/>
-      <c r="K9" s="72"/>
-      <c r="L9" s="55"/>
-      <c r="M9" s="73"/>
-      <c r="N9" s="74"/>
-      <c r="O9" s="70"/>
-      <c r="P9" s="71"/>
-      <c r="Q9" s="71"/>
-      <c r="R9" s="72"/>
-      <c r="S9" s="55"/>
-      <c r="T9" s="75">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U9" s="76">
-        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
-        <v>0</v>
-      </c>
-      <c r="V9" s="76">
-        <f t="shared" ref="V9:V11" si="3">U9/24</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="50"/>
-      <c r="AF9" s="12"/>
-      <c r="AG9" s="12"/>
-      <c r="AH9" s="12"/>
-      <c r="AI9" s="12"/>
-      <c r="AJ9" s="12"/>
-      <c r="AK9" s="12"/>
-      <c r="AL9" s="12"/>
-      <c r="AM9" s="12"/>
-      <c r="AN9" s="12"/>
-      <c r="AO9" s="12"/>
-      <c r="AP9" s="12"/>
-      <c r="AQ9" s="12"/>
-      <c r="AR9" s="12"/>
-      <c r="AS9" s="12"/>
-      <c r="AT9" s="12"/>
-      <c r="AU9" s="12"/>
-      <c r="AV9" s="12"/>
-      <c r="AW9" s="12"/>
-      <c r="AX9" s="12"/>
-      <c r="AY9" s="12"/>
-      <c r="AZ9" s="12"/>
-      <c r="BA9" s="12"/>
-      <c r="BB9" s="12"/>
-    </row>
-    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A10" s="27">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="B10" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="70"/>
-      <c r="D10" s="70"/>
-      <c r="E10" s="70"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="70"/>
-      <c r="H10" s="70"/>
-      <c r="I10" s="70"/>
-      <c r="J10" s="71"/>
-      <c r="K10" s="72"/>
-      <c r="L10" s="55"/>
-      <c r="M10" s="73"/>
-      <c r="N10" s="74"/>
-      <c r="O10" s="70"/>
-      <c r="P10" s="71"/>
-      <c r="Q10" s="71"/>
-      <c r="R10" s="72"/>
-      <c r="S10" s="55"/>
-      <c r="T10" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U10" s="58">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="V10" s="58">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="50"/>
-      <c r="AF10" s="12"/>
-      <c r="AG10" s="12"/>
-      <c r="AH10" s="12"/>
-      <c r="AI10" s="12"/>
-      <c r="AJ10" s="12"/>
-      <c r="AK10" s="12"/>
-      <c r="AL10" s="12"/>
-      <c r="AM10" s="12"/>
-      <c r="AN10" s="12"/>
-      <c r="AO10" s="12"/>
-      <c r="AP10" s="12"/>
-      <c r="AQ10" s="12"/>
-      <c r="AR10" s="12"/>
-      <c r="AS10" s="12"/>
-      <c r="AT10" s="12"/>
-      <c r="AU10" s="12"/>
-      <c r="AV10" s="12"/>
-      <c r="AW10" s="12"/>
-      <c r="AX10" s="12"/>
-      <c r="AY10" s="12"/>
-      <c r="AZ10" s="12"/>
-      <c r="BA10" s="12"/>
-      <c r="BB10" s="12"/>
-    </row>
-    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A11" s="27">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="B11" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="70"/>
-      <c r="D11" s="70"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="70"/>
-      <c r="H11" s="70"/>
-      <c r="I11" s="70"/>
-      <c r="J11" s="71"/>
-      <c r="K11" s="72"/>
-      <c r="L11" s="55"/>
-      <c r="M11" s="73"/>
-      <c r="N11" s="74"/>
-      <c r="O11" s="70"/>
-      <c r="P11" s="71"/>
-      <c r="Q11" s="71"/>
-      <c r="R11" s="72"/>
-      <c r="S11" s="55"/>
-      <c r="T11" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U11" s="58">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="V11" s="58">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AF11" s="12"/>
-      <c r="AG11" s="12"/>
-      <c r="AH11" s="12"/>
-      <c r="AI11" s="12"/>
-      <c r="AJ11" s="12"/>
-      <c r="AK11" s="12"/>
-      <c r="AL11" s="12"/>
-      <c r="AM11" s="12"/>
-      <c r="AN11" s="12"/>
-      <c r="AO11" s="12"/>
-      <c r="AP11" s="12"/>
-      <c r="AQ11" s="12"/>
-      <c r="AR11" s="12"/>
-      <c r="AS11" s="12"/>
-      <c r="AT11" s="12"/>
-      <c r="AU11" s="12"/>
-      <c r="AV11" s="12"/>
-      <c r="AW11" s="12"/>
-      <c r="AX11" s="12"/>
-      <c r="AY11" s="12"/>
-      <c r="AZ11" s="12"/>
-      <c r="BA11" s="12"/>
-      <c r="BB11" s="12"/>
-    </row>
-    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="27">
-        <v>7</v>
-      </c>
-      <c r="B12" s="42" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="59"/>
-      <c r="D12" s="59"/>
-      <c r="E12" s="59"/>
-      <c r="F12" s="59"/>
-      <c r="G12" s="59"/>
-      <c r="H12" s="59"/>
-      <c r="I12" s="59"/>
-      <c r="J12" s="60"/>
-      <c r="K12" s="61"/>
-      <c r="L12" s="62"/>
-      <c r="M12" s="63"/>
-      <c r="N12" s="64"/>
-      <c r="O12" s="65"/>
-      <c r="P12" s="66"/>
-      <c r="Q12" s="66"/>
-      <c r="R12" s="67"/>
-      <c r="S12" s="62"/>
-      <c r="T12" s="69">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U12" s="69">
-        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
-      </c>
-      <c r="V12" s="69">
-        <f>U12/24</f>
-        <v>0</v>
-      </c>
-      <c r="W12" s="9"/>
-      <c r="X12" s="9"/>
-      <c r="Y12" s="9"/>
-      <c r="Z12" s="9"/>
-      <c r="AA12" s="9"/>
-      <c r="AB12" s="9"/>
-      <c r="AC12" s="9"/>
-      <c r="AD12" s="9"/>
-      <c r="AE12" s="9"/>
-      <c r="AF12" s="12"/>
-      <c r="AG12" s="12"/>
-      <c r="AH12" s="12"/>
-      <c r="AI12" s="12"/>
-      <c r="AJ12" s="12"/>
-      <c r="AK12" s="12"/>
-      <c r="AL12" s="12"/>
-      <c r="AM12" s="12"/>
-      <c r="AN12" s="12"/>
-      <c r="AO12" s="12"/>
-      <c r="AP12" s="12"/>
-      <c r="AQ12" s="12"/>
-      <c r="AR12" s="12"/>
-      <c r="AS12" s="12"/>
-      <c r="AT12" s="12"/>
-      <c r="AU12" s="12"/>
-      <c r="AV12" s="12"/>
-      <c r="AW12" s="12"/>
-      <c r="AX12" s="12"/>
-      <c r="AY12" s="12"/>
-      <c r="AZ12" s="12"/>
-      <c r="BA12" s="12"/>
-      <c r="BB12" s="12"/>
-    </row>
-    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A13" s="27">
-        <v>11</v>
-      </c>
-      <c r="B13" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" s="70"/>
-      <c r="D13" s="70"/>
-      <c r="E13" s="70"/>
-      <c r="F13" s="70"/>
-      <c r="G13" s="70"/>
-      <c r="H13" s="70"/>
-      <c r="I13" s="70"/>
-      <c r="J13" s="71"/>
-      <c r="K13" s="72"/>
-      <c r="L13" s="55"/>
-      <c r="M13" s="73"/>
-      <c r="N13" s="74"/>
-      <c r="O13" s="70"/>
-      <c r="P13" s="71"/>
-      <c r="Q13" s="71"/>
-      <c r="R13" s="72"/>
-      <c r="S13" s="55"/>
-      <c r="T13" s="76">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U13" s="76">
-        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
-      </c>
-      <c r="V13" s="76">
-        <f>U13/24</f>
-        <v>0</v>
-      </c>
-      <c r="AF13" s="12"/>
-      <c r="AG13" s="12"/>
-      <c r="AH13" s="12"/>
-      <c r="AI13" s="12"/>
-      <c r="AJ13" s="12"/>
-      <c r="AK13" s="12"/>
-      <c r="AL13" s="12"/>
-      <c r="AM13" s="12"/>
-      <c r="AN13" s="12"/>
-      <c r="AO13" s="12"/>
-      <c r="AP13" s="12"/>
-      <c r="AQ13" s="12"/>
-      <c r="AR13" s="12"/>
-      <c r="AS13" s="12"/>
-      <c r="AT13" s="12"/>
-      <c r="AU13" s="12"/>
-      <c r="AV13" s="12"/>
-      <c r="AW13" s="12"/>
-      <c r="AX13" s="12"/>
-      <c r="AY13" s="12"/>
-      <c r="AZ13" s="12"/>
-      <c r="BA13" s="12"/>
-      <c r="BB13" s="12"/>
-    </row>
-    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A14" s="27">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="B14" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="C14" s="70"/>
-      <c r="D14" s="70"/>
-      <c r="E14" s="70"/>
-      <c r="F14" s="70"/>
-      <c r="G14" s="70"/>
-      <c r="H14" s="70"/>
-      <c r="I14" s="70"/>
-      <c r="J14" s="71"/>
-      <c r="K14" s="72"/>
-      <c r="L14" s="55"/>
-      <c r="M14" s="73"/>
-      <c r="N14" s="74"/>
-      <c r="O14" s="70"/>
-      <c r="P14" s="71"/>
-      <c r="Q14" s="71"/>
-      <c r="R14" s="72"/>
-      <c r="S14" s="55"/>
-      <c r="T14" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U14" s="75">
-        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
-        <v>0</v>
-      </c>
-      <c r="V14" s="75">
-        <f t="shared" ref="V14:V36" si="5">U14/24</f>
-        <v>0</v>
-      </c>
-      <c r="AF14" s="12"/>
-      <c r="AG14" s="12"/>
-      <c r="AH14" s="12"/>
-      <c r="AI14" s="12"/>
-      <c r="AJ14" s="12"/>
-      <c r="AK14" s="12"/>
-      <c r="AL14" s="12"/>
-      <c r="AM14" s="12"/>
-      <c r="AN14" s="12"/>
-      <c r="AO14" s="12"/>
-      <c r="AP14" s="12"/>
-      <c r="AQ14" s="12"/>
-      <c r="AR14" s="12"/>
-      <c r="AS14" s="12"/>
-      <c r="AT14" s="12"/>
-      <c r="AU14" s="12"/>
-      <c r="AV14" s="12"/>
-      <c r="AW14" s="12"/>
-      <c r="AX14" s="12"/>
-      <c r="AY14" s="12"/>
-      <c r="AZ14" s="12"/>
-      <c r="BA14" s="12"/>
-      <c r="BB14" s="12"/>
-    </row>
-    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A15" s="27">
-        <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-      <c r="B15" s="26" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="70"/>
-      <c r="D15" s="70"/>
-      <c r="E15" s="70"/>
-      <c r="F15" s="70"/>
-      <c r="G15" s="70"/>
-      <c r="H15" s="70"/>
-      <c r="I15" s="70"/>
-      <c r="J15" s="71"/>
-      <c r="K15" s="72"/>
-      <c r="L15" s="55"/>
-      <c r="M15" s="73"/>
-      <c r="N15" s="74"/>
-      <c r="O15" s="70"/>
-      <c r="P15" s="71"/>
-      <c r="Q15" s="71"/>
-      <c r="R15" s="72"/>
-      <c r="S15" s="55"/>
-      <c r="T15" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U15" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V15" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AF15" s="12"/>
-      <c r="AG15" s="12"/>
-      <c r="AH15" s="12"/>
-      <c r="AI15" s="12"/>
-      <c r="AJ15" s="12"/>
-      <c r="AK15" s="12"/>
-      <c r="AL15" s="12"/>
-      <c r="AM15" s="12"/>
-      <c r="AN15" s="12"/>
-      <c r="AO15" s="12"/>
-      <c r="AP15" s="12"/>
-      <c r="AQ15" s="12"/>
-      <c r="AR15" s="12"/>
-      <c r="AS15" s="12"/>
-      <c r="AT15" s="12"/>
-      <c r="AU15" s="12"/>
-      <c r="AV15" s="12"/>
-      <c r="AW15" s="12"/>
-      <c r="AX15" s="12"/>
-      <c r="AY15" s="12"/>
-      <c r="AZ15" s="12"/>
-      <c r="BA15" s="12"/>
-      <c r="BB15" s="12"/>
-    </row>
-    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A16" s="27">
-        <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-      <c r="B16" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="C16" s="70"/>
-      <c r="D16" s="70"/>
-      <c r="E16" s="70"/>
-      <c r="F16" s="70"/>
-      <c r="G16" s="70"/>
-      <c r="H16" s="70"/>
-      <c r="I16" s="70"/>
-      <c r="J16" s="71"/>
-      <c r="K16" s="72"/>
-      <c r="L16" s="55"/>
-      <c r="M16" s="73"/>
-      <c r="N16" s="74"/>
-      <c r="O16" s="70"/>
-      <c r="P16" s="71"/>
-      <c r="Q16" s="71"/>
-      <c r="R16" s="72"/>
-      <c r="S16" s="55"/>
-      <c r="T16" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U16" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V16" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AF16" s="12"/>
-      <c r="AG16" s="12"/>
-      <c r="AH16" s="12"/>
-      <c r="AI16" s="12"/>
-      <c r="AJ16" s="12"/>
-      <c r="AK16" s="12"/>
-      <c r="AL16" s="12"/>
-      <c r="AM16" s="12"/>
-      <c r="AN16" s="12"/>
-      <c r="AO16" s="12"/>
-      <c r="AP16" s="12"/>
-      <c r="AQ16" s="12"/>
-      <c r="AR16" s="12"/>
-      <c r="AS16" s="12"/>
-      <c r="AT16" s="12"/>
-      <c r="AU16" s="12"/>
-      <c r="AV16" s="12"/>
-      <c r="AW16" s="12"/>
-      <c r="AX16" s="12"/>
-      <c r="AY16" s="12"/>
-      <c r="AZ16" s="12"/>
-      <c r="BA16" s="12"/>
-      <c r="BB16" s="12"/>
-    </row>
-    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A17" s="27">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="B17" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="70"/>
-      <c r="D17" s="70"/>
-      <c r="E17" s="70"/>
-      <c r="F17" s="70"/>
-      <c r="G17" s="70"/>
-      <c r="H17" s="70"/>
-      <c r="I17" s="70"/>
-      <c r="J17" s="71"/>
-      <c r="K17" s="72"/>
-      <c r="L17" s="55"/>
-      <c r="M17" s="73"/>
-      <c r="N17" s="74"/>
-      <c r="O17" s="70"/>
-      <c r="P17" s="71"/>
-      <c r="Q17" s="71"/>
-      <c r="R17" s="72"/>
-      <c r="S17" s="55"/>
-      <c r="T17" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U17" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V17" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AF17" s="12"/>
-      <c r="AG17" s="12"/>
-      <c r="AH17" s="12"/>
-      <c r="AI17" s="12"/>
-      <c r="AJ17" s="12"/>
-      <c r="AK17" s="12"/>
-      <c r="AL17" s="12"/>
-      <c r="AM17" s="12"/>
-      <c r="AN17" s="12"/>
-      <c r="AO17" s="12"/>
-      <c r="AP17" s="12"/>
-      <c r="AQ17" s="12"/>
-      <c r="AR17" s="12"/>
-      <c r="AS17" s="12"/>
-      <c r="AT17" s="12"/>
-      <c r="AU17" s="12"/>
-      <c r="AV17" s="12"/>
-      <c r="AW17" s="12"/>
-      <c r="AX17" s="12"/>
-      <c r="AY17" s="12"/>
-      <c r="AZ17" s="12"/>
-      <c r="BA17" s="12"/>
-      <c r="BB17" s="12"/>
-    </row>
-    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="27">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="B18" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="70"/>
-      <c r="D18" s="70"/>
-      <c r="E18" s="70"/>
-      <c r="F18" s="70"/>
-      <c r="G18" s="70"/>
-      <c r="H18" s="70"/>
-      <c r="I18" s="70"/>
-      <c r="J18" s="71"/>
-      <c r="K18" s="72"/>
-      <c r="L18" s="55"/>
-      <c r="M18" s="73"/>
-      <c r="N18" s="74"/>
-      <c r="O18" s="70"/>
-      <c r="P18" s="71"/>
-      <c r="Q18" s="71"/>
-      <c r="R18" s="72"/>
-      <c r="S18" s="55"/>
-      <c r="T18" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U18" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V18" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AF18" s="12"/>
-      <c r="AG18" s="12"/>
-      <c r="AH18" s="12"/>
-      <c r="AI18" s="12"/>
-      <c r="AJ18" s="12"/>
-      <c r="AK18" s="12"/>
-      <c r="AL18" s="12"/>
-      <c r="AM18" s="12"/>
-      <c r="AN18" s="12"/>
-      <c r="AO18" s="12"/>
-      <c r="AP18" s="12"/>
-      <c r="AQ18" s="12"/>
-      <c r="AR18" s="12"/>
-      <c r="AS18" s="12"/>
-      <c r="AT18" s="12"/>
-      <c r="AU18" s="12"/>
-      <c r="AV18" s="12"/>
-      <c r="AW18" s="12"/>
-      <c r="AX18" s="12"/>
-      <c r="AY18" s="12"/>
-      <c r="AZ18" s="12"/>
-      <c r="BA18" s="12"/>
-      <c r="BB18" s="12"/>
-    </row>
-    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A19" s="27">
-        <v>16</v>
-      </c>
-      <c r="B19" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" s="70"/>
-      <c r="D19" s="70"/>
-      <c r="E19" s="70"/>
-      <c r="F19" s="70"/>
-      <c r="G19" s="70"/>
-      <c r="H19" s="70"/>
-      <c r="I19" s="70"/>
-      <c r="J19" s="71"/>
-      <c r="K19" s="72"/>
-      <c r="L19" s="55"/>
-      <c r="M19" s="73"/>
-      <c r="N19" s="74"/>
-      <c r="O19" s="70"/>
-      <c r="P19" s="71"/>
-      <c r="Q19" s="71"/>
-      <c r="R19" s="72"/>
-      <c r="S19" s="55"/>
-      <c r="T19" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U19" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V19" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AF19" s="12"/>
-      <c r="AG19" s="12"/>
-      <c r="AH19" s="12"/>
-      <c r="AI19" s="12"/>
-      <c r="AJ19" s="12"/>
-      <c r="AK19" s="12"/>
-      <c r="AL19" s="12"/>
-      <c r="AM19" s="12"/>
-      <c r="AN19" s="12"/>
-      <c r="AO19" s="12"/>
-      <c r="AP19" s="12"/>
-      <c r="AQ19" s="12"/>
-      <c r="AR19" s="12"/>
-      <c r="AS19" s="12"/>
-      <c r="AT19" s="12"/>
-      <c r="AU19" s="12"/>
-      <c r="AV19" s="12"/>
-      <c r="AW19" s="12"/>
-      <c r="AX19" s="12"/>
-      <c r="AY19" s="12"/>
-      <c r="AZ19" s="12"/>
-      <c r="BA19" s="12"/>
-      <c r="BB19" s="12"/>
-    </row>
-    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A20" s="27">
-        <f t="shared" si="1"/>
-        <v>17</v>
-      </c>
-      <c r="B20" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="70"/>
-      <c r="D20" s="70"/>
-      <c r="E20" s="70"/>
-      <c r="F20" s="70"/>
-      <c r="G20" s="70"/>
-      <c r="H20" s="70"/>
-      <c r="I20" s="70"/>
-      <c r="J20" s="71"/>
-      <c r="K20" s="72"/>
-      <c r="L20" s="55"/>
-      <c r="M20" s="73"/>
-      <c r="N20" s="74"/>
-      <c r="O20" s="70"/>
-      <c r="P20" s="71"/>
-      <c r="Q20" s="71"/>
-      <c r="R20" s="72"/>
-      <c r="S20" s="55"/>
-      <c r="T20" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U20" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V20" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AF20" s="12"/>
-      <c r="AG20" s="12"/>
-      <c r="AH20" s="12"/>
-      <c r="AI20" s="12"/>
-      <c r="AJ20" s="12"/>
-      <c r="AK20" s="12"/>
-      <c r="AL20" s="12"/>
-      <c r="AM20" s="12"/>
-      <c r="AN20" s="12"/>
-      <c r="AO20" s="12"/>
-      <c r="AP20" s="12"/>
-      <c r="AQ20" s="12"/>
-      <c r="AR20" s="12"/>
-      <c r="AS20" s="12"/>
-      <c r="AT20" s="12"/>
-      <c r="AU20" s="12"/>
-      <c r="AV20" s="12"/>
-      <c r="AW20" s="12"/>
-      <c r="AX20" s="12"/>
-      <c r="AY20" s="12"/>
-      <c r="AZ20" s="12"/>
-      <c r="BA20" s="12"/>
-      <c r="BB20" s="12"/>
-    </row>
-    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A21" s="27">
-        <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="B21" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="70"/>
-      <c r="D21" s="70"/>
-      <c r="E21" s="70"/>
-      <c r="F21" s="70"/>
-      <c r="G21" s="70"/>
-      <c r="H21" s="70"/>
-      <c r="I21" s="70"/>
-      <c r="J21" s="71"/>
-      <c r="K21" s="72"/>
-      <c r="L21" s="55"/>
-      <c r="M21" s="73"/>
-      <c r="N21" s="74"/>
-      <c r="O21" s="70"/>
-      <c r="P21" s="71"/>
-      <c r="Q21" s="71"/>
-      <c r="R21" s="72"/>
-      <c r="S21" s="55"/>
-      <c r="T21" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U21" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V21" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AF21" s="12"/>
-      <c r="AG21" s="12"/>
-      <c r="AH21" s="12"/>
-      <c r="AI21" s="12"/>
-      <c r="AJ21" s="12"/>
-      <c r="AK21" s="12"/>
-      <c r="AL21" s="12"/>
-      <c r="AM21" s="12"/>
-      <c r="AN21" s="12"/>
-      <c r="AO21" s="12"/>
-      <c r="AP21" s="12"/>
-      <c r="AQ21" s="12"/>
-      <c r="AR21" s="12"/>
-      <c r="AS21" s="12"/>
-      <c r="AT21" s="12"/>
-      <c r="AU21" s="12"/>
-      <c r="AV21" s="12"/>
-      <c r="AW21" s="12"/>
-      <c r="AX21" s="12"/>
-      <c r="AY21" s="12"/>
-      <c r="AZ21" s="12"/>
-      <c r="BA21" s="12"/>
-      <c r="BB21" s="12"/>
-    </row>
-    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="27">
-        <f t="shared" si="1"/>
-        <v>19</v>
-      </c>
-      <c r="B22" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="C22" s="70"/>
-      <c r="D22" s="70"/>
-      <c r="E22" s="70"/>
-      <c r="F22" s="70"/>
-      <c r="G22" s="70"/>
-      <c r="H22" s="70"/>
-      <c r="I22" s="70"/>
-      <c r="J22" s="71"/>
-      <c r="K22" s="72"/>
-      <c r="L22" s="55"/>
-      <c r="M22" s="73"/>
-      <c r="N22" s="74"/>
-      <c r="O22" s="70"/>
-      <c r="P22" s="71"/>
-      <c r="Q22" s="71"/>
-      <c r="R22" s="72"/>
-      <c r="S22" s="55"/>
-      <c r="T22" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U22" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V22" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="W22" s="9"/>
-      <c r="X22" s="9"/>
-      <c r="Y22" s="9"/>
-      <c r="Z22" s="9"/>
-      <c r="AA22" s="9"/>
-      <c r="AB22" s="9"/>
-      <c r="AC22" s="9"/>
-      <c r="AD22" s="9"/>
-      <c r="AE22" s="9"/>
-      <c r="AF22" s="12"/>
-      <c r="AG22" s="12"/>
-      <c r="AH22" s="12"/>
-      <c r="AI22" s="12"/>
-      <c r="AJ22" s="12"/>
-      <c r="AK22" s="12"/>
-      <c r="AL22" s="12"/>
-      <c r="AM22" s="12"/>
-      <c r="AN22" s="12"/>
-      <c r="AO22" s="12"/>
-      <c r="AP22" s="12"/>
-      <c r="AQ22" s="12"/>
-      <c r="AR22" s="12"/>
-      <c r="AS22" s="12"/>
-      <c r="AT22" s="12"/>
-      <c r="AU22" s="12"/>
-      <c r="AV22" s="12"/>
-      <c r="AW22" s="12"/>
-      <c r="AX22" s="12"/>
-      <c r="AY22" s="12"/>
-      <c r="AZ22" s="12"/>
-      <c r="BA22" s="12"/>
-      <c r="BB22" s="12"/>
-    </row>
-    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="27">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="B23" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="C23" s="70"/>
-      <c r="D23" s="70"/>
-      <c r="E23" s="70"/>
-      <c r="F23" s="70"/>
-      <c r="G23" s="70"/>
-      <c r="H23" s="70"/>
-      <c r="I23" s="70"/>
-      <c r="J23" s="71"/>
-      <c r="K23" s="72"/>
-      <c r="L23" s="55"/>
-      <c r="M23" s="73"/>
-      <c r="N23" s="74"/>
-      <c r="O23" s="70"/>
-      <c r="P23" s="71"/>
-      <c r="Q23" s="71"/>
-      <c r="R23" s="72"/>
-      <c r="S23" s="55"/>
-      <c r="T23" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U23" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V23" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="W23" s="9"/>
-      <c r="X23" s="9"/>
-      <c r="Y23" s="9"/>
-      <c r="Z23" s="9"/>
-      <c r="AA23" s="9"/>
-      <c r="AB23" s="9"/>
-      <c r="AC23" s="9"/>
-      <c r="AD23" s="9"/>
-      <c r="AE23" s="9"/>
-      <c r="AF23" s="12"/>
-      <c r="AG23" s="12"/>
-      <c r="AH23" s="12"/>
-      <c r="AI23" s="12"/>
-      <c r="AJ23" s="12"/>
-      <c r="AK23" s="12"/>
-      <c r="AL23" s="12"/>
-      <c r="AM23" s="12"/>
-      <c r="AN23" s="12"/>
-      <c r="AO23" s="12"/>
-      <c r="AP23" s="12"/>
-      <c r="AQ23" s="12"/>
-      <c r="AR23" s="12"/>
-      <c r="AS23" s="12"/>
-      <c r="AT23" s="12"/>
-      <c r="AU23" s="12"/>
-      <c r="AV23" s="12"/>
-      <c r="AW23" s="12"/>
-      <c r="AX23" s="12"/>
-      <c r="AY23" s="12"/>
-      <c r="AZ23" s="12"/>
-      <c r="BA23" s="12"/>
-      <c r="BB23" s="12"/>
-    </row>
-    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A24" s="27">
-        <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-      <c r="B24" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="C24" s="70"/>
-      <c r="D24" s="70"/>
-      <c r="E24" s="70"/>
-      <c r="F24" s="70"/>
-      <c r="G24" s="70"/>
-      <c r="H24" s="70"/>
-      <c r="I24" s="70"/>
-      <c r="J24" s="71"/>
-      <c r="K24" s="72"/>
-      <c r="L24" s="55"/>
-      <c r="M24" s="73"/>
-      <c r="N24" s="74"/>
-      <c r="O24" s="70"/>
-      <c r="P24" s="71"/>
-      <c r="Q24" s="71"/>
-      <c r="R24" s="72"/>
-      <c r="S24" s="55"/>
-      <c r="T24" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U24" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V24" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AF24" s="12"/>
-      <c r="AG24" s="12"/>
-      <c r="AH24" s="12"/>
-      <c r="AI24" s="12"/>
-      <c r="AJ24" s="12"/>
-      <c r="AK24" s="12"/>
-      <c r="AL24" s="12"/>
-      <c r="AM24" s="12"/>
-      <c r="AN24" s="12"/>
-      <c r="AO24" s="12"/>
-      <c r="AP24" s="12"/>
-      <c r="AQ24" s="12"/>
-      <c r="AR24" s="12"/>
-      <c r="AS24" s="12"/>
-      <c r="AT24" s="12"/>
-      <c r="AU24" s="12"/>
-      <c r="AV24" s="12"/>
-      <c r="AW24" s="12"/>
-      <c r="AX24" s="12"/>
-      <c r="AY24" s="12"/>
-      <c r="AZ24" s="12"/>
-      <c r="BA24" s="12"/>
-      <c r="BB24" s="12"/>
-    </row>
-    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A25" s="27">
-        <f t="shared" si="1"/>
-        <v>22</v>
-      </c>
-      <c r="B25" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="70"/>
-      <c r="D25" s="70"/>
-      <c r="E25" s="70"/>
-      <c r="F25" s="70"/>
-      <c r="G25" s="70"/>
-      <c r="H25" s="70"/>
-      <c r="I25" s="70"/>
-      <c r="J25" s="71"/>
-      <c r="K25" s="72"/>
-      <c r="L25" s="55"/>
-      <c r="M25" s="73"/>
-      <c r="N25" s="74"/>
-      <c r="O25" s="70"/>
-      <c r="P25" s="71"/>
-      <c r="Q25" s="71"/>
-      <c r="R25" s="72"/>
-      <c r="S25" s="55"/>
-      <c r="T25" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U25" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V25" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AY25" s="14" t="e">
-        <f>#REF!-AY24</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="27">
-        <f t="shared" si="1"/>
-        <v>23</v>
-      </c>
-      <c r="B26" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="70"/>
-      <c r="D26" s="70"/>
-      <c r="E26" s="70"/>
-      <c r="F26" s="70"/>
-      <c r="G26" s="70"/>
-      <c r="H26" s="70"/>
-      <c r="I26" s="70"/>
-      <c r="J26" s="71"/>
-      <c r="K26" s="72"/>
-      <c r="L26" s="55"/>
-      <c r="M26" s="73"/>
-      <c r="N26" s="74"/>
-      <c r="O26" s="70"/>
-      <c r="P26" s="71"/>
-      <c r="Q26" s="71"/>
-      <c r="R26" s="72"/>
-      <c r="S26" s="55"/>
-      <c r="T26" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U26" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V26" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="W26" s="9"/>
-      <c r="X26" s="9"/>
-      <c r="Y26" s="9"/>
-      <c r="Z26" s="9"/>
-      <c r="AA26" s="9"/>
-      <c r="AB26" s="9"/>
-      <c r="AC26" s="9"/>
-      <c r="AD26" s="9"/>
-      <c r="AE26" s="9"/>
-    </row>
-    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="27">
-        <f t="shared" si="1"/>
-        <v>24</v>
-      </c>
-      <c r="B27" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="C27" s="70"/>
-      <c r="D27" s="70"/>
-      <c r="E27" s="70"/>
-      <c r="F27" s="70"/>
-      <c r="G27" s="70"/>
-      <c r="H27" s="70"/>
-      <c r="I27" s="70"/>
-      <c r="J27" s="71"/>
-      <c r="K27" s="72"/>
-      <c r="L27" s="55"/>
-      <c r="M27" s="73"/>
-      <c r="N27" s="74"/>
-      <c r="O27" s="70"/>
-      <c r="P27" s="71"/>
-      <c r="Q27" s="71"/>
-      <c r="R27" s="72"/>
-      <c r="S27" s="55"/>
-      <c r="T27" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U27" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V27" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="W27" s="9"/>
-      <c r="X27" s="9"/>
-      <c r="Y27" s="9"/>
-      <c r="Z27" s="9"/>
-      <c r="AA27" s="9"/>
-      <c r="AB27" s="9"/>
-      <c r="AC27" s="9"/>
-      <c r="AD27" s="9"/>
-      <c r="AE27" s="9"/>
-    </row>
-    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="27">
-        <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-      <c r="B28" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="70"/>
-      <c r="D28" s="70"/>
-      <c r="E28" s="70"/>
-      <c r="F28" s="70"/>
-      <c r="G28" s="70"/>
-      <c r="H28" s="70"/>
-      <c r="I28" s="70"/>
-      <c r="J28" s="71"/>
-      <c r="K28" s="72"/>
-      <c r="L28" s="55"/>
-      <c r="M28" s="73"/>
-      <c r="N28" s="74"/>
-      <c r="O28" s="70"/>
-      <c r="P28" s="71"/>
-      <c r="Q28" s="71"/>
-      <c r="R28" s="72"/>
-      <c r="S28" s="55"/>
-      <c r="T28" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U28" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V28" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="W28" s="9"/>
-      <c r="X28" s="9"/>
-      <c r="Y28" s="9"/>
-      <c r="Z28" s="9"/>
-      <c r="AA28" s="9"/>
-      <c r="AB28" s="9"/>
-      <c r="AC28" s="9"/>
-      <c r="AD28" s="9"/>
-      <c r="AE28" s="9"/>
-    </row>
-    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A29" s="27">
-        <f t="shared" si="1"/>
-        <v>26</v>
-      </c>
-      <c r="B29" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="C29" s="70"/>
-      <c r="D29" s="70"/>
-      <c r="E29" s="70"/>
-      <c r="F29" s="70"/>
-      <c r="G29" s="70"/>
-      <c r="H29" s="70"/>
-      <c r="I29" s="70"/>
-      <c r="J29" s="71"/>
-      <c r="K29" s="72"/>
-      <c r="L29" s="55"/>
-      <c r="M29" s="73"/>
-      <c r="N29" s="74"/>
-      <c r="O29" s="70"/>
-      <c r="P29" s="71"/>
-      <c r="Q29" s="71"/>
-      <c r="R29" s="72"/>
-      <c r="S29" s="55"/>
-      <c r="T29" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U29" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V29" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A30" s="27">
-        <f t="shared" si="1"/>
-        <v>27</v>
-      </c>
-      <c r="B30" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="70"/>
-      <c r="D30" s="70"/>
-      <c r="E30" s="70"/>
-      <c r="F30" s="70"/>
-      <c r="G30" s="70"/>
-      <c r="H30" s="70"/>
-      <c r="I30" s="70"/>
-      <c r="J30" s="71"/>
-      <c r="K30" s="72"/>
-      <c r="L30" s="55"/>
-      <c r="M30" s="73"/>
-      <c r="N30" s="74"/>
-      <c r="O30" s="70"/>
-      <c r="P30" s="71"/>
-      <c r="Q30" s="71"/>
-      <c r="R30" s="72"/>
-      <c r="S30" s="55"/>
-      <c r="T30" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U30" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V30" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A31" s="27">
-        <f t="shared" si="1"/>
-        <v>28</v>
-      </c>
-      <c r="B31" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="C31" s="70"/>
-      <c r="D31" s="70"/>
-      <c r="E31" s="70"/>
-      <c r="F31" s="70"/>
-      <c r="G31" s="70"/>
-      <c r="H31" s="70"/>
-      <c r="I31" s="70"/>
-      <c r="J31" s="71"/>
-      <c r="K31" s="72"/>
-      <c r="L31" s="55"/>
-      <c r="M31" s="73"/>
-      <c r="N31" s="74"/>
-      <c r="O31" s="70"/>
-      <c r="P31" s="71"/>
-      <c r="Q31" s="71"/>
-      <c r="R31" s="72"/>
-      <c r="S31" s="55"/>
-      <c r="T31" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U31" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V31" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A32" s="27">
-        <f t="shared" si="1"/>
-        <v>29</v>
-      </c>
-      <c r="B32" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="C32" s="70"/>
-      <c r="D32" s="70"/>
-      <c r="E32" s="70"/>
-      <c r="F32" s="70"/>
-      <c r="G32" s="70"/>
-      <c r="H32" s="70"/>
-      <c r="I32" s="70"/>
-      <c r="J32" s="71"/>
-      <c r="K32" s="72"/>
-      <c r="L32" s="55"/>
-      <c r="M32" s="73"/>
-      <c r="N32" s="74"/>
-      <c r="O32" s="70"/>
-      <c r="P32" s="71"/>
-      <c r="Q32" s="71"/>
-      <c r="R32" s="72"/>
-      <c r="S32" s="55"/>
-      <c r="T32" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U32" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V32" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A33" s="27">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="B33" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" s="70"/>
-      <c r="D33" s="70"/>
-      <c r="E33" s="70"/>
-      <c r="F33" s="70"/>
-      <c r="G33" s="70"/>
-      <c r="H33" s="70"/>
-      <c r="I33" s="70"/>
-      <c r="J33" s="71"/>
-      <c r="K33" s="72"/>
-      <c r="L33" s="55"/>
-      <c r="M33" s="73"/>
-      <c r="N33" s="74"/>
-      <c r="O33" s="70"/>
-      <c r="P33" s="71"/>
-      <c r="Q33" s="71"/>
-      <c r="R33" s="72"/>
-      <c r="S33" s="55"/>
-      <c r="T33" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U33" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V33" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A34" s="27">
-        <f t="shared" si="1"/>
-        <v>31</v>
-      </c>
-      <c r="B34" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="C34" s="70"/>
-      <c r="D34" s="70"/>
-      <c r="E34" s="70"/>
-      <c r="F34" s="70"/>
-      <c r="G34" s="70"/>
-      <c r="H34" s="70"/>
-      <c r="I34" s="70"/>
-      <c r="J34" s="71"/>
-      <c r="K34" s="72"/>
-      <c r="L34" s="55"/>
-      <c r="M34" s="73"/>
-      <c r="N34" s="74"/>
-      <c r="O34" s="70"/>
-      <c r="P34" s="71"/>
-      <c r="Q34" s="71"/>
-      <c r="R34" s="72"/>
-      <c r="S34" s="55"/>
-      <c r="T34" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U34" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V34" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="27">
-        <f t="shared" si="1"/>
-        <v>32</v>
-      </c>
-      <c r="B35" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="C35" s="70"/>
-      <c r="D35" s="70"/>
-      <c r="E35" s="70"/>
-      <c r="F35" s="70"/>
-      <c r="G35" s="70"/>
-      <c r="H35" s="70"/>
-      <c r="I35" s="70"/>
-      <c r="J35" s="71"/>
-      <c r="K35" s="72"/>
-      <c r="L35" s="55"/>
-      <c r="M35" s="73"/>
-      <c r="N35" s="74"/>
-      <c r="O35" s="70"/>
-      <c r="P35" s="71"/>
-      <c r="Q35" s="71"/>
-      <c r="R35" s="72"/>
-      <c r="S35" s="55"/>
-      <c r="T35" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U35" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V35" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A36" s="27">
-        <f t="shared" si="1"/>
-        <v>33</v>
-      </c>
-      <c r="B36" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="C36" s="70"/>
-      <c r="D36" s="70"/>
-      <c r="E36" s="70"/>
-      <c r="F36" s="70"/>
-      <c r="G36" s="70"/>
-      <c r="H36" s="70"/>
-      <c r="I36" s="70"/>
-      <c r="J36" s="71"/>
-      <c r="K36" s="72"/>
-      <c r="L36" s="55"/>
-      <c r="M36" s="73"/>
-      <c r="N36" s="74"/>
-      <c r="O36" s="70"/>
-      <c r="P36" s="71"/>
-      <c r="Q36" s="71"/>
-      <c r="R36" s="72"/>
-      <c r="S36" s="55"/>
-      <c r="T36" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U36" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V36" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="27">
-        <f t="shared" si="1"/>
-        <v>34</v>
-      </c>
-      <c r="B37" s="42" t="s">
-        <v>19</v>
-      </c>
-      <c r="C37" s="59"/>
-      <c r="D37" s="59"/>
-      <c r="E37" s="59"/>
-      <c r="F37" s="59"/>
-      <c r="G37" s="59"/>
-      <c r="H37" s="59"/>
-      <c r="I37" s="59"/>
-      <c r="J37" s="60"/>
-      <c r="K37" s="61"/>
-      <c r="L37" s="62"/>
-      <c r="M37" s="63"/>
-      <c r="N37" s="64"/>
-      <c r="O37" s="65"/>
-      <c r="P37" s="66"/>
-      <c r="Q37" s="66"/>
-      <c r="R37" s="67"/>
-      <c r="S37" s="62"/>
-      <c r="T37" s="77">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U37" s="77">
-        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
-      </c>
-      <c r="V37" s="77">
-        <f>U37/6</f>
-        <v>0</v>
-      </c>
-      <c r="W37" s="50"/>
-    </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A38" s="27">
-        <f t="shared" si="1"/>
-        <v>35</v>
-      </c>
-      <c r="B38" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="C38" s="70"/>
-      <c r="D38" s="70"/>
-      <c r="E38" s="70"/>
-      <c r="F38" s="70"/>
-      <c r="G38" s="70"/>
-      <c r="H38" s="70"/>
-      <c r="I38" s="70"/>
-      <c r="J38" s="71"/>
-      <c r="K38" s="72"/>
-      <c r="L38" s="55"/>
-      <c r="M38" s="73"/>
-      <c r="N38" s="74"/>
-      <c r="O38" s="70"/>
-      <c r="P38" s="71"/>
-      <c r="Q38" s="71"/>
-      <c r="R38" s="72"/>
-      <c r="S38" s="55"/>
-      <c r="T38" s="75">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U38" s="75">
-        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
-        <v>0</v>
-      </c>
-      <c r="V38" s="75">
-        <f>U38/24</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A39" s="27">
-        <f t="shared" si="1"/>
-        <v>36</v>
-      </c>
-      <c r="B39" s="51" t="s">
-        <v>62</v>
-      </c>
-      <c r="C39" s="78"/>
-      <c r="D39" s="78"/>
-      <c r="E39" s="78"/>
-      <c r="F39" s="78"/>
-      <c r="G39" s="78"/>
-      <c r="H39" s="78"/>
-      <c r="I39" s="78"/>
-      <c r="J39" s="79"/>
-      <c r="K39" s="80"/>
-      <c r="L39" s="55"/>
-      <c r="M39" s="73"/>
-      <c r="N39" s="74"/>
-      <c r="O39" s="70"/>
-      <c r="P39" s="71"/>
-      <c r="Q39" s="71"/>
-      <c r="R39" s="72"/>
-      <c r="S39" s="95"/>
-      <c r="T39" s="75">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U39" s="75">
-        <f>C39*24+M39*24+O39*24+Q39*24+T39</f>
-        <v>0</v>
-      </c>
-      <c r="V39" s="75">
-        <f>U39/24</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="27">
-        <f t="shared" si="1"/>
-        <v>37</v>
-      </c>
-      <c r="B40" s="42" t="s">
-        <v>21</v>
-      </c>
-      <c r="C40" s="59"/>
-      <c r="D40" s="59"/>
-      <c r="E40" s="59"/>
-      <c r="F40" s="59"/>
-      <c r="G40" s="59"/>
-      <c r="H40" s="59"/>
-      <c r="I40" s="59"/>
-      <c r="J40" s="60"/>
-      <c r="K40" s="61"/>
-      <c r="L40" s="62"/>
-      <c r="M40" s="63"/>
-      <c r="N40" s="64"/>
-      <c r="O40" s="65"/>
-      <c r="P40" s="66"/>
-      <c r="Q40" s="66"/>
-      <c r="R40" s="67"/>
-      <c r="S40" s="62"/>
-      <c r="T40" s="77">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U40" s="77">
-        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
-      </c>
-      <c r="V40" s="77">
-        <f>U40/24</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="27">
-        <f t="shared" si="1"/>
-        <v>38</v>
-      </c>
-      <c r="B41" s="43" t="s">
-        <v>22</v>
-      </c>
-      <c r="C41" s="82"/>
-      <c r="D41" s="82"/>
-      <c r="E41" s="82"/>
-      <c r="F41" s="82"/>
-      <c r="G41" s="82"/>
-      <c r="H41" s="82"/>
-      <c r="I41" s="82"/>
-      <c r="J41" s="83"/>
-      <c r="K41" s="84"/>
-      <c r="L41" s="85"/>
-      <c r="M41" s="86"/>
-      <c r="N41" s="87"/>
-      <c r="O41" s="82"/>
-      <c r="P41" s="83"/>
-      <c r="Q41" s="83"/>
-      <c r="R41" s="84"/>
-      <c r="S41" s="85"/>
-      <c r="T41" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U41" s="88">
-        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
-      </c>
-      <c r="V41" s="88">
-        <f>U41/12</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="27">
-        <f t="shared" si="1"/>
-        <v>39</v>
-      </c>
-      <c r="B42" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="C42" s="70"/>
-      <c r="D42" s="70"/>
-      <c r="E42" s="70"/>
-      <c r="F42" s="70"/>
-      <c r="G42" s="70"/>
-      <c r="H42" s="70"/>
-      <c r="I42" s="70"/>
-      <c r="J42" s="71"/>
-      <c r="K42" s="72"/>
-      <c r="L42" s="55"/>
-      <c r="M42" s="73"/>
-      <c r="N42" s="74"/>
-      <c r="O42" s="70"/>
-      <c r="P42" s="71"/>
-      <c r="Q42" s="71"/>
-      <c r="R42" s="72"/>
-      <c r="S42" s="55"/>
-      <c r="T42" s="75"/>
-      <c r="U42" s="75"/>
-      <c r="V42" s="75"/>
-    </row>
-    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="27">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="B43" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="C43" s="65"/>
-      <c r="D43" s="65"/>
-      <c r="E43" s="65"/>
-      <c r="F43" s="65"/>
-      <c r="G43" s="65"/>
-      <c r="H43" s="65"/>
-      <c r="I43" s="65"/>
-      <c r="J43" s="66"/>
-      <c r="K43" s="67"/>
-      <c r="L43" s="62"/>
-      <c r="M43" s="63"/>
-      <c r="N43" s="64"/>
-      <c r="O43" s="65"/>
-      <c r="P43" s="66"/>
-      <c r="Q43" s="66"/>
-      <c r="R43" s="67"/>
-      <c r="S43" s="62"/>
-      <c r="T43" s="77">
-        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
-      </c>
-      <c r="U43" s="77">
-        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
-      </c>
-      <c r="V43" s="77">
-        <f>U43/6</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="27">
-        <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-      <c r="B44" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="70"/>
-      <c r="D44" s="70"/>
-      <c r="E44" s="70"/>
-      <c r="F44" s="70"/>
-      <c r="G44" s="70"/>
-      <c r="H44" s="70"/>
-      <c r="I44" s="70"/>
-      <c r="J44" s="71"/>
-      <c r="K44" s="72"/>
-      <c r="L44" s="55"/>
-      <c r="M44" s="73"/>
-      <c r="N44" s="74"/>
-      <c r="O44" s="70"/>
-      <c r="P44" s="71"/>
-      <c r="Q44" s="71"/>
-      <c r="R44" s="72"/>
-      <c r="S44" s="55"/>
-      <c r="T44" s="75"/>
-      <c r="U44" s="75"/>
-      <c r="V44" s="75"/>
-    </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A45" s="27">
-        <f t="shared" si="1"/>
-        <v>42</v>
-      </c>
-      <c r="B45" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" s="70"/>
-      <c r="D45" s="70"/>
-      <c r="E45" s="70"/>
-      <c r="F45" s="70"/>
-      <c r="G45" s="70"/>
-      <c r="H45" s="70"/>
-      <c r="I45" s="70"/>
-      <c r="J45" s="71"/>
-      <c r="K45" s="72"/>
-      <c r="L45" s="55"/>
-      <c r="M45" s="73"/>
-      <c r="N45" s="74"/>
-      <c r="O45" s="70"/>
-      <c r="P45" s="71"/>
-      <c r="Q45" s="71"/>
-      <c r="R45" s="72"/>
-      <c r="S45" s="55"/>
-      <c r="T45" s="75">
-        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
-        <v>0</v>
-      </c>
-      <c r="U45" s="75">
-        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
-        <v>0</v>
-      </c>
-      <c r="V45" s="75">
-        <f>U45/24</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A46" s="27">
-        <f t="shared" si="1"/>
-        <v>43</v>
-      </c>
-      <c r="B46" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="C46" s="70"/>
-      <c r="D46" s="70"/>
-      <c r="E46" s="70"/>
-      <c r="F46" s="70"/>
-      <c r="G46" s="70"/>
-      <c r="H46" s="70"/>
-      <c r="I46" s="70"/>
-      <c r="J46" s="71"/>
-      <c r="K46" s="72"/>
-      <c r="L46" s="55"/>
-      <c r="M46" s="73"/>
-      <c r="N46" s="74"/>
-      <c r="O46" s="70"/>
-      <c r="P46" s="71"/>
-      <c r="Q46" s="71"/>
-      <c r="R46" s="72"/>
-      <c r="S46" s="55"/>
-      <c r="T46" s="75">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U46" s="75">
-        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
-        <v>0</v>
-      </c>
-      <c r="V46" s="75">
-        <f t="shared" ref="V46:V54" si="9">U46/24</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="27">
-        <f t="shared" si="1"/>
-        <v>44</v>
-      </c>
-      <c r="B47" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="C47" s="65"/>
-      <c r="D47" s="65"/>
-      <c r="E47" s="65"/>
-      <c r="F47" s="65"/>
-      <c r="G47" s="65"/>
-      <c r="H47" s="65"/>
-      <c r="I47" s="65"/>
-      <c r="J47" s="66"/>
-      <c r="K47" s="67"/>
-      <c r="L47" s="62"/>
-      <c r="M47" s="63"/>
-      <c r="N47" s="64"/>
-      <c r="O47" s="65"/>
-      <c r="P47" s="66"/>
-      <c r="Q47" s="66"/>
-      <c r="R47" s="67"/>
-      <c r="S47" s="62"/>
-      <c r="T47" s="77">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U47" s="77">
-        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
-      </c>
-      <c r="V47" s="77">
-        <f>U47/6</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A48" s="27">
-        <f t="shared" si="1"/>
-        <v>45</v>
-      </c>
-      <c r="B48" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="C48" s="70"/>
-      <c r="D48" s="70"/>
-      <c r="E48" s="70"/>
-      <c r="F48" s="70"/>
-      <c r="G48" s="70"/>
-      <c r="H48" s="70"/>
-      <c r="I48" s="70"/>
-      <c r="J48" s="71"/>
-      <c r="K48" s="72"/>
-      <c r="L48" s="55"/>
-      <c r="M48" s="73"/>
-      <c r="N48" s="74"/>
-      <c r="O48" s="70"/>
-      <c r="P48" s="71"/>
-      <c r="Q48" s="71"/>
-      <c r="R48" s="72"/>
-      <c r="S48" s="55"/>
-      <c r="T48" s="75">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U48" s="75">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V48" s="75">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A49" s="27">
-        <f t="shared" si="1"/>
-        <v>46</v>
-      </c>
-      <c r="B49" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="C49" s="70"/>
-      <c r="D49" s="70"/>
-      <c r="E49" s="70"/>
-      <c r="F49" s="70"/>
-      <c r="G49" s="70"/>
-      <c r="H49" s="70"/>
-      <c r="I49" s="70"/>
-      <c r="J49" s="71"/>
-      <c r="K49" s="72"/>
-      <c r="L49" s="55"/>
-      <c r="M49" s="73"/>
-      <c r="N49" s="74"/>
-      <c r="O49" s="70"/>
-      <c r="P49" s="71"/>
-      <c r="Q49" s="71"/>
-      <c r="R49" s="72"/>
-      <c r="S49" s="55"/>
-      <c r="T49" s="75">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U49" s="75">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V49" s="75">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A50" s="27">
-        <f t="shared" si="1"/>
-        <v>47</v>
-      </c>
-      <c r="B50" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="C50" s="70"/>
-      <c r="D50" s="70"/>
-      <c r="E50" s="70"/>
-      <c r="F50" s="70"/>
-      <c r="G50" s="70"/>
-      <c r="H50" s="70"/>
-      <c r="I50" s="70"/>
-      <c r="J50" s="71"/>
-      <c r="K50" s="72"/>
-      <c r="L50" s="55"/>
-      <c r="M50" s="73"/>
-      <c r="N50" s="74"/>
-      <c r="O50" s="70"/>
-      <c r="P50" s="71"/>
-      <c r="Q50" s="71"/>
-      <c r="R50" s="72"/>
-      <c r="S50" s="55"/>
-      <c r="T50" s="75">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U50" s="75">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V50" s="75">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="27">
-        <f t="shared" si="1"/>
-        <v>48</v>
-      </c>
-      <c r="B51" s="42" t="s">
-        <v>27</v>
-      </c>
-      <c r="C51" s="65"/>
-      <c r="D51" s="65"/>
-      <c r="E51" s="65"/>
-      <c r="F51" s="65"/>
-      <c r="G51" s="65"/>
-      <c r="H51" s="65"/>
-      <c r="I51" s="65"/>
-      <c r="J51" s="66"/>
-      <c r="K51" s="67"/>
-      <c r="L51" s="62"/>
-      <c r="M51" s="63"/>
-      <c r="N51" s="64"/>
-      <c r="O51" s="65"/>
-      <c r="P51" s="66"/>
-      <c r="Q51" s="66"/>
-      <c r="R51" s="67"/>
-      <c r="S51" s="62"/>
-      <c r="T51" s="77">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U51" s="77">
-        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
-      </c>
-      <c r="V51" s="77">
-        <f>U51/6</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A52" s="27">
-        <f t="shared" si="1"/>
-        <v>49</v>
-      </c>
-      <c r="B52" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="C52" s="70"/>
-      <c r="D52" s="70"/>
-      <c r="E52" s="70"/>
-      <c r="F52" s="70"/>
-      <c r="G52" s="70"/>
-      <c r="H52" s="70"/>
-      <c r="I52" s="70"/>
-      <c r="J52" s="71"/>
-      <c r="K52" s="72"/>
-      <c r="L52" s="55"/>
-      <c r="M52" s="73"/>
-      <c r="N52" s="74"/>
-      <c r="O52" s="70"/>
-      <c r="P52" s="71"/>
-      <c r="Q52" s="71"/>
-      <c r="R52" s="72"/>
-      <c r="S52" s="55"/>
-      <c r="T52" s="75">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U52" s="75">
-        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
-        <v>0</v>
-      </c>
-      <c r="V52" s="75">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A53" s="27">
-        <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-      <c r="B53" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="C53" s="70"/>
-      <c r="D53" s="70"/>
-      <c r="E53" s="70"/>
-      <c r="F53" s="70"/>
-      <c r="G53" s="70"/>
-      <c r="H53" s="70"/>
-      <c r="I53" s="70"/>
-      <c r="J53" s="71"/>
-      <c r="K53" s="72"/>
-      <c r="L53" s="55"/>
-      <c r="M53" s="73"/>
-      <c r="N53" s="74"/>
-      <c r="O53" s="70"/>
-      <c r="P53" s="71"/>
-      <c r="Q53" s="71"/>
-      <c r="R53" s="72"/>
-      <c r="S53" s="55"/>
-      <c r="T53" s="75">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U53" s="75">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="V53" s="75">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A54" s="27">
-        <f t="shared" si="1"/>
-        <v>51</v>
-      </c>
-      <c r="B54" s="26"/>
-      <c r="C54" s="70"/>
-      <c r="D54" s="70"/>
-      <c r="E54" s="70"/>
-      <c r="F54" s="70"/>
-      <c r="G54" s="70"/>
-      <c r="H54" s="70"/>
-      <c r="I54" s="70"/>
-      <c r="J54" s="71"/>
-      <c r="K54" s="72"/>
-      <c r="L54" s="55"/>
-      <c r="M54" s="73"/>
-      <c r="N54" s="74"/>
-      <c r="O54" s="70"/>
-      <c r="P54" s="71"/>
-      <c r="Q54" s="71"/>
-      <c r="R54" s="72"/>
-      <c r="S54" s="55"/>
-      <c r="T54" s="75">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U54" s="75">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="V54" s="75">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A55" s="27">
-        <f t="shared" si="1"/>
-        <v>52</v>
-      </c>
-      <c r="B55" s="26"/>
-      <c r="C55" s="70"/>
-      <c r="D55" s="70"/>
-      <c r="E55" s="70"/>
-      <c r="F55" s="70"/>
-      <c r="G55" s="70"/>
-      <c r="H55" s="70"/>
-      <c r="I55" s="70"/>
-      <c r="J55" s="71"/>
-      <c r="K55" s="72"/>
-      <c r="L55" s="55"/>
-      <c r="M55" s="73"/>
-      <c r="N55" s="74"/>
-      <c r="O55" s="70"/>
-      <c r="P55" s="71"/>
-      <c r="Q55" s="71"/>
-      <c r="R55" s="72"/>
-      <c r="S55" s="55"/>
-      <c r="T55" s="75"/>
-      <c r="U55" s="75"/>
-      <c r="V55" s="75"/>
-    </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A56" s="27">
-        <f t="shared" si="1"/>
-        <v>53</v>
-      </c>
-      <c r="B56" s="26"/>
-      <c r="C56" s="70"/>
-      <c r="D56" s="70"/>
-      <c r="E56" s="70"/>
-      <c r="F56" s="70"/>
-      <c r="G56" s="70"/>
-      <c r="H56" s="70"/>
-      <c r="I56" s="70"/>
-      <c r="J56" s="71"/>
-      <c r="K56" s="72"/>
-      <c r="L56" s="55"/>
-      <c r="M56" s="73"/>
-      <c r="N56" s="74"/>
-      <c r="O56" s="70"/>
-      <c r="P56" s="71"/>
-      <c r="Q56" s="71"/>
-      <c r="R56" s="72"/>
-      <c r="S56" s="55"/>
-      <c r="T56" s="75"/>
-      <c r="U56" s="75"/>
-      <c r="V56" s="75"/>
-    </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A57" s="27">
-        <f t="shared" si="1"/>
-        <v>54</v>
-      </c>
-      <c r="B57" s="26"/>
-      <c r="C57" s="70"/>
-      <c r="D57" s="70"/>
-      <c r="E57" s="70"/>
-      <c r="F57" s="70"/>
-      <c r="G57" s="70"/>
-      <c r="H57" s="70"/>
-      <c r="I57" s="70"/>
-      <c r="J57" s="71"/>
-      <c r="K57" s="72"/>
-      <c r="L57" s="55"/>
-      <c r="M57" s="73"/>
-      <c r="N57" s="74"/>
-      <c r="O57" s="70"/>
-      <c r="P57" s="71"/>
-      <c r="Q57" s="71"/>
-      <c r="R57" s="72"/>
-      <c r="S57" s="55"/>
-      <c r="T57" s="75"/>
-      <c r="U57" s="75"/>
-      <c r="V57" s="75"/>
-    </row>
-    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="29" t="s">
-        <v>50</v>
-      </c>
-      <c r="C58" s="2">
-        <f>SUM(C7:C57)</f>
-        <v>0</v>
-      </c>
-      <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2">
-        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
-        <v>0</v>
-      </c>
-      <c r="G58" s="2">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="H58" s="2">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I58" s="6">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J58" s="6">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="K58" s="6">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="M58" s="5">
-        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
-      </c>
-      <c r="N58" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="O58" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="P58" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="Q58" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="R58" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S58" s="55"/>
-      <c r="T58" s="4">
-        <f>SUM(T7:T57)</f>
-        <v>0</v>
-      </c>
-      <c r="U58" s="90">
-        <f>SUM(U7:U57)</f>
-        <v>0</v>
-      </c>
-      <c r="V58" s="4">
-        <f>SUM(V7:V57)</f>
-        <v>0</v>
+        <v>49536.083333333336</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>

--- a/GBDS JUNE FILES 2026/INVENTORY COUNT SHEET - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/INVENTORY COUNT SHEET - JUNE 2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B0C753E-0D1D-4017-9A93-30A07130E4A3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27DD60A4-9820-4627-8F1F-D2CDDC442507}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
@@ -16,12 +16,12 @@
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
     <sheet name="06-01-2026" sheetId="57" r:id="rId2"/>
     <sheet name="06-02-2026" sheetId="55" r:id="rId3"/>
-    <sheet name="06-04-2026" sheetId="56" r:id="rId4"/>
+    <sheet name="06-03-2026" sheetId="56" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'06-01-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'06-02-2026'!$A$1:$W$59</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'06-04-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'06-03-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>

--- a/GBDS JUNE FILES 2026/INVENTORY COUNT SHEET - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/INVENTORY COUNT SHEET - JUNE 2026.xlsx
@@ -5,23 +5,25 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS\GBDS JUNE FILES 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27DD60A4-9820-4627-8F1F-D2CDDC442507}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE879483-3325-4525-883A-638253C6419D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
     <sheet name="06-01-2026" sheetId="57" r:id="rId2"/>
     <sheet name="06-02-2026" sheetId="55" r:id="rId3"/>
     <sheet name="06-03-2026" sheetId="56" r:id="rId4"/>
+    <sheet name="06-04-2026 " sheetId="58" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'06-01-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'06-02-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'06-03-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'06-04-2026 '!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="74">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -1249,7 +1251,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1535,6 +1537,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1954,21 +1959,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="105" t="s">
+      <c r="I1" s="106" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="105"/>
-      <c r="K1" s="105"/>
-      <c r="L1" s="105"/>
-      <c r="M1" s="105"/>
-      <c r="N1" s="105"/>
-      <c r="O1" s="105"/>
-      <c r="P1" s="105"/>
-      <c r="Q1" s="105"/>
-      <c r="R1" s="105"/>
-      <c r="S1" s="105"/>
-      <c r="T1" s="105"/>
-      <c r="U1" s="105"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
+      <c r="S1" s="106"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="106"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -1980,17 +1985,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="106" t="s">
+      <c r="C4" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="106"/>
-      <c r="E4" s="106"/>
-      <c r="F4" s="106"/>
-      <c r="G4" s="106"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="107"/>
-      <c r="K4" s="108"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="107"/>
+      <c r="G4" s="107"/>
+      <c r="H4" s="107"/>
+      <c r="I4" s="107"/>
+      <c r="J4" s="108"/>
+      <c r="K4" s="109"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -2010,13 +2015,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="109" t="s">
+      <c r="T4" s="110" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="111" t="s">
+      <c r="U4" s="112" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="98" t="s">
+      <c r="V4" s="99" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2056,10 +2061,10 @@
       <c r="I5" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="100" t="s">
+      <c r="J5" s="101" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="101"/>
+      <c r="K5" s="102"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2067,9 +2072,9 @@
       <c r="Q5" s="89"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="110"/>
-      <c r="U5" s="112"/>
-      <c r="V5" s="99"/>
+      <c r="T5" s="111"/>
+      <c r="U5" s="113"/>
+      <c r="V5" s="100"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -4600,17 +4605,17 @@
       <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="102" t="s">
+      <c r="C62" s="103" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="103"/>
-      <c r="E62" s="103"/>
-      <c r="F62" s="103"/>
-      <c r="G62" s="103"/>
-      <c r="H62" s="103"/>
-      <c r="I62" s="103"/>
-      <c r="J62" s="103"/>
-      <c r="K62" s="104"/>
+      <c r="D62" s="104"/>
+      <c r="E62" s="104"/>
+      <c r="F62" s="104"/>
+      <c r="G62" s="104"/>
+      <c r="H62" s="104"/>
+      <c r="I62" s="104"/>
+      <c r="J62" s="104"/>
+      <c r="K62" s="105"/>
       <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
@@ -4919,21 +4924,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="105" t="s">
+      <c r="I1" s="106" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="105"/>
-      <c r="K1" s="105"/>
-      <c r="L1" s="105"/>
-      <c r="M1" s="105"/>
-      <c r="N1" s="105"/>
-      <c r="O1" s="105"/>
-      <c r="P1" s="105"/>
-      <c r="Q1" s="105"/>
-      <c r="R1" s="105"/>
-      <c r="S1" s="105"/>
-      <c r="T1" s="105"/>
-      <c r="U1" s="105"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
+      <c r="S1" s="106"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="106"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -4945,17 +4950,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="106" t="s">
+      <c r="C4" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="106"/>
-      <c r="E4" s="106"/>
-      <c r="F4" s="106"/>
-      <c r="G4" s="106"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="107"/>
-      <c r="K4" s="108"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="107"/>
+      <c r="G4" s="107"/>
+      <c r="H4" s="107"/>
+      <c r="I4" s="107"/>
+      <c r="J4" s="108"/>
+      <c r="K4" s="109"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -4975,13 +4980,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="109" t="s">
+      <c r="T4" s="110" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="115" t="s">
+      <c r="U4" s="116" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="98" t="s">
+      <c r="V4" s="99" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -5021,10 +5026,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="113" t="s">
+      <c r="J5" s="114" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="114"/>
+      <c r="K5" s="115"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -5032,9 +5037,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="110"/>
-      <c r="U5" s="116"/>
-      <c r="V5" s="99"/>
+      <c r="T5" s="111"/>
+      <c r="U5" s="117"/>
+      <c r="V5" s="100"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -7746,17 +7751,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="102" t="s">
+      <c r="C60" s="103" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="103"/>
-      <c r="E60" s="103"/>
-      <c r="F60" s="103"/>
-      <c r="G60" s="103"/>
-      <c r="H60" s="103"/>
-      <c r="I60" s="103"/>
-      <c r="J60" s="103"/>
-      <c r="K60" s="104"/>
+      <c r="D60" s="104"/>
+      <c r="E60" s="104"/>
+      <c r="F60" s="104"/>
+      <c r="G60" s="104"/>
+      <c r="H60" s="104"/>
+      <c r="I60" s="104"/>
+      <c r="J60" s="104"/>
+      <c r="K60" s="105"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -8065,21 +8070,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="105" t="s">
+      <c r="I1" s="106" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="105"/>
-      <c r="K1" s="105"/>
-      <c r="L1" s="105"/>
-      <c r="M1" s="105"/>
-      <c r="N1" s="105"/>
-      <c r="O1" s="105"/>
-      <c r="P1" s="105"/>
-      <c r="Q1" s="105"/>
-      <c r="R1" s="105"/>
-      <c r="S1" s="105"/>
-      <c r="T1" s="105"/>
-      <c r="U1" s="105"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
+      <c r="S1" s="106"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="106"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -8091,17 +8096,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="106" t="s">
+      <c r="C4" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="106"/>
-      <c r="E4" s="106"/>
-      <c r="F4" s="106"/>
-      <c r="G4" s="106"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="107"/>
-      <c r="K4" s="108"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="107"/>
+      <c r="G4" s="107"/>
+      <c r="H4" s="107"/>
+      <c r="I4" s="107"/>
+      <c r="J4" s="108"/>
+      <c r="K4" s="109"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -8121,13 +8126,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="109" t="s">
+      <c r="T4" s="110" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="115" t="s">
+      <c r="U4" s="116" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="98" t="s">
+      <c r="V4" s="99" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -8167,10 +8172,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="113" t="s">
+      <c r="J5" s="114" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="114"/>
+      <c r="K5" s="115"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -8178,9 +8183,9 @@
       <c r="Q5" s="96"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="110"/>
-      <c r="U5" s="116"/>
-      <c r="V5" s="99"/>
+      <c r="T5" s="111"/>
+      <c r="U5" s="117"/>
+      <c r="V5" s="100"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -10915,17 +10920,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="102" t="s">
+      <c r="C60" s="103" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="103"/>
-      <c r="E60" s="103"/>
-      <c r="F60" s="103"/>
-      <c r="G60" s="103"/>
-      <c r="H60" s="103"/>
-      <c r="I60" s="103"/>
-      <c r="J60" s="103"/>
-      <c r="K60" s="104"/>
+      <c r="D60" s="104"/>
+      <c r="E60" s="104"/>
+      <c r="F60" s="104"/>
+      <c r="G60" s="104"/>
+      <c r="H60" s="104"/>
+      <c r="I60" s="104"/>
+      <c r="J60" s="104"/>
+      <c r="K60" s="105"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -11234,21 +11239,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="105" t="s">
+      <c r="I1" s="106" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="105"/>
-      <c r="K1" s="105"/>
-      <c r="L1" s="105"/>
-      <c r="M1" s="105"/>
-      <c r="N1" s="105"/>
-      <c r="O1" s="105"/>
-      <c r="P1" s="105"/>
-      <c r="Q1" s="105"/>
-      <c r="R1" s="105"/>
-      <c r="S1" s="105"/>
-      <c r="T1" s="105"/>
-      <c r="U1" s="105"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
+      <c r="S1" s="106"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="106"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -11260,17 +11265,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="106" t="s">
+      <c r="C4" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="106"/>
-      <c r="E4" s="106"/>
-      <c r="F4" s="106"/>
-      <c r="G4" s="106"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="107"/>
-      <c r="K4" s="108"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="107"/>
+      <c r="G4" s="107"/>
+      <c r="H4" s="107"/>
+      <c r="I4" s="107"/>
+      <c r="J4" s="108"/>
+      <c r="K4" s="109"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -11290,13 +11295,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="109" t="s">
+      <c r="T4" s="110" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="115" t="s">
+      <c r="U4" s="116" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="98" t="s">
+      <c r="V4" s="99" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -11336,10 +11341,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="113" t="s">
+      <c r="J5" s="114" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="114"/>
+      <c r="K5" s="115"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -11347,9 +11352,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="110"/>
-      <c r="U5" s="116"/>
-      <c r="V5" s="99"/>
+      <c r="T5" s="111"/>
+      <c r="U5" s="117"/>
+      <c r="V5" s="100"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -14044,17 +14049,3151 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="102" t="s">
+      <c r="C60" s="103" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="103"/>
-      <c r="E60" s="103"/>
-      <c r="F60" s="103"/>
-      <c r="G60" s="103"/>
-      <c r="H60" s="103"/>
-      <c r="I60" s="103"/>
-      <c r="J60" s="103"/>
-      <c r="K60" s="104"/>
+      <c r="D60" s="104"/>
+      <c r="E60" s="104"/>
+      <c r="F60" s="104"/>
+      <c r="G60" s="104"/>
+      <c r="H60" s="104"/>
+      <c r="I60" s="104"/>
+      <c r="J60" s="104"/>
+      <c r="K60" s="105"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C3B8CD2-395D-43D6-BA4D-0BFC9B6269E5}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="9" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="106" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
+      <c r="S1" s="106"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="106"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="107" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="107"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="107"/>
+      <c r="G4" s="107"/>
+      <c r="H4" s="107"/>
+      <c r="I4" s="107"/>
+      <c r="J4" s="108"/>
+      <c r="K4" s="109"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="110" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="116" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="99" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="114" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="115"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="98"/>
+      <c r="Q5" s="98"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="111"/>
+      <c r="U5" s="117"/>
+      <c r="V5" s="100"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="98"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="98"/>
+      <c r="Q6" s="98"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="52">
+        <v>20</v>
+      </c>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
+      <c r="J7" s="53"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
+      <c r="L7" s="55"/>
+      <c r="M7" s="56">
+        <v>1</v>
+      </c>
+      <c r="N7" s="57"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="53">
+        <v>1</v>
+      </c>
+      <c r="R7" s="54"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="58">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>9</v>
+      </c>
+      <c r="U7" s="58">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>561</v>
+      </c>
+      <c r="V7" s="58">
+        <f>U7/24</f>
+        <v>23.375</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="59">
+        <f>61+33</f>
+        <v>94</v>
+      </c>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="63"/>
+      <c r="N8" s="64"/>
+      <c r="O8" s="65"/>
+      <c r="P8" s="66"/>
+      <c r="Q8" s="66">
+        <v>2</v>
+      </c>
+      <c r="R8" s="67"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="68">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="69">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>2304</v>
+      </c>
+      <c r="V8" s="69">
+        <f>U8/24</f>
+        <v>96</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="70">
+        <f>90+49</f>
+        <v>139</v>
+      </c>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="73"/>
+      <c r="N9" s="74"/>
+      <c r="O9" s="70">
+        <v>2</v>
+      </c>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71">
+        <v>2</v>
+      </c>
+      <c r="R9" s="72"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="76">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>3432</v>
+      </c>
+      <c r="V9" s="76">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>143</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="70">
+        <v>23</v>
+      </c>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="74"/>
+      <c r="O10" s="70">
+        <v>2</v>
+      </c>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71">
+        <v>7</v>
+      </c>
+      <c r="R10" s="72"/>
+      <c r="S10" s="55"/>
+      <c r="T10" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="58">
+        <f t="shared" si="2"/>
+        <v>768</v>
+      </c>
+      <c r="V10" s="58">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="70">
+        <v>5</v>
+      </c>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
+      <c r="L11" s="55"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="55"/>
+      <c r="T11" s="58">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U11" s="58">
+        <f t="shared" si="2"/>
+        <v>122</v>
+      </c>
+      <c r="V11" s="58">
+        <f t="shared" si="3"/>
+        <v>5.083333333333333</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="59">
+        <f>720+34+1440+288+576+19</f>
+        <v>3077</v>
+      </c>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="63">
+        <v>21</v>
+      </c>
+      <c r="N12" s="64"/>
+      <c r="O12" s="65">
+        <v>10</v>
+      </c>
+      <c r="P12" s="66"/>
+      <c r="Q12" s="66">
+        <v>24</v>
+      </c>
+      <c r="R12" s="67"/>
+      <c r="S12" s="62"/>
+      <c r="T12" s="69">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U12" s="69">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>75168</v>
+      </c>
+      <c r="V12" s="69">
+        <f>U12/24</f>
+        <v>3132</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
+      <c r="I13" s="70"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="55"/>
+      <c r="T13" s="76">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="U13" s="76">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>64</v>
+      </c>
+      <c r="V13" s="76">
+        <f>U13/24</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="70">
+        <v>4</v>
+      </c>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="55"/>
+      <c r="T14" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="75">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>96</v>
+      </c>
+      <c r="V14" s="75">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>4</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="55"/>
+      <c r="T15" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="55"/>
+      <c r="T16" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I17" s="70"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U17" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V17" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="55"/>
+      <c r="T18" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="70">
+        <v>2</v>
+      </c>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70">
+        <f>24+20</f>
+        <v>44</v>
+      </c>
+      <c r="I19" s="70"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="55"/>
+      <c r="T19" s="58">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="U19" s="75">
+        <f t="shared" si="4"/>
+        <v>92</v>
+      </c>
+      <c r="V19" s="75">
+        <f t="shared" si="5"/>
+        <v>3.8333333333333335</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="74"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="55"/>
+      <c r="T20" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V20" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70">
+        <f>24*2</f>
+        <v>48</v>
+      </c>
+      <c r="I21" s="70"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="58">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="U21" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V21" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="70"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
+      <c r="J22" s="71"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="55"/>
+      <c r="T22" s="58">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U22" s="75">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="V22" s="75">
+        <f t="shared" si="5"/>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
+      <c r="I23" s="70"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="74"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="55"/>
+      <c r="T23" s="58">
+        <f t="shared" si="0"/>
+        <v>907</v>
+      </c>
+      <c r="U23" s="75">
+        <f t="shared" si="4"/>
+        <v>907</v>
+      </c>
+      <c r="V23" s="75">
+        <f t="shared" si="5"/>
+        <v>37.791666666666664</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="70">
+        <v>5</v>
+      </c>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70">
+        <f>24*3</f>
+        <v>72</v>
+      </c>
+      <c r="I24" s="70"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="55"/>
+      <c r="T24" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U24" s="75">
+        <f t="shared" si="4"/>
+        <v>192</v>
+      </c>
+      <c r="V24" s="75">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="70">
+        <v>126</v>
+      </c>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70"/>
+      <c r="J25" s="71">
+        <v>1</v>
+      </c>
+      <c r="K25" s="72"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="73">
+        <v>1</v>
+      </c>
+      <c r="N25" s="74"/>
+      <c r="O25" s="70"/>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71">
+        <v>20</v>
+      </c>
+      <c r="R25" s="72"/>
+      <c r="S25" s="55"/>
+      <c r="T25" s="58">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="U25" s="75">
+        <f t="shared" si="4"/>
+        <v>3529</v>
+      </c>
+      <c r="V25" s="75">
+        <f t="shared" si="5"/>
+        <v>147.04166666666666</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="74"/>
+      <c r="O26" s="70"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="71"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="55"/>
+      <c r="T26" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="70"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="70"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="55"/>
+      <c r="T27" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="70">
+        <v>49</v>
+      </c>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="73">
+        <v>27</v>
+      </c>
+      <c r="N28" s="74"/>
+      <c r="O28" s="70">
+        <v>2</v>
+      </c>
+      <c r="P28" s="71"/>
+      <c r="Q28" s="71">
+        <v>20</v>
+      </c>
+      <c r="R28" s="72"/>
+      <c r="S28" s="55"/>
+      <c r="T28" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="75">
+        <f t="shared" si="4"/>
+        <v>2352</v>
+      </c>
+      <c r="V28" s="75">
+        <f t="shared" si="5"/>
+        <v>98</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="70">
+        <v>51</v>
+      </c>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70">
+        <v>5</v>
+      </c>
+      <c r="J29" s="71"/>
+      <c r="K29" s="72"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="73">
+        <v>1</v>
+      </c>
+      <c r="N29" s="74"/>
+      <c r="O29" s="70">
+        <v>1</v>
+      </c>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71"/>
+      <c r="R29" s="72"/>
+      <c r="S29" s="55"/>
+      <c r="T29" s="58">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U29" s="75">
+        <f t="shared" si="4"/>
+        <v>1277</v>
+      </c>
+      <c r="V29" s="75">
+        <f t="shared" si="5"/>
+        <v>53.208333333333336</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="70">
+        <v>13</v>
+      </c>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="74"/>
+      <c r="O30" s="70"/>
+      <c r="P30" s="71"/>
+      <c r="Q30" s="71"/>
+      <c r="R30" s="72"/>
+      <c r="S30" s="55"/>
+      <c r="T30" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="75">
+        <f t="shared" si="4"/>
+        <v>312</v>
+      </c>
+      <c r="V30" s="75">
+        <f t="shared" si="5"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="70"/>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="70">
+        <v>4</v>
+      </c>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="74"/>
+      <c r="O32" s="70"/>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="55"/>
+      <c r="T32" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="75">
+        <f t="shared" si="4"/>
+        <v>96</v>
+      </c>
+      <c r="V32" s="75">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="70"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="73"/>
+      <c r="N33" s="74"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="55"/>
+      <c r="T33" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="70">
+        <v>66</v>
+      </c>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
+      <c r="J34" s="71"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
+      <c r="L34" s="55"/>
+      <c r="M34" s="73">
+        <v>2</v>
+      </c>
+      <c r="N34" s="74"/>
+      <c r="O34" s="70">
+        <v>1</v>
+      </c>
+      <c r="P34" s="71">
+        <v>12</v>
+      </c>
+      <c r="Q34" s="71">
+        <v>7</v>
+      </c>
+      <c r="R34" s="72"/>
+      <c r="S34" s="55"/>
+      <c r="T34" s="58">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="U34" s="75">
+        <f t="shared" si="4"/>
+        <v>1838</v>
+      </c>
+      <c r="V34" s="75">
+        <f t="shared" si="5"/>
+        <v>76.583333333333329</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="72"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="74"/>
+      <c r="O35" s="70"/>
+      <c r="P35" s="71"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="72"/>
+      <c r="S35" s="55"/>
+      <c r="T35" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="73"/>
+      <c r="N36" s="74"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="71"/>
+      <c r="Q36" s="71"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="55"/>
+      <c r="T36" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="59">
+        <f>864+3240+44</f>
+        <v>4148</v>
+      </c>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59"/>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>2</v>
+      </c>
+      <c r="K37" s="61">
+        <v>3</v>
+      </c>
+      <c r="L37" s="62"/>
+      <c r="M37" s="63">
+        <v>127</v>
+      </c>
+      <c r="N37" s="64"/>
+      <c r="O37" s="65">
+        <v>23</v>
+      </c>
+      <c r="P37" s="66"/>
+      <c r="Q37" s="66">
+        <v>136</v>
+      </c>
+      <c r="R37" s="67"/>
+      <c r="S37" s="62"/>
+      <c r="T37" s="77">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="U37" s="77">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>26611</v>
+      </c>
+      <c r="V37" s="77">
+        <f>U37/6</f>
+        <v>4435.166666666667</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="73"/>
+      <c r="N38" s="74"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="71"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="55"/>
+      <c r="T38" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="75">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="75">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="74"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="71"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="95"/>
+      <c r="T39" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U39" s="75">
+        <f>C39*24+M39*24+O39*24+Q39*24+T39</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="75">
+        <f>U39/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="59">
+        <f>63+24</f>
+        <v>87</v>
+      </c>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
+      <c r="L40" s="62"/>
+      <c r="M40" s="63">
+        <v>2</v>
+      </c>
+      <c r="N40" s="64"/>
+      <c r="O40" s="65">
+        <v>1</v>
+      </c>
+      <c r="P40" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q40" s="66">
+        <v>2</v>
+      </c>
+      <c r="R40" s="67"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="77">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="U40" s="77">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>2240</v>
+      </c>
+      <c r="V40" s="77">
+        <f>U40/24</f>
+        <v>93.333333333333329</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="82">
+        <f>96+60</f>
+        <v>156</v>
+      </c>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="85"/>
+      <c r="M41" s="86">
+        <v>58</v>
+      </c>
+      <c r="N41" s="87"/>
+      <c r="O41" s="82">
+        <v>6</v>
+      </c>
+      <c r="P41" s="83"/>
+      <c r="Q41" s="83">
+        <v>20</v>
+      </c>
+      <c r="R41" s="84"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="88">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>2880</v>
+      </c>
+      <c r="V41" s="88">
+        <f>U41/12</f>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="71"/>
+      <c r="K42" s="72"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="73"/>
+      <c r="N42" s="74"/>
+      <c r="O42" s="70"/>
+      <c r="P42" s="71"/>
+      <c r="Q42" s="71"/>
+      <c r="R42" s="72"/>
+      <c r="S42" s="55"/>
+      <c r="T42" s="75"/>
+      <c r="U42" s="75"/>
+      <c r="V42" s="75"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="65">
+        <f>7776+2484+72+3024+8424+5508+3024+5832</f>
+        <v>36144</v>
+      </c>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65"/>
+      <c r="I43" s="65">
+        <v>7</v>
+      </c>
+      <c r="J43" s="66">
+        <f>10*6+1</f>
+        <v>61</v>
+      </c>
+      <c r="K43" s="67">
+        <f>69*6+7</f>
+        <v>421</v>
+      </c>
+      <c r="L43" s="62"/>
+      <c r="M43" s="63">
+        <v>399</v>
+      </c>
+      <c r="N43" s="64"/>
+      <c r="O43" s="65">
+        <v>387</v>
+      </c>
+      <c r="P43" s="66"/>
+      <c r="Q43" s="66">
+        <v>541</v>
+      </c>
+      <c r="R43" s="67"/>
+      <c r="S43" s="62"/>
+      <c r="T43" s="77">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>489</v>
+      </c>
+      <c r="U43" s="77">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>225315</v>
+      </c>
+      <c r="V43" s="77">
+        <f>U43/6</f>
+        <v>37552.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="70"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="71"/>
+      <c r="K44" s="72"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="73"/>
+      <c r="N44" s="74"/>
+      <c r="O44" s="70"/>
+      <c r="P44" s="71"/>
+      <c r="Q44" s="71"/>
+      <c r="R44" s="72"/>
+      <c r="S44" s="55"/>
+      <c r="T44" s="75"/>
+      <c r="U44" s="75"/>
+      <c r="V44" s="75"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="70"/>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="70"/>
+      <c r="I45" s="70"/>
+      <c r="J45" s="71"/>
+      <c r="K45" s="72"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="73"/>
+      <c r="N45" s="74"/>
+      <c r="O45" s="70"/>
+      <c r="P45" s="71"/>
+      <c r="Q45" s="71"/>
+      <c r="R45" s="72"/>
+      <c r="S45" s="55"/>
+      <c r="T45" s="75">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="75">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="75">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="73"/>
+      <c r="N46" s="74"/>
+      <c r="O46" s="70"/>
+      <c r="P46" s="71"/>
+      <c r="Q46" s="71"/>
+      <c r="R46" s="72"/>
+      <c r="S46" s="55"/>
+      <c r="T46" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="75">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="75">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="65">
+        <f>14+432+106+2160+71</f>
+        <v>2783</v>
+      </c>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
+      <c r="I47" s="65"/>
+      <c r="J47" s="66">
+        <v>1</v>
+      </c>
+      <c r="K47" s="67">
+        <v>4</v>
+      </c>
+      <c r="L47" s="62"/>
+      <c r="M47" s="63">
+        <v>6</v>
+      </c>
+      <c r="N47" s="64"/>
+      <c r="O47" s="65">
+        <v>5</v>
+      </c>
+      <c r="P47" s="66">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="66">
+        <v>2</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
+      <c r="S47" s="62"/>
+      <c r="T47" s="77">
+        <f t="shared" si="7"/>
+        <v>13</v>
+      </c>
+      <c r="U47" s="77">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>16789</v>
+      </c>
+      <c r="V47" s="77">
+        <f>U47/6</f>
+        <v>2798.1666666666665</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
+      <c r="I48" s="70"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="72"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="73"/>
+      <c r="N48" s="74"/>
+      <c r="O48" s="70"/>
+      <c r="P48" s="71"/>
+      <c r="Q48" s="71"/>
+      <c r="R48" s="72"/>
+      <c r="S48" s="55"/>
+      <c r="T48" s="75">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="U48" s="75">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="V48" s="75">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="70"/>
+      <c r="I49" s="70"/>
+      <c r="J49" s="71"/>
+      <c r="K49" s="72"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="74"/>
+      <c r="O49" s="70"/>
+      <c r="P49" s="71"/>
+      <c r="Q49" s="71">
+        <v>1</v>
+      </c>
+      <c r="R49" s="72"/>
+      <c r="S49" s="55"/>
+      <c r="T49" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="75">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="V49" s="75">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="70"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="70"/>
+      <c r="F50" s="70"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
+      <c r="J50" s="71"/>
+      <c r="K50" s="72"/>
+      <c r="L50" s="55"/>
+      <c r="M50" s="73"/>
+      <c r="N50" s="74"/>
+      <c r="O50" s="70"/>
+      <c r="P50" s="71"/>
+      <c r="Q50" s="71"/>
+      <c r="R50" s="72"/>
+      <c r="S50" s="55"/>
+      <c r="T50" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="65"/>
+      <c r="I51" s="65"/>
+      <c r="J51" s="66"/>
+      <c r="K51" s="67"/>
+      <c r="L51" s="62"/>
+      <c r="M51" s="63"/>
+      <c r="N51" s="64"/>
+      <c r="O51" s="65"/>
+      <c r="P51" s="66"/>
+      <c r="Q51" s="66"/>
+      <c r="R51" s="67"/>
+      <c r="S51" s="62"/>
+      <c r="T51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="77">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>204</v>
+      </c>
+      <c r="V51" s="77">
+        <f>U51/6</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="70"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="70"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="71"/>
+      <c r="K52" s="72"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="73"/>
+      <c r="N52" s="74"/>
+      <c r="O52" s="70"/>
+      <c r="P52" s="71"/>
+      <c r="Q52" s="71"/>
+      <c r="R52" s="72"/>
+      <c r="S52" s="55"/>
+      <c r="T52" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="75">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="70">
+        <v>9</v>
+      </c>
+      <c r="D53" s="70"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="70"/>
+      <c r="H53" s="70"/>
+      <c r="I53" s="70"/>
+      <c r="J53" s="71"/>
+      <c r="K53" s="72"/>
+      <c r="L53" s="55"/>
+      <c r="M53" s="73"/>
+      <c r="N53" s="74"/>
+      <c r="O53" s="70"/>
+      <c r="P53" s="71"/>
+      <c r="Q53" s="71"/>
+      <c r="R53" s="72"/>
+      <c r="S53" s="55"/>
+      <c r="T53" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="75">
+        <f t="shared" si="10"/>
+        <v>216</v>
+      </c>
+      <c r="V53" s="75">
+        <f t="shared" si="9"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="71"/>
+      <c r="K54" s="72"/>
+      <c r="L54" s="55"/>
+      <c r="M54" s="73"/>
+      <c r="N54" s="74"/>
+      <c r="O54" s="70"/>
+      <c r="P54" s="71"/>
+      <c r="Q54" s="71"/>
+      <c r="R54" s="72"/>
+      <c r="S54" s="55"/>
+      <c r="T54" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="70"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="70"/>
+      <c r="I55" s="70"/>
+      <c r="J55" s="71"/>
+      <c r="K55" s="72"/>
+      <c r="L55" s="55"/>
+      <c r="M55" s="73"/>
+      <c r="N55" s="74"/>
+      <c r="O55" s="70"/>
+      <c r="P55" s="71"/>
+      <c r="Q55" s="71"/>
+      <c r="R55" s="72"/>
+      <c r="S55" s="55"/>
+      <c r="T55" s="75"/>
+      <c r="U55" s="75"/>
+      <c r="V55" s="75"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="70"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="70"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="71"/>
+      <c r="K56" s="72"/>
+      <c r="L56" s="55"/>
+      <c r="M56" s="73"/>
+      <c r="N56" s="74"/>
+      <c r="O56" s="70"/>
+      <c r="P56" s="71"/>
+      <c r="Q56" s="71"/>
+      <c r="R56" s="72"/>
+      <c r="S56" s="55"/>
+      <c r="T56" s="75"/>
+      <c r="U56" s="75"/>
+      <c r="V56" s="75"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="70"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="70"/>
+      <c r="I57" s="70"/>
+      <c r="J57" s="71"/>
+      <c r="K57" s="72"/>
+      <c r="L57" s="55"/>
+      <c r="M57" s="73"/>
+      <c r="N57" s="74"/>
+      <c r="O57" s="70"/>
+      <c r="P57" s="71"/>
+      <c r="Q57" s="71"/>
+      <c r="R57" s="72"/>
+      <c r="S57" s="55"/>
+      <c r="T57" s="75"/>
+      <c r="U57" s="75"/>
+      <c r="V57" s="75"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>47046</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>1184</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>38</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>65</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>457</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>645</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>441</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>28</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>785</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>3</v>
+      </c>
+      <c r="S58" s="55"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>1775</v>
+      </c>
+      <c r="U58" s="90">
+        <f>SUM(U7:U57)</f>
+        <v>367673</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>49054.583333333336</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="103" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="104"/>
+      <c r="E60" s="104"/>
+      <c r="F60" s="104"/>
+      <c r="G60" s="104"/>
+      <c r="H60" s="104"/>
+      <c r="I60" s="104"/>
+      <c r="J60" s="104"/>
+      <c r="K60" s="105"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>

--- a/GBDS JUNE FILES 2026/INVENTORY COUNT SHEET - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/INVENTORY COUNT SHEET - JUNE 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE879483-3325-4525-883A-638253C6419D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7386F9DA-E4E5-4048-9FB4-B93FC7F43B58}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -18,12 +18,16 @@
     <sheet name="06-02-2026" sheetId="55" r:id="rId3"/>
     <sheet name="06-03-2026" sheetId="56" r:id="rId4"/>
     <sheet name="06-04-2026 " sheetId="58" r:id="rId5"/>
+    <sheet name="06-05-2026 " sheetId="59" r:id="rId6"/>
+    <sheet name="06-08-2026 " sheetId="60" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'06-01-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'06-02-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'06-03-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'06-04-2026 '!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'06-05-2026 '!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'06-08-2026 '!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -42,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="74">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -1251,7 +1255,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1537,6 +1541,12 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1959,21 +1969,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="106" t="s">
+      <c r="I1" s="108" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="106"/>
-      <c r="S1" s="106"/>
-      <c r="T1" s="106"/>
-      <c r="U1" s="106"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="108"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -1985,17 +1995,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="107" t="s">
+      <c r="C4" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="107"/>
-      <c r="G4" s="107"/>
-      <c r="H4" s="107"/>
-      <c r="I4" s="107"/>
-      <c r="J4" s="108"/>
-      <c r="K4" s="109"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="111"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -2015,13 +2025,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="110" t="s">
+      <c r="T4" s="112" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="112" t="s">
+      <c r="U4" s="114" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="99" t="s">
+      <c r="V4" s="101" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2061,10 +2071,10 @@
       <c r="I5" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="101" t="s">
+      <c r="J5" s="103" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="102"/>
+      <c r="K5" s="104"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2072,9 +2082,9 @@
       <c r="Q5" s="89"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="111"/>
-      <c r="U5" s="113"/>
-      <c r="V5" s="100"/>
+      <c r="T5" s="113"/>
+      <c r="U5" s="115"/>
+      <c r="V5" s="102"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -4605,17 +4615,17 @@
       <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="103" t="s">
+      <c r="C62" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="104"/>
-      <c r="E62" s="104"/>
-      <c r="F62" s="104"/>
-      <c r="G62" s="104"/>
-      <c r="H62" s="104"/>
-      <c r="I62" s="104"/>
-      <c r="J62" s="104"/>
-      <c r="K62" s="105"/>
+      <c r="D62" s="106"/>
+      <c r="E62" s="106"/>
+      <c r="F62" s="106"/>
+      <c r="G62" s="106"/>
+      <c r="H62" s="106"/>
+      <c r="I62" s="106"/>
+      <c r="J62" s="106"/>
+      <c r="K62" s="107"/>
       <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
@@ -4924,21 +4934,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="106" t="s">
+      <c r="I1" s="108" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="106"/>
-      <c r="S1" s="106"/>
-      <c r="T1" s="106"/>
-      <c r="U1" s="106"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="108"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -4950,17 +4960,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="107" t="s">
+      <c r="C4" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="107"/>
-      <c r="G4" s="107"/>
-      <c r="H4" s="107"/>
-      <c r="I4" s="107"/>
-      <c r="J4" s="108"/>
-      <c r="K4" s="109"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="111"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -4980,13 +4990,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="110" t="s">
+      <c r="T4" s="112" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="116" t="s">
+      <c r="U4" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="99" t="s">
+      <c r="V4" s="101" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -5026,10 +5036,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="114" t="s">
+      <c r="J5" s="116" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="115"/>
+      <c r="K5" s="117"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -5037,9 +5047,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="111"/>
-      <c r="U5" s="117"/>
-      <c r="V5" s="100"/>
+      <c r="T5" s="113"/>
+      <c r="U5" s="119"/>
+      <c r="V5" s="102"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -7751,17 +7761,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="103" t="s">
+      <c r="C60" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="104"/>
-      <c r="E60" s="104"/>
-      <c r="F60" s="104"/>
-      <c r="G60" s="104"/>
-      <c r="H60" s="104"/>
-      <c r="I60" s="104"/>
-      <c r="J60" s="104"/>
-      <c r="K60" s="105"/>
+      <c r="D60" s="106"/>
+      <c r="E60" s="106"/>
+      <c r="F60" s="106"/>
+      <c r="G60" s="106"/>
+      <c r="H60" s="106"/>
+      <c r="I60" s="106"/>
+      <c r="J60" s="106"/>
+      <c r="K60" s="107"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -8070,21 +8080,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="106" t="s">
+      <c r="I1" s="108" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="106"/>
-      <c r="S1" s="106"/>
-      <c r="T1" s="106"/>
-      <c r="U1" s="106"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="108"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -8096,17 +8106,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="107" t="s">
+      <c r="C4" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="107"/>
-      <c r="G4" s="107"/>
-      <c r="H4" s="107"/>
-      <c r="I4" s="107"/>
-      <c r="J4" s="108"/>
-      <c r="K4" s="109"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="111"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -8126,13 +8136,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="110" t="s">
+      <c r="T4" s="112" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="116" t="s">
+      <c r="U4" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="99" t="s">
+      <c r="V4" s="101" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -8172,10 +8182,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="114" t="s">
+      <c r="J5" s="116" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="115"/>
+      <c r="K5" s="117"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -8183,9 +8193,9 @@
       <c r="Q5" s="96"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="111"/>
-      <c r="U5" s="117"/>
-      <c r="V5" s="100"/>
+      <c r="T5" s="113"/>
+      <c r="U5" s="119"/>
+      <c r="V5" s="102"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -10920,17 +10930,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="103" t="s">
+      <c r="C60" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="104"/>
-      <c r="E60" s="104"/>
-      <c r="F60" s="104"/>
-      <c r="G60" s="104"/>
-      <c r="H60" s="104"/>
-      <c r="I60" s="104"/>
-      <c r="J60" s="104"/>
-      <c r="K60" s="105"/>
+      <c r="D60" s="106"/>
+      <c r="E60" s="106"/>
+      <c r="F60" s="106"/>
+      <c r="G60" s="106"/>
+      <c r="H60" s="106"/>
+      <c r="I60" s="106"/>
+      <c r="J60" s="106"/>
+      <c r="K60" s="107"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -11239,21 +11249,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="106" t="s">
+      <c r="I1" s="108" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="106"/>
-      <c r="S1" s="106"/>
-      <c r="T1" s="106"/>
-      <c r="U1" s="106"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="108"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -11265,17 +11275,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="107" t="s">
+      <c r="C4" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="107"/>
-      <c r="G4" s="107"/>
-      <c r="H4" s="107"/>
-      <c r="I4" s="107"/>
-      <c r="J4" s="108"/>
-      <c r="K4" s="109"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="111"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -11295,13 +11305,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="110" t="s">
+      <c r="T4" s="112" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="116" t="s">
+      <c r="U4" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="99" t="s">
+      <c r="V4" s="101" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -11341,10 +11351,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="114" t="s">
+      <c r="J5" s="116" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="115"/>
+      <c r="K5" s="117"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -11352,9 +11362,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="111"/>
-      <c r="U5" s="117"/>
-      <c r="V5" s="100"/>
+      <c r="T5" s="113"/>
+      <c r="U5" s="119"/>
+      <c r="V5" s="102"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -14049,17 +14059,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="103" t="s">
+      <c r="C60" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="104"/>
-      <c r="E60" s="104"/>
-      <c r="F60" s="104"/>
-      <c r="G60" s="104"/>
-      <c r="H60" s="104"/>
-      <c r="I60" s="104"/>
-      <c r="J60" s="104"/>
-      <c r="K60" s="105"/>
+      <c r="D60" s="106"/>
+      <c r="E60" s="106"/>
+      <c r="F60" s="106"/>
+      <c r="G60" s="106"/>
+      <c r="H60" s="106"/>
+      <c r="I60" s="106"/>
+      <c r="J60" s="106"/>
+      <c r="K60" s="107"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -14368,21 +14378,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="106" t="s">
+      <c r="I1" s="108" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="106"/>
-      <c r="S1" s="106"/>
-      <c r="T1" s="106"/>
-      <c r="U1" s="106"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="108"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -14394,17 +14404,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="107" t="s">
+      <c r="C4" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="107"/>
-      <c r="G4" s="107"/>
-      <c r="H4" s="107"/>
-      <c r="I4" s="107"/>
-      <c r="J4" s="108"/>
-      <c r="K4" s="109"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="111"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -14424,13 +14434,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="110" t="s">
+      <c r="T4" s="112" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="116" t="s">
+      <c r="U4" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="99" t="s">
+      <c r="V4" s="101" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -14470,10 +14480,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="114" t="s">
+      <c r="J5" s="116" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="115"/>
+      <c r="K5" s="117"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -14481,9 +14491,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="111"/>
-      <c r="U5" s="117"/>
-      <c r="V5" s="100"/>
+      <c r="T5" s="113"/>
+      <c r="U5" s="119"/>
+      <c r="V5" s="102"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -17183,17 +17193,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="103" t="s">
+      <c r="C60" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="104"/>
-      <c r="E60" s="104"/>
-      <c r="F60" s="104"/>
-      <c r="G60" s="104"/>
-      <c r="H60" s="104"/>
-      <c r="I60" s="104"/>
-      <c r="J60" s="104"/>
-      <c r="K60" s="105"/>
+      <c r="D60" s="106"/>
+      <c r="E60" s="106"/>
+      <c r="F60" s="106"/>
+      <c r="G60" s="106"/>
+      <c r="H60" s="106"/>
+      <c r="I60" s="106"/>
+      <c r="J60" s="106"/>
+      <c r="K60" s="107"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -17460,4 +17470,6262 @@
     <brk id="24" max="80" man="1"/>
   </colBreaks>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4973CE5-2315-4869-BE9F-BD6543F78682}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="9" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="108" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="108"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="109" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="111"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="112" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="118" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="101" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="116" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="117"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="99"/>
+      <c r="Q5" s="99"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="113"/>
+      <c r="U5" s="119"/>
+      <c r="V5" s="102"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="99"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="99"/>
+      <c r="Q6" s="99"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="52">
+        <v>20</v>
+      </c>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
+      <c r="J7" s="53"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
+      <c r="L7" s="55"/>
+      <c r="M7" s="56">
+        <v>1</v>
+      </c>
+      <c r="N7" s="57"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="53">
+        <v>1</v>
+      </c>
+      <c r="R7" s="54"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="58">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>9</v>
+      </c>
+      <c r="U7" s="58">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>561</v>
+      </c>
+      <c r="V7" s="58">
+        <f>U7/24</f>
+        <v>23.375</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="59">
+        <f>61+33</f>
+        <v>94</v>
+      </c>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="63"/>
+      <c r="N8" s="64"/>
+      <c r="O8" s="65"/>
+      <c r="P8" s="66"/>
+      <c r="Q8" s="66">
+        <v>2</v>
+      </c>
+      <c r="R8" s="67"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="68">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="69">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>2304</v>
+      </c>
+      <c r="V8" s="69">
+        <f>U8/24</f>
+        <v>96</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="70">
+        <f>90+49</f>
+        <v>139</v>
+      </c>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="73"/>
+      <c r="N9" s="74"/>
+      <c r="O9" s="70"/>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71"/>
+      <c r="R9" s="72"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="76">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>3336</v>
+      </c>
+      <c r="V9" s="76">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>139</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="70">
+        <v>23</v>
+      </c>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="74"/>
+      <c r="O10" s="70"/>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71"/>
+      <c r="R10" s="72"/>
+      <c r="S10" s="55"/>
+      <c r="T10" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="58">
+        <f t="shared" si="2"/>
+        <v>552</v>
+      </c>
+      <c r="V10" s="58">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="70">
+        <v>5</v>
+      </c>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
+      <c r="L11" s="55"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="55"/>
+      <c r="T11" s="58">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U11" s="58">
+        <f t="shared" si="2"/>
+        <v>122</v>
+      </c>
+      <c r="V11" s="58">
+        <f t="shared" si="3"/>
+        <v>5.083333333333333</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="59">
+        <f>720+34+1440+288+576</f>
+        <v>3058</v>
+      </c>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="63">
+        <v>4</v>
+      </c>
+      <c r="N12" s="64">
+        <v>12</v>
+      </c>
+      <c r="O12" s="65">
+        <v>9</v>
+      </c>
+      <c r="P12" s="66"/>
+      <c r="Q12" s="66">
+        <v>19</v>
+      </c>
+      <c r="R12" s="67"/>
+      <c r="S12" s="62"/>
+      <c r="T12" s="69">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="U12" s="69">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>74172</v>
+      </c>
+      <c r="V12" s="69">
+        <f>U12/24</f>
+        <v>3090.5</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
+      <c r="I13" s="70"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="55"/>
+      <c r="T13" s="76">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="U13" s="76">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>64</v>
+      </c>
+      <c r="V13" s="76">
+        <f>U13/24</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="70">
+        <v>4</v>
+      </c>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="55"/>
+      <c r="T14" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="75">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>96</v>
+      </c>
+      <c r="V14" s="75">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>4</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="55"/>
+      <c r="T15" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="55"/>
+      <c r="T16" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I17" s="70"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U17" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V17" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="55"/>
+      <c r="T18" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="70">
+        <v>2</v>
+      </c>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70">
+        <f>1*24+20</f>
+        <v>44</v>
+      </c>
+      <c r="I19" s="70"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="55"/>
+      <c r="T19" s="58">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="U19" s="75">
+        <f t="shared" si="4"/>
+        <v>92</v>
+      </c>
+      <c r="V19" s="75">
+        <f t="shared" si="5"/>
+        <v>3.8333333333333335</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="74"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="55"/>
+      <c r="T20" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V20" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70">
+        <f>2*24</f>
+        <v>48</v>
+      </c>
+      <c r="I21" s="70"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="58">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="U21" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V21" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="70"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
+      <c r="J22" s="71"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="55"/>
+      <c r="T22" s="58">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U22" s="75">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="V22" s="75">
+        <f t="shared" si="5"/>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
+      <c r="I23" s="70"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="74"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="55"/>
+      <c r="T23" s="58">
+        <f t="shared" si="0"/>
+        <v>907</v>
+      </c>
+      <c r="U23" s="75">
+        <f t="shared" si="4"/>
+        <v>907</v>
+      </c>
+      <c r="V23" s="75">
+        <f t="shared" si="5"/>
+        <v>37.791666666666664</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="70">
+        <v>5</v>
+      </c>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I24" s="70"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="55"/>
+      <c r="T24" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U24" s="75">
+        <f t="shared" si="4"/>
+        <v>192</v>
+      </c>
+      <c r="V24" s="75">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="70">
+        <f>63+61</f>
+        <v>124</v>
+      </c>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70">
+        <v>1</v>
+      </c>
+      <c r="J25" s="71"/>
+      <c r="K25" s="72"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="73">
+        <v>1</v>
+      </c>
+      <c r="N25" s="74"/>
+      <c r="O25" s="70"/>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71">
+        <v>2</v>
+      </c>
+      <c r="R25" s="72"/>
+      <c r="S25" s="55"/>
+      <c r="T25" s="58">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="U25" s="75">
+        <f t="shared" si="4"/>
+        <v>3049</v>
+      </c>
+      <c r="V25" s="75">
+        <f t="shared" si="5"/>
+        <v>127.04166666666667</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="74"/>
+      <c r="O26" s="70"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="71"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="55"/>
+      <c r="T26" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="70"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="70"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="55"/>
+      <c r="T27" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="70">
+        <v>45</v>
+      </c>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="73">
+        <v>1</v>
+      </c>
+      <c r="N28" s="74"/>
+      <c r="O28" s="70">
+        <v>2</v>
+      </c>
+      <c r="P28" s="71"/>
+      <c r="Q28" s="71">
+        <v>4</v>
+      </c>
+      <c r="R28" s="72"/>
+      <c r="S28" s="55"/>
+      <c r="T28" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="75">
+        <f t="shared" si="4"/>
+        <v>1248</v>
+      </c>
+      <c r="V28" s="75">
+        <f t="shared" si="5"/>
+        <v>52</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="70">
+        <v>51</v>
+      </c>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70">
+        <v>5</v>
+      </c>
+      <c r="J29" s="71"/>
+      <c r="K29" s="72"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="73">
+        <v>1</v>
+      </c>
+      <c r="N29" s="74"/>
+      <c r="O29" s="70">
+        <v>1</v>
+      </c>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71"/>
+      <c r="R29" s="72"/>
+      <c r="S29" s="55"/>
+      <c r="T29" s="58">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U29" s="75">
+        <f t="shared" si="4"/>
+        <v>1277</v>
+      </c>
+      <c r="V29" s="75">
+        <f t="shared" si="5"/>
+        <v>53.208333333333336</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="70">
+        <v>12</v>
+      </c>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="74"/>
+      <c r="O30" s="70"/>
+      <c r="P30" s="71"/>
+      <c r="Q30" s="71">
+        <v>1</v>
+      </c>
+      <c r="R30" s="72"/>
+      <c r="S30" s="55"/>
+      <c r="T30" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="75">
+        <f t="shared" si="4"/>
+        <v>312</v>
+      </c>
+      <c r="V30" s="75">
+        <f t="shared" si="5"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="70"/>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="70">
+        <v>4</v>
+      </c>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="74"/>
+      <c r="O32" s="70"/>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="55"/>
+      <c r="T32" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="75">
+        <f t="shared" si="4"/>
+        <v>96</v>
+      </c>
+      <c r="V32" s="75">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="70"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="73"/>
+      <c r="N33" s="74"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="55"/>
+      <c r="T33" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="70">
+        <v>66</v>
+      </c>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
+      <c r="J34" s="71"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
+      <c r="L34" s="55"/>
+      <c r="M34" s="73">
+        <v>2</v>
+      </c>
+      <c r="N34" s="74"/>
+      <c r="O34" s="70">
+        <v>1</v>
+      </c>
+      <c r="P34" s="71">
+        <v>12</v>
+      </c>
+      <c r="Q34" s="71">
+        <v>7</v>
+      </c>
+      <c r="R34" s="72"/>
+      <c r="S34" s="55"/>
+      <c r="T34" s="58">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="U34" s="75">
+        <f t="shared" si="4"/>
+        <v>1838</v>
+      </c>
+      <c r="V34" s="75">
+        <f t="shared" si="5"/>
+        <v>76.583333333333329</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="72"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="74"/>
+      <c r="O35" s="70"/>
+      <c r="P35" s="71"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="72"/>
+      <c r="S35" s="55"/>
+      <c r="T35" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="73"/>
+      <c r="N36" s="74"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="71"/>
+      <c r="Q36" s="71"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="55"/>
+      <c r="T36" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="59">
+        <f>864+3132+68</f>
+        <v>4064</v>
+      </c>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59">
+        <v>2</v>
+      </c>
+      <c r="I37" s="59"/>
+      <c r="J37" s="60">
+        <v>2</v>
+      </c>
+      <c r="K37" s="61">
+        <v>3</v>
+      </c>
+      <c r="L37" s="62"/>
+      <c r="M37" s="63">
+        <v>10</v>
+      </c>
+      <c r="N37" s="64"/>
+      <c r="O37" s="65">
+        <v>30</v>
+      </c>
+      <c r="P37" s="66"/>
+      <c r="Q37" s="66">
+        <v>55</v>
+      </c>
+      <c r="R37" s="67"/>
+      <c r="S37" s="62"/>
+      <c r="T37" s="77">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="U37" s="77">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>24961</v>
+      </c>
+      <c r="V37" s="77">
+        <f>U37/6</f>
+        <v>4160.166666666667</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="73"/>
+      <c r="N38" s="74"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="71"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="55"/>
+      <c r="T38" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="75">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="75">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="74"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="71"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="95"/>
+      <c r="T39" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U39" s="75">
+        <f>C39*24+M39*24+O39*24+Q39*24+T39</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="75">
+        <f>U39/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="59">
+        <v>23</v>
+      </c>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
+      <c r="L40" s="62"/>
+      <c r="M40" s="63">
+        <v>1</v>
+      </c>
+      <c r="N40" s="64"/>
+      <c r="O40" s="65">
+        <v>1</v>
+      </c>
+      <c r="P40" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q40" s="66">
+        <v>2</v>
+      </c>
+      <c r="R40" s="67"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="77">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="U40" s="77">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>680</v>
+      </c>
+      <c r="V40" s="77">
+        <f>U40/24</f>
+        <v>28.333333333333332</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="82">
+        <f>96+40</f>
+        <v>136</v>
+      </c>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="85"/>
+      <c r="M41" s="86">
+        <v>8</v>
+      </c>
+      <c r="N41" s="87"/>
+      <c r="O41" s="82">
+        <v>5</v>
+      </c>
+      <c r="P41" s="83"/>
+      <c r="Q41" s="83">
+        <v>20</v>
+      </c>
+      <c r="R41" s="84"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="88">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>2028</v>
+      </c>
+      <c r="V41" s="88">
+        <f>U41/12</f>
+        <v>169</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="71"/>
+      <c r="K42" s="72"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="73"/>
+      <c r="N42" s="74"/>
+      <c r="O42" s="70"/>
+      <c r="P42" s="71"/>
+      <c r="Q42" s="71"/>
+      <c r="R42" s="72"/>
+      <c r="S42" s="55"/>
+      <c r="T42" s="75"/>
+      <c r="U42" s="75"/>
+      <c r="V42" s="75"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="65">
+        <f>7776+1836+3024+8424+5508+3024+5832</f>
+        <v>35424</v>
+      </c>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65">
+        <v>7</v>
+      </c>
+      <c r="I43" s="65">
+        <f>10*6+1</f>
+        <v>61</v>
+      </c>
+      <c r="J43" s="66">
+        <f>69*6+7</f>
+        <v>421</v>
+      </c>
+      <c r="K43" s="67"/>
+      <c r="L43" s="62"/>
+      <c r="M43" s="63">
+        <v>29</v>
+      </c>
+      <c r="N43" s="64"/>
+      <c r="O43" s="65">
+        <v>378</v>
+      </c>
+      <c r="P43" s="66"/>
+      <c r="Q43" s="66">
+        <v>434</v>
+      </c>
+      <c r="R43" s="67"/>
+      <c r="S43" s="62"/>
+      <c r="T43" s="77">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>489</v>
+      </c>
+      <c r="U43" s="77">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>218079</v>
+      </c>
+      <c r="V43" s="77">
+        <f>U43/6</f>
+        <v>36346.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="70"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="71"/>
+      <c r="K44" s="72"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="73"/>
+      <c r="N44" s="74"/>
+      <c r="O44" s="70"/>
+      <c r="P44" s="71"/>
+      <c r="Q44" s="71"/>
+      <c r="R44" s="72"/>
+      <c r="S44" s="55"/>
+      <c r="T44" s="75"/>
+      <c r="U44" s="75"/>
+      <c r="V44" s="75"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="70"/>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="70"/>
+      <c r="I45" s="70"/>
+      <c r="J45" s="71"/>
+      <c r="K45" s="72"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="73"/>
+      <c r="N45" s="74"/>
+      <c r="O45" s="70"/>
+      <c r="P45" s="71"/>
+      <c r="Q45" s="71"/>
+      <c r="R45" s="72"/>
+      <c r="S45" s="55"/>
+      <c r="T45" s="75">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="75">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="75">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="73"/>
+      <c r="N46" s="74"/>
+      <c r="O46" s="70"/>
+      <c r="P46" s="71"/>
+      <c r="Q46" s="71"/>
+      <c r="R46" s="72"/>
+      <c r="S46" s="55"/>
+      <c r="T46" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="75">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="75">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="65">
+        <f>14+432+106+71+2160</f>
+        <v>2783</v>
+      </c>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
+      <c r="I47" s="65">
+        <v>1</v>
+      </c>
+      <c r="J47" s="66"/>
+      <c r="K47" s="67">
+        <v>4</v>
+      </c>
+      <c r="L47" s="62"/>
+      <c r="M47" s="63">
+        <v>3</v>
+      </c>
+      <c r="N47" s="64"/>
+      <c r="O47" s="65">
+        <v>5</v>
+      </c>
+      <c r="P47" s="66">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="66">
+        <v>2</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
+      <c r="S47" s="62"/>
+      <c r="T47" s="77">
+        <f t="shared" si="7"/>
+        <v>13</v>
+      </c>
+      <c r="U47" s="77">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>16771</v>
+      </c>
+      <c r="V47" s="77">
+        <f>U47/6</f>
+        <v>2795.1666666666665</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
+      <c r="I48" s="70"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="72"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="73"/>
+      <c r="N48" s="74"/>
+      <c r="O48" s="70"/>
+      <c r="P48" s="71"/>
+      <c r="Q48" s="71"/>
+      <c r="R48" s="72"/>
+      <c r="S48" s="55"/>
+      <c r="T48" s="75">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="U48" s="75">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="V48" s="75">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="70"/>
+      <c r="I49" s="70"/>
+      <c r="J49" s="71"/>
+      <c r="K49" s="72"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="74"/>
+      <c r="O49" s="70"/>
+      <c r="P49" s="71"/>
+      <c r="Q49" s="71"/>
+      <c r="R49" s="72"/>
+      <c r="S49" s="55"/>
+      <c r="T49" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="70"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="70"/>
+      <c r="F50" s="70"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
+      <c r="J50" s="71"/>
+      <c r="K50" s="72"/>
+      <c r="L50" s="55"/>
+      <c r="M50" s="73"/>
+      <c r="N50" s="74"/>
+      <c r="O50" s="70"/>
+      <c r="P50" s="71"/>
+      <c r="Q50" s="71"/>
+      <c r="R50" s="72"/>
+      <c r="S50" s="55"/>
+      <c r="T50" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="65"/>
+      <c r="I51" s="65"/>
+      <c r="J51" s="66"/>
+      <c r="K51" s="67"/>
+      <c r="L51" s="62"/>
+      <c r="M51" s="63"/>
+      <c r="N51" s="64"/>
+      <c r="O51" s="65"/>
+      <c r="P51" s="66"/>
+      <c r="Q51" s="66"/>
+      <c r="R51" s="67"/>
+      <c r="S51" s="62"/>
+      <c r="T51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="77">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>204</v>
+      </c>
+      <c r="V51" s="77">
+        <f>U51/6</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="70"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="70"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="71"/>
+      <c r="K52" s="72"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="73"/>
+      <c r="N52" s="74"/>
+      <c r="O52" s="70"/>
+      <c r="P52" s="71"/>
+      <c r="Q52" s="71"/>
+      <c r="R52" s="72"/>
+      <c r="S52" s="55"/>
+      <c r="T52" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="75">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="70">
+        <v>9</v>
+      </c>
+      <c r="D53" s="70"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="70"/>
+      <c r="H53" s="70"/>
+      <c r="I53" s="70"/>
+      <c r="J53" s="71"/>
+      <c r="K53" s="72"/>
+      <c r="L53" s="55"/>
+      <c r="M53" s="73"/>
+      <c r="N53" s="74"/>
+      <c r="O53" s="70"/>
+      <c r="P53" s="71"/>
+      <c r="Q53" s="71"/>
+      <c r="R53" s="72"/>
+      <c r="S53" s="55"/>
+      <c r="T53" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="75">
+        <f t="shared" si="10"/>
+        <v>216</v>
+      </c>
+      <c r="V53" s="75">
+        <f t="shared" si="9"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="71"/>
+      <c r="K54" s="72"/>
+      <c r="L54" s="55"/>
+      <c r="M54" s="73"/>
+      <c r="N54" s="74"/>
+      <c r="O54" s="70"/>
+      <c r="P54" s="71"/>
+      <c r="Q54" s="71"/>
+      <c r="R54" s="72"/>
+      <c r="S54" s="55"/>
+      <c r="T54" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="70"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="70"/>
+      <c r="I55" s="70"/>
+      <c r="J55" s="71"/>
+      <c r="K55" s="72"/>
+      <c r="L55" s="55"/>
+      <c r="M55" s="73"/>
+      <c r="N55" s="74"/>
+      <c r="O55" s="70"/>
+      <c r="P55" s="71"/>
+      <c r="Q55" s="71"/>
+      <c r="R55" s="72"/>
+      <c r="S55" s="55"/>
+      <c r="T55" s="75"/>
+      <c r="U55" s="75"/>
+      <c r="V55" s="75"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="70"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="70"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="71"/>
+      <c r="K56" s="72"/>
+      <c r="L56" s="55"/>
+      <c r="M56" s="73"/>
+      <c r="N56" s="74"/>
+      <c r="O56" s="70"/>
+      <c r="P56" s="71"/>
+      <c r="Q56" s="71"/>
+      <c r="R56" s="72"/>
+      <c r="S56" s="55"/>
+      <c r="T56" s="75"/>
+      <c r="U56" s="75"/>
+      <c r="V56" s="75"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="70"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="70"/>
+      <c r="I57" s="70"/>
+      <c r="J57" s="71"/>
+      <c r="K57" s="72"/>
+      <c r="L57" s="55"/>
+      <c r="M57" s="73"/>
+      <c r="N57" s="74"/>
+      <c r="O57" s="70"/>
+      <c r="P57" s="71"/>
+      <c r="Q57" s="71"/>
+      <c r="R57" s="72"/>
+      <c r="S57" s="55"/>
+      <c r="T57" s="75"/>
+      <c r="U57" s="75"/>
+      <c r="V57" s="75"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>46132</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>1193</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>92</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>423</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>36</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>61</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>12</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>433</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>28</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>549</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>3</v>
+      </c>
+      <c r="S58" s="55"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>1787</v>
+      </c>
+      <c r="U58" s="90">
+        <f>SUM(U7:U57)</f>
+        <v>353441</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>47313.083333333328</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="105" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="106"/>
+      <c r="E60" s="106"/>
+      <c r="F60" s="106"/>
+      <c r="G60" s="106"/>
+      <c r="H60" s="106"/>
+      <c r="I60" s="106"/>
+      <c r="J60" s="106"/>
+      <c r="K60" s="107"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F72DA74C-20E5-4035-B6CA-2758DFD4669B}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="9" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="108" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="108"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="109" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="111"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="112" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="118" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="101" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="116" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="117"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="100"/>
+      <c r="Q5" s="100"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="113"/>
+      <c r="U5" s="119"/>
+      <c r="V5" s="102"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="100"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="100"/>
+      <c r="Q6" s="100"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="52">
+        <v>20</v>
+      </c>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
+      <c r="J7" s="53"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
+      <c r="L7" s="55"/>
+      <c r="M7" s="56">
+        <v>1</v>
+      </c>
+      <c r="N7" s="57"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="53">
+        <v>1</v>
+      </c>
+      <c r="R7" s="54"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="58">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>9</v>
+      </c>
+      <c r="U7" s="58">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>561</v>
+      </c>
+      <c r="V7" s="58">
+        <f>U7/24</f>
+        <v>23.375</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="59">
+        <f>61+33</f>
+        <v>94</v>
+      </c>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="63"/>
+      <c r="N8" s="64"/>
+      <c r="O8" s="65"/>
+      <c r="P8" s="66"/>
+      <c r="Q8" s="66">
+        <v>2</v>
+      </c>
+      <c r="R8" s="67"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="68">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="69">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>2304</v>
+      </c>
+      <c r="V8" s="69">
+        <f>U8/24</f>
+        <v>96</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="70">
+        <f>90+49</f>
+        <v>139</v>
+      </c>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="73"/>
+      <c r="N9" s="74"/>
+      <c r="O9" s="70"/>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71"/>
+      <c r="R9" s="72"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="76">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>3336</v>
+      </c>
+      <c r="V9" s="76">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>139</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="70">
+        <f>16+7</f>
+        <v>23</v>
+      </c>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="74"/>
+      <c r="O10" s="70"/>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71"/>
+      <c r="R10" s="72"/>
+      <c r="S10" s="55"/>
+      <c r="T10" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="58">
+        <f t="shared" si="2"/>
+        <v>552</v>
+      </c>
+      <c r="V10" s="58">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="70">
+        <v>5</v>
+      </c>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
+      <c r="L11" s="55"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="55"/>
+      <c r="T11" s="58">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U11" s="58">
+        <f t="shared" si="2"/>
+        <v>122</v>
+      </c>
+      <c r="V11" s="58">
+        <f t="shared" si="3"/>
+        <v>5.083333333333333</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="59">
+        <f>720+34+1440+216+576+47</f>
+        <v>3033</v>
+      </c>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="63">
+        <v>4</v>
+      </c>
+      <c r="N12" s="64">
+        <v>12</v>
+      </c>
+      <c r="O12" s="65">
+        <v>15</v>
+      </c>
+      <c r="P12" s="66"/>
+      <c r="Q12" s="66">
+        <v>20</v>
+      </c>
+      <c r="R12" s="67">
+        <v>12</v>
+      </c>
+      <c r="S12" s="62"/>
+      <c r="T12" s="69">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="U12" s="69">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>73752</v>
+      </c>
+      <c r="V12" s="69">
+        <f>U12/24</f>
+        <v>3073</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
+      <c r="I13" s="70"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="55"/>
+      <c r="T13" s="76">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="U13" s="76">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>64</v>
+      </c>
+      <c r="V13" s="76">
+        <f>U13/24</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="70">
+        <v>4</v>
+      </c>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="55"/>
+      <c r="T14" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="75">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>96</v>
+      </c>
+      <c r="V14" s="75">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>4</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="55"/>
+      <c r="T15" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="55"/>
+      <c r="T16" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I17" s="70"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U17" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V17" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="55"/>
+      <c r="T18" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="70">
+        <v>2</v>
+      </c>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70">
+        <f>24+20</f>
+        <v>44</v>
+      </c>
+      <c r="I19" s="70"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="55"/>
+      <c r="T19" s="58">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="U19" s="75">
+        <f t="shared" si="4"/>
+        <v>92</v>
+      </c>
+      <c r="V19" s="75">
+        <f t="shared" si="5"/>
+        <v>3.8333333333333335</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="74"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="55"/>
+      <c r="T20" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V20" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70">
+        <f>2*24</f>
+        <v>48</v>
+      </c>
+      <c r="I21" s="70"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="58">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="U21" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V21" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="70"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
+      <c r="J22" s="71"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="55"/>
+      <c r="T22" s="58">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U22" s="75">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="V22" s="75">
+        <f t="shared" si="5"/>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70">
+        <f>24*37+19</f>
+        <v>907</v>
+      </c>
+      <c r="I23" s="70"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="74"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="55"/>
+      <c r="T23" s="58">
+        <f t="shared" si="0"/>
+        <v>907</v>
+      </c>
+      <c r="U23" s="75">
+        <f t="shared" si="4"/>
+        <v>907</v>
+      </c>
+      <c r="V23" s="75">
+        <f t="shared" si="5"/>
+        <v>37.791666666666664</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="70">
+        <v>5</v>
+      </c>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70">
+        <f>24*3</f>
+        <v>72</v>
+      </c>
+      <c r="I24" s="70"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="55"/>
+      <c r="T24" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U24" s="75">
+        <f t="shared" si="4"/>
+        <v>192</v>
+      </c>
+      <c r="V24" s="75">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="70">
+        <f>63+59</f>
+        <v>122</v>
+      </c>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70">
+        <v>1</v>
+      </c>
+      <c r="J25" s="71"/>
+      <c r="K25" s="72"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="73">
+        <v>1</v>
+      </c>
+      <c r="N25" s="74"/>
+      <c r="O25" s="70"/>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71">
+        <v>2</v>
+      </c>
+      <c r="R25" s="72"/>
+      <c r="S25" s="55"/>
+      <c r="T25" s="58">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="U25" s="75">
+        <f t="shared" si="4"/>
+        <v>3001</v>
+      </c>
+      <c r="V25" s="75">
+        <f t="shared" si="5"/>
+        <v>125.04166666666667</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="74"/>
+      <c r="O26" s="70"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="71"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="55"/>
+      <c r="T26" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="70"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="70"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="55"/>
+      <c r="T27" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="70">
+        <v>40</v>
+      </c>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="73">
+        <v>1</v>
+      </c>
+      <c r="N28" s="74"/>
+      <c r="O28" s="70">
+        <v>2</v>
+      </c>
+      <c r="P28" s="71"/>
+      <c r="Q28" s="71">
+        <v>5</v>
+      </c>
+      <c r="R28" s="72"/>
+      <c r="S28" s="55"/>
+      <c r="T28" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="75">
+        <f t="shared" si="4"/>
+        <v>1152</v>
+      </c>
+      <c r="V28" s="75">
+        <f t="shared" si="5"/>
+        <v>48</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="70">
+        <v>51</v>
+      </c>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70">
+        <v>5</v>
+      </c>
+      <c r="J29" s="71"/>
+      <c r="K29" s="72"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="73">
+        <v>1</v>
+      </c>
+      <c r="N29" s="74"/>
+      <c r="O29" s="70">
+        <v>1</v>
+      </c>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71"/>
+      <c r="R29" s="72"/>
+      <c r="S29" s="55"/>
+      <c r="T29" s="58">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U29" s="75">
+        <f t="shared" si="4"/>
+        <v>1277</v>
+      </c>
+      <c r="V29" s="75">
+        <f t="shared" si="5"/>
+        <v>53.208333333333336</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="70">
+        <v>12</v>
+      </c>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="74"/>
+      <c r="O30" s="70"/>
+      <c r="P30" s="71"/>
+      <c r="Q30" s="71"/>
+      <c r="R30" s="72"/>
+      <c r="S30" s="55"/>
+      <c r="T30" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="75">
+        <f t="shared" si="4"/>
+        <v>288</v>
+      </c>
+      <c r="V30" s="75">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="70"/>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="70">
+        <v>4</v>
+      </c>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="74"/>
+      <c r="O32" s="70"/>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="55"/>
+      <c r="T32" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="75">
+        <f t="shared" si="4"/>
+        <v>96</v>
+      </c>
+      <c r="V32" s="75">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="70"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="73"/>
+      <c r="N33" s="74"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="55"/>
+      <c r="T33" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="70">
+        <f>65+1</f>
+        <v>66</v>
+      </c>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
+      <c r="J34" s="71"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
+      <c r="L34" s="55"/>
+      <c r="M34" s="73">
+        <v>2</v>
+      </c>
+      <c r="N34" s="74"/>
+      <c r="O34" s="70">
+        <v>1</v>
+      </c>
+      <c r="P34" s="71">
+        <v>12</v>
+      </c>
+      <c r="Q34" s="71">
+        <v>5</v>
+      </c>
+      <c r="R34" s="72"/>
+      <c r="S34" s="55"/>
+      <c r="T34" s="58">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="U34" s="75">
+        <f t="shared" si="4"/>
+        <v>1790</v>
+      </c>
+      <c r="V34" s="75">
+        <f t="shared" si="5"/>
+        <v>74.583333333333329</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="72"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="74"/>
+      <c r="O35" s="70"/>
+      <c r="P35" s="71"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="72"/>
+      <c r="S35" s="55"/>
+      <c r="T35" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="73"/>
+      <c r="N36" s="74"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="71"/>
+      <c r="Q36" s="71"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="55"/>
+      <c r="T36" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="59">
+        <f>864+3024+82</f>
+        <v>3970</v>
+      </c>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59"/>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>2</v>
+      </c>
+      <c r="K37" s="61">
+        <v>3</v>
+      </c>
+      <c r="L37" s="62"/>
+      <c r="M37" s="63">
+        <v>10</v>
+      </c>
+      <c r="N37" s="64"/>
+      <c r="O37" s="65">
+        <v>50</v>
+      </c>
+      <c r="P37" s="66"/>
+      <c r="Q37" s="66">
+        <v>77</v>
+      </c>
+      <c r="R37" s="67"/>
+      <c r="S37" s="62"/>
+      <c r="T37" s="77">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="U37" s="77">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>24649</v>
+      </c>
+      <c r="V37" s="77">
+        <f>U37/6</f>
+        <v>4108.166666666667</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="73"/>
+      <c r="N38" s="74"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="71"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="55"/>
+      <c r="T38" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="75">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="75">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="74"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="71"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="95"/>
+      <c r="T39" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U39" s="75">
+        <f>C39*24+M39*24+O39*24+Q39*24+T39</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="75">
+        <f>U39/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="59">
+        <v>23</v>
+      </c>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
+      <c r="L40" s="62"/>
+      <c r="M40" s="63">
+        <v>1</v>
+      </c>
+      <c r="N40" s="64"/>
+      <c r="O40" s="65">
+        <v>1</v>
+      </c>
+      <c r="P40" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q40" s="66">
+        <v>2</v>
+      </c>
+      <c r="R40" s="67"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="77">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="U40" s="77">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>680</v>
+      </c>
+      <c r="V40" s="77">
+        <f>U40/24</f>
+        <v>28.333333333333332</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="82">
+        <f>96+17</f>
+        <v>113</v>
+      </c>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="85"/>
+      <c r="M41" s="86">
+        <v>8</v>
+      </c>
+      <c r="N41" s="87"/>
+      <c r="O41" s="82">
+        <v>8</v>
+      </c>
+      <c r="P41" s="83"/>
+      <c r="Q41" s="83">
+        <v>16</v>
+      </c>
+      <c r="R41" s="84"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="88">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>1740</v>
+      </c>
+      <c r="V41" s="88">
+        <f>U41/12</f>
+        <v>145</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="71"/>
+      <c r="K42" s="72"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="73"/>
+      <c r="N42" s="74"/>
+      <c r="O42" s="70"/>
+      <c r="P42" s="71"/>
+      <c r="Q42" s="71"/>
+      <c r="R42" s="72"/>
+      <c r="S42" s="55"/>
+      <c r="T42" s="75"/>
+      <c r="U42" s="75"/>
+      <c r="V42" s="75"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="65">
+        <f>7776+864+52+3024+8424+5508+3024+5832</f>
+        <v>34504</v>
+      </c>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65"/>
+      <c r="I43" s="65">
+        <v>7</v>
+      </c>
+      <c r="J43" s="66">
+        <f>10*6+1</f>
+        <v>61</v>
+      </c>
+      <c r="K43" s="67">
+        <f>69*6+7</f>
+        <v>421</v>
+      </c>
+      <c r="L43" s="62"/>
+      <c r="M43" s="63">
+        <v>29</v>
+      </c>
+      <c r="N43" s="64"/>
+      <c r="O43" s="65">
+        <v>482</v>
+      </c>
+      <c r="P43" s="66"/>
+      <c r="Q43" s="66">
+        <v>477</v>
+      </c>
+      <c r="R43" s="67"/>
+      <c r="S43" s="62"/>
+      <c r="T43" s="77">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>489</v>
+      </c>
+      <c r="U43" s="77">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>213441</v>
+      </c>
+      <c r="V43" s="77">
+        <f>U43/6</f>
+        <v>35573.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="70"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="71"/>
+      <c r="K44" s="72"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="73"/>
+      <c r="N44" s="74"/>
+      <c r="O44" s="70"/>
+      <c r="P44" s="71"/>
+      <c r="Q44" s="71"/>
+      <c r="R44" s="72"/>
+      <c r="S44" s="55"/>
+      <c r="T44" s="75"/>
+      <c r="U44" s="75"/>
+      <c r="V44" s="75"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="70"/>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="70"/>
+      <c r="I45" s="70"/>
+      <c r="J45" s="71"/>
+      <c r="K45" s="72"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="73"/>
+      <c r="N45" s="74"/>
+      <c r="O45" s="70"/>
+      <c r="P45" s="71"/>
+      <c r="Q45" s="71"/>
+      <c r="R45" s="72"/>
+      <c r="S45" s="55"/>
+      <c r="T45" s="75">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="75">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="75">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="73"/>
+      <c r="N46" s="74"/>
+      <c r="O46" s="70"/>
+      <c r="P46" s="71"/>
+      <c r="Q46" s="71"/>
+      <c r="R46" s="72"/>
+      <c r="S46" s="55"/>
+      <c r="T46" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="75">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="75">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="65">
+        <f>14+432+106+2160+71</f>
+        <v>2783</v>
+      </c>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
+      <c r="I47" s="65"/>
+      <c r="J47" s="66">
+        <v>1</v>
+      </c>
+      <c r="K47" s="67">
+        <v>4</v>
+      </c>
+      <c r="L47" s="62"/>
+      <c r="M47" s="63">
+        <v>3</v>
+      </c>
+      <c r="N47" s="64"/>
+      <c r="O47" s="65">
+        <v>5</v>
+      </c>
+      <c r="P47" s="66">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="66">
+        <v>2</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
+      <c r="S47" s="62"/>
+      <c r="T47" s="77">
+        <f t="shared" si="7"/>
+        <v>13</v>
+      </c>
+      <c r="U47" s="77">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>16771</v>
+      </c>
+      <c r="V47" s="77">
+        <f>U47/6</f>
+        <v>2795.1666666666665</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
+      <c r="I48" s="70"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="72"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="73"/>
+      <c r="N48" s="74"/>
+      <c r="O48" s="70"/>
+      <c r="P48" s="71"/>
+      <c r="Q48" s="71"/>
+      <c r="R48" s="72"/>
+      <c r="S48" s="55"/>
+      <c r="T48" s="75">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="U48" s="75">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="V48" s="75">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="70"/>
+      <c r="I49" s="70"/>
+      <c r="J49" s="71"/>
+      <c r="K49" s="72"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="74"/>
+      <c r="O49" s="70"/>
+      <c r="P49" s="71"/>
+      <c r="Q49" s="71"/>
+      <c r="R49" s="72"/>
+      <c r="S49" s="55"/>
+      <c r="T49" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="70"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="70"/>
+      <c r="F50" s="70"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
+      <c r="J50" s="71"/>
+      <c r="K50" s="72"/>
+      <c r="L50" s="55"/>
+      <c r="M50" s="73"/>
+      <c r="N50" s="74"/>
+      <c r="O50" s="70"/>
+      <c r="P50" s="71"/>
+      <c r="Q50" s="71"/>
+      <c r="R50" s="72"/>
+      <c r="S50" s="55"/>
+      <c r="T50" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="65"/>
+      <c r="I51" s="65"/>
+      <c r="J51" s="66"/>
+      <c r="K51" s="67"/>
+      <c r="L51" s="62"/>
+      <c r="M51" s="63"/>
+      <c r="N51" s="64"/>
+      <c r="O51" s="65"/>
+      <c r="P51" s="66"/>
+      <c r="Q51" s="66"/>
+      <c r="R51" s="67"/>
+      <c r="S51" s="62"/>
+      <c r="T51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="77">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>204</v>
+      </c>
+      <c r="V51" s="77">
+        <f>U51/6</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="70"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="70"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="71"/>
+      <c r="K52" s="72"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="73"/>
+      <c r="N52" s="74"/>
+      <c r="O52" s="70"/>
+      <c r="P52" s="71"/>
+      <c r="Q52" s="71"/>
+      <c r="R52" s="72"/>
+      <c r="S52" s="55"/>
+      <c r="T52" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="75">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="70">
+        <v>9</v>
+      </c>
+      <c r="D53" s="70"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="70"/>
+      <c r="H53" s="70"/>
+      <c r="I53" s="70"/>
+      <c r="J53" s="71"/>
+      <c r="K53" s="72"/>
+      <c r="L53" s="55"/>
+      <c r="M53" s="73"/>
+      <c r="N53" s="74"/>
+      <c r="O53" s="70"/>
+      <c r="P53" s="71"/>
+      <c r="Q53" s="71"/>
+      <c r="R53" s="72"/>
+      <c r="S53" s="55"/>
+      <c r="T53" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="75">
+        <f t="shared" si="10"/>
+        <v>216</v>
+      </c>
+      <c r="V53" s="75">
+        <f t="shared" si="9"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="71"/>
+      <c r="K54" s="72"/>
+      <c r="L54" s="55"/>
+      <c r="M54" s="73"/>
+      <c r="N54" s="74"/>
+      <c r="O54" s="70"/>
+      <c r="P54" s="71"/>
+      <c r="Q54" s="71"/>
+      <c r="R54" s="72"/>
+      <c r="S54" s="55"/>
+      <c r="T54" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="70"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="70"/>
+      <c r="I55" s="70"/>
+      <c r="J55" s="71"/>
+      <c r="K55" s="72"/>
+      <c r="L55" s="55"/>
+      <c r="M55" s="73"/>
+      <c r="N55" s="74"/>
+      <c r="O55" s="70"/>
+      <c r="P55" s="71"/>
+      <c r="Q55" s="71"/>
+      <c r="R55" s="72"/>
+      <c r="S55" s="55"/>
+      <c r="T55" s="75"/>
+      <c r="U55" s="75"/>
+      <c r="V55" s="75"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="70"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="70"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="71"/>
+      <c r="K56" s="72"/>
+      <c r="L56" s="55"/>
+      <c r="M56" s="73"/>
+      <c r="N56" s="74"/>
+      <c r="O56" s="70"/>
+      <c r="P56" s="71"/>
+      <c r="Q56" s="71"/>
+      <c r="R56" s="72"/>
+      <c r="S56" s="55"/>
+      <c r="T56" s="75"/>
+      <c r="U56" s="75"/>
+      <c r="V56" s="75"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="70"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="70"/>
+      <c r="I57" s="70"/>
+      <c r="J57" s="71"/>
+      <c r="K57" s="72"/>
+      <c r="L57" s="55"/>
+      <c r="M57" s="73"/>
+      <c r="N57" s="74"/>
+      <c r="O57" s="70"/>
+      <c r="P57" s="71"/>
+      <c r="Q57" s="71"/>
+      <c r="R57" s="72"/>
+      <c r="S57" s="55"/>
+      <c r="T57" s="75"/>
+      <c r="U57" s="75"/>
+      <c r="V57" s="75"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>45063</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>1184</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>39</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>64</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>457</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>61</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>12</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>566</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>28</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>609</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>15</v>
+      </c>
+      <c r="S58" s="55"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>1799</v>
+      </c>
+      <c r="U58" s="90">
+        <f>SUM(U7:U57)</f>
+        <v>347567</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>46437.583333333328</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="105" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="106"/>
+      <c r="E60" s="106"/>
+      <c r="F60" s="106"/>
+      <c r="G60" s="106"/>
+      <c r="H60" s="106"/>
+      <c r="I60" s="106"/>
+      <c r="J60" s="106"/>
+      <c r="K60" s="107"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
 </file>
--- a/GBDS JUNE FILES 2026/INVENTORY COUNT SHEET - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/INVENTORY COUNT SHEET - JUNE 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7386F9DA-E4E5-4048-9FB4-B93FC7F43B58}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{450606C5-1988-49D4-868B-0D788EA4B013}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="06-04-2026 " sheetId="58" r:id="rId5"/>
     <sheet name="06-05-2026 " sheetId="59" r:id="rId6"/>
     <sheet name="06-08-2026 " sheetId="60" r:id="rId7"/>
+    <sheet name="06-09-2026" sheetId="61" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'06-01-2026'!$A$1:$W$59</definedName>
@@ -28,6 +29,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="4">'06-04-2026 '!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'06-05-2026 '!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'06-08-2026 '!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'06-09-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -46,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="74">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -1255,7 +1257,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1541,6 +1543,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1969,21 +1974,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="108" t="s">
+      <c r="I1" s="109" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="108"/>
-      <c r="T1" s="108"/>
-      <c r="U1" s="108"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -1995,17 +2000,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="109" t="s">
+      <c r="C4" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="111"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="112"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -2025,13 +2030,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="112" t="s">
+      <c r="T4" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="114" t="s">
+      <c r="U4" s="115" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="101" t="s">
+      <c r="V4" s="102" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2071,10 +2076,10 @@
       <c r="I5" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="103" t="s">
+      <c r="J5" s="104" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="104"/>
+      <c r="K5" s="105"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2082,9 +2087,9 @@
       <c r="Q5" s="89"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="113"/>
-      <c r="U5" s="115"/>
-      <c r="V5" s="102"/>
+      <c r="T5" s="114"/>
+      <c r="U5" s="116"/>
+      <c r="V5" s="103"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -4615,17 +4620,17 @@
       <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="105" t="s">
+      <c r="C62" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="106"/>
-      <c r="E62" s="106"/>
-      <c r="F62" s="106"/>
-      <c r="G62" s="106"/>
-      <c r="H62" s="106"/>
-      <c r="I62" s="106"/>
-      <c r="J62" s="106"/>
-      <c r="K62" s="107"/>
+      <c r="D62" s="107"/>
+      <c r="E62" s="107"/>
+      <c r="F62" s="107"/>
+      <c r="G62" s="107"/>
+      <c r="H62" s="107"/>
+      <c r="I62" s="107"/>
+      <c r="J62" s="107"/>
+      <c r="K62" s="108"/>
       <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
@@ -4934,21 +4939,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="108" t="s">
+      <c r="I1" s="109" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="108"/>
-      <c r="T1" s="108"/>
-      <c r="U1" s="108"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -4960,17 +4965,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="109" t="s">
+      <c r="C4" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="111"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="112"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -4990,13 +4995,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="112" t="s">
+      <c r="T4" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="118" t="s">
+      <c r="U4" s="119" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="101" t="s">
+      <c r="V4" s="102" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -5036,10 +5041,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="116" t="s">
+      <c r="J5" s="117" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="117"/>
+      <c r="K5" s="118"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -5047,9 +5052,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="113"/>
-      <c r="U5" s="119"/>
-      <c r="V5" s="102"/>
+      <c r="T5" s="114"/>
+      <c r="U5" s="120"/>
+      <c r="V5" s="103"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -7761,17 +7766,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="105" t="s">
+      <c r="C60" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="106"/>
-      <c r="E60" s="106"/>
-      <c r="F60" s="106"/>
-      <c r="G60" s="106"/>
-      <c r="H60" s="106"/>
-      <c r="I60" s="106"/>
-      <c r="J60" s="106"/>
-      <c r="K60" s="107"/>
+      <c r="D60" s="107"/>
+      <c r="E60" s="107"/>
+      <c r="F60" s="107"/>
+      <c r="G60" s="107"/>
+      <c r="H60" s="107"/>
+      <c r="I60" s="107"/>
+      <c r="J60" s="107"/>
+      <c r="K60" s="108"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -8080,21 +8085,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="108" t="s">
+      <c r="I1" s="109" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="108"/>
-      <c r="T1" s="108"/>
-      <c r="U1" s="108"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -8106,17 +8111,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="109" t="s">
+      <c r="C4" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="111"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="112"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -8136,13 +8141,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="112" t="s">
+      <c r="T4" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="118" t="s">
+      <c r="U4" s="119" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="101" t="s">
+      <c r="V4" s="102" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -8182,10 +8187,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="116" t="s">
+      <c r="J5" s="117" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="117"/>
+      <c r="K5" s="118"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -8193,9 +8198,9 @@
       <c r="Q5" s="96"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="113"/>
-      <c r="U5" s="119"/>
-      <c r="V5" s="102"/>
+      <c r="T5" s="114"/>
+      <c r="U5" s="120"/>
+      <c r="V5" s="103"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -10930,17 +10935,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="105" t="s">
+      <c r="C60" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="106"/>
-      <c r="E60" s="106"/>
-      <c r="F60" s="106"/>
-      <c r="G60" s="106"/>
-      <c r="H60" s="106"/>
-      <c r="I60" s="106"/>
-      <c r="J60" s="106"/>
-      <c r="K60" s="107"/>
+      <c r="D60" s="107"/>
+      <c r="E60" s="107"/>
+      <c r="F60" s="107"/>
+      <c r="G60" s="107"/>
+      <c r="H60" s="107"/>
+      <c r="I60" s="107"/>
+      <c r="J60" s="107"/>
+      <c r="K60" s="108"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -11249,21 +11254,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="108" t="s">
+      <c r="I1" s="109" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="108"/>
-      <c r="T1" s="108"/>
-      <c r="U1" s="108"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -11275,17 +11280,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="109" t="s">
+      <c r="C4" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="111"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="112"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -11305,13 +11310,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="112" t="s">
+      <c r="T4" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="118" t="s">
+      <c r="U4" s="119" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="101" t="s">
+      <c r="V4" s="102" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -11351,10 +11356,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="116" t="s">
+      <c r="J5" s="117" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="117"/>
+      <c r="K5" s="118"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -11362,9 +11367,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="113"/>
-      <c r="U5" s="119"/>
-      <c r="V5" s="102"/>
+      <c r="T5" s="114"/>
+      <c r="U5" s="120"/>
+      <c r="V5" s="103"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -14059,17 +14064,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="105" t="s">
+      <c r="C60" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="106"/>
-      <c r="E60" s="106"/>
-      <c r="F60" s="106"/>
-      <c r="G60" s="106"/>
-      <c r="H60" s="106"/>
-      <c r="I60" s="106"/>
-      <c r="J60" s="106"/>
-      <c r="K60" s="107"/>
+      <c r="D60" s="107"/>
+      <c r="E60" s="107"/>
+      <c r="F60" s="107"/>
+      <c r="G60" s="107"/>
+      <c r="H60" s="107"/>
+      <c r="I60" s="107"/>
+      <c r="J60" s="107"/>
+      <c r="K60" s="108"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -14378,21 +14383,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="108" t="s">
+      <c r="I1" s="109" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="108"/>
-      <c r="T1" s="108"/>
-      <c r="U1" s="108"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -14404,17 +14409,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="109" t="s">
+      <c r="C4" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="111"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="112"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -14434,13 +14439,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="112" t="s">
+      <c r="T4" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="118" t="s">
+      <c r="U4" s="119" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="101" t="s">
+      <c r="V4" s="102" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -14480,10 +14485,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="116" t="s">
+      <c r="J5" s="117" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="117"/>
+      <c r="K5" s="118"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -14491,9 +14496,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="113"/>
-      <c r="U5" s="119"/>
-      <c r="V5" s="102"/>
+      <c r="T5" s="114"/>
+      <c r="U5" s="120"/>
+      <c r="V5" s="103"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -17193,17 +17198,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="105" t="s">
+      <c r="C60" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="106"/>
-      <c r="E60" s="106"/>
-      <c r="F60" s="106"/>
-      <c r="G60" s="106"/>
-      <c r="H60" s="106"/>
-      <c r="I60" s="106"/>
-      <c r="J60" s="106"/>
-      <c r="K60" s="107"/>
+      <c r="D60" s="107"/>
+      <c r="E60" s="107"/>
+      <c r="F60" s="107"/>
+      <c r="G60" s="107"/>
+      <c r="H60" s="107"/>
+      <c r="I60" s="107"/>
+      <c r="J60" s="107"/>
+      <c r="K60" s="108"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -17512,21 +17517,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="108" t="s">
+      <c r="I1" s="109" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="108"/>
-      <c r="T1" s="108"/>
-      <c r="U1" s="108"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -17538,17 +17543,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="109" t="s">
+      <c r="C4" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="111"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="112"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -17568,13 +17573,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="112" t="s">
+      <c r="T4" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="118" t="s">
+      <c r="U4" s="119" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="101" t="s">
+      <c r="V4" s="102" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -17614,10 +17619,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="116" t="s">
+      <c r="J5" s="117" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="117"/>
+      <c r="K5" s="118"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -17625,9 +17630,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="113"/>
-      <c r="U5" s="119"/>
-      <c r="V5" s="102"/>
+      <c r="T5" s="114"/>
+      <c r="U5" s="120"/>
+      <c r="V5" s="103"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -20321,17 +20326,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="105" t="s">
+      <c r="C60" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="106"/>
-      <c r="E60" s="106"/>
-      <c r="F60" s="106"/>
-      <c r="G60" s="106"/>
-      <c r="H60" s="106"/>
-      <c r="I60" s="106"/>
-      <c r="J60" s="106"/>
-      <c r="K60" s="107"/>
+      <c r="D60" s="107"/>
+      <c r="E60" s="107"/>
+      <c r="F60" s="107"/>
+      <c r="G60" s="107"/>
+      <c r="H60" s="107"/>
+      <c r="I60" s="107"/>
+      <c r="J60" s="107"/>
+      <c r="K60" s="108"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -20640,21 +20645,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="108" t="s">
+      <c r="I1" s="109" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="108"/>
-      <c r="T1" s="108"/>
-      <c r="U1" s="108"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -20666,17 +20671,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="109" t="s">
+      <c r="C4" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="111"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="112"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -20696,13 +20701,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="112" t="s">
+      <c r="T4" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="118" t="s">
+      <c r="U4" s="119" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="101" t="s">
+      <c r="V4" s="102" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -20742,10 +20747,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="116" t="s">
+      <c r="J5" s="117" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="117"/>
+      <c r="K5" s="118"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -20753,9 +20758,9 @@
       <c r="Q5" s="100"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="113"/>
-      <c r="U5" s="119"/>
-      <c r="V5" s="102"/>
+      <c r="T5" s="114"/>
+      <c r="U5" s="120"/>
+      <c r="V5" s="103"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -23451,17 +23456,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="105" t="s">
+      <c r="C60" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="106"/>
-      <c r="E60" s="106"/>
-      <c r="F60" s="106"/>
-      <c r="G60" s="106"/>
-      <c r="H60" s="106"/>
-      <c r="I60" s="106"/>
-      <c r="J60" s="106"/>
-      <c r="K60" s="107"/>
+      <c r="D60" s="107"/>
+      <c r="E60" s="107"/>
+      <c r="F60" s="107"/>
+      <c r="G60" s="107"/>
+      <c r="H60" s="107"/>
+      <c r="I60" s="107"/>
+      <c r="J60" s="107"/>
+      <c r="K60" s="108"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -23713,13 +23718,3148 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87BC2308-B0E6-4A75-AB2A-FD7C2169E77B}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="9" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="109" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="110" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="112"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="113" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="119" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="102" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="117" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="118"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="101"/>
+      <c r="Q5" s="101"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="114"/>
+      <c r="U5" s="120"/>
+      <c r="V5" s="103"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="101"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="101"/>
+      <c r="Q6" s="101"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="52">
+        <v>20</v>
+      </c>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
+      <c r="J7" s="53"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
+      <c r="L7" s="55"/>
+      <c r="M7" s="56">
+        <v>1</v>
+      </c>
+      <c r="N7" s="57"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="53">
+        <v>1</v>
+      </c>
+      <c r="R7" s="54"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="58">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>9</v>
+      </c>
+      <c r="U7" s="58">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>561</v>
+      </c>
+      <c r="V7" s="58">
+        <f>U7/24</f>
+        <v>23.375</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="59">
+        <f>61+33</f>
+        <v>94</v>
+      </c>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="63"/>
+      <c r="N8" s="64"/>
+      <c r="O8" s="65"/>
+      <c r="P8" s="66"/>
+      <c r="Q8" s="66">
+        <v>2</v>
+      </c>
+      <c r="R8" s="67"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="68">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="69">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>2304</v>
+      </c>
+      <c r="V8" s="69">
+        <f>U8/24</f>
+        <v>96</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="70">
+        <f>90+47</f>
+        <v>137</v>
+      </c>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="73">
+        <v>2</v>
+      </c>
+      <c r="N9" s="74"/>
+      <c r="O9" s="70"/>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71"/>
+      <c r="R9" s="72"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="76">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>3336</v>
+      </c>
+      <c r="V9" s="76">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>139</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="70">
+        <v>21</v>
+      </c>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="73">
+        <v>2</v>
+      </c>
+      <c r="N10" s="74"/>
+      <c r="O10" s="70"/>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71"/>
+      <c r="R10" s="72"/>
+      <c r="S10" s="55"/>
+      <c r="T10" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="58">
+        <f t="shared" si="2"/>
+        <v>552</v>
+      </c>
+      <c r="V10" s="58">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="70">
+        <v>5</v>
+      </c>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
+      <c r="L11" s="55"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="55"/>
+      <c r="T11" s="58">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U11" s="58">
+        <f t="shared" si="2"/>
+        <v>122</v>
+      </c>
+      <c r="V11" s="58">
+        <f t="shared" si="3"/>
+        <v>5.083333333333333</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="59">
+        <f>720+34+1440+216+576+19</f>
+        <v>3005</v>
+      </c>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="63">
+        <v>9</v>
+      </c>
+      <c r="N12" s="64">
+        <v>12</v>
+      </c>
+      <c r="O12" s="65">
+        <v>13</v>
+      </c>
+      <c r="P12" s="66"/>
+      <c r="Q12" s="66">
+        <v>20</v>
+      </c>
+      <c r="R12" s="67"/>
+      <c r="S12" s="62"/>
+      <c r="T12" s="69">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="U12" s="69">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>73140</v>
+      </c>
+      <c r="V12" s="69">
+        <f>U12/24</f>
+        <v>3047.5</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
+      <c r="I13" s="70"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="55"/>
+      <c r="T13" s="76">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="U13" s="76">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>64</v>
+      </c>
+      <c r="V13" s="76">
+        <f>U13/24</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="70">
+        <v>4</v>
+      </c>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="55"/>
+      <c r="T14" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="75">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>96</v>
+      </c>
+      <c r="V14" s="75">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>4</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="55"/>
+      <c r="T15" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="55"/>
+      <c r="T16" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I17" s="70"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U17" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V17" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="55"/>
+      <c r="T18" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="70">
+        <v>2</v>
+      </c>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70">
+        <f>24+20</f>
+        <v>44</v>
+      </c>
+      <c r="I19" s="70"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="55"/>
+      <c r="T19" s="58">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="U19" s="75">
+        <f t="shared" si="4"/>
+        <v>92</v>
+      </c>
+      <c r="V19" s="75">
+        <f t="shared" si="5"/>
+        <v>3.8333333333333335</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="74"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="55"/>
+      <c r="T20" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V20" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70">
+        <f>24*2</f>
+        <v>48</v>
+      </c>
+      <c r="I21" s="70"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="58">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="U21" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V21" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="70"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
+      <c r="J22" s="71"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="55"/>
+      <c r="T22" s="58">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U22" s="75">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="V22" s="75">
+        <f t="shared" si="5"/>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
+      <c r="I23" s="70"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="74"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="55"/>
+      <c r="T23" s="58">
+        <f t="shared" si="0"/>
+        <v>907</v>
+      </c>
+      <c r="U23" s="75">
+        <f t="shared" si="4"/>
+        <v>907</v>
+      </c>
+      <c r="V23" s="75">
+        <f t="shared" si="5"/>
+        <v>37.791666666666664</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="70">
+        <v>5</v>
+      </c>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70">
+        <f>24*3</f>
+        <v>72</v>
+      </c>
+      <c r="I24" s="70"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="55"/>
+      <c r="T24" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U24" s="75">
+        <f t="shared" si="4"/>
+        <v>192</v>
+      </c>
+      <c r="V24" s="75">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="70">
+        <f>63+59</f>
+        <v>122</v>
+      </c>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70">
+        <v>1</v>
+      </c>
+      <c r="J25" s="71"/>
+      <c r="K25" s="72"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="73">
+        <v>1</v>
+      </c>
+      <c r="N25" s="74"/>
+      <c r="O25" s="70"/>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71">
+        <v>1</v>
+      </c>
+      <c r="R25" s="72"/>
+      <c r="S25" s="55"/>
+      <c r="T25" s="58">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="U25" s="75">
+        <f t="shared" si="4"/>
+        <v>2977</v>
+      </c>
+      <c r="V25" s="75">
+        <f t="shared" si="5"/>
+        <v>124.04166666666667</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="74"/>
+      <c r="O26" s="70"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="71"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="55"/>
+      <c r="T26" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="70"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="70"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="55"/>
+      <c r="T27" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="70">
+        <v>33</v>
+      </c>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="73">
+        <v>1</v>
+      </c>
+      <c r="N28" s="74"/>
+      <c r="O28" s="70">
+        <v>2</v>
+      </c>
+      <c r="P28" s="71"/>
+      <c r="Q28" s="71">
+        <v>7</v>
+      </c>
+      <c r="R28" s="72"/>
+      <c r="S28" s="55"/>
+      <c r="T28" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="75">
+        <f t="shared" si="4"/>
+        <v>1032</v>
+      </c>
+      <c r="V28" s="75">
+        <f t="shared" si="5"/>
+        <v>43</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="70">
+        <v>49</v>
+      </c>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70">
+        <v>5</v>
+      </c>
+      <c r="J29" s="71"/>
+      <c r="K29" s="72"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="73">
+        <v>1</v>
+      </c>
+      <c r="N29" s="74"/>
+      <c r="O29" s="70">
+        <v>1</v>
+      </c>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71">
+        <v>2</v>
+      </c>
+      <c r="R29" s="72"/>
+      <c r="S29" s="55"/>
+      <c r="T29" s="58">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U29" s="75">
+        <f t="shared" si="4"/>
+        <v>1277</v>
+      </c>
+      <c r="V29" s="75">
+        <f t="shared" si="5"/>
+        <v>53.208333333333336</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="70">
+        <v>11</v>
+      </c>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="74"/>
+      <c r="O30" s="70"/>
+      <c r="P30" s="71"/>
+      <c r="Q30" s="71">
+        <v>1</v>
+      </c>
+      <c r="R30" s="72"/>
+      <c r="S30" s="55"/>
+      <c r="T30" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="75">
+        <f t="shared" si="4"/>
+        <v>288</v>
+      </c>
+      <c r="V30" s="75">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="70"/>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="70">
+        <v>4</v>
+      </c>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="74"/>
+      <c r="O32" s="70"/>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="55"/>
+      <c r="T32" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="75">
+        <f t="shared" si="4"/>
+        <v>96</v>
+      </c>
+      <c r="V32" s="75">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="70"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="73"/>
+      <c r="N33" s="74"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="55"/>
+      <c r="T33" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="70">
+        <v>66</v>
+      </c>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
+      <c r="J34" s="71"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
+      <c r="L34" s="55"/>
+      <c r="M34" s="73">
+        <v>2</v>
+      </c>
+      <c r="N34" s="74"/>
+      <c r="O34" s="70">
+        <v>1</v>
+      </c>
+      <c r="P34" s="71">
+        <v>12</v>
+      </c>
+      <c r="Q34" s="71">
+        <v>5</v>
+      </c>
+      <c r="R34" s="72"/>
+      <c r="S34" s="55"/>
+      <c r="T34" s="58">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="U34" s="75">
+        <f t="shared" si="4"/>
+        <v>1790</v>
+      </c>
+      <c r="V34" s="75">
+        <f t="shared" si="5"/>
+        <v>74.583333333333329</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="72"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="74"/>
+      <c r="O35" s="70"/>
+      <c r="P35" s="71"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="72"/>
+      <c r="S35" s="55"/>
+      <c r="T35" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="73"/>
+      <c r="N36" s="74"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="71"/>
+      <c r="Q36" s="71"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="55"/>
+      <c r="T36" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="59">
+        <f>864+2916+58</f>
+        <v>3838</v>
+      </c>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59"/>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>2</v>
+      </c>
+      <c r="K37" s="61">
+        <v>3</v>
+      </c>
+      <c r="L37" s="62"/>
+      <c r="M37" s="63">
+        <v>21</v>
+      </c>
+      <c r="N37" s="64"/>
+      <c r="O37" s="65">
+        <v>30</v>
+      </c>
+      <c r="P37" s="66"/>
+      <c r="Q37" s="66">
+        <v>109</v>
+      </c>
+      <c r="R37" s="67"/>
+      <c r="S37" s="62"/>
+      <c r="T37" s="77">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="U37" s="77">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>23995</v>
+      </c>
+      <c r="V37" s="77">
+        <f>U37/6</f>
+        <v>3999.1666666666665</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="73"/>
+      <c r="N38" s="74"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="71"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="55"/>
+      <c r="T38" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="75">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="75">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="74"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="71"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="95"/>
+      <c r="T39" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U39" s="75">
+        <f>C39*24+M39*24+O39*24+Q39*24+T39</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="75">
+        <f>U39/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="59">
+        <v>23</v>
+      </c>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
+      <c r="L40" s="62"/>
+      <c r="M40" s="63">
+        <v>1</v>
+      </c>
+      <c r="N40" s="64"/>
+      <c r="O40" s="65">
+        <v>1</v>
+      </c>
+      <c r="P40" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q40" s="66">
+        <v>2</v>
+      </c>
+      <c r="R40" s="67"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="77">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="U40" s="77">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>680</v>
+      </c>
+      <c r="V40" s="77">
+        <f>U40/24</f>
+        <v>28.333333333333332</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="82">
+        <v>84</v>
+      </c>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="85"/>
+      <c r="M41" s="86">
+        <v>8</v>
+      </c>
+      <c r="N41" s="87"/>
+      <c r="O41" s="82">
+        <v>4</v>
+      </c>
+      <c r="P41" s="83"/>
+      <c r="Q41" s="83">
+        <v>35</v>
+      </c>
+      <c r="R41" s="84"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="88">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>1572</v>
+      </c>
+      <c r="V41" s="88">
+        <f>U41/12</f>
+        <v>131</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="71"/>
+      <c r="K42" s="72"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="73"/>
+      <c r="N42" s="74"/>
+      <c r="O42" s="70"/>
+      <c r="P42" s="71"/>
+      <c r="Q42" s="71"/>
+      <c r="R42" s="72"/>
+      <c r="S42" s="55"/>
+      <c r="T42" s="75"/>
+      <c r="U42" s="75"/>
+      <c r="V42" s="75"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="65">
+        <f>7776+3024+8424+5508+3024+5616+52</f>
+        <v>33424</v>
+      </c>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65">
+        <v>3</v>
+      </c>
+      <c r="I43" s="65">
+        <v>7</v>
+      </c>
+      <c r="J43" s="66">
+        <f>10*6+4</f>
+        <v>64</v>
+      </c>
+      <c r="K43" s="67">
+        <f>69*6+7</f>
+        <v>421</v>
+      </c>
+      <c r="L43" s="62"/>
+      <c r="M43" s="63">
+        <v>333</v>
+      </c>
+      <c r="N43" s="64"/>
+      <c r="O43" s="65">
+        <v>368</v>
+      </c>
+      <c r="P43" s="66"/>
+      <c r="Q43" s="66">
+        <v>493</v>
+      </c>
+      <c r="R43" s="67"/>
+      <c r="S43" s="62"/>
+      <c r="T43" s="77">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>495</v>
+      </c>
+      <c r="U43" s="77">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>208203</v>
+      </c>
+      <c r="V43" s="77">
+        <f>U43/6</f>
+        <v>34700.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="70"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="71"/>
+      <c r="K44" s="72"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="73"/>
+      <c r="N44" s="74"/>
+      <c r="O44" s="70"/>
+      <c r="P44" s="71"/>
+      <c r="Q44" s="71"/>
+      <c r="R44" s="72"/>
+      <c r="S44" s="55"/>
+      <c r="T44" s="75"/>
+      <c r="U44" s="75"/>
+      <c r="V44" s="75"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="70"/>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="70"/>
+      <c r="I45" s="70"/>
+      <c r="J45" s="71"/>
+      <c r="K45" s="72"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="73"/>
+      <c r="N45" s="74"/>
+      <c r="O45" s="70"/>
+      <c r="P45" s="71"/>
+      <c r="Q45" s="71"/>
+      <c r="R45" s="72"/>
+      <c r="S45" s="55"/>
+      <c r="T45" s="75">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="75">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="75">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="73"/>
+      <c r="N46" s="74"/>
+      <c r="O46" s="70"/>
+      <c r="P46" s="71"/>
+      <c r="Q46" s="71"/>
+      <c r="R46" s="72"/>
+      <c r="S46" s="55"/>
+      <c r="T46" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="75">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="75">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="65">
+        <f>432+106+2160+67</f>
+        <v>2765</v>
+      </c>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
+      <c r="I47" s="65"/>
+      <c r="J47" s="66">
+        <v>1</v>
+      </c>
+      <c r="K47" s="67">
+        <v>4</v>
+      </c>
+      <c r="L47" s="62"/>
+      <c r="M47" s="63">
+        <v>10</v>
+      </c>
+      <c r="N47" s="64"/>
+      <c r="O47" s="65">
+        <v>9</v>
+      </c>
+      <c r="P47" s="66">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="66">
+        <v>9</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
+      <c r="S47" s="62"/>
+      <c r="T47" s="77">
+        <f t="shared" si="7"/>
+        <v>13</v>
+      </c>
+      <c r="U47" s="77">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>16771</v>
+      </c>
+      <c r="V47" s="77">
+        <f>U47/6</f>
+        <v>2795.1666666666665</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
+      <c r="I48" s="70"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="72"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="73"/>
+      <c r="N48" s="74"/>
+      <c r="O48" s="70"/>
+      <c r="P48" s="71"/>
+      <c r="Q48" s="71"/>
+      <c r="R48" s="72"/>
+      <c r="S48" s="55"/>
+      <c r="T48" s="75">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="U48" s="75">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="V48" s="75">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="70"/>
+      <c r="I49" s="70"/>
+      <c r="J49" s="71"/>
+      <c r="K49" s="72"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="74"/>
+      <c r="O49" s="70"/>
+      <c r="P49" s="71"/>
+      <c r="Q49" s="71"/>
+      <c r="R49" s="72"/>
+      <c r="S49" s="55"/>
+      <c r="T49" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="70"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="70"/>
+      <c r="F50" s="70"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
+      <c r="J50" s="71"/>
+      <c r="K50" s="72"/>
+      <c r="L50" s="55"/>
+      <c r="M50" s="73"/>
+      <c r="N50" s="74"/>
+      <c r="O50" s="70"/>
+      <c r="P50" s="71"/>
+      <c r="Q50" s="71"/>
+      <c r="R50" s="72"/>
+      <c r="S50" s="55"/>
+      <c r="T50" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="65"/>
+      <c r="I51" s="65"/>
+      <c r="J51" s="66"/>
+      <c r="K51" s="67"/>
+      <c r="L51" s="62"/>
+      <c r="M51" s="63"/>
+      <c r="N51" s="64"/>
+      <c r="O51" s="65"/>
+      <c r="P51" s="66"/>
+      <c r="Q51" s="66"/>
+      <c r="R51" s="67"/>
+      <c r="S51" s="62"/>
+      <c r="T51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="77">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>204</v>
+      </c>
+      <c r="V51" s="77">
+        <f>U51/6</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="70"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="70"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="71"/>
+      <c r="K52" s="72"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="73"/>
+      <c r="N52" s="74"/>
+      <c r="O52" s="70"/>
+      <c r="P52" s="71"/>
+      <c r="Q52" s="71"/>
+      <c r="R52" s="72"/>
+      <c r="S52" s="55"/>
+      <c r="T52" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="75">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="70">
+        <v>9</v>
+      </c>
+      <c r="D53" s="70"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="70"/>
+      <c r="H53" s="70"/>
+      <c r="I53" s="70"/>
+      <c r="J53" s="71"/>
+      <c r="K53" s="72"/>
+      <c r="L53" s="55"/>
+      <c r="M53" s="73"/>
+      <c r="N53" s="74"/>
+      <c r="O53" s="70"/>
+      <c r="P53" s="71"/>
+      <c r="Q53" s="71"/>
+      <c r="R53" s="72"/>
+      <c r="S53" s="55"/>
+      <c r="T53" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="75">
+        <f t="shared" si="10"/>
+        <v>216</v>
+      </c>
+      <c r="V53" s="75">
+        <f t="shared" si="9"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="71"/>
+      <c r="K54" s="72"/>
+      <c r="L54" s="55"/>
+      <c r="M54" s="73"/>
+      <c r="N54" s="74"/>
+      <c r="O54" s="70"/>
+      <c r="P54" s="71"/>
+      <c r="Q54" s="71"/>
+      <c r="R54" s="72"/>
+      <c r="S54" s="55"/>
+      <c r="T54" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="70"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="70"/>
+      <c r="I55" s="70"/>
+      <c r="J55" s="71"/>
+      <c r="K55" s="72"/>
+      <c r="L55" s="55"/>
+      <c r="M55" s="73"/>
+      <c r="N55" s="74"/>
+      <c r="O55" s="70"/>
+      <c r="P55" s="71"/>
+      <c r="Q55" s="71"/>
+      <c r="R55" s="72"/>
+      <c r="S55" s="55"/>
+      <c r="T55" s="75"/>
+      <c r="U55" s="75"/>
+      <c r="V55" s="75"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="70"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="70"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="71"/>
+      <c r="K56" s="72"/>
+      <c r="L56" s="55"/>
+      <c r="M56" s="73"/>
+      <c r="N56" s="74"/>
+      <c r="O56" s="70"/>
+      <c r="P56" s="71"/>
+      <c r="Q56" s="71"/>
+      <c r="R56" s="72"/>
+      <c r="S56" s="55"/>
+      <c r="T56" s="75"/>
+      <c r="U56" s="75"/>
+      <c r="V56" s="75"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="70"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="70"/>
+      <c r="I57" s="70"/>
+      <c r="J57" s="71"/>
+      <c r="K57" s="72"/>
+      <c r="L57" s="55"/>
+      <c r="M57" s="73"/>
+      <c r="N57" s="74"/>
+      <c r="O57" s="70"/>
+      <c r="P57" s="71"/>
+      <c r="Q57" s="71"/>
+      <c r="R57" s="72"/>
+      <c r="S57" s="55"/>
+      <c r="T57" s="75"/>
+      <c r="U57" s="75"/>
+      <c r="V57" s="75"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>43762</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>1187</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>39</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>67</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>457</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>392</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>12</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>430</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>28</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>687</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>3</v>
+      </c>
+      <c r="S58" s="55"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>1793</v>
+      </c>
+      <c r="U58" s="90">
+        <f>SUM(U7:U57)</f>
+        <v>340751</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>45410.083333333328</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="106" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="107"/>
+      <c r="E60" s="107"/>
+      <c r="F60" s="107"/>
+      <c r="G60" s="107"/>
+      <c r="H60" s="107"/>
+      <c r="I60" s="107"/>
+      <c r="J60" s="107"/>
+      <c r="K60" s="108"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
     <mergeCell ref="V4:V5"/>
     <mergeCell ref="J5:K5"/>
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>

--- a/GBDS JUNE FILES 2026/INVENTORY COUNT SHEET - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/INVENTORY COUNT SHEET - JUNE 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{450606C5-1988-49D4-868B-0D788EA4B013}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A12E9452-FC22-416F-91E9-8EB41A63A4C0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="9" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -21,6 +21,8 @@
     <sheet name="06-05-2026 " sheetId="59" r:id="rId6"/>
     <sheet name="06-08-2026 " sheetId="60" r:id="rId7"/>
     <sheet name="06-09-2026" sheetId="61" r:id="rId8"/>
+    <sheet name="06-10-2026" sheetId="62" r:id="rId9"/>
+    <sheet name="06-11-2026" sheetId="63" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'06-01-2026'!$A$1:$W$59</definedName>
@@ -30,6 +32,8 @@
     <definedName name="_xlnm.Print_Area" localSheetId="5">'06-05-2026 '!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'06-08-2026 '!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'06-09-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'06-10-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'06-11-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -48,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="74">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -1257,7 +1261,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1543,6 +1547,12 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1974,21 +1984,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="109" t="s">
+      <c r="I1" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -2000,17 +2010,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="110" t="s">
+      <c r="C4" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="112"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="114"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -2030,13 +2040,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="113" t="s">
+      <c r="T4" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="115" t="s">
+      <c r="U4" s="117" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="102" t="s">
+      <c r="V4" s="104" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2076,10 +2086,10 @@
       <c r="I5" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="104" t="s">
+      <c r="J5" s="106" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="105"/>
+      <c r="K5" s="107"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2087,9 +2097,9 @@
       <c r="Q5" s="89"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="114"/>
-      <c r="U5" s="116"/>
-      <c r="V5" s="103"/>
+      <c r="T5" s="116"/>
+      <c r="U5" s="118"/>
+      <c r="V5" s="105"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -4620,17 +4630,17 @@
       <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="106" t="s">
+      <c r="C62" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="107"/>
-      <c r="E62" s="107"/>
-      <c r="F62" s="107"/>
-      <c r="G62" s="107"/>
-      <c r="H62" s="107"/>
-      <c r="I62" s="107"/>
-      <c r="J62" s="107"/>
-      <c r="K62" s="108"/>
+      <c r="D62" s="109"/>
+      <c r="E62" s="109"/>
+      <c r="F62" s="109"/>
+      <c r="G62" s="109"/>
+      <c r="H62" s="109"/>
+      <c r="I62" s="109"/>
+      <c r="J62" s="109"/>
+      <c r="K62" s="110"/>
       <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
@@ -4893,6 +4903,3125 @@
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
   <pageSetup paperSize="14" scale="53" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C78FA54C-F0FF-4F87-83F3-3422B1318445}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="9" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="111" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="112" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="114"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="115" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="121" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="104" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="119" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="120"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="103"/>
+      <c r="Q5" s="103"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="116"/>
+      <c r="U5" s="122"/>
+      <c r="V5" s="105"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="103"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="103"/>
+      <c r="Q6" s="103"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="52">
+        <v>18</v>
+      </c>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
+      <c r="J7" s="53"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
+      <c r="L7" s="55"/>
+      <c r="M7" s="56">
+        <v>1</v>
+      </c>
+      <c r="N7" s="57"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="53">
+        <v>1</v>
+      </c>
+      <c r="R7" s="54"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="58">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>9</v>
+      </c>
+      <c r="U7" s="58">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>513</v>
+      </c>
+      <c r="V7" s="58">
+        <f>U7/24</f>
+        <v>21.375</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="59">
+        <f>61+33</f>
+        <v>94</v>
+      </c>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="63"/>
+      <c r="N8" s="64"/>
+      <c r="O8" s="65"/>
+      <c r="P8" s="66"/>
+      <c r="Q8" s="66">
+        <v>2</v>
+      </c>
+      <c r="R8" s="67"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="68">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="69">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>2304</v>
+      </c>
+      <c r="V8" s="69">
+        <f>U8/24</f>
+        <v>96</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="70">
+        <f>90+24</f>
+        <v>114</v>
+      </c>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="73"/>
+      <c r="N9" s="74"/>
+      <c r="O9" s="70">
+        <v>2</v>
+      </c>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71"/>
+      <c r="R9" s="72"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="76">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>2784</v>
+      </c>
+      <c r="V9" s="76">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>116</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="70"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="74"/>
+      <c r="O10" s="70"/>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71"/>
+      <c r="R10" s="72"/>
+      <c r="S10" s="55"/>
+      <c r="T10" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V10" s="58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="70">
+        <v>5</v>
+      </c>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
+      <c r="L11" s="55"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="55"/>
+      <c r="T11" s="58">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U11" s="58">
+        <f t="shared" si="2"/>
+        <v>122</v>
+      </c>
+      <c r="V11" s="58">
+        <f t="shared" si="3"/>
+        <v>5.083333333333333</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="59">
+        <f>720+34+1440+144+51+576</f>
+        <v>2965</v>
+      </c>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="63">
+        <v>7</v>
+      </c>
+      <c r="N12" s="64"/>
+      <c r="O12" s="65">
+        <v>16</v>
+      </c>
+      <c r="P12" s="66"/>
+      <c r="Q12" s="66">
+        <v>16</v>
+      </c>
+      <c r="R12" s="67"/>
+      <c r="S12" s="62"/>
+      <c r="T12" s="69">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U12" s="69">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>72096</v>
+      </c>
+      <c r="V12" s="69">
+        <f>U12/24</f>
+        <v>3004</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
+      <c r="I13" s="70"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="55"/>
+      <c r="T13" s="76">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="U13" s="76">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>64</v>
+      </c>
+      <c r="V13" s="76">
+        <f>U13/24</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="70">
+        <v>4</v>
+      </c>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="55"/>
+      <c r="T14" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="75">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>96</v>
+      </c>
+      <c r="V14" s="75">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>4</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="55"/>
+      <c r="T15" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="55"/>
+      <c r="T16" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I17" s="70"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U17" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V17" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="55"/>
+      <c r="T18" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="70">
+        <v>2</v>
+      </c>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70">
+        <f>20+24</f>
+        <v>44</v>
+      </c>
+      <c r="I19" s="70"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="55"/>
+      <c r="T19" s="58">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="U19" s="75">
+        <f t="shared" si="4"/>
+        <v>92</v>
+      </c>
+      <c r="V19" s="75">
+        <f t="shared" si="5"/>
+        <v>3.8333333333333335</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="74"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="55"/>
+      <c r="T20" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V20" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70">
+        <f>2*24</f>
+        <v>48</v>
+      </c>
+      <c r="I21" s="70"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="58">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="U21" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V21" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="70"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
+      <c r="J22" s="71"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="55"/>
+      <c r="T22" s="58">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U22" s="75">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="V22" s="75">
+        <f t="shared" si="5"/>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
+      <c r="I23" s="70"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="74"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="55"/>
+      <c r="T23" s="58">
+        <f t="shared" si="0"/>
+        <v>907</v>
+      </c>
+      <c r="U23" s="75">
+        <f t="shared" si="4"/>
+        <v>907</v>
+      </c>
+      <c r="V23" s="75">
+        <f t="shared" si="5"/>
+        <v>37.791666666666664</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="70">
+        <v>5</v>
+      </c>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I24" s="70"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="55"/>
+      <c r="T24" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U24" s="75">
+        <f t="shared" si="4"/>
+        <v>192</v>
+      </c>
+      <c r="V24" s="75">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="70">
+        <f>63+58</f>
+        <v>121</v>
+      </c>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70"/>
+      <c r="J25" s="71">
+        <v>1</v>
+      </c>
+      <c r="K25" s="72"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="73">
+        <v>1</v>
+      </c>
+      <c r="N25" s="74"/>
+      <c r="O25" s="70"/>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71">
+        <v>2</v>
+      </c>
+      <c r="R25" s="72"/>
+      <c r="S25" s="55"/>
+      <c r="T25" s="58">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="U25" s="75">
+        <f t="shared" si="4"/>
+        <v>2977</v>
+      </c>
+      <c r="V25" s="75">
+        <f t="shared" si="5"/>
+        <v>124.04166666666667</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="74"/>
+      <c r="O26" s="70"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="71"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="55"/>
+      <c r="T26" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="70"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="70"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="55"/>
+      <c r="T27" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="70">
+        <v>22</v>
+      </c>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="73">
+        <v>1</v>
+      </c>
+      <c r="N28" s="74"/>
+      <c r="O28" s="70">
+        <v>2</v>
+      </c>
+      <c r="P28" s="71"/>
+      <c r="Q28" s="71">
+        <v>3</v>
+      </c>
+      <c r="R28" s="72"/>
+      <c r="S28" s="55"/>
+      <c r="T28" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="75">
+        <f t="shared" si="4"/>
+        <v>672</v>
+      </c>
+      <c r="V28" s="75">
+        <f t="shared" si="5"/>
+        <v>28</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="70">
+        <v>49</v>
+      </c>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70"/>
+      <c r="J29" s="71">
+        <v>5</v>
+      </c>
+      <c r="K29" s="72"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="73"/>
+      <c r="N29" s="74"/>
+      <c r="O29" s="70">
+        <v>1</v>
+      </c>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71"/>
+      <c r="R29" s="72"/>
+      <c r="S29" s="55"/>
+      <c r="T29" s="58">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U29" s="75">
+        <f t="shared" si="4"/>
+        <v>1205</v>
+      </c>
+      <c r="V29" s="75">
+        <f t="shared" si="5"/>
+        <v>50.208333333333336</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="70">
+        <v>11</v>
+      </c>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="74"/>
+      <c r="O30" s="70"/>
+      <c r="P30" s="71"/>
+      <c r="Q30" s="71">
+        <v>1</v>
+      </c>
+      <c r="R30" s="72"/>
+      <c r="S30" s="55"/>
+      <c r="T30" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="75">
+        <f t="shared" si="4"/>
+        <v>288</v>
+      </c>
+      <c r="V30" s="75">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="70"/>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="70">
+        <v>4</v>
+      </c>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="74"/>
+      <c r="O32" s="70"/>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="55"/>
+      <c r="T32" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="75">
+        <f t="shared" si="4"/>
+        <v>96</v>
+      </c>
+      <c r="V32" s="75">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="70"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="73"/>
+      <c r="N33" s="74"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="55"/>
+      <c r="T33" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="70">
+        <v>61</v>
+      </c>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="70"/>
+      <c r="J34" s="71">
+        <v>1</v>
+      </c>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
+      <c r="L34" s="55"/>
+      <c r="M34" s="73">
+        <v>2</v>
+      </c>
+      <c r="N34" s="74"/>
+      <c r="O34" s="70">
+        <v>1</v>
+      </c>
+      <c r="P34" s="71">
+        <v>12</v>
+      </c>
+      <c r="Q34" s="71"/>
+      <c r="R34" s="72"/>
+      <c r="S34" s="55"/>
+      <c r="T34" s="58">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="U34" s="75">
+        <f t="shared" si="4"/>
+        <v>1550</v>
+      </c>
+      <c r="V34" s="75">
+        <f t="shared" si="5"/>
+        <v>64.583333333333329</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="72"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="74"/>
+      <c r="O35" s="70"/>
+      <c r="P35" s="71"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="72"/>
+      <c r="S35" s="55"/>
+      <c r="T35" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="73"/>
+      <c r="N36" s="74"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="71"/>
+      <c r="Q36" s="71"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="55"/>
+      <c r="T36" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="59">
+        <f>864+2700+58</f>
+        <v>3622</v>
+      </c>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59">
+        <v>5</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>3</v>
+      </c>
+      <c r="K37" s="61">
+        <v>3</v>
+      </c>
+      <c r="L37" s="62"/>
+      <c r="M37" s="63">
+        <v>6</v>
+      </c>
+      <c r="N37" s="64"/>
+      <c r="O37" s="65">
+        <v>108</v>
+      </c>
+      <c r="P37" s="66"/>
+      <c r="Q37" s="66">
+        <v>54</v>
+      </c>
+      <c r="R37" s="67"/>
+      <c r="S37" s="62"/>
+      <c r="T37" s="77">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="U37" s="77">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>22753</v>
+      </c>
+      <c r="V37" s="77">
+        <f>U37/6</f>
+        <v>3792.1666666666665</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="73"/>
+      <c r="N38" s="74"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="71"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="55"/>
+      <c r="T38" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="75">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="75">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="74"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="71"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="95"/>
+      <c r="T39" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U39" s="75">
+        <f>C39*24+M39*24+O39*24+Q39*24+T39</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="75">
+        <f>U39/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="59">
+        <v>26</v>
+      </c>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
+      <c r="L40" s="62"/>
+      <c r="M40" s="63"/>
+      <c r="N40" s="64"/>
+      <c r="O40" s="65"/>
+      <c r="P40" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q40" s="66"/>
+      <c r="R40" s="67"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="77">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="U40" s="77">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>656</v>
+      </c>
+      <c r="V40" s="77">
+        <f>U40/24</f>
+        <v>27.333333333333332</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="82">
+        <v>60</v>
+      </c>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="85"/>
+      <c r="M41" s="86">
+        <v>2</v>
+      </c>
+      <c r="N41" s="87"/>
+      <c r="O41" s="82">
+        <v>6</v>
+      </c>
+      <c r="P41" s="83"/>
+      <c r="Q41" s="83">
+        <v>15</v>
+      </c>
+      <c r="R41" s="84"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="88">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>996</v>
+      </c>
+      <c r="V41" s="88">
+        <f>U41/12</f>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="71"/>
+      <c r="K42" s="72"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="73"/>
+      <c r="N42" s="74"/>
+      <c r="O42" s="70"/>
+      <c r="P42" s="71"/>
+      <c r="Q42" s="71"/>
+      <c r="R42" s="72"/>
+      <c r="S42" s="55"/>
+      <c r="T42" s="75"/>
+      <c r="U42" s="75"/>
+      <c r="V42" s="75"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="65">
+        <f>7776+3024+8424+5508+3024+4212</f>
+        <v>31968</v>
+      </c>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65">
+        <v>3</v>
+      </c>
+      <c r="I43" s="65">
+        <v>7</v>
+      </c>
+      <c r="J43" s="66">
+        <f>6*12+4</f>
+        <v>76</v>
+      </c>
+      <c r="K43" s="67">
+        <f>69*6+7</f>
+        <v>421</v>
+      </c>
+      <c r="L43" s="62"/>
+      <c r="M43" s="63">
+        <v>58</v>
+      </c>
+      <c r="N43" s="64"/>
+      <c r="O43" s="65">
+        <v>369</v>
+      </c>
+      <c r="P43" s="66"/>
+      <c r="Q43" s="66">
+        <v>419</v>
+      </c>
+      <c r="R43" s="67"/>
+      <c r="S43" s="62"/>
+      <c r="T43" s="77">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>507</v>
+      </c>
+      <c r="U43" s="77">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>197391</v>
+      </c>
+      <c r="V43" s="77">
+        <f>U43/6</f>
+        <v>32898.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="70"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="71"/>
+      <c r="K44" s="72"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="73"/>
+      <c r="N44" s="74"/>
+      <c r="O44" s="70"/>
+      <c r="P44" s="71"/>
+      <c r="Q44" s="71"/>
+      <c r="R44" s="72"/>
+      <c r="S44" s="55"/>
+      <c r="T44" s="75"/>
+      <c r="U44" s="75"/>
+      <c r="V44" s="75"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="70"/>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="70"/>
+      <c r="I45" s="70"/>
+      <c r="J45" s="71"/>
+      <c r="K45" s="72"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="73"/>
+      <c r="N45" s="74"/>
+      <c r="O45" s="70"/>
+      <c r="P45" s="71"/>
+      <c r="Q45" s="71"/>
+      <c r="R45" s="72"/>
+      <c r="S45" s="55"/>
+      <c r="T45" s="75">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="75">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="75">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="73"/>
+      <c r="N46" s="74"/>
+      <c r="O46" s="70"/>
+      <c r="P46" s="71"/>
+      <c r="Q46" s="71"/>
+      <c r="R46" s="72"/>
+      <c r="S46" s="55"/>
+      <c r="T46" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="75">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="75">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="65">
+        <f>432+106+2160+67</f>
+        <v>2765</v>
+      </c>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
+      <c r="I47" s="65"/>
+      <c r="J47" s="66">
+        <v>1</v>
+      </c>
+      <c r="K47" s="67">
+        <v>4</v>
+      </c>
+      <c r="L47" s="62"/>
+      <c r="M47" s="63">
+        <v>8</v>
+      </c>
+      <c r="N47" s="64"/>
+      <c r="O47" s="65">
+        <v>9</v>
+      </c>
+      <c r="P47" s="66">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="66">
+        <v>9</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
+      <c r="S47" s="62"/>
+      <c r="T47" s="77">
+        <f t="shared" si="7"/>
+        <v>13</v>
+      </c>
+      <c r="U47" s="77">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>16759</v>
+      </c>
+      <c r="V47" s="77">
+        <f>U47/6</f>
+        <v>2793.1666666666665</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
+      <c r="I48" s="70"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="72"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="73"/>
+      <c r="N48" s="74"/>
+      <c r="O48" s="70"/>
+      <c r="P48" s="71"/>
+      <c r="Q48" s="71"/>
+      <c r="R48" s="72"/>
+      <c r="S48" s="55"/>
+      <c r="T48" s="75">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="U48" s="75">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="V48" s="75">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="70"/>
+      <c r="I49" s="70"/>
+      <c r="J49" s="71"/>
+      <c r="K49" s="72"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="74"/>
+      <c r="O49" s="70"/>
+      <c r="P49" s="71"/>
+      <c r="Q49" s="71"/>
+      <c r="R49" s="72"/>
+      <c r="S49" s="55"/>
+      <c r="T49" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="70"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="70"/>
+      <c r="F50" s="70"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
+      <c r="J50" s="71"/>
+      <c r="K50" s="72"/>
+      <c r="L50" s="55"/>
+      <c r="M50" s="73"/>
+      <c r="N50" s="74"/>
+      <c r="O50" s="70"/>
+      <c r="P50" s="71"/>
+      <c r="Q50" s="71"/>
+      <c r="R50" s="72"/>
+      <c r="S50" s="55"/>
+      <c r="T50" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="65"/>
+      <c r="I51" s="65"/>
+      <c r="J51" s="66"/>
+      <c r="K51" s="67"/>
+      <c r="L51" s="62"/>
+      <c r="M51" s="63"/>
+      <c r="N51" s="64"/>
+      <c r="O51" s="65"/>
+      <c r="P51" s="66"/>
+      <c r="Q51" s="66"/>
+      <c r="R51" s="67"/>
+      <c r="S51" s="62"/>
+      <c r="T51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="77">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>204</v>
+      </c>
+      <c r="V51" s="77">
+        <f>U51/6</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="70">
+        <v>9</v>
+      </c>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="70"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="71"/>
+      <c r="K52" s="72"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="73"/>
+      <c r="N52" s="74"/>
+      <c r="O52" s="70"/>
+      <c r="P52" s="71"/>
+      <c r="Q52" s="71"/>
+      <c r="R52" s="72"/>
+      <c r="S52" s="55"/>
+      <c r="T52" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="75">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>216</v>
+      </c>
+      <c r="V52" s="75">
+        <f t="shared" si="9"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="70"/>
+      <c r="D53" s="70"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="70"/>
+      <c r="H53" s="70"/>
+      <c r="I53" s="70"/>
+      <c r="J53" s="71"/>
+      <c r="K53" s="72"/>
+      <c r="L53" s="55"/>
+      <c r="M53" s="73"/>
+      <c r="N53" s="74"/>
+      <c r="O53" s="70"/>
+      <c r="P53" s="71"/>
+      <c r="Q53" s="71"/>
+      <c r="R53" s="72"/>
+      <c r="S53" s="55"/>
+      <c r="T53" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V53" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="71"/>
+      <c r="K54" s="72"/>
+      <c r="L54" s="55"/>
+      <c r="M54" s="73"/>
+      <c r="N54" s="74"/>
+      <c r="O54" s="70"/>
+      <c r="P54" s="71"/>
+      <c r="Q54" s="71"/>
+      <c r="R54" s="72"/>
+      <c r="S54" s="55"/>
+      <c r="T54" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="70"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="70"/>
+      <c r="I55" s="70"/>
+      <c r="J55" s="71"/>
+      <c r="K55" s="72"/>
+      <c r="L55" s="55"/>
+      <c r="M55" s="73"/>
+      <c r="N55" s="74"/>
+      <c r="O55" s="70"/>
+      <c r="P55" s="71"/>
+      <c r="Q55" s="71"/>
+      <c r="R55" s="72"/>
+      <c r="S55" s="55"/>
+      <c r="T55" s="75"/>
+      <c r="U55" s="75"/>
+      <c r="V55" s="75"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="70"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="70"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="71"/>
+      <c r="K56" s="72"/>
+      <c r="L56" s="55"/>
+      <c r="M56" s="73"/>
+      <c r="N56" s="74"/>
+      <c r="O56" s="70"/>
+      <c r="P56" s="71"/>
+      <c r="Q56" s="71"/>
+      <c r="R56" s="72"/>
+      <c r="S56" s="55"/>
+      <c r="T56" s="75"/>
+      <c r="U56" s="75"/>
+      <c r="V56" s="75"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="70"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="70"/>
+      <c r="I57" s="70"/>
+      <c r="J57" s="71"/>
+      <c r="K57" s="72"/>
+      <c r="L57" s="55"/>
+      <c r="M57" s="73"/>
+      <c r="N57" s="74"/>
+      <c r="O57" s="70"/>
+      <c r="P57" s="71"/>
+      <c r="Q57" s="71"/>
+      <c r="R57" s="72"/>
+      <c r="S57" s="55"/>
+      <c r="T57" s="75"/>
+      <c r="U57" s="75"/>
+      <c r="V57" s="75"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>41966</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>1192</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>32</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>87</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>457</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>86</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>515</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>28</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>522</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>3</v>
+      </c>
+      <c r="S58" s="55"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>1799</v>
+      </c>
+      <c r="U58" s="90">
+        <f>SUM(U7:U57)</f>
+        <v>325217</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>43230.583333333328</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="108" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="109"/>
+      <c r="E60" s="109"/>
+      <c r="F60" s="109"/>
+      <c r="G60" s="109"/>
+      <c r="H60" s="109"/>
+      <c r="I60" s="109"/>
+      <c r="J60" s="109"/>
+      <c r="K60" s="110"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="24" max="80" man="1"/>
   </colBreaks>
@@ -4939,21 +8068,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="109" t="s">
+      <c r="I1" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -4965,17 +8094,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="110" t="s">
+      <c r="C4" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="112"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="114"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -4995,13 +8124,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="113" t="s">
+      <c r="T4" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="119" t="s">
+      <c r="U4" s="121" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="102" t="s">
+      <c r="V4" s="104" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -5041,10 +8170,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="117" t="s">
+      <c r="J5" s="119" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="118"/>
+      <c r="K5" s="120"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -5052,9 +8181,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="114"/>
-      <c r="U5" s="120"/>
-      <c r="V5" s="103"/>
+      <c r="T5" s="116"/>
+      <c r="U5" s="122"/>
+      <c r="V5" s="105"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -7766,17 +10895,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="106" t="s">
+      <c r="C60" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="107"/>
-      <c r="E60" s="107"/>
-      <c r="F60" s="107"/>
-      <c r="G60" s="107"/>
-      <c r="H60" s="107"/>
-      <c r="I60" s="107"/>
-      <c r="J60" s="107"/>
-      <c r="K60" s="108"/>
+      <c r="D60" s="109"/>
+      <c r="E60" s="109"/>
+      <c r="F60" s="109"/>
+      <c r="G60" s="109"/>
+      <c r="H60" s="109"/>
+      <c r="I60" s="109"/>
+      <c r="J60" s="109"/>
+      <c r="K60" s="110"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -8085,21 +11214,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="109" t="s">
+      <c r="I1" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -8111,17 +11240,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="110" t="s">
+      <c r="C4" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="112"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="114"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -8141,13 +11270,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="113" t="s">
+      <c r="T4" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="119" t="s">
+      <c r="U4" s="121" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="102" t="s">
+      <c r="V4" s="104" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -8187,10 +11316,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="117" t="s">
+      <c r="J5" s="119" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="118"/>
+      <c r="K5" s="120"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -8198,9 +11327,9 @@
       <c r="Q5" s="96"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="114"/>
-      <c r="U5" s="120"/>
-      <c r="V5" s="103"/>
+      <c r="T5" s="116"/>
+      <c r="U5" s="122"/>
+      <c r="V5" s="105"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -10935,17 +14064,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="106" t="s">
+      <c r="C60" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="107"/>
-      <c r="E60" s="107"/>
-      <c r="F60" s="107"/>
-      <c r="G60" s="107"/>
-      <c r="H60" s="107"/>
-      <c r="I60" s="107"/>
-      <c r="J60" s="107"/>
-      <c r="K60" s="108"/>
+      <c r="D60" s="109"/>
+      <c r="E60" s="109"/>
+      <c r="F60" s="109"/>
+      <c r="G60" s="109"/>
+      <c r="H60" s="109"/>
+      <c r="I60" s="109"/>
+      <c r="J60" s="109"/>
+      <c r="K60" s="110"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -11254,21 +14383,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="109" t="s">
+      <c r="I1" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -11280,17 +14409,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="110" t="s">
+      <c r="C4" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="112"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="114"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -11310,13 +14439,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="113" t="s">
+      <c r="T4" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="119" t="s">
+      <c r="U4" s="121" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="102" t="s">
+      <c r="V4" s="104" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -11356,10 +14485,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="117" t="s">
+      <c r="J5" s="119" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="118"/>
+      <c r="K5" s="120"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -11367,9 +14496,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="114"/>
-      <c r="U5" s="120"/>
-      <c r="V5" s="103"/>
+      <c r="T5" s="116"/>
+      <c r="U5" s="122"/>
+      <c r="V5" s="105"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -14064,17 +17193,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="106" t="s">
+      <c r="C60" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="107"/>
-      <c r="E60" s="107"/>
-      <c r="F60" s="107"/>
-      <c r="G60" s="107"/>
-      <c r="H60" s="107"/>
-      <c r="I60" s="107"/>
-      <c r="J60" s="107"/>
-      <c r="K60" s="108"/>
+      <c r="D60" s="109"/>
+      <c r="E60" s="109"/>
+      <c r="F60" s="109"/>
+      <c r="G60" s="109"/>
+      <c r="H60" s="109"/>
+      <c r="I60" s="109"/>
+      <c r="J60" s="109"/>
+      <c r="K60" s="110"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -14383,21 +17512,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="109" t="s">
+      <c r="I1" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -14409,17 +17538,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="110" t="s">
+      <c r="C4" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="112"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="114"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -14439,13 +17568,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="113" t="s">
+      <c r="T4" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="119" t="s">
+      <c r="U4" s="121" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="102" t="s">
+      <c r="V4" s="104" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -14485,10 +17614,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="117" t="s">
+      <c r="J5" s="119" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="118"/>
+      <c r="K5" s="120"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -14496,9 +17625,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="114"/>
-      <c r="U5" s="120"/>
-      <c r="V5" s="103"/>
+      <c r="T5" s="116"/>
+      <c r="U5" s="122"/>
+      <c r="V5" s="105"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -17198,17 +20327,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="106" t="s">
+      <c r="C60" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="107"/>
-      <c r="E60" s="107"/>
-      <c r="F60" s="107"/>
-      <c r="G60" s="107"/>
-      <c r="H60" s="107"/>
-      <c r="I60" s="107"/>
-      <c r="J60" s="107"/>
-      <c r="K60" s="108"/>
+      <c r="D60" s="109"/>
+      <c r="E60" s="109"/>
+      <c r="F60" s="109"/>
+      <c r="G60" s="109"/>
+      <c r="H60" s="109"/>
+      <c r="I60" s="109"/>
+      <c r="J60" s="109"/>
+      <c r="K60" s="110"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -17517,21 +20646,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="109" t="s">
+      <c r="I1" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -17543,17 +20672,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="110" t="s">
+      <c r="C4" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="112"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="114"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -17573,13 +20702,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="113" t="s">
+      <c r="T4" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="119" t="s">
+      <c r="U4" s="121" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="102" t="s">
+      <c r="V4" s="104" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -17619,10 +20748,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="117" t="s">
+      <c r="J5" s="119" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="118"/>
+      <c r="K5" s="120"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -17630,9 +20759,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="114"/>
-      <c r="U5" s="120"/>
-      <c r="V5" s="103"/>
+      <c r="T5" s="116"/>
+      <c r="U5" s="122"/>
+      <c r="V5" s="105"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -20326,17 +23455,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="106" t="s">
+      <c r="C60" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="107"/>
-      <c r="E60" s="107"/>
-      <c r="F60" s="107"/>
-      <c r="G60" s="107"/>
-      <c r="H60" s="107"/>
-      <c r="I60" s="107"/>
-      <c r="J60" s="107"/>
-      <c r="K60" s="108"/>
+      <c r="D60" s="109"/>
+      <c r="E60" s="109"/>
+      <c r="F60" s="109"/>
+      <c r="G60" s="109"/>
+      <c r="H60" s="109"/>
+      <c r="I60" s="109"/>
+      <c r="J60" s="109"/>
+      <c r="K60" s="110"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -20645,21 +23774,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="109" t="s">
+      <c r="I1" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -20671,17 +23800,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="110" t="s">
+      <c r="C4" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="112"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="114"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -20701,13 +23830,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="113" t="s">
+      <c r="T4" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="119" t="s">
+      <c r="U4" s="121" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="102" t="s">
+      <c r="V4" s="104" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -20747,10 +23876,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="117" t="s">
+      <c r="J5" s="119" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="118"/>
+      <c r="K5" s="120"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -20758,9 +23887,9 @@
       <c r="Q5" s="100"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="114"/>
-      <c r="U5" s="120"/>
-      <c r="V5" s="103"/>
+      <c r="T5" s="116"/>
+      <c r="U5" s="122"/>
+      <c r="V5" s="105"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -23456,17 +26585,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="106" t="s">
+      <c r="C60" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="107"/>
-      <c r="E60" s="107"/>
-      <c r="F60" s="107"/>
-      <c r="G60" s="107"/>
-      <c r="H60" s="107"/>
-      <c r="I60" s="107"/>
-      <c r="J60" s="107"/>
-      <c r="K60" s="108"/>
+      <c r="D60" s="109"/>
+      <c r="E60" s="109"/>
+      <c r="F60" s="109"/>
+      <c r="G60" s="109"/>
+      <c r="H60" s="109"/>
+      <c r="I60" s="109"/>
+      <c r="J60" s="109"/>
+      <c r="K60" s="110"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -23775,21 +26904,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="109" t="s">
+      <c r="I1" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -23801,17 +26930,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="110" t="s">
+      <c r="C4" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="112"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="114"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -23831,13 +26960,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="113" t="s">
+      <c r="T4" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="119" t="s">
+      <c r="U4" s="121" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="102" t="s">
+      <c r="V4" s="104" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -23877,10 +27006,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="117" t="s">
+      <c r="J5" s="119" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="118"/>
+      <c r="K5" s="120"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -23888,9 +27017,9 @@
       <c r="Q5" s="101"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="114"/>
-      <c r="U5" s="120"/>
-      <c r="V5" s="103"/>
+      <c r="T5" s="116"/>
+      <c r="U5" s="122"/>
+      <c r="V5" s="105"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -26591,17 +29720,3147 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="106" t="s">
+      <c r="C60" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="107"/>
-      <c r="E60" s="107"/>
-      <c r="F60" s="107"/>
-      <c r="G60" s="107"/>
-      <c r="H60" s="107"/>
-      <c r="I60" s="107"/>
-      <c r="J60" s="107"/>
-      <c r="K60" s="108"/>
+      <c r="D60" s="109"/>
+      <c r="E60" s="109"/>
+      <c r="F60" s="109"/>
+      <c r="G60" s="109"/>
+      <c r="H60" s="109"/>
+      <c r="I60" s="109"/>
+      <c r="J60" s="109"/>
+      <c r="K60" s="110"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2C6FA4E-6F18-47E1-BB68-EA59840B35B2}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="9" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="111" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="112" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="114"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="115" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="121" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="104" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="119" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="120"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="102"/>
+      <c r="Q5" s="102"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="116"/>
+      <c r="U5" s="122"/>
+      <c r="V5" s="105"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="102"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="102"/>
+      <c r="Q6" s="102"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="52">
+        <v>18</v>
+      </c>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
+      <c r="J7" s="53"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
+      <c r="L7" s="55"/>
+      <c r="M7" s="56">
+        <v>3</v>
+      </c>
+      <c r="N7" s="57"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="53">
+        <v>1</v>
+      </c>
+      <c r="R7" s="54"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="58">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>9</v>
+      </c>
+      <c r="U7" s="58">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>561</v>
+      </c>
+      <c r="V7" s="58">
+        <f>U7/24</f>
+        <v>23.375</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="59">
+        <f>61+33</f>
+        <v>94</v>
+      </c>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="63"/>
+      <c r="N8" s="64"/>
+      <c r="O8" s="65"/>
+      <c r="P8" s="66"/>
+      <c r="Q8" s="66">
+        <v>2</v>
+      </c>
+      <c r="R8" s="67"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="68">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="69">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>2304</v>
+      </c>
+      <c r="V8" s="69">
+        <f>U8/24</f>
+        <v>96</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="70">
+        <f>90+25</f>
+        <v>115</v>
+      </c>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="73">
+        <v>2</v>
+      </c>
+      <c r="N9" s="74"/>
+      <c r="O9" s="70">
+        <v>1</v>
+      </c>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71">
+        <v>17</v>
+      </c>
+      <c r="R9" s="72"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="76">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>3240</v>
+      </c>
+      <c r="V9" s="76">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>135</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="70"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="73">
+        <v>4</v>
+      </c>
+      <c r="N10" s="74"/>
+      <c r="O10" s="70"/>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71">
+        <v>16</v>
+      </c>
+      <c r="R10" s="72"/>
+      <c r="S10" s="55"/>
+      <c r="T10" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="58">
+        <f t="shared" si="2"/>
+        <v>480</v>
+      </c>
+      <c r="V10" s="58">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="70">
+        <v>5</v>
+      </c>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
+      <c r="L11" s="55"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="55"/>
+      <c r="T11" s="58">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U11" s="58">
+        <f t="shared" si="2"/>
+        <v>122</v>
+      </c>
+      <c r="V11" s="58">
+        <f t="shared" si="3"/>
+        <v>5.083333333333333</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="59">
+        <f>720+34+216+4+1440+576</f>
+        <v>2990</v>
+      </c>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="63">
+        <v>7</v>
+      </c>
+      <c r="N12" s="64"/>
+      <c r="O12" s="65">
+        <v>1</v>
+      </c>
+      <c r="P12" s="66"/>
+      <c r="Q12" s="66">
+        <v>16</v>
+      </c>
+      <c r="R12" s="67"/>
+      <c r="S12" s="62"/>
+      <c r="T12" s="69">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U12" s="69">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>72336</v>
+      </c>
+      <c r="V12" s="69">
+        <f>U12/24</f>
+        <v>3014</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
+      <c r="I13" s="70"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="55"/>
+      <c r="T13" s="76">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="U13" s="76">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>64</v>
+      </c>
+      <c r="V13" s="76">
+        <f>U13/24</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="70">
+        <v>4</v>
+      </c>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="55"/>
+      <c r="T14" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="75">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>96</v>
+      </c>
+      <c r="V14" s="75">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>4</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="55"/>
+      <c r="T15" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="55"/>
+      <c r="T16" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I17" s="70"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U17" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V17" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="55"/>
+      <c r="T18" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="70">
+        <v>2</v>
+      </c>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70">
+        <f>20+24</f>
+        <v>44</v>
+      </c>
+      <c r="I19" s="70"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="55"/>
+      <c r="T19" s="58">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="U19" s="75">
+        <f t="shared" si="4"/>
+        <v>92</v>
+      </c>
+      <c r="V19" s="75">
+        <f t="shared" si="5"/>
+        <v>3.8333333333333335</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="74"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="55"/>
+      <c r="T20" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V20" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70">
+        <f>2*24</f>
+        <v>48</v>
+      </c>
+      <c r="I21" s="70"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="58">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="U21" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V21" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="70"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
+      <c r="J22" s="71"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="55"/>
+      <c r="T22" s="58">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U22" s="75">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="V22" s="75">
+        <f t="shared" si="5"/>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
+      <c r="I23" s="70"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="74"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="55"/>
+      <c r="T23" s="58">
+        <f t="shared" si="0"/>
+        <v>907</v>
+      </c>
+      <c r="U23" s="75">
+        <f t="shared" si="4"/>
+        <v>907</v>
+      </c>
+      <c r="V23" s="75">
+        <f t="shared" si="5"/>
+        <v>37.791666666666664</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="70">
+        <v>5</v>
+      </c>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I24" s="70"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="55"/>
+      <c r="T24" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U24" s="75">
+        <f t="shared" si="4"/>
+        <v>192</v>
+      </c>
+      <c r="V24" s="75">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="70">
+        <f>63+59</f>
+        <v>122</v>
+      </c>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70">
+        <v>1</v>
+      </c>
+      <c r="J25" s="71"/>
+      <c r="K25" s="72"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="73">
+        <v>1</v>
+      </c>
+      <c r="N25" s="74"/>
+      <c r="O25" s="70"/>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71">
+        <v>1</v>
+      </c>
+      <c r="R25" s="72"/>
+      <c r="S25" s="55"/>
+      <c r="T25" s="58">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="U25" s="75">
+        <f t="shared" si="4"/>
+        <v>2977</v>
+      </c>
+      <c r="V25" s="75">
+        <f t="shared" si="5"/>
+        <v>124.04166666666667</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="74"/>
+      <c r="O26" s="70"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="71"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="55"/>
+      <c r="T26" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="70"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="70"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="55"/>
+      <c r="T27" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="70">
+        <v>26</v>
+      </c>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="73">
+        <v>2</v>
+      </c>
+      <c r="N28" s="74"/>
+      <c r="O28" s="70">
+        <v>1</v>
+      </c>
+      <c r="P28" s="71"/>
+      <c r="Q28" s="71">
+        <v>5</v>
+      </c>
+      <c r="R28" s="72"/>
+      <c r="S28" s="55"/>
+      <c r="T28" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="75">
+        <f t="shared" si="4"/>
+        <v>816</v>
+      </c>
+      <c r="V28" s="75">
+        <f t="shared" si="5"/>
+        <v>34</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="70">
+        <v>49</v>
+      </c>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70">
+        <v>5</v>
+      </c>
+      <c r="J29" s="71"/>
+      <c r="K29" s="72"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="73"/>
+      <c r="N29" s="74"/>
+      <c r="O29" s="70">
+        <v>1</v>
+      </c>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71"/>
+      <c r="R29" s="72"/>
+      <c r="S29" s="55"/>
+      <c r="T29" s="58">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U29" s="75">
+        <f t="shared" si="4"/>
+        <v>1205</v>
+      </c>
+      <c r="V29" s="75">
+        <f t="shared" si="5"/>
+        <v>50.208333333333336</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="70">
+        <v>11</v>
+      </c>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="74"/>
+      <c r="O30" s="70"/>
+      <c r="P30" s="71"/>
+      <c r="Q30" s="71">
+        <v>1</v>
+      </c>
+      <c r="R30" s="72"/>
+      <c r="S30" s="55"/>
+      <c r="T30" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="75">
+        <f t="shared" si="4"/>
+        <v>288</v>
+      </c>
+      <c r="V30" s="75">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="70"/>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="70">
+        <v>4</v>
+      </c>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="74"/>
+      <c r="O32" s="70"/>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="55"/>
+      <c r="T32" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="75">
+        <f t="shared" si="4"/>
+        <v>96</v>
+      </c>
+      <c r="V32" s="75">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="70"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="73"/>
+      <c r="N33" s="74"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="55"/>
+      <c r="T33" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="70">
+        <f>62</f>
+        <v>62</v>
+      </c>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
+      <c r="J34" s="71"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
+      <c r="L34" s="55"/>
+      <c r="M34" s="73">
+        <v>2</v>
+      </c>
+      <c r="N34" s="74"/>
+      <c r="O34" s="70"/>
+      <c r="P34" s="71">
+        <v>12</v>
+      </c>
+      <c r="Q34" s="71"/>
+      <c r="R34" s="72"/>
+      <c r="S34" s="55"/>
+      <c r="T34" s="58">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="U34" s="75">
+        <f t="shared" si="4"/>
+        <v>1550</v>
+      </c>
+      <c r="V34" s="75">
+        <f t="shared" si="5"/>
+        <v>64.583333333333329</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="72"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="74"/>
+      <c r="O35" s="70"/>
+      <c r="P35" s="71"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="72"/>
+      <c r="S35" s="55"/>
+      <c r="T35" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="73"/>
+      <c r="N36" s="74"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="71"/>
+      <c r="Q36" s="71"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="55"/>
+      <c r="T36" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="59">
+        <f>864+2808+88</f>
+        <v>3760</v>
+      </c>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59">
+        <v>5</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>3</v>
+      </c>
+      <c r="K37" s="61">
+        <v>3</v>
+      </c>
+      <c r="L37" s="62"/>
+      <c r="M37" s="63">
+        <v>21</v>
+      </c>
+      <c r="N37" s="64"/>
+      <c r="O37" s="65"/>
+      <c r="P37" s="66"/>
+      <c r="Q37" s="66">
+        <v>38</v>
+      </c>
+      <c r="R37" s="67"/>
+      <c r="S37" s="62"/>
+      <c r="T37" s="77">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="U37" s="77">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>22927</v>
+      </c>
+      <c r="V37" s="77">
+        <f>U37/6</f>
+        <v>3821.1666666666665</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="73"/>
+      <c r="N38" s="74"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="71"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="55"/>
+      <c r="T38" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="75">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="75">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="74"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="71"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="95"/>
+      <c r="T39" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U39" s="75">
+        <f>C39*24+M39*24+O39*24+Q39*24+T39</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="75">
+        <f>U39/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="59">
+        <v>23</v>
+      </c>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
+      <c r="L40" s="62"/>
+      <c r="M40" s="63">
+        <v>1</v>
+      </c>
+      <c r="N40" s="64"/>
+      <c r="O40" s="65">
+        <v>1</v>
+      </c>
+      <c r="P40" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q40" s="66">
+        <v>1</v>
+      </c>
+      <c r="R40" s="67"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="77">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="U40" s="77">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>656</v>
+      </c>
+      <c r="V40" s="77">
+        <f>U40/24</f>
+        <v>27.333333333333332</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="82">
+        <v>73</v>
+      </c>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="85"/>
+      <c r="M41" s="86">
+        <v>10</v>
+      </c>
+      <c r="N41" s="87"/>
+      <c r="O41" s="82">
+        <v>1</v>
+      </c>
+      <c r="P41" s="83"/>
+      <c r="Q41" s="83">
+        <v>8</v>
+      </c>
+      <c r="R41" s="84"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="88">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>1104</v>
+      </c>
+      <c r="V41" s="88">
+        <f>U41/12</f>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="71"/>
+      <c r="K42" s="72"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="73"/>
+      <c r="N42" s="74"/>
+      <c r="O42" s="70"/>
+      <c r="P42" s="71"/>
+      <c r="Q42" s="71"/>
+      <c r="R42" s="72"/>
+      <c r="S42" s="55"/>
+      <c r="T42" s="75"/>
+      <c r="U42" s="75"/>
+      <c r="V42" s="75"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="65">
+        <f>7776+3024+8424+5508+3024+4860</f>
+        <v>32616</v>
+      </c>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65">
+        <v>3</v>
+      </c>
+      <c r="I43" s="65">
+        <v>7</v>
+      </c>
+      <c r="J43" s="66">
+        <f>11*6+4</f>
+        <v>70</v>
+      </c>
+      <c r="K43" s="67">
+        <f>69*6+7</f>
+        <v>421</v>
+      </c>
+      <c r="L43" s="62"/>
+      <c r="M43" s="63">
+        <v>370</v>
+      </c>
+      <c r="N43" s="64"/>
+      <c r="O43" s="65">
+        <v>45</v>
+      </c>
+      <c r="P43" s="66"/>
+      <c r="Q43" s="66">
+        <v>434</v>
+      </c>
+      <c r="R43" s="67"/>
+      <c r="S43" s="62"/>
+      <c r="T43" s="77">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>501</v>
+      </c>
+      <c r="U43" s="77">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>201291</v>
+      </c>
+      <c r="V43" s="77">
+        <f>U43/6</f>
+        <v>33548.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="70"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="71"/>
+      <c r="K44" s="72"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="73"/>
+      <c r="N44" s="74"/>
+      <c r="O44" s="70"/>
+      <c r="P44" s="71"/>
+      <c r="Q44" s="71"/>
+      <c r="R44" s="72"/>
+      <c r="S44" s="55"/>
+      <c r="T44" s="75"/>
+      <c r="U44" s="75"/>
+      <c r="V44" s="75"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="70"/>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="70"/>
+      <c r="I45" s="70"/>
+      <c r="J45" s="71"/>
+      <c r="K45" s="72"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="73"/>
+      <c r="N45" s="74"/>
+      <c r="O45" s="70"/>
+      <c r="P45" s="71"/>
+      <c r="Q45" s="71"/>
+      <c r="R45" s="72"/>
+      <c r="S45" s="55"/>
+      <c r="T45" s="75">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="75">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="75">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="73"/>
+      <c r="N46" s="74"/>
+      <c r="O46" s="70"/>
+      <c r="P46" s="71"/>
+      <c r="Q46" s="71"/>
+      <c r="R46" s="72"/>
+      <c r="S46" s="55"/>
+      <c r="T46" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="75">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="75">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="65">
+        <f>432+106+2160+67</f>
+        <v>2765</v>
+      </c>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
+      <c r="I47" s="65"/>
+      <c r="J47" s="66">
+        <v>1</v>
+      </c>
+      <c r="K47" s="67">
+        <v>4</v>
+      </c>
+      <c r="L47" s="62"/>
+      <c r="M47" s="63">
+        <v>10</v>
+      </c>
+      <c r="N47" s="64"/>
+      <c r="O47" s="65">
+        <v>9</v>
+      </c>
+      <c r="P47" s="66">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="66">
+        <v>9</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
+      <c r="S47" s="62"/>
+      <c r="T47" s="77">
+        <f t="shared" si="7"/>
+        <v>13</v>
+      </c>
+      <c r="U47" s="77">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>16771</v>
+      </c>
+      <c r="V47" s="77">
+        <f>U47/6</f>
+        <v>2795.1666666666665</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
+      <c r="I48" s="70"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="72"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="73"/>
+      <c r="N48" s="74"/>
+      <c r="O48" s="70"/>
+      <c r="P48" s="71"/>
+      <c r="Q48" s="71"/>
+      <c r="R48" s="72"/>
+      <c r="S48" s="55"/>
+      <c r="T48" s="75">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="U48" s="75">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="V48" s="75">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="70"/>
+      <c r="I49" s="70"/>
+      <c r="J49" s="71"/>
+      <c r="K49" s="72"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="74"/>
+      <c r="O49" s="70"/>
+      <c r="P49" s="71"/>
+      <c r="Q49" s="71"/>
+      <c r="R49" s="72"/>
+      <c r="S49" s="55"/>
+      <c r="T49" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="70"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="70"/>
+      <c r="F50" s="70"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
+      <c r="J50" s="71"/>
+      <c r="K50" s="72"/>
+      <c r="L50" s="55"/>
+      <c r="M50" s="73"/>
+      <c r="N50" s="74"/>
+      <c r="O50" s="70"/>
+      <c r="P50" s="71"/>
+      <c r="Q50" s="71"/>
+      <c r="R50" s="72"/>
+      <c r="S50" s="55"/>
+      <c r="T50" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="65"/>
+      <c r="I51" s="65"/>
+      <c r="J51" s="66"/>
+      <c r="K51" s="67"/>
+      <c r="L51" s="62"/>
+      <c r="M51" s="63"/>
+      <c r="N51" s="64"/>
+      <c r="O51" s="65"/>
+      <c r="P51" s="66"/>
+      <c r="Q51" s="66"/>
+      <c r="R51" s="67"/>
+      <c r="S51" s="62"/>
+      <c r="T51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="77">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>204</v>
+      </c>
+      <c r="V51" s="77">
+        <f>U51/6</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="70"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="70"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="71"/>
+      <c r="K52" s="72"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="73"/>
+      <c r="N52" s="74"/>
+      <c r="O52" s="70"/>
+      <c r="P52" s="71"/>
+      <c r="Q52" s="71"/>
+      <c r="R52" s="72"/>
+      <c r="S52" s="55"/>
+      <c r="T52" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="75">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="70">
+        <v>9</v>
+      </c>
+      <c r="D53" s="70"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="70"/>
+      <c r="H53" s="70"/>
+      <c r="I53" s="70"/>
+      <c r="J53" s="71"/>
+      <c r="K53" s="72"/>
+      <c r="L53" s="55"/>
+      <c r="M53" s="73"/>
+      <c r="N53" s="74"/>
+      <c r="O53" s="70"/>
+      <c r="P53" s="71"/>
+      <c r="Q53" s="71"/>
+      <c r="R53" s="72"/>
+      <c r="S53" s="55"/>
+      <c r="T53" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="75">
+        <f t="shared" si="10"/>
+        <v>216</v>
+      </c>
+      <c r="V53" s="75">
+        <f t="shared" si="9"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="71"/>
+      <c r="K54" s="72"/>
+      <c r="L54" s="55"/>
+      <c r="M54" s="73"/>
+      <c r="N54" s="74"/>
+      <c r="O54" s="70"/>
+      <c r="P54" s="71"/>
+      <c r="Q54" s="71"/>
+      <c r="R54" s="72"/>
+      <c r="S54" s="55"/>
+      <c r="T54" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="70"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="70"/>
+      <c r="I55" s="70"/>
+      <c r="J55" s="71"/>
+      <c r="K55" s="72"/>
+      <c r="L55" s="55"/>
+      <c r="M55" s="73"/>
+      <c r="N55" s="74"/>
+      <c r="O55" s="70"/>
+      <c r="P55" s="71"/>
+      <c r="Q55" s="71"/>
+      <c r="R55" s="72"/>
+      <c r="S55" s="55"/>
+      <c r="T55" s="75"/>
+      <c r="U55" s="75"/>
+      <c r="V55" s="75"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="70"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="70"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="71"/>
+      <c r="K56" s="72"/>
+      <c r="L56" s="55"/>
+      <c r="M56" s="73"/>
+      <c r="N56" s="74"/>
+      <c r="O56" s="70"/>
+      <c r="P56" s="71"/>
+      <c r="Q56" s="71"/>
+      <c r="R56" s="72"/>
+      <c r="S56" s="55"/>
+      <c r="T56" s="75"/>
+      <c r="U56" s="75"/>
+      <c r="V56" s="75"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="70"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="70"/>
+      <c r="I57" s="70"/>
+      <c r="J57" s="71"/>
+      <c r="K57" s="72"/>
+      <c r="L57" s="55"/>
+      <c r="M57" s="73"/>
+      <c r="N57" s="74"/>
+      <c r="O57" s="70"/>
+      <c r="P57" s="71"/>
+      <c r="Q57" s="71"/>
+      <c r="R57" s="72"/>
+      <c r="S57" s="55"/>
+      <c r="T57" s="75"/>
+      <c r="U57" s="75"/>
+      <c r="V57" s="75"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>42794</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>1192</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>39</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>74</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>457</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>433</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>61</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>28</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>549</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>3</v>
+      </c>
+      <c r="S58" s="55"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>1793</v>
+      </c>
+      <c r="U58" s="90">
+        <f>SUM(U7:U57)</f>
+        <v>330779</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>43977.583333333328</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="108" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="109"/>
+      <c r="E60" s="109"/>
+      <c r="F60" s="109"/>
+      <c r="G60" s="109"/>
+      <c r="H60" s="109"/>
+      <c r="I60" s="109"/>
+      <c r="J60" s="109"/>
+      <c r="K60" s="110"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>

--- a/GBDS JUNE FILES 2026/INVENTORY COUNT SHEET - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/INVENTORY COUNT SHEET - JUNE 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A12E9452-FC22-416F-91E9-8EB41A63A4C0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0C71558-F8EF-4974-9572-5C2E031C3EC2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="9" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="10" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="06-09-2026" sheetId="61" r:id="rId8"/>
     <sheet name="06-10-2026" sheetId="62" r:id="rId9"/>
     <sheet name="06-11-2026" sheetId="63" r:id="rId10"/>
+    <sheet name="06-12-2026" sheetId="64" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'06-01-2026'!$A$1:$W$59</definedName>
@@ -34,6 +35,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="7">'06-09-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'06-10-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="9">'06-11-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'06-12-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -52,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="74">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -1261,7 +1263,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1547,6 +1549,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1984,21 +1989,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="112" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -2010,17 +2015,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="115"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -2040,13 +2045,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="116" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="117" t="s">
+      <c r="U4" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="105" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2086,10 +2091,10 @@
       <c r="I5" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="106" t="s">
+      <c r="J5" s="107" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="107"/>
+      <c r="K5" s="108"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2097,9 +2102,9 @@
       <c r="Q5" s="89"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="118"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="119"/>
+      <c r="V5" s="106"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -4630,17 +4635,17 @@
       <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="108" t="s">
+      <c r="C62" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="109"/>
-      <c r="E62" s="109"/>
-      <c r="F62" s="109"/>
-      <c r="G62" s="109"/>
-      <c r="H62" s="109"/>
-      <c r="I62" s="109"/>
-      <c r="J62" s="109"/>
-      <c r="K62" s="110"/>
+      <c r="D62" s="110"/>
+      <c r="E62" s="110"/>
+      <c r="F62" s="110"/>
+      <c r="G62" s="110"/>
+      <c r="H62" s="110"/>
+      <c r="I62" s="110"/>
+      <c r="J62" s="110"/>
+      <c r="K62" s="111"/>
       <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
@@ -4949,21 +4954,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="112" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -4975,17 +4980,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="115"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -5005,13 +5010,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="116" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="122" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="105" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -5051,10 +5056,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="120" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="121"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -5062,9 +5067,9 @@
       <c r="Q5" s="103"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="106"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -7485,9 +7490,7 @@
       <c r="B52" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="C52" s="70">
-        <v>9</v>
-      </c>
+      <c r="C52" s="70"/>
       <c r="D52" s="70"/>
       <c r="E52" s="70"/>
       <c r="F52" s="70"/>
@@ -7510,11 +7513,11 @@
       </c>
       <c r="U52" s="75">
         <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
-        <v>216</v>
+        <v>0</v>
       </c>
       <c r="V52" s="75">
         <f t="shared" si="9"/>
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.25">
@@ -7525,7 +7528,9 @@
       <c r="B53" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="70"/>
+      <c r="C53" s="70">
+        <v>9</v>
+      </c>
       <c r="D53" s="70"/>
       <c r="E53" s="70"/>
       <c r="F53" s="70"/>
@@ -7548,11 +7553,11 @@
       </c>
       <c r="U53" s="75">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="V53" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -7749,17 +7754,3145 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="110"/>
+      <c r="E60" s="110"/>
+      <c r="F60" s="110"/>
+      <c r="G60" s="110"/>
+      <c r="H60" s="110"/>
+      <c r="I60" s="110"/>
+      <c r="J60" s="110"/>
+      <c r="K60" s="111"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80837BAA-A524-43AB-A68D-722EBC86F0F3}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="9" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="112" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="113" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="115"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="116" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="122" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="105" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="120" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="121"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="104"/>
+      <c r="Q5" s="104"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="106"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="104"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="104"/>
+      <c r="Q6" s="104"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="52">
+        <v>15</v>
+      </c>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
+      <c r="J7" s="53"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
+      <c r="L7" s="55"/>
+      <c r="M7" s="56">
+        <v>4</v>
+      </c>
+      <c r="N7" s="57"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="53">
+        <v>1</v>
+      </c>
+      <c r="R7" s="54"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="58">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>9</v>
+      </c>
+      <c r="U7" s="58">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>513</v>
+      </c>
+      <c r="V7" s="58">
+        <f>U7/24</f>
+        <v>21.375</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="59">
+        <f>33+57</f>
+        <v>90</v>
+      </c>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="63">
+        <v>3</v>
+      </c>
+      <c r="N8" s="64"/>
+      <c r="O8" s="65">
+        <v>1</v>
+      </c>
+      <c r="P8" s="66"/>
+      <c r="Q8" s="66">
+        <v>2</v>
+      </c>
+      <c r="R8" s="67"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="68">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="69">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>2304</v>
+      </c>
+      <c r="V8" s="69">
+        <f>U8/24</f>
+        <v>96</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="70">
+        <f>90+19</f>
+        <v>109</v>
+      </c>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="73">
+        <v>2</v>
+      </c>
+      <c r="N9" s="74"/>
+      <c r="O9" s="70">
+        <v>3</v>
+      </c>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71"/>
+      <c r="R9" s="72"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="76">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>2736</v>
+      </c>
+      <c r="V9" s="76">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>114</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="70"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="74"/>
+      <c r="O10" s="70"/>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71"/>
+      <c r="R10" s="72"/>
+      <c r="S10" s="55"/>
+      <c r="T10" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V10" s="58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="70">
+        <v>5</v>
+      </c>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
+      <c r="L11" s="55"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="55"/>
+      <c r="T11" s="58">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U11" s="58">
+        <f t="shared" si="2"/>
+        <v>122</v>
+      </c>
+      <c r="V11" s="58">
+        <f t="shared" si="3"/>
+        <v>5.083333333333333</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="59">
+        <f>720+34+1440+144+41+576</f>
+        <v>2955</v>
+      </c>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="63">
+        <v>12</v>
+      </c>
+      <c r="N12" s="64"/>
+      <c r="O12" s="65">
+        <v>10</v>
+      </c>
+      <c r="P12" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q12" s="66">
+        <v>8</v>
+      </c>
+      <c r="R12" s="67">
+        <v>12</v>
+      </c>
+      <c r="S12" s="62"/>
+      <c r="T12" s="69">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="U12" s="69">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>71664</v>
+      </c>
+      <c r="V12" s="69">
+        <f>U12/24</f>
+        <v>2986</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
+      <c r="I13" s="70"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="55"/>
+      <c r="T13" s="76">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="U13" s="76">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>64</v>
+      </c>
+      <c r="V13" s="76">
+        <f>U13/24</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="70">
+        <v>4</v>
+      </c>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="55"/>
+      <c r="T14" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="75">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>96</v>
+      </c>
+      <c r="V14" s="75">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>4</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="55"/>
+      <c r="T15" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="55"/>
+      <c r="T16" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I17" s="70"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U17" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V17" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="55"/>
+      <c r="T18" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="70">
+        <v>2</v>
+      </c>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70">
+        <f>20+24</f>
+        <v>44</v>
+      </c>
+      <c r="I19" s="70"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="55"/>
+      <c r="T19" s="58">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="U19" s="75">
+        <f t="shared" si="4"/>
+        <v>92</v>
+      </c>
+      <c r="V19" s="75">
+        <f t="shared" si="5"/>
+        <v>3.8333333333333335</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="74"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="55"/>
+      <c r="T20" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V20" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70">
+        <f>2*24</f>
+        <v>48</v>
+      </c>
+      <c r="I21" s="70"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="58">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="U21" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V21" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="70"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70">
+        <v>20</v>
+      </c>
+      <c r="I22" s="70"/>
+      <c r="J22" s="71"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="55"/>
+      <c r="T22" s="58">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U22" s="75">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="V22" s="75">
+        <f t="shared" si="5"/>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
+      <c r="I23" s="70"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="74"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="55"/>
+      <c r="T23" s="58">
+        <f t="shared" si="0"/>
+        <v>907</v>
+      </c>
+      <c r="U23" s="75">
+        <f t="shared" si="4"/>
+        <v>907</v>
+      </c>
+      <c r="V23" s="75">
+        <f t="shared" si="5"/>
+        <v>37.791666666666664</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="70">
+        <v>5</v>
+      </c>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I24" s="70"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="55"/>
+      <c r="T24" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U24" s="75">
+        <f t="shared" si="4"/>
+        <v>192</v>
+      </c>
+      <c r="V24" s="75">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="70">
+        <f>63+53</f>
+        <v>116</v>
+      </c>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70">
+        <v>1</v>
+      </c>
+      <c r="J25" s="71"/>
+      <c r="K25" s="72"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="73">
+        <v>1</v>
+      </c>
+      <c r="N25" s="74"/>
+      <c r="O25" s="70"/>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71">
+        <v>2</v>
+      </c>
+      <c r="R25" s="72"/>
+      <c r="S25" s="55"/>
+      <c r="T25" s="58">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="U25" s="75">
+        <f t="shared" si="4"/>
+        <v>2857</v>
+      </c>
+      <c r="V25" s="75">
+        <f t="shared" si="5"/>
+        <v>119.04166666666667</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="74"/>
+      <c r="O26" s="70"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="71"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="55"/>
+      <c r="T26" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="70"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="70"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="55"/>
+      <c r="T27" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="70">
+        <v>21</v>
+      </c>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="73">
+        <v>2</v>
+      </c>
+      <c r="N28" s="74"/>
+      <c r="O28" s="70">
+        <v>2</v>
+      </c>
+      <c r="P28" s="71"/>
+      <c r="Q28" s="71">
+        <v>1</v>
+      </c>
+      <c r="R28" s="72"/>
+      <c r="S28" s="55"/>
+      <c r="T28" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="75">
+        <f t="shared" si="4"/>
+        <v>624</v>
+      </c>
+      <c r="V28" s="75">
+        <f t="shared" si="5"/>
+        <v>26</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="70">
+        <v>49</v>
+      </c>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70">
+        <v>5</v>
+      </c>
+      <c r="J29" s="71"/>
+      <c r="K29" s="72"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="73"/>
+      <c r="N29" s="74"/>
+      <c r="O29" s="70">
+        <v>1</v>
+      </c>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71"/>
+      <c r="R29" s="72"/>
+      <c r="S29" s="55"/>
+      <c r="T29" s="58">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U29" s="75">
+        <f t="shared" si="4"/>
+        <v>1205</v>
+      </c>
+      <c r="V29" s="75">
+        <f t="shared" si="5"/>
+        <v>50.208333333333336</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="70">
+        <v>11</v>
+      </c>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="74"/>
+      <c r="O30" s="70"/>
+      <c r="P30" s="71"/>
+      <c r="Q30" s="71">
+        <v>1</v>
+      </c>
+      <c r="R30" s="72"/>
+      <c r="S30" s="55"/>
+      <c r="T30" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="75">
+        <f t="shared" si="4"/>
+        <v>288</v>
+      </c>
+      <c r="V30" s="75">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="70"/>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="70">
+        <v>2</v>
+      </c>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="74"/>
+      <c r="O32" s="70">
+        <v>2</v>
+      </c>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="55"/>
+      <c r="T32" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="75">
+        <f t="shared" si="4"/>
+        <v>96</v>
+      </c>
+      <c r="V32" s="75">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="70"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="73"/>
+      <c r="N33" s="74"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="55"/>
+      <c r="T33" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="70">
+        <v>61</v>
+      </c>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
+      <c r="J34" s="71"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
+      <c r="L34" s="55"/>
+      <c r="M34" s="73">
+        <v>2</v>
+      </c>
+      <c r="N34" s="74"/>
+      <c r="O34" s="70">
+        <v>1</v>
+      </c>
+      <c r="P34" s="71">
+        <v>12</v>
+      </c>
+      <c r="Q34" s="71"/>
+      <c r="R34" s="72"/>
+      <c r="S34" s="55"/>
+      <c r="T34" s="58">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="U34" s="75">
+        <f t="shared" si="4"/>
+        <v>1550</v>
+      </c>
+      <c r="V34" s="75">
+        <f t="shared" si="5"/>
+        <v>64.583333333333329</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="72"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="74"/>
+      <c r="O35" s="70"/>
+      <c r="P35" s="71"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="72"/>
+      <c r="S35" s="55"/>
+      <c r="T35" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="73"/>
+      <c r="N36" s="74"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="71"/>
+      <c r="Q36" s="71"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="55"/>
+      <c r="T36" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="59">
+        <f>864+2592+73</f>
+        <v>3529</v>
+      </c>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59">
+        <v>5</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>3</v>
+      </c>
+      <c r="K37" s="61">
+        <v>3</v>
+      </c>
+      <c r="L37" s="62"/>
+      <c r="M37" s="63">
+        <v>33</v>
+      </c>
+      <c r="N37" s="64"/>
+      <c r="O37" s="65">
+        <v>66</v>
+      </c>
+      <c r="P37" s="66"/>
+      <c r="Q37" s="66">
+        <v>1</v>
+      </c>
+      <c r="R37" s="67"/>
+      <c r="S37" s="62"/>
+      <c r="T37" s="77">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="U37" s="77">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>21787</v>
+      </c>
+      <c r="V37" s="77">
+        <f>U37/6</f>
+        <v>3631.1666666666665</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="73"/>
+      <c r="N38" s="74"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="71"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="55"/>
+      <c r="T38" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="75">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="75">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="74"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="71"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="95"/>
+      <c r="T39" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U39" s="75">
+        <f>C39*24+M39*24+O39*24+Q39*24+T39</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="75">
+        <f>U39/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="59"/>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
+      <c r="L40" s="62"/>
+      <c r="M40" s="63"/>
+      <c r="N40" s="64"/>
+      <c r="O40" s="65"/>
+      <c r="P40" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q40" s="66"/>
+      <c r="R40" s="67"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="77">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="U40" s="77">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>32</v>
+      </c>
+      <c r="V40" s="77">
+        <f>U40/24</f>
+        <v>1.3333333333333333</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="82">
+        <v>48</v>
+      </c>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="85"/>
+      <c r="M41" s="86">
+        <v>14</v>
+      </c>
+      <c r="N41" s="87"/>
+      <c r="O41" s="82">
+        <v>6</v>
+      </c>
+      <c r="P41" s="83"/>
+      <c r="Q41" s="83">
+        <v>4</v>
+      </c>
+      <c r="R41" s="84"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="88">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>864</v>
+      </c>
+      <c r="V41" s="88">
+        <f>U41/12</f>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="71"/>
+      <c r="K42" s="72"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="73"/>
+      <c r="N42" s="74"/>
+      <c r="O42" s="70"/>
+      <c r="P42" s="71"/>
+      <c r="Q42" s="71"/>
+      <c r="R42" s="72"/>
+      <c r="S42" s="55"/>
+      <c r="T42" s="75"/>
+      <c r="U42" s="75"/>
+      <c r="V42" s="75"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="65">
+        <f>7776+3024+8424+5508+3024+3564+91</f>
+        <v>31411</v>
+      </c>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65"/>
+      <c r="I43" s="65">
+        <f>7</f>
+        <v>7</v>
+      </c>
+      <c r="J43" s="66">
+        <f>13*6</f>
+        <v>78</v>
+      </c>
+      <c r="K43" s="67">
+        <f>69*6+7</f>
+        <v>421</v>
+      </c>
+      <c r="L43" s="62"/>
+      <c r="M43" s="63">
+        <v>333</v>
+      </c>
+      <c r="N43" s="64"/>
+      <c r="O43" s="65">
+        <v>374</v>
+      </c>
+      <c r="P43" s="66"/>
+      <c r="Q43" s="66">
+        <v>162</v>
+      </c>
+      <c r="R43" s="67"/>
+      <c r="S43" s="62"/>
+      <c r="T43" s="77">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>506</v>
+      </c>
+      <c r="U43" s="77">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>194186</v>
+      </c>
+      <c r="V43" s="77">
+        <f>U43/6</f>
+        <v>32364.333333333332</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="70"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="71"/>
+      <c r="K44" s="72"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="73"/>
+      <c r="N44" s="74"/>
+      <c r="O44" s="70"/>
+      <c r="P44" s="71"/>
+      <c r="Q44" s="71"/>
+      <c r="R44" s="72"/>
+      <c r="S44" s="55"/>
+      <c r="T44" s="75"/>
+      <c r="U44" s="75"/>
+      <c r="V44" s="75"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="70"/>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="70"/>
+      <c r="I45" s="70"/>
+      <c r="J45" s="71"/>
+      <c r="K45" s="72"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="73"/>
+      <c r="N45" s="74"/>
+      <c r="O45" s="70"/>
+      <c r="P45" s="71"/>
+      <c r="Q45" s="71"/>
+      <c r="R45" s="72"/>
+      <c r="S45" s="55"/>
+      <c r="T45" s="75">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="75">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="75">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="73"/>
+      <c r="N46" s="74"/>
+      <c r="O46" s="70"/>
+      <c r="P46" s="71"/>
+      <c r="Q46" s="71"/>
+      <c r="R46" s="72"/>
+      <c r="S46" s="55"/>
+      <c r="T46" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="75">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="75">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="65">
+        <f>432+106+2160+67</f>
+        <v>2765</v>
+      </c>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
+      <c r="I47" s="65"/>
+      <c r="J47" s="66">
+        <v>1</v>
+      </c>
+      <c r="K47" s="67">
+        <v>4</v>
+      </c>
+      <c r="L47" s="62"/>
+      <c r="M47" s="63">
+        <v>8</v>
+      </c>
+      <c r="N47" s="64"/>
+      <c r="O47" s="65">
+        <v>9</v>
+      </c>
+      <c r="P47" s="66">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="66">
+        <v>6</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
+      <c r="S47" s="62"/>
+      <c r="T47" s="77">
+        <f t="shared" si="7"/>
+        <v>13</v>
+      </c>
+      <c r="U47" s="77">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>16741</v>
+      </c>
+      <c r="V47" s="77">
+        <f>U47/6</f>
+        <v>2790.1666666666665</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
+      <c r="I48" s="70"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="72"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="73"/>
+      <c r="N48" s="74"/>
+      <c r="O48" s="70"/>
+      <c r="P48" s="71"/>
+      <c r="Q48" s="71"/>
+      <c r="R48" s="72"/>
+      <c r="S48" s="55"/>
+      <c r="T48" s="75">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="U48" s="75">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="V48" s="75">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="70"/>
+      <c r="I49" s="70"/>
+      <c r="J49" s="71"/>
+      <c r="K49" s="72"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="74"/>
+      <c r="O49" s="70"/>
+      <c r="P49" s="71"/>
+      <c r="Q49" s="71"/>
+      <c r="R49" s="72"/>
+      <c r="S49" s="55"/>
+      <c r="T49" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="70"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="70"/>
+      <c r="F50" s="70"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
+      <c r="J50" s="71"/>
+      <c r="K50" s="72"/>
+      <c r="L50" s="55"/>
+      <c r="M50" s="73"/>
+      <c r="N50" s="74"/>
+      <c r="O50" s="70"/>
+      <c r="P50" s="71"/>
+      <c r="Q50" s="71"/>
+      <c r="R50" s="72"/>
+      <c r="S50" s="55"/>
+      <c r="T50" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="65"/>
+      <c r="I51" s="65"/>
+      <c r="J51" s="66"/>
+      <c r="K51" s="67"/>
+      <c r="L51" s="62"/>
+      <c r="M51" s="63"/>
+      <c r="N51" s="64"/>
+      <c r="O51" s="65"/>
+      <c r="P51" s="66"/>
+      <c r="Q51" s="66"/>
+      <c r="R51" s="67"/>
+      <c r="S51" s="62"/>
+      <c r="T51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="77">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>204</v>
+      </c>
+      <c r="V51" s="77">
+        <f>U51/6</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="70"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="70"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="71"/>
+      <c r="K52" s="72"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="73"/>
+      <c r="N52" s="74"/>
+      <c r="O52" s="70"/>
+      <c r="P52" s="71"/>
+      <c r="Q52" s="71"/>
+      <c r="R52" s="72"/>
+      <c r="S52" s="55"/>
+      <c r="T52" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="75">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="70">
+        <v>9</v>
+      </c>
+      <c r="D53" s="70"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="70"/>
+      <c r="H53" s="70"/>
+      <c r="I53" s="70"/>
+      <c r="J53" s="71"/>
+      <c r="K53" s="72"/>
+      <c r="L53" s="55"/>
+      <c r="M53" s="73"/>
+      <c r="N53" s="74"/>
+      <c r="O53" s="70"/>
+      <c r="P53" s="71"/>
+      <c r="Q53" s="71"/>
+      <c r="R53" s="72"/>
+      <c r="S53" s="55"/>
+      <c r="T53" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="75">
+        <f t="shared" si="10"/>
+        <v>216</v>
+      </c>
+      <c r="V53" s="75">
+        <f t="shared" si="9"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="71"/>
+      <c r="K54" s="72"/>
+      <c r="L54" s="55"/>
+      <c r="M54" s="73"/>
+      <c r="N54" s="74"/>
+      <c r="O54" s="70"/>
+      <c r="P54" s="71"/>
+      <c r="Q54" s="71"/>
+      <c r="R54" s="72"/>
+      <c r="S54" s="55"/>
+      <c r="T54" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="70"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="70"/>
+      <c r="I55" s="70"/>
+      <c r="J55" s="71"/>
+      <c r="K55" s="72"/>
+      <c r="L55" s="55"/>
+      <c r="M55" s="73"/>
+      <c r="N55" s="74"/>
+      <c r="O55" s="70"/>
+      <c r="P55" s="71"/>
+      <c r="Q55" s="71"/>
+      <c r="R55" s="72"/>
+      <c r="S55" s="55"/>
+      <c r="T55" s="75"/>
+      <c r="U55" s="75"/>
+      <c r="V55" s="75"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="70"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="70"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="71"/>
+      <c r="K56" s="72"/>
+      <c r="L56" s="55"/>
+      <c r="M56" s="73"/>
+      <c r="N56" s="74"/>
+      <c r="O56" s="70"/>
+      <c r="P56" s="71"/>
+      <c r="Q56" s="71"/>
+      <c r="R56" s="72"/>
+      <c r="S56" s="55"/>
+      <c r="T56" s="75"/>
+      <c r="U56" s="75"/>
+      <c r="V56" s="75"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="70"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="70"/>
+      <c r="I57" s="70"/>
+      <c r="J57" s="71"/>
+      <c r="K57" s="72"/>
+      <c r="L57" s="55"/>
+      <c r="M57" s="73"/>
+      <c r="N57" s="74"/>
+      <c r="O57" s="70"/>
+      <c r="P57" s="71"/>
+      <c r="Q57" s="71"/>
+      <c r="R57" s="72"/>
+      <c r="S57" s="55"/>
+      <c r="T57" s="75"/>
+      <c r="U57" s="75"/>
+      <c r="V57" s="75"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>41248</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>1209</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>19</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>82</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>457</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>414</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>476</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>40</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>188</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>15</v>
+      </c>
+      <c r="S58" s="55"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>1822</v>
+      </c>
+      <c r="U58" s="90">
+        <f>SUM(U7:U57)</f>
+        <v>319624</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>42468.416666666664</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="109" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="110"/>
+      <c r="E60" s="110"/>
+      <c r="F60" s="110"/>
+      <c r="G60" s="110"/>
+      <c r="H60" s="110"/>
+      <c r="I60" s="110"/>
+      <c r="J60" s="110"/>
+      <c r="K60" s="111"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -8068,21 +11201,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="112" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -8094,17 +11227,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="115"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -8124,13 +11257,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="116" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="122" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="105" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -8170,10 +11303,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="120" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="121"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -8181,9 +11314,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="106"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -10895,17 +14028,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="110"/>
+      <c r="E60" s="110"/>
+      <c r="F60" s="110"/>
+      <c r="G60" s="110"/>
+      <c r="H60" s="110"/>
+      <c r="I60" s="110"/>
+      <c r="J60" s="110"/>
+      <c r="K60" s="111"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -11214,21 +14347,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="112" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -11240,17 +14373,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="115"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -11270,13 +14403,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="116" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="122" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="105" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -11316,10 +14449,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="120" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="121"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -11327,9 +14460,9 @@
       <c r="Q5" s="96"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="106"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -14064,17 +17197,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="110"/>
+      <c r="E60" s="110"/>
+      <c r="F60" s="110"/>
+      <c r="G60" s="110"/>
+      <c r="H60" s="110"/>
+      <c r="I60" s="110"/>
+      <c r="J60" s="110"/>
+      <c r="K60" s="111"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -14383,21 +17516,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="112" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -14409,17 +17542,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="115"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -14439,13 +17572,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="116" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="122" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="105" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -14485,10 +17618,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="120" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="121"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -14496,9 +17629,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="106"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -17193,17 +20326,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="110"/>
+      <c r="E60" s="110"/>
+      <c r="F60" s="110"/>
+      <c r="G60" s="110"/>
+      <c r="H60" s="110"/>
+      <c r="I60" s="110"/>
+      <c r="J60" s="110"/>
+      <c r="K60" s="111"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -17512,21 +20645,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="112" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -17538,17 +20671,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="115"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -17568,13 +20701,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="116" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="122" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="105" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -17614,10 +20747,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="120" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="121"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -17625,9 +20758,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="106"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -20327,17 +23460,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="110"/>
+      <c r="E60" s="110"/>
+      <c r="F60" s="110"/>
+      <c r="G60" s="110"/>
+      <c r="H60" s="110"/>
+      <c r="I60" s="110"/>
+      <c r="J60" s="110"/>
+      <c r="K60" s="111"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -20646,21 +23779,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="112" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -20672,17 +23805,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="115"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -20702,13 +23835,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="116" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="122" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="105" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -20748,10 +23881,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="120" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="121"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -20759,9 +23892,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="106"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -23455,17 +26588,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="110"/>
+      <c r="E60" s="110"/>
+      <c r="F60" s="110"/>
+      <c r="G60" s="110"/>
+      <c r="H60" s="110"/>
+      <c r="I60" s="110"/>
+      <c r="J60" s="110"/>
+      <c r="K60" s="111"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -23774,21 +26907,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="112" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -23800,17 +26933,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="115"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -23830,13 +26963,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="116" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="122" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="105" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -23876,10 +27009,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="120" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="121"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -23887,9 +27020,9 @@
       <c r="Q5" s="100"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="106"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -26585,17 +29718,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="110"/>
+      <c r="E60" s="110"/>
+      <c r="F60" s="110"/>
+      <c r="G60" s="110"/>
+      <c r="H60" s="110"/>
+      <c r="I60" s="110"/>
+      <c r="J60" s="110"/>
+      <c r="K60" s="111"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -26904,21 +30037,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="112" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -26930,17 +30063,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="115"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -26960,13 +30093,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="116" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="122" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="105" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -27006,10 +30139,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="120" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="121"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -27017,9 +30150,9 @@
       <c r="Q5" s="101"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="106"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -29720,17 +32853,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="110"/>
+      <c r="E60" s="110"/>
+      <c r="F60" s="110"/>
+      <c r="G60" s="110"/>
+      <c r="H60" s="110"/>
+      <c r="I60" s="110"/>
+      <c r="J60" s="110"/>
+      <c r="K60" s="111"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -30039,21 +33172,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="112" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -30065,17 +33198,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="115"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -30095,13 +33228,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="116" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="122" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="105" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -30141,10 +33274,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="120" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="121"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -30152,9 +33285,9 @@
       <c r="Q5" s="102"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="106"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -32850,17 +35983,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="110"/>
+      <c r="E60" s="110"/>
+      <c r="F60" s="110"/>
+      <c r="G60" s="110"/>
+      <c r="H60" s="110"/>
+      <c r="I60" s="110"/>
+      <c r="J60" s="110"/>
+      <c r="K60" s="111"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>

--- a/GBDS JUNE FILES 2026/INVENTORY COUNT SHEET - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/INVENTORY COUNT SHEET - JUNE 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0C71558-F8EF-4974-9572-5C2E031C3EC2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1D97D92-B2D3-4E2A-87BA-874527938C06}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="10" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="11" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <sheet name="06-10-2026" sheetId="62" r:id="rId9"/>
     <sheet name="06-11-2026" sheetId="63" r:id="rId10"/>
     <sheet name="06-12-2026" sheetId="64" r:id="rId11"/>
+    <sheet name="06-15-2026 " sheetId="65" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'06-01-2026'!$A$1:$W$59</definedName>
@@ -36,6 +37,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="8">'06-10-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="9">'06-11-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="10">'06-12-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="11">'06-15-2026 '!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -54,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="74">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -1263,7 +1265,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1549,6 +1551,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1989,21 +1994,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="112" t="s">
+      <c r="I1" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -2015,17 +2020,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="113" t="s">
+      <c r="C4" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="114"/>
-      <c r="K4" s="115"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -2045,13 +2050,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="116" t="s">
+      <c r="T4" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="118" t="s">
+      <c r="U4" s="119" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="105" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2091,10 +2096,10 @@
       <c r="I5" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="107" t="s">
+      <c r="J5" s="108" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="108"/>
+      <c r="K5" s="109"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2102,9 +2107,9 @@
       <c r="Q5" s="89"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="117"/>
-      <c r="U5" s="119"/>
-      <c r="V5" s="106"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="120"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -4635,17 +4640,17 @@
       <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="109" t="s">
+      <c r="C62" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="110"/>
-      <c r="E62" s="110"/>
-      <c r="F62" s="110"/>
-      <c r="G62" s="110"/>
-      <c r="H62" s="110"/>
-      <c r="I62" s="110"/>
-      <c r="J62" s="110"/>
-      <c r="K62" s="111"/>
+      <c r="D62" s="111"/>
+      <c r="E62" s="111"/>
+      <c r="F62" s="111"/>
+      <c r="G62" s="111"/>
+      <c r="H62" s="111"/>
+      <c r="I62" s="111"/>
+      <c r="J62" s="111"/>
+      <c r="K62" s="112"/>
       <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
@@ -4954,21 +4959,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="112" t="s">
+      <c r="I1" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -4980,17 +4985,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="113" t="s">
+      <c r="C4" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="114"/>
-      <c r="K4" s="115"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -5010,13 +5015,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="116" t="s">
+      <c r="T4" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="122" t="s">
+      <c r="U4" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="105" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -5056,10 +5061,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="120" t="s">
+      <c r="J5" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="121"/>
+      <c r="K5" s="122"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -5067,9 +5072,9 @@
       <c r="Q5" s="103"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="117"/>
-      <c r="U5" s="123"/>
-      <c r="V5" s="106"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -7754,17 +7759,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="109" t="s">
+      <c r="C60" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="110"/>
-      <c r="E60" s="110"/>
-      <c r="F60" s="110"/>
-      <c r="G60" s="110"/>
-      <c r="H60" s="110"/>
-      <c r="I60" s="110"/>
-      <c r="J60" s="110"/>
-      <c r="K60" s="111"/>
+      <c r="D60" s="111"/>
+      <c r="E60" s="111"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="111"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
+      <c r="J60" s="111"/>
+      <c r="K60" s="112"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -8073,21 +8078,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="112" t="s">
+      <c r="I1" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -8099,17 +8104,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="113" t="s">
+      <c r="C4" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="114"/>
-      <c r="K4" s="115"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -8129,13 +8134,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="116" t="s">
+      <c r="T4" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="122" t="s">
+      <c r="U4" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="105" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -8175,10 +8180,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="120" t="s">
+      <c r="J5" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="121"/>
+      <c r="K5" s="122"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -8186,9 +8191,9 @@
       <c r="Q5" s="104"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="117"/>
-      <c r="U5" s="123"/>
-      <c r="V5" s="106"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -10882,17 +10887,3146 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="109" t="s">
+      <c r="C60" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="110"/>
-      <c r="E60" s="110"/>
-      <c r="F60" s="110"/>
-      <c r="G60" s="110"/>
-      <c r="H60" s="110"/>
-      <c r="I60" s="110"/>
-      <c r="J60" s="110"/>
-      <c r="K60" s="111"/>
+      <c r="D60" s="111"/>
+      <c r="E60" s="111"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="111"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
+      <c r="J60" s="111"/>
+      <c r="K60" s="112"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11594D50-5105-482B-A3FE-262EC85AC025}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="9" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="113" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="114" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="117" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="123" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="106" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="121" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="122"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="105"/>
+      <c r="Q5" s="105"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="107"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="105"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="105"/>
+      <c r="Q6" s="105"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="52">
+        <v>15</v>
+      </c>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
+      <c r="J7" s="53"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
+      <c r="L7" s="55"/>
+      <c r="M7" s="56">
+        <v>1</v>
+      </c>
+      <c r="N7" s="57"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="53">
+        <v>1</v>
+      </c>
+      <c r="R7" s="54"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="58">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>9</v>
+      </c>
+      <c r="U7" s="58">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>441</v>
+      </c>
+      <c r="V7" s="58">
+        <f>U7/24</f>
+        <v>18.375</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="59">
+        <f>57+33</f>
+        <v>90</v>
+      </c>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="63">
+        <v>2</v>
+      </c>
+      <c r="N8" s="64"/>
+      <c r="O8" s="65"/>
+      <c r="P8" s="66"/>
+      <c r="Q8" s="66">
+        <v>2</v>
+      </c>
+      <c r="R8" s="67"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="68">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="69">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>2256</v>
+      </c>
+      <c r="V8" s="69">
+        <f>U8/24</f>
+        <v>94</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="70">
+        <f>90+5</f>
+        <v>95</v>
+      </c>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="73">
+        <v>2</v>
+      </c>
+      <c r="N9" s="74"/>
+      <c r="O9" s="70"/>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71">
+        <v>10</v>
+      </c>
+      <c r="R9" s="72"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="76">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>2568</v>
+      </c>
+      <c r="V9" s="76">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>107</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="70"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="74"/>
+      <c r="O10" s="70"/>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71"/>
+      <c r="R10" s="72"/>
+      <c r="S10" s="55"/>
+      <c r="T10" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V10" s="58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="70">
+        <v>5</v>
+      </c>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
+      <c r="L11" s="55"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="55"/>
+      <c r="T11" s="58">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U11" s="58">
+        <f t="shared" si="2"/>
+        <v>122</v>
+      </c>
+      <c r="V11" s="58">
+        <f t="shared" si="3"/>
+        <v>5.083333333333333</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="59">
+        <f>720+29+1440+576+144+4</f>
+        <v>2913</v>
+      </c>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="62">
+        <v>10</v>
+      </c>
+      <c r="M12" s="63">
+        <v>10</v>
+      </c>
+      <c r="N12" s="64"/>
+      <c r="O12" s="65">
+        <v>15</v>
+      </c>
+      <c r="P12" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q12" s="66">
+        <v>25</v>
+      </c>
+      <c r="R12" s="67">
+        <v>12</v>
+      </c>
+      <c r="S12" s="62"/>
+      <c r="T12" s="69">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="U12" s="69">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>71136</v>
+      </c>
+      <c r="V12" s="69">
+        <f>U12/24</f>
+        <v>2964</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
+      <c r="I13" s="70"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="55"/>
+      <c r="T13" s="76">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="U13" s="76">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>64</v>
+      </c>
+      <c r="V13" s="76">
+        <f>U13/24</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="70">
+        <v>4</v>
+      </c>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="55"/>
+      <c r="T14" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="75">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>96</v>
+      </c>
+      <c r="V14" s="75">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>4</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="55"/>
+      <c r="T15" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="55"/>
+      <c r="T16" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I17" s="70"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U17" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V17" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="55"/>
+      <c r="T18" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="70">
+        <v>2</v>
+      </c>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70">
+        <f>20+24</f>
+        <v>44</v>
+      </c>
+      <c r="I19" s="70"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="55"/>
+      <c r="T19" s="58">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="U19" s="75">
+        <f t="shared" si="4"/>
+        <v>92</v>
+      </c>
+      <c r="V19" s="75">
+        <f t="shared" si="5"/>
+        <v>3.8333333333333335</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="74"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="55"/>
+      <c r="T20" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V20" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70">
+        <f>2*24</f>
+        <v>48</v>
+      </c>
+      <c r="I21" s="70"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="58">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="U21" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V21" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="70"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70">
+        <v>20</v>
+      </c>
+      <c r="I22" s="70"/>
+      <c r="J22" s="71"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="55"/>
+      <c r="T22" s="58">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U22" s="75">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="V22" s="75">
+        <f t="shared" si="5"/>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
+      <c r="I23" s="70"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="74"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="55"/>
+      <c r="T23" s="58">
+        <f t="shared" si="0"/>
+        <v>907</v>
+      </c>
+      <c r="U23" s="75">
+        <f t="shared" si="4"/>
+        <v>907</v>
+      </c>
+      <c r="V23" s="75">
+        <f t="shared" si="5"/>
+        <v>37.791666666666664</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="70">
+        <v>5</v>
+      </c>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I24" s="70"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="55"/>
+      <c r="T24" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U24" s="75">
+        <f t="shared" si="4"/>
+        <v>192</v>
+      </c>
+      <c r="V24" s="75">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="70">
+        <f>63+53</f>
+        <v>116</v>
+      </c>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70">
+        <v>1</v>
+      </c>
+      <c r="J25" s="71"/>
+      <c r="K25" s="72"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="73">
+        <v>1</v>
+      </c>
+      <c r="N25" s="74"/>
+      <c r="O25" s="70"/>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71">
+        <v>2</v>
+      </c>
+      <c r="R25" s="72"/>
+      <c r="S25" s="55"/>
+      <c r="T25" s="58">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="U25" s="75">
+        <f t="shared" si="4"/>
+        <v>2857</v>
+      </c>
+      <c r="V25" s="75">
+        <f t="shared" si="5"/>
+        <v>119.04166666666667</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="74"/>
+      <c r="O26" s="70"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="71"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="55"/>
+      <c r="T26" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="70"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="70"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="55"/>
+      <c r="T27" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="70">
+        <v>17</v>
+      </c>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="73">
+        <v>2</v>
+      </c>
+      <c r="N28" s="74"/>
+      <c r="O28" s="70">
+        <v>3</v>
+      </c>
+      <c r="P28" s="71"/>
+      <c r="Q28" s="71">
+        <v>3</v>
+      </c>
+      <c r="R28" s="72"/>
+      <c r="S28" s="55"/>
+      <c r="T28" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="75">
+        <f t="shared" si="4"/>
+        <v>600</v>
+      </c>
+      <c r="V28" s="75">
+        <f t="shared" si="5"/>
+        <v>25</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="70">
+        <f>49</f>
+        <v>49</v>
+      </c>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70">
+        <v>5</v>
+      </c>
+      <c r="J29" s="71"/>
+      <c r="K29" s="72"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="73"/>
+      <c r="N29" s="74"/>
+      <c r="O29" s="70">
+        <v>1</v>
+      </c>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71"/>
+      <c r="R29" s="72"/>
+      <c r="S29" s="55"/>
+      <c r="T29" s="58">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U29" s="75">
+        <f t="shared" si="4"/>
+        <v>1205</v>
+      </c>
+      <c r="V29" s="75">
+        <f t="shared" si="5"/>
+        <v>50.208333333333336</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="70">
+        <v>11</v>
+      </c>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="74"/>
+      <c r="O30" s="70"/>
+      <c r="P30" s="71"/>
+      <c r="Q30" s="71">
+        <v>1</v>
+      </c>
+      <c r="R30" s="72"/>
+      <c r="S30" s="55"/>
+      <c r="T30" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="75">
+        <f t="shared" si="4"/>
+        <v>288</v>
+      </c>
+      <c r="V30" s="75">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="70"/>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="70">
+        <v>2</v>
+      </c>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="74"/>
+      <c r="O32" s="70">
+        <v>1</v>
+      </c>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="55"/>
+      <c r="T32" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V32" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="70"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="73"/>
+      <c r="N33" s="74"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="55"/>
+      <c r="T33" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="70">
+        <v>61</v>
+      </c>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
+      <c r="J34" s="71"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
+      <c r="L34" s="55"/>
+      <c r="M34" s="73">
+        <v>2</v>
+      </c>
+      <c r="N34" s="74"/>
+      <c r="O34" s="70">
+        <v>1</v>
+      </c>
+      <c r="P34" s="71">
+        <v>12</v>
+      </c>
+      <c r="Q34" s="71"/>
+      <c r="R34" s="72"/>
+      <c r="S34" s="55"/>
+      <c r="T34" s="58">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="U34" s="75">
+        <f t="shared" si="4"/>
+        <v>1550</v>
+      </c>
+      <c r="V34" s="75">
+        <f t="shared" si="5"/>
+        <v>64.583333333333329</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="72"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="74"/>
+      <c r="O35" s="70"/>
+      <c r="P35" s="71"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="72"/>
+      <c r="S35" s="55"/>
+      <c r="T35" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="73"/>
+      <c r="N36" s="74"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="71"/>
+      <c r="Q36" s="71"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="55"/>
+      <c r="T36" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="59">
+        <f>864+2268</f>
+        <v>3132</v>
+      </c>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59">
+        <f>5</f>
+        <v>5</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>3</v>
+      </c>
+      <c r="K37" s="61">
+        <v>3</v>
+      </c>
+      <c r="L37" s="62"/>
+      <c r="M37" s="63">
+        <v>117</v>
+      </c>
+      <c r="N37" s="64"/>
+      <c r="O37" s="65">
+        <v>46</v>
+      </c>
+      <c r="P37" s="66"/>
+      <c r="Q37" s="66">
+        <v>163</v>
+      </c>
+      <c r="R37" s="67"/>
+      <c r="S37" s="62"/>
+      <c r="T37" s="77">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="U37" s="77">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>20761</v>
+      </c>
+      <c r="V37" s="77">
+        <f>U37/6</f>
+        <v>3460.1666666666665</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="73"/>
+      <c r="N38" s="74"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="71"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="55"/>
+      <c r="T38" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="75">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="75">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="74"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="71"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="95"/>
+      <c r="T39" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U39" s="75">
+        <f>C39*24+M39*24+O39*24+Q39*24+T39</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="75">
+        <f>U39/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="59"/>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
+      <c r="L40" s="62"/>
+      <c r="M40" s="63"/>
+      <c r="N40" s="64"/>
+      <c r="O40" s="65"/>
+      <c r="P40" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q40" s="66"/>
+      <c r="R40" s="67"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="77">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="U40" s="77">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>32</v>
+      </c>
+      <c r="V40" s="77">
+        <f>U40/24</f>
+        <v>1.3333333333333333</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="82">
+        <v>32</v>
+      </c>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="85"/>
+      <c r="M41" s="86">
+        <v>6</v>
+      </c>
+      <c r="N41" s="87"/>
+      <c r="O41" s="82">
+        <v>7</v>
+      </c>
+      <c r="P41" s="83"/>
+      <c r="Q41" s="83">
+        <v>14</v>
+      </c>
+      <c r="R41" s="84"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="88">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>708</v>
+      </c>
+      <c r="V41" s="88">
+        <f>U41/12</f>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="71"/>
+      <c r="K42" s="72"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="73"/>
+      <c r="N42" s="74"/>
+      <c r="O42" s="70"/>
+      <c r="P42" s="71"/>
+      <c r="Q42" s="71"/>
+      <c r="R42" s="72"/>
+      <c r="S42" s="55"/>
+      <c r="T42" s="75"/>
+      <c r="U42" s="75"/>
+      <c r="V42" s="75"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="65">
+        <f>7776+3024+8424+5508+3024+2484</f>
+        <v>30240</v>
+      </c>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65"/>
+      <c r="I43" s="65">
+        <v>7</v>
+      </c>
+      <c r="J43" s="66">
+        <f>13*6</f>
+        <v>78</v>
+      </c>
+      <c r="K43" s="67">
+        <f>69*6+7</f>
+        <v>421</v>
+      </c>
+      <c r="L43" s="62"/>
+      <c r="M43" s="63">
+        <v>326</v>
+      </c>
+      <c r="N43" s="64"/>
+      <c r="O43" s="65">
+        <v>529</v>
+      </c>
+      <c r="P43" s="66"/>
+      <c r="Q43" s="66">
+        <v>486</v>
+      </c>
+      <c r="R43" s="67"/>
+      <c r="S43" s="62"/>
+      <c r="T43" s="77">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>506</v>
+      </c>
+      <c r="U43" s="77">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>189992</v>
+      </c>
+      <c r="V43" s="77">
+        <f>U43/6</f>
+        <v>31665.333333333332</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="70"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="71"/>
+      <c r="K44" s="72"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="73"/>
+      <c r="N44" s="74"/>
+      <c r="O44" s="70"/>
+      <c r="P44" s="71"/>
+      <c r="Q44" s="71"/>
+      <c r="R44" s="72"/>
+      <c r="S44" s="55"/>
+      <c r="T44" s="75"/>
+      <c r="U44" s="75"/>
+      <c r="V44" s="75"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="70"/>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="70"/>
+      <c r="I45" s="70"/>
+      <c r="J45" s="71"/>
+      <c r="K45" s="72"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="73"/>
+      <c r="N45" s="74"/>
+      <c r="O45" s="70"/>
+      <c r="P45" s="71"/>
+      <c r="Q45" s="71"/>
+      <c r="R45" s="72"/>
+      <c r="S45" s="55"/>
+      <c r="T45" s="75">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="75">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="75">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="73"/>
+      <c r="N46" s="74"/>
+      <c r="O46" s="70"/>
+      <c r="P46" s="71"/>
+      <c r="Q46" s="71"/>
+      <c r="R46" s="72"/>
+      <c r="S46" s="55"/>
+      <c r="T46" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="75">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="75">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="65">
+        <f>432+106+2160+67</f>
+        <v>2765</v>
+      </c>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
+      <c r="I47" s="65"/>
+      <c r="J47" s="66">
+        <v>1</v>
+      </c>
+      <c r="K47" s="67">
+        <v>4</v>
+      </c>
+      <c r="L47" s="62"/>
+      <c r="M47" s="63">
+        <v>8</v>
+      </c>
+      <c r="N47" s="64"/>
+      <c r="O47" s="65">
+        <v>9</v>
+      </c>
+      <c r="P47" s="66">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="66">
+        <v>6</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
+      <c r="S47" s="62"/>
+      <c r="T47" s="77">
+        <f t="shared" si="7"/>
+        <v>13</v>
+      </c>
+      <c r="U47" s="77">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>16741</v>
+      </c>
+      <c r="V47" s="77">
+        <f>U47/6</f>
+        <v>2790.1666666666665</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
+      <c r="I48" s="70"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="72"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="73"/>
+      <c r="N48" s="74"/>
+      <c r="O48" s="70"/>
+      <c r="P48" s="71"/>
+      <c r="Q48" s="71"/>
+      <c r="R48" s="72"/>
+      <c r="S48" s="55"/>
+      <c r="T48" s="75">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="U48" s="75">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="V48" s="75">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="70"/>
+      <c r="I49" s="70"/>
+      <c r="J49" s="71"/>
+      <c r="K49" s="72"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="74"/>
+      <c r="O49" s="70"/>
+      <c r="P49" s="71"/>
+      <c r="Q49" s="71"/>
+      <c r="R49" s="72"/>
+      <c r="S49" s="55"/>
+      <c r="T49" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="70"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="70"/>
+      <c r="F50" s="70"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
+      <c r="J50" s="71"/>
+      <c r="K50" s="72"/>
+      <c r="L50" s="55"/>
+      <c r="M50" s="73"/>
+      <c r="N50" s="74"/>
+      <c r="O50" s="70"/>
+      <c r="P50" s="71"/>
+      <c r="Q50" s="71"/>
+      <c r="R50" s="72"/>
+      <c r="S50" s="55"/>
+      <c r="T50" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="65"/>
+      <c r="I51" s="65"/>
+      <c r="J51" s="66"/>
+      <c r="K51" s="67"/>
+      <c r="L51" s="62"/>
+      <c r="M51" s="63"/>
+      <c r="N51" s="64"/>
+      <c r="O51" s="65"/>
+      <c r="P51" s="66"/>
+      <c r="Q51" s="66"/>
+      <c r="R51" s="67"/>
+      <c r="S51" s="62"/>
+      <c r="T51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="77">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>204</v>
+      </c>
+      <c r="V51" s="77">
+        <f>U51/6</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="70"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="70"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="71"/>
+      <c r="K52" s="72"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="73"/>
+      <c r="N52" s="74"/>
+      <c r="O52" s="70"/>
+      <c r="P52" s="71"/>
+      <c r="Q52" s="71"/>
+      <c r="R52" s="72"/>
+      <c r="S52" s="55"/>
+      <c r="T52" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="75">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="70">
+        <v>9</v>
+      </c>
+      <c r="D53" s="70"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="70"/>
+      <c r="H53" s="70"/>
+      <c r="I53" s="70"/>
+      <c r="J53" s="71"/>
+      <c r="K53" s="72"/>
+      <c r="L53" s="55"/>
+      <c r="M53" s="73"/>
+      <c r="N53" s="74"/>
+      <c r="O53" s="70"/>
+      <c r="P53" s="71"/>
+      <c r="Q53" s="71"/>
+      <c r="R53" s="72"/>
+      <c r="S53" s="55"/>
+      <c r="T53" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="75">
+        <f t="shared" si="10"/>
+        <v>216</v>
+      </c>
+      <c r="V53" s="75">
+        <f t="shared" si="9"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="71"/>
+      <c r="K54" s="72"/>
+      <c r="L54" s="55"/>
+      <c r="M54" s="73"/>
+      <c r="N54" s="74"/>
+      <c r="O54" s="70"/>
+      <c r="P54" s="71"/>
+      <c r="Q54" s="71"/>
+      <c r="R54" s="72"/>
+      <c r="S54" s="55"/>
+      <c r="T54" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="70"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="70"/>
+      <c r="I55" s="70"/>
+      <c r="J55" s="71"/>
+      <c r="K55" s="72"/>
+      <c r="L55" s="55"/>
+      <c r="M55" s="73"/>
+      <c r="N55" s="74"/>
+      <c r="O55" s="70"/>
+      <c r="P55" s="71"/>
+      <c r="Q55" s="71"/>
+      <c r="R55" s="72"/>
+      <c r="S55" s="55"/>
+      <c r="T55" s="75"/>
+      <c r="U55" s="75"/>
+      <c r="V55" s="75"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="70"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="70"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="71"/>
+      <c r="K56" s="72"/>
+      <c r="L56" s="55"/>
+      <c r="M56" s="73"/>
+      <c r="N56" s="74"/>
+      <c r="O56" s="70"/>
+      <c r="P56" s="71"/>
+      <c r="Q56" s="71"/>
+      <c r="R56" s="72"/>
+      <c r="S56" s="55"/>
+      <c r="T56" s="75"/>
+      <c r="U56" s="75"/>
+      <c r="V56" s="75"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="70"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="70"/>
+      <c r="I57" s="70"/>
+      <c r="J57" s="71"/>
+      <c r="K57" s="72"/>
+      <c r="L57" s="55"/>
+      <c r="M57" s="73"/>
+      <c r="N57" s="74"/>
+      <c r="O57" s="70"/>
+      <c r="P57" s="71"/>
+      <c r="Q57" s="71"/>
+      <c r="R57" s="72"/>
+      <c r="S57" s="55"/>
+      <c r="T57" s="75"/>
+      <c r="U57" s="75"/>
+      <c r="V57" s="75"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>39604</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>1209</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>19</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>82</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>457</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>477</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>613</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>40</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>713</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>15</v>
+      </c>
+      <c r="S58" s="55"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>1822</v>
+      </c>
+      <c r="U58" s="90">
+        <f>SUM(U7:U57)</f>
+        <v>313384</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>41549.416666666664</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="110" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="111"/>
+      <c r="E60" s="111"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="111"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
+      <c r="J60" s="111"/>
+      <c r="K60" s="112"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -11201,21 +14335,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="112" t="s">
+      <c r="I1" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -11227,17 +14361,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="113" t="s">
+      <c r="C4" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="114"/>
-      <c r="K4" s="115"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -11257,13 +14391,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="116" t="s">
+      <c r="T4" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="122" t="s">
+      <c r="U4" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="105" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -11303,10 +14437,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="120" t="s">
+      <c r="J5" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="121"/>
+      <c r="K5" s="122"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -11314,9 +14448,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="117"/>
-      <c r="U5" s="123"/>
-      <c r="V5" s="106"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -14028,17 +17162,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="109" t="s">
+      <c r="C60" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="110"/>
-      <c r="E60" s="110"/>
-      <c r="F60" s="110"/>
-      <c r="G60" s="110"/>
-      <c r="H60" s="110"/>
-      <c r="I60" s="110"/>
-      <c r="J60" s="110"/>
-      <c r="K60" s="111"/>
+      <c r="D60" s="111"/>
+      <c r="E60" s="111"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="111"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
+      <c r="J60" s="111"/>
+      <c r="K60" s="112"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -14347,21 +17481,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="112" t="s">
+      <c r="I1" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -14373,17 +17507,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="113" t="s">
+      <c r="C4" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="114"/>
-      <c r="K4" s="115"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -14403,13 +17537,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="116" t="s">
+      <c r="T4" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="122" t="s">
+      <c r="U4" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="105" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -14449,10 +17583,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="120" t="s">
+      <c r="J5" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="121"/>
+      <c r="K5" s="122"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -14460,9 +17594,9 @@
       <c r="Q5" s="96"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="117"/>
-      <c r="U5" s="123"/>
-      <c r="V5" s="106"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -17197,17 +20331,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="109" t="s">
+      <c r="C60" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="110"/>
-      <c r="E60" s="110"/>
-      <c r="F60" s="110"/>
-      <c r="G60" s="110"/>
-      <c r="H60" s="110"/>
-      <c r="I60" s="110"/>
-      <c r="J60" s="110"/>
-      <c r="K60" s="111"/>
+      <c r="D60" s="111"/>
+      <c r="E60" s="111"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="111"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
+      <c r="J60" s="111"/>
+      <c r="K60" s="112"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -17516,21 +20650,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="112" t="s">
+      <c r="I1" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -17542,17 +20676,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="113" t="s">
+      <c r="C4" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="114"/>
-      <c r="K4" s="115"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -17572,13 +20706,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="116" t="s">
+      <c r="T4" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="122" t="s">
+      <c r="U4" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="105" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -17618,10 +20752,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="120" t="s">
+      <c r="J5" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="121"/>
+      <c r="K5" s="122"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -17629,9 +20763,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="117"/>
-      <c r="U5" s="123"/>
-      <c r="V5" s="106"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -20326,17 +23460,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="109" t="s">
+      <c r="C60" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="110"/>
-      <c r="E60" s="110"/>
-      <c r="F60" s="110"/>
-      <c r="G60" s="110"/>
-      <c r="H60" s="110"/>
-      <c r="I60" s="110"/>
-      <c r="J60" s="110"/>
-      <c r="K60" s="111"/>
+      <c r="D60" s="111"/>
+      <c r="E60" s="111"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="111"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
+      <c r="J60" s="111"/>
+      <c r="K60" s="112"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -20645,21 +23779,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="112" t="s">
+      <c r="I1" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -20671,17 +23805,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="113" t="s">
+      <c r="C4" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="114"/>
-      <c r="K4" s="115"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -20701,13 +23835,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="116" t="s">
+      <c r="T4" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="122" t="s">
+      <c r="U4" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="105" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -20747,10 +23881,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="120" t="s">
+      <c r="J5" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="121"/>
+      <c r="K5" s="122"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -20758,9 +23892,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="117"/>
-      <c r="U5" s="123"/>
-      <c r="V5" s="106"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -23460,17 +26594,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="109" t="s">
+      <c r="C60" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="110"/>
-      <c r="E60" s="110"/>
-      <c r="F60" s="110"/>
-      <c r="G60" s="110"/>
-      <c r="H60" s="110"/>
-      <c r="I60" s="110"/>
-      <c r="J60" s="110"/>
-      <c r="K60" s="111"/>
+      <c r="D60" s="111"/>
+      <c r="E60" s="111"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="111"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
+      <c r="J60" s="111"/>
+      <c r="K60" s="112"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -23779,21 +26913,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="112" t="s">
+      <c r="I1" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -23805,17 +26939,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="113" t="s">
+      <c r="C4" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="114"/>
-      <c r="K4" s="115"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -23835,13 +26969,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="116" t="s">
+      <c r="T4" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="122" t="s">
+      <c r="U4" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="105" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -23881,10 +27015,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="120" t="s">
+      <c r="J5" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="121"/>
+      <c r="K5" s="122"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -23892,9 +27026,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="117"/>
-      <c r="U5" s="123"/>
-      <c r="V5" s="106"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -26588,17 +29722,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="109" t="s">
+      <c r="C60" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="110"/>
-      <c r="E60" s="110"/>
-      <c r="F60" s="110"/>
-      <c r="G60" s="110"/>
-      <c r="H60" s="110"/>
-      <c r="I60" s="110"/>
-      <c r="J60" s="110"/>
-      <c r="K60" s="111"/>
+      <c r="D60" s="111"/>
+      <c r="E60" s="111"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="111"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
+      <c r="J60" s="111"/>
+      <c r="K60" s="112"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -26907,21 +30041,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="112" t="s">
+      <c r="I1" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -26933,17 +30067,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="113" t="s">
+      <c r="C4" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="114"/>
-      <c r="K4" s="115"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -26963,13 +30097,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="116" t="s">
+      <c r="T4" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="122" t="s">
+      <c r="U4" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="105" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -27009,10 +30143,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="120" t="s">
+      <c r="J5" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="121"/>
+      <c r="K5" s="122"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -27020,9 +30154,9 @@
       <c r="Q5" s="100"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="117"/>
-      <c r="U5" s="123"/>
-      <c r="V5" s="106"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -29718,17 +32852,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="109" t="s">
+      <c r="C60" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="110"/>
-      <c r="E60" s="110"/>
-      <c r="F60" s="110"/>
-      <c r="G60" s="110"/>
-      <c r="H60" s="110"/>
-      <c r="I60" s="110"/>
-      <c r="J60" s="110"/>
-      <c r="K60" s="111"/>
+      <c r="D60" s="111"/>
+      <c r="E60" s="111"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="111"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
+      <c r="J60" s="111"/>
+      <c r="K60" s="112"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -30037,21 +33171,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="112" t="s">
+      <c r="I1" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -30063,17 +33197,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="113" t="s">
+      <c r="C4" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="114"/>
-      <c r="K4" s="115"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -30093,13 +33227,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="116" t="s">
+      <c r="T4" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="122" t="s">
+      <c r="U4" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="105" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -30139,10 +33273,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="120" t="s">
+      <c r="J5" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="121"/>
+      <c r="K5" s="122"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -30150,9 +33284,9 @@
       <c r="Q5" s="101"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="117"/>
-      <c r="U5" s="123"/>
-      <c r="V5" s="106"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -32853,17 +35987,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="109" t="s">
+      <c r="C60" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="110"/>
-      <c r="E60" s="110"/>
-      <c r="F60" s="110"/>
-      <c r="G60" s="110"/>
-      <c r="H60" s="110"/>
-      <c r="I60" s="110"/>
-      <c r="J60" s="110"/>
-      <c r="K60" s="111"/>
+      <c r="D60" s="111"/>
+      <c r="E60" s="111"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="111"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
+      <c r="J60" s="111"/>
+      <c r="K60" s="112"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -33172,21 +36306,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="112" t="s">
+      <c r="I1" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -33198,17 +36332,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="113" t="s">
+      <c r="C4" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="114"/>
-      <c r="K4" s="115"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -33228,13 +36362,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="116" t="s">
+      <c r="T4" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="122" t="s">
+      <c r="U4" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="105" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -33274,10 +36408,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="120" t="s">
+      <c r="J5" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="121"/>
+      <c r="K5" s="122"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -33285,9 +36419,9 @@
       <c r="Q5" s="102"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="117"/>
-      <c r="U5" s="123"/>
-      <c r="V5" s="106"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -35983,17 +39117,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="109" t="s">
+      <c r="C60" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="110"/>
-      <c r="E60" s="110"/>
-      <c r="F60" s="110"/>
-      <c r="G60" s="110"/>
-      <c r="H60" s="110"/>
-      <c r="I60" s="110"/>
-      <c r="J60" s="110"/>
-      <c r="K60" s="111"/>
+      <c r="D60" s="111"/>
+      <c r="E60" s="111"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="111"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
+      <c r="J60" s="111"/>
+      <c r="K60" s="112"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>

--- a/GBDS JUNE FILES 2026/INVENTORY COUNT SHEET - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/INVENTORY COUNT SHEET - JUNE 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1D97D92-B2D3-4E2A-87BA-874527938C06}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{825E77FF-0424-48DB-AD0F-5BB1C351AD15}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="11" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="12" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -25,6 +25,7 @@
     <sheet name="06-11-2026" sheetId="63" r:id="rId10"/>
     <sheet name="06-12-2026" sheetId="64" r:id="rId11"/>
     <sheet name="06-15-2026 " sheetId="65" r:id="rId12"/>
+    <sheet name="06-16-2026" sheetId="66" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'06-01-2026'!$A$1:$W$59</definedName>
@@ -38,6 +39,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="9">'06-11-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="10">'06-12-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="11">'06-15-2026 '!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="12">'06-16-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -56,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="74">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -1265,7 +1267,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1551,6 +1553,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1994,21 +1999,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -2020,17 +2025,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -2050,13 +2055,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="119" t="s">
+      <c r="U4" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2096,10 +2101,10 @@
       <c r="I5" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="108" t="s">
+      <c r="J5" s="109" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="109"/>
+      <c r="K5" s="110"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2107,9 +2112,9 @@
       <c r="Q5" s="89"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="120"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="121"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -4640,17 +4645,17 @@
       <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="110" t="s">
+      <c r="C62" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="111"/>
-      <c r="E62" s="111"/>
-      <c r="F62" s="111"/>
-      <c r="G62" s="111"/>
-      <c r="H62" s="111"/>
-      <c r="I62" s="111"/>
-      <c r="J62" s="111"/>
-      <c r="K62" s="112"/>
+      <c r="D62" s="112"/>
+      <c r="E62" s="112"/>
+      <c r="F62" s="112"/>
+      <c r="G62" s="112"/>
+      <c r="H62" s="112"/>
+      <c r="I62" s="112"/>
+      <c r="J62" s="112"/>
+      <c r="K62" s="113"/>
       <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
@@ -4959,21 +4964,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -4985,17 +4990,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -5015,13 +5020,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="123" t="s">
+      <c r="U4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -5061,10 +5066,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="121" t="s">
+      <c r="J5" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="122"/>
+      <c r="K5" s="123"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -5072,9 +5077,9 @@
       <c r="Q5" s="103"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -7759,17 +7764,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="110" t="s">
+      <c r="C60" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="111"/>
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="112"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -8078,21 +8083,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -8104,17 +8109,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -8134,13 +8139,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="123" t="s">
+      <c r="U4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -8180,10 +8185,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="121" t="s">
+      <c r="J5" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="122"/>
+      <c r="K5" s="123"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -8191,9 +8196,9 @@
       <c r="Q5" s="104"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -10887,17 +10892,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="110" t="s">
+      <c r="C60" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="111"/>
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="112"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -11206,21 +11211,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -11232,17 +11237,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -11262,13 +11267,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="123" t="s">
+      <c r="U4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -11308,10 +11313,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="121" t="s">
+      <c r="J5" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="122"/>
+      <c r="K5" s="123"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -11319,9 +11324,9 @@
       <c r="Q5" s="105"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -14016,17 +14021,3144 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="110" t="s">
+      <c r="C60" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="111"/>
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="112"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB3D73BA-545B-416B-B982-577C234B39E1}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="9" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="114" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="115" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="118" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="124" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="107" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="122" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="123"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="106"/>
+      <c r="Q5" s="106"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="108"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="106"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="106"/>
+      <c r="Q6" s="106"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="52">
+        <v>14</v>
+      </c>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
+      <c r="J7" s="53"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
+      <c r="L7" s="55"/>
+      <c r="M7" s="56">
+        <v>2</v>
+      </c>
+      <c r="N7" s="57"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="53">
+        <v>1</v>
+      </c>
+      <c r="R7" s="54"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="58">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>9</v>
+      </c>
+      <c r="U7" s="58">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>441</v>
+      </c>
+      <c r="V7" s="58">
+        <f>U7/24</f>
+        <v>18.375</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="59">
+        <f>56+33</f>
+        <v>89</v>
+      </c>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="63">
+        <v>3</v>
+      </c>
+      <c r="N8" s="64"/>
+      <c r="O8" s="65"/>
+      <c r="P8" s="66"/>
+      <c r="Q8" s="66">
+        <v>2</v>
+      </c>
+      <c r="R8" s="67"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="68">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="69">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>2256</v>
+      </c>
+      <c r="V8" s="69">
+        <f>U8/24</f>
+        <v>94</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="70">
+        <f>90+2</f>
+        <v>92</v>
+      </c>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="73"/>
+      <c r="N9" s="74"/>
+      <c r="O9" s="70">
+        <v>1</v>
+      </c>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71">
+        <v>2</v>
+      </c>
+      <c r="R9" s="72"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="76">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>2280</v>
+      </c>
+      <c r="V9" s="76">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>95</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="70"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="74"/>
+      <c r="O10" s="70"/>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71"/>
+      <c r="R10" s="72"/>
+      <c r="S10" s="55"/>
+      <c r="T10" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V10" s="58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="70">
+        <v>5</v>
+      </c>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
+      <c r="L11" s="55"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="55"/>
+      <c r="T11" s="58">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U11" s="58">
+        <f t="shared" si="2"/>
+        <v>122</v>
+      </c>
+      <c r="V11" s="58">
+        <f t="shared" si="3"/>
+        <v>5.083333333333333</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="59">
+        <f>720+29+1440+576+72+22+4</f>
+        <v>2863</v>
+      </c>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="63">
+        <v>21</v>
+      </c>
+      <c r="N12" s="64"/>
+      <c r="O12" s="65">
+        <v>13</v>
+      </c>
+      <c r="P12" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q12" s="66">
+        <v>22</v>
+      </c>
+      <c r="R12" s="67">
+        <v>12</v>
+      </c>
+      <c r="S12" s="62"/>
+      <c r="T12" s="69">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="U12" s="69">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>70080</v>
+      </c>
+      <c r="V12" s="69">
+        <f>U12/24</f>
+        <v>2920</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
+      <c r="I13" s="70"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="55"/>
+      <c r="T13" s="76">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="U13" s="76">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>64</v>
+      </c>
+      <c r="V13" s="76">
+        <f>U13/24</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="70">
+        <v>4</v>
+      </c>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="55"/>
+      <c r="T14" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="75">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>96</v>
+      </c>
+      <c r="V14" s="75">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>4</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="55"/>
+      <c r="T15" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="55"/>
+      <c r="T16" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I17" s="70"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U17" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V17" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="55"/>
+      <c r="T18" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="70">
+        <v>2</v>
+      </c>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70">
+        <f>20+24</f>
+        <v>44</v>
+      </c>
+      <c r="I19" s="70"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="55"/>
+      <c r="T19" s="58">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="U19" s="75">
+        <f t="shared" si="4"/>
+        <v>92</v>
+      </c>
+      <c r="V19" s="75">
+        <f t="shared" si="5"/>
+        <v>3.8333333333333335</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="74"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="55"/>
+      <c r="T20" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V20" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70">
+        <f>2*24</f>
+        <v>48</v>
+      </c>
+      <c r="I21" s="70"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="58">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="U21" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V21" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="70"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
+      <c r="J22" s="71"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="55"/>
+      <c r="T22" s="58">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U22" s="75">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="V22" s="75">
+        <f t="shared" si="5"/>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
+      <c r="I23" s="70"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="74"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="55"/>
+      <c r="T23" s="58">
+        <f t="shared" si="0"/>
+        <v>907</v>
+      </c>
+      <c r="U23" s="75">
+        <f t="shared" si="4"/>
+        <v>907</v>
+      </c>
+      <c r="V23" s="75">
+        <f t="shared" si="5"/>
+        <v>37.791666666666664</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="70">
+        <v>5</v>
+      </c>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I24" s="70"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="55"/>
+      <c r="T24" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U24" s="75">
+        <f t="shared" si="4"/>
+        <v>192</v>
+      </c>
+      <c r="V24" s="75">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="70">
+        <f>63+35</f>
+        <v>98</v>
+      </c>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70">
+        <v>1</v>
+      </c>
+      <c r="J25" s="71"/>
+      <c r="K25" s="72"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="73">
+        <v>4</v>
+      </c>
+      <c r="N25" s="74"/>
+      <c r="O25" s="70"/>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71">
+        <v>15</v>
+      </c>
+      <c r="R25" s="72"/>
+      <c r="S25" s="55"/>
+      <c r="T25" s="58">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="U25" s="75">
+        <f t="shared" si="4"/>
+        <v>2809</v>
+      </c>
+      <c r="V25" s="75">
+        <f t="shared" si="5"/>
+        <v>117.04166666666667</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="74"/>
+      <c r="O26" s="70"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="71"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="55"/>
+      <c r="T26" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="70"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="70"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="55"/>
+      <c r="T27" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="70"/>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="73"/>
+      <c r="N28" s="74"/>
+      <c r="O28" s="70">
+        <v>3</v>
+      </c>
+      <c r="P28" s="71"/>
+      <c r="Q28" s="71">
+        <v>17</v>
+      </c>
+      <c r="R28" s="72"/>
+      <c r="S28" s="55"/>
+      <c r="T28" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="75">
+        <f t="shared" si="4"/>
+        <v>480</v>
+      </c>
+      <c r="V28" s="75">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="70">
+        <v>43</v>
+      </c>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70">
+        <v>5</v>
+      </c>
+      <c r="J29" s="71"/>
+      <c r="K29" s="72"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="73">
+        <v>1</v>
+      </c>
+      <c r="N29" s="74"/>
+      <c r="O29" s="70">
+        <v>1</v>
+      </c>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71">
+        <v>5</v>
+      </c>
+      <c r="R29" s="72"/>
+      <c r="S29" s="55"/>
+      <c r="T29" s="58">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U29" s="75">
+        <f t="shared" si="4"/>
+        <v>1205</v>
+      </c>
+      <c r="V29" s="75">
+        <f t="shared" si="5"/>
+        <v>50.208333333333336</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="70">
+        <v>10</v>
+      </c>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="73">
+        <v>1</v>
+      </c>
+      <c r="N30" s="74"/>
+      <c r="O30" s="70"/>
+      <c r="P30" s="71"/>
+      <c r="Q30" s="71"/>
+      <c r="R30" s="72"/>
+      <c r="S30" s="55"/>
+      <c r="T30" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="75">
+        <f t="shared" si="4"/>
+        <v>264</v>
+      </c>
+      <c r="V30" s="75">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="70"/>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="70">
+        <v>2</v>
+      </c>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="74"/>
+      <c r="O32" s="70">
+        <v>1</v>
+      </c>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="55"/>
+      <c r="T32" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V32" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="70"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="73"/>
+      <c r="N33" s="74"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="55"/>
+      <c r="T33" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="70">
+        <v>57</v>
+      </c>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
+      <c r="J34" s="71"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
+      <c r="L34" s="55"/>
+      <c r="M34" s="73">
+        <v>4</v>
+      </c>
+      <c r="N34" s="74"/>
+      <c r="O34" s="70">
+        <v>1</v>
+      </c>
+      <c r="P34" s="71">
+        <v>12</v>
+      </c>
+      <c r="Q34" s="71">
+        <v>2</v>
+      </c>
+      <c r="R34" s="72"/>
+      <c r="S34" s="55"/>
+      <c r="T34" s="58">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="U34" s="75">
+        <f t="shared" si="4"/>
+        <v>1550</v>
+      </c>
+      <c r="V34" s="75">
+        <f t="shared" si="5"/>
+        <v>64.583333333333329</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="72"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="74"/>
+      <c r="O35" s="70"/>
+      <c r="P35" s="71"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="72"/>
+      <c r="S35" s="55"/>
+      <c r="T35" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="73"/>
+      <c r="N36" s="74"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="71"/>
+      <c r="Q36" s="71"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="55"/>
+      <c r="T36" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="59">
+        <f>864+58+2052</f>
+        <v>2974</v>
+      </c>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59">
+        <v>5</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>3</v>
+      </c>
+      <c r="K37" s="61">
+        <v>3</v>
+      </c>
+      <c r="L37" s="62"/>
+      <c r="M37" s="63">
+        <v>134</v>
+      </c>
+      <c r="N37" s="64"/>
+      <c r="O37" s="65">
+        <v>30</v>
+      </c>
+      <c r="P37" s="66"/>
+      <c r="Q37" s="66">
+        <v>41</v>
+      </c>
+      <c r="R37" s="67"/>
+      <c r="S37" s="62"/>
+      <c r="T37" s="77">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="U37" s="77">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>19087</v>
+      </c>
+      <c r="V37" s="77">
+        <f>U37/6</f>
+        <v>3181.1666666666665</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="73"/>
+      <c r="N38" s="74"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="71"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="55"/>
+      <c r="T38" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="75">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="75">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="74"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="71"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="95"/>
+      <c r="T39" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U39" s="75">
+        <f>C39*24+M39*24+O39*24+Q39*24+T39</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="75">
+        <f>U39/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="59"/>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
+      <c r="L40" s="62"/>
+      <c r="M40" s="63"/>
+      <c r="N40" s="64"/>
+      <c r="O40" s="65"/>
+      <c r="P40" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q40" s="66"/>
+      <c r="R40" s="67"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="77">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="U40" s="77">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>32</v>
+      </c>
+      <c r="V40" s="77">
+        <f>U40/24</f>
+        <v>1.3333333333333333</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="82">
+        <v>8</v>
+      </c>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="85"/>
+      <c r="M41" s="86">
+        <v>8</v>
+      </c>
+      <c r="N41" s="87"/>
+      <c r="O41" s="82">
+        <v>7</v>
+      </c>
+      <c r="P41" s="83"/>
+      <c r="Q41" s="83">
+        <v>19</v>
+      </c>
+      <c r="R41" s="84"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="88">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>504</v>
+      </c>
+      <c r="V41" s="88">
+        <f>U41/12</f>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="71"/>
+      <c r="K42" s="72"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="73"/>
+      <c r="N42" s="74"/>
+      <c r="O42" s="70"/>
+      <c r="P42" s="71"/>
+      <c r="Q42" s="71"/>
+      <c r="R42" s="72"/>
+      <c r="S42" s="55"/>
+      <c r="T42" s="75"/>
+      <c r="U42" s="75"/>
+      <c r="V42" s="75"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="65">
+        <f>7776+3024+8424+5508+3024+1080</f>
+        <v>28836</v>
+      </c>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65"/>
+      <c r="I43" s="65">
+        <v>7</v>
+      </c>
+      <c r="J43" s="66">
+        <f>13*6</f>
+        <v>78</v>
+      </c>
+      <c r="K43" s="67">
+        <f>69*6+7</f>
+        <v>421</v>
+      </c>
+      <c r="L43" s="62"/>
+      <c r="M43" s="63">
+        <v>544</v>
+      </c>
+      <c r="N43" s="64"/>
+      <c r="O43" s="65">
+        <v>366</v>
+      </c>
+      <c r="P43" s="66"/>
+      <c r="Q43" s="66">
+        <v>651</v>
+      </c>
+      <c r="R43" s="67"/>
+      <c r="S43" s="62"/>
+      <c r="T43" s="77">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>506</v>
+      </c>
+      <c r="U43" s="77">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>182888</v>
+      </c>
+      <c r="V43" s="77">
+        <f>U43/6</f>
+        <v>30481.333333333332</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="70"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="71"/>
+      <c r="K44" s="72"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="73"/>
+      <c r="N44" s="74"/>
+      <c r="O44" s="70"/>
+      <c r="P44" s="71"/>
+      <c r="Q44" s="71"/>
+      <c r="R44" s="72"/>
+      <c r="S44" s="55"/>
+      <c r="T44" s="75"/>
+      <c r="U44" s="75"/>
+      <c r="V44" s="75"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="70"/>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="70"/>
+      <c r="I45" s="70"/>
+      <c r="J45" s="71"/>
+      <c r="K45" s="72"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="73"/>
+      <c r="N45" s="74"/>
+      <c r="O45" s="70"/>
+      <c r="P45" s="71"/>
+      <c r="Q45" s="71"/>
+      <c r="R45" s="72"/>
+      <c r="S45" s="55"/>
+      <c r="T45" s="75">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="75">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="75">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="73"/>
+      <c r="N46" s="74"/>
+      <c r="O46" s="70"/>
+      <c r="P46" s="71"/>
+      <c r="Q46" s="71"/>
+      <c r="R46" s="72"/>
+      <c r="S46" s="55"/>
+      <c r="T46" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="75">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="75">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="65">
+        <f>432+106+2160+64</f>
+        <v>2762</v>
+      </c>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
+      <c r="I47" s="65"/>
+      <c r="J47" s="66">
+        <v>1</v>
+      </c>
+      <c r="K47" s="67">
+        <v>4</v>
+      </c>
+      <c r="L47" s="62"/>
+      <c r="M47" s="63">
+        <v>11</v>
+      </c>
+      <c r="N47" s="64"/>
+      <c r="O47" s="65">
+        <v>9</v>
+      </c>
+      <c r="P47" s="66">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="66">
+        <v>6</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
+      <c r="S47" s="62"/>
+      <c r="T47" s="77">
+        <f t="shared" si="7"/>
+        <v>13</v>
+      </c>
+      <c r="U47" s="77">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>16741</v>
+      </c>
+      <c r="V47" s="77">
+        <f>U47/6</f>
+        <v>2790.1666666666665</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
+      <c r="I48" s="70"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="72"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="73"/>
+      <c r="N48" s="74"/>
+      <c r="O48" s="70"/>
+      <c r="P48" s="71"/>
+      <c r="Q48" s="71"/>
+      <c r="R48" s="72"/>
+      <c r="S48" s="55"/>
+      <c r="T48" s="75">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="U48" s="75">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="V48" s="75">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="70"/>
+      <c r="I49" s="70"/>
+      <c r="J49" s="71"/>
+      <c r="K49" s="72"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="74"/>
+      <c r="O49" s="70"/>
+      <c r="P49" s="71"/>
+      <c r="Q49" s="71"/>
+      <c r="R49" s="72"/>
+      <c r="S49" s="55"/>
+      <c r="T49" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="70"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="70"/>
+      <c r="F50" s="70"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
+      <c r="J50" s="71"/>
+      <c r="K50" s="72"/>
+      <c r="L50" s="55"/>
+      <c r="M50" s="73"/>
+      <c r="N50" s="74"/>
+      <c r="O50" s="70"/>
+      <c r="P50" s="71"/>
+      <c r="Q50" s="71"/>
+      <c r="R50" s="72"/>
+      <c r="S50" s="55"/>
+      <c r="T50" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="65"/>
+      <c r="I51" s="65"/>
+      <c r="J51" s="66"/>
+      <c r="K51" s="67"/>
+      <c r="L51" s="62"/>
+      <c r="M51" s="63"/>
+      <c r="N51" s="64"/>
+      <c r="O51" s="65"/>
+      <c r="P51" s="66"/>
+      <c r="Q51" s="66"/>
+      <c r="R51" s="67"/>
+      <c r="S51" s="62"/>
+      <c r="T51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="77">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>204</v>
+      </c>
+      <c r="V51" s="77">
+        <f>U51/6</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="70"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="70"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="71"/>
+      <c r="K52" s="72"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="73"/>
+      <c r="N52" s="74"/>
+      <c r="O52" s="70"/>
+      <c r="P52" s="71"/>
+      <c r="Q52" s="71"/>
+      <c r="R52" s="72"/>
+      <c r="S52" s="55"/>
+      <c r="T52" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="75">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="70">
+        <v>9</v>
+      </c>
+      <c r="D53" s="70"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="70"/>
+      <c r="H53" s="70"/>
+      <c r="I53" s="70"/>
+      <c r="J53" s="71"/>
+      <c r="K53" s="72"/>
+      <c r="L53" s="55"/>
+      <c r="M53" s="73"/>
+      <c r="N53" s="74"/>
+      <c r="O53" s="70"/>
+      <c r="P53" s="71"/>
+      <c r="Q53" s="71"/>
+      <c r="R53" s="72"/>
+      <c r="S53" s="55"/>
+      <c r="T53" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="75">
+        <f t="shared" si="10"/>
+        <v>216</v>
+      </c>
+      <c r="V53" s="75">
+        <f t="shared" si="9"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="71"/>
+      <c r="K54" s="72"/>
+      <c r="L54" s="55"/>
+      <c r="M54" s="73"/>
+      <c r="N54" s="74"/>
+      <c r="O54" s="70"/>
+      <c r="P54" s="71"/>
+      <c r="Q54" s="71"/>
+      <c r="R54" s="72"/>
+      <c r="S54" s="55"/>
+      <c r="T54" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="70"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="70"/>
+      <c r="I55" s="70"/>
+      <c r="J55" s="71"/>
+      <c r="K55" s="72"/>
+      <c r="L55" s="55"/>
+      <c r="M55" s="73"/>
+      <c r="N55" s="74"/>
+      <c r="O55" s="70"/>
+      <c r="P55" s="71"/>
+      <c r="Q55" s="71"/>
+      <c r="R55" s="72"/>
+      <c r="S55" s="55"/>
+      <c r="T55" s="75"/>
+      <c r="U55" s="75"/>
+      <c r="V55" s="75"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="70"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="70"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="71"/>
+      <c r="K56" s="72"/>
+      <c r="L56" s="55"/>
+      <c r="M56" s="73"/>
+      <c r="N56" s="74"/>
+      <c r="O56" s="70"/>
+      <c r="P56" s="71"/>
+      <c r="Q56" s="71"/>
+      <c r="R56" s="72"/>
+      <c r="S56" s="55"/>
+      <c r="T56" s="75"/>
+      <c r="U56" s="75"/>
+      <c r="V56" s="75"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="70"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="70"/>
+      <c r="I57" s="70"/>
+      <c r="J57" s="71"/>
+      <c r="K57" s="72"/>
+      <c r="L57" s="55"/>
+      <c r="M57" s="73"/>
+      <c r="N57" s="74"/>
+      <c r="O57" s="70"/>
+      <c r="P57" s="71"/>
+      <c r="Q57" s="71"/>
+      <c r="R57" s="72"/>
+      <c r="S57" s="55"/>
+      <c r="T57" s="75"/>
+      <c r="U57" s="75"/>
+      <c r="V57" s="75"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>37914</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>1189</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>39</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>82</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>457</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>733</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>433</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>40</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>783</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>15</v>
+      </c>
+      <c r="S58" s="55"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>1822</v>
+      </c>
+      <c r="U58" s="90">
+        <f>SUM(U7:U57)</f>
+        <v>302866</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>40005.416666666664</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="111" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -14335,21 +17467,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -14361,17 +17493,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -14391,13 +17523,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="123" t="s">
+      <c r="U4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -14437,10 +17569,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="121" t="s">
+      <c r="J5" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="122"/>
+      <c r="K5" s="123"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -14448,9 +17580,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -17162,17 +20294,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="110" t="s">
+      <c r="C60" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="111"/>
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="112"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -17481,21 +20613,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -17507,17 +20639,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -17537,13 +20669,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="123" t="s">
+      <c r="U4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -17583,10 +20715,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="121" t="s">
+      <c r="J5" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="122"/>
+      <c r="K5" s="123"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -17594,9 +20726,9 @@
       <c r="Q5" s="96"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -20331,17 +23463,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="110" t="s">
+      <c r="C60" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="111"/>
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="112"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -20650,21 +23782,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -20676,17 +23808,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -20706,13 +23838,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="123" t="s">
+      <c r="U4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -20752,10 +23884,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="121" t="s">
+      <c r="J5" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="122"/>
+      <c r="K5" s="123"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -20763,9 +23895,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -23460,17 +26592,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="110" t="s">
+      <c r="C60" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="111"/>
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="112"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -23779,21 +26911,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -23805,17 +26937,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -23835,13 +26967,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="123" t="s">
+      <c r="U4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -23881,10 +27013,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="121" t="s">
+      <c r="J5" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="122"/>
+      <c r="K5" s="123"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -23892,9 +27024,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -26594,17 +29726,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="110" t="s">
+      <c r="C60" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="111"/>
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="112"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -26913,21 +30045,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -26939,17 +30071,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -26969,13 +30101,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="123" t="s">
+      <c r="U4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -27015,10 +30147,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="121" t="s">
+      <c r="J5" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="122"/>
+      <c r="K5" s="123"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -27026,9 +30158,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -29722,17 +32854,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="110" t="s">
+      <c r="C60" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="111"/>
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="112"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -30041,21 +33173,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -30067,17 +33199,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -30097,13 +33229,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="123" t="s">
+      <c r="U4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -30143,10 +33275,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="121" t="s">
+      <c r="J5" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="122"/>
+      <c r="K5" s="123"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -30154,9 +33286,9 @@
       <c r="Q5" s="100"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -32852,17 +35984,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="110" t="s">
+      <c r="C60" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="111"/>
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="112"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -33171,21 +36303,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -33197,17 +36329,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -33227,13 +36359,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="123" t="s">
+      <c r="U4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -33273,10 +36405,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="121" t="s">
+      <c r="J5" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="122"/>
+      <c r="K5" s="123"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -33284,9 +36416,9 @@
       <c r="Q5" s="101"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -35987,17 +39119,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="110" t="s">
+      <c r="C60" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="111"/>
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="112"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -36306,21 +39438,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -36332,17 +39464,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -36362,13 +39494,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="123" t="s">
+      <c r="U4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -36408,10 +39540,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="121" t="s">
+      <c r="J5" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="122"/>
+      <c r="K5" s="123"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -36419,9 +39551,9 @@
       <c r="Q5" s="102"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -39117,17 +42249,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="110" t="s">
+      <c r="C60" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="111"/>
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="112"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>

--- a/GBDS JUNE FILES 2026/INVENTORY COUNT SHEET - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/INVENTORY COUNT SHEET - JUNE 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E90BEFD-9E4F-463E-A7A8-B47E5598B90F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B475FC0-A242-4053-9406-1BC00D932AA4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="420" windowWidth="29040" windowHeight="15900" firstSheet="7" activeTab="16" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="8" activeTab="17" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -30,6 +30,7 @@
     <sheet name="06-18-2026" sheetId="68" r:id="rId15"/>
     <sheet name="06-19-2026 " sheetId="69" r:id="rId16"/>
     <sheet name="06-22-2026" sheetId="70" r:id="rId17"/>
+    <sheet name="06-23-2026" sheetId="71" r:id="rId18"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'06-01-2026'!$A$1:$W$59</definedName>
@@ -48,6 +49,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="14">'06-18-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="15">'06-19-2026 '!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="16">'06-22-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="17">'06-23-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -66,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1428" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1512" uniqueCount="74">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -1275,7 +1277,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1561,6 +1563,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2010,21 +2015,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -2036,17 +2041,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -2066,13 +2071,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="122" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2112,10 +2117,10 @@
       <c r="I5" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="110" t="s">
+      <c r="J5" s="111" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="111"/>
+      <c r="K5" s="112"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2123,9 +2128,9 @@
       <c r="Q5" s="89"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -4656,17 +4661,17 @@
       <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="112" t="s">
+      <c r="C62" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="113"/>
-      <c r="E62" s="113"/>
-      <c r="F62" s="113"/>
-      <c r="G62" s="113"/>
-      <c r="H62" s="113"/>
-      <c r="I62" s="113"/>
-      <c r="J62" s="113"/>
-      <c r="K62" s="114"/>
+      <c r="D62" s="114"/>
+      <c r="E62" s="114"/>
+      <c r="F62" s="114"/>
+      <c r="G62" s="114"/>
+      <c r="H62" s="114"/>
+      <c r="I62" s="114"/>
+      <c r="J62" s="114"/>
+      <c r="K62" s="115"/>
       <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
@@ -4975,21 +4980,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -5001,17 +5006,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -5031,13 +5036,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -5077,10 +5082,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -5088,9 +5093,9 @@
       <c r="Q5" s="103"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -7775,17 +7780,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -8094,21 +8099,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -8120,17 +8125,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -8150,13 +8155,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -8196,10 +8201,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -8207,9 +8212,9 @@
       <c r="Q5" s="104"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -10903,17 +10908,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -11222,21 +11227,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -11248,17 +11253,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -11278,13 +11283,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -11324,10 +11329,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -11335,9 +11340,9 @@
       <c r="Q5" s="105"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -14032,17 +14037,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -14351,21 +14356,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -14377,17 +14382,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -14407,13 +14412,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -14453,10 +14458,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -14464,9 +14469,9 @@
       <c r="Q5" s="106"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -17159,17 +17164,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -17478,21 +17483,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -17504,17 +17509,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -17534,13 +17539,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -17580,10 +17585,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -17591,9 +17596,9 @@
       <c r="Q5" s="107"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -20282,17 +20287,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -20544,13 +20549,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -20601,21 +20606,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -20627,17 +20632,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -20657,13 +20662,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -20703,10 +20708,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -20714,9 +20719,9 @@
       <c r="Q5" s="107"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -23363,27 +23368,27 @@
         <v>457</v>
       </c>
       <c r="M58" s="5">
-        <f>SUM(M7:M53)</f>
+        <f t="shared" ref="M58:R58" si="11">SUM(M7:M53)</f>
         <v>480</v>
       </c>
       <c r="N58" s="5">
-        <f>SUM(N7:N53)</f>
+        <f t="shared" si="11"/>
         <v>12</v>
       </c>
       <c r="O58" s="5">
-        <f>SUM(O7:O53)</f>
+        <f t="shared" si="11"/>
         <v>415</v>
       </c>
       <c r="P58" s="5">
-        <f>SUM(P7:P53)</f>
+        <f t="shared" si="11"/>
         <v>16</v>
       </c>
       <c r="Q58" s="5">
-        <f>SUM(Q7:Q53)</f>
+        <f t="shared" si="11"/>
         <v>623</v>
       </c>
       <c r="R58" s="5">
-        <f>SUM(R7:R53)</f>
+        <f t="shared" si="11"/>
         <v>15</v>
       </c>
       <c r="S58" s="55"/>
@@ -23405,17 +23410,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -23667,13 +23672,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -23724,21 +23729,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -23750,17 +23755,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -23780,13 +23785,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -23826,10 +23831,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -23837,9 +23842,9 @@
       <c r="Q5" s="107"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -26537,17 +26542,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -26799,13 +26804,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -26856,21 +26861,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -26882,17 +26887,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -26912,13 +26917,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -26958,10 +26963,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -26969,9 +26974,9 @@
       <c r="Q5" s="107"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -29679,17 +29684,3145 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18F48825-6195-4651-9B8A-9591CDCBBADF}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="9" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="116" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="117" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="120" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="126" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="109" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="124" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="125"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="108"/>
+      <c r="Q5" s="108"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="108"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="108"/>
+      <c r="Q6" s="108"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="52">
+        <v>14</v>
+      </c>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
+      <c r="J7" s="53"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
+      <c r="L7" s="55"/>
+      <c r="M7" s="56">
+        <v>2</v>
+      </c>
+      <c r="N7" s="57"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="53">
+        <v>1</v>
+      </c>
+      <c r="R7" s="54"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="58">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>9</v>
+      </c>
+      <c r="U7" s="58">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>441</v>
+      </c>
+      <c r="V7" s="58">
+        <f>U7/24</f>
+        <v>18.375</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="59">
+        <f>33+55</f>
+        <v>88</v>
+      </c>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="63">
+        <v>3</v>
+      </c>
+      <c r="N8" s="64"/>
+      <c r="O8" s="65">
+        <v>1</v>
+      </c>
+      <c r="P8" s="66"/>
+      <c r="Q8" s="66">
+        <v>2</v>
+      </c>
+      <c r="R8" s="67"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="68">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="69">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>2256</v>
+      </c>
+      <c r="V8" s="69">
+        <f>U8/24</f>
+        <v>94</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="70">
+        <v>83</v>
+      </c>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="73"/>
+      <c r="N9" s="74"/>
+      <c r="O9" s="70">
+        <v>1</v>
+      </c>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71"/>
+      <c r="R9" s="72"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="76">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>2016</v>
+      </c>
+      <c r="V9" s="76">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>84</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="70"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="74"/>
+      <c r="O10" s="70"/>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71"/>
+      <c r="R10" s="72"/>
+      <c r="S10" s="55"/>
+      <c r="T10" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V10" s="58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="70">
+        <v>5</v>
+      </c>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
+      <c r="L11" s="55"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="55"/>
+      <c r="T11" s="58">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U11" s="58">
+        <f t="shared" si="2"/>
+        <v>122</v>
+      </c>
+      <c r="V11" s="58">
+        <f t="shared" si="3"/>
+        <v>5.083333333333333</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="59">
+        <f>720+11+1440+432+53+64</f>
+        <v>2720</v>
+      </c>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="63">
+        <v>15</v>
+      </c>
+      <c r="N12" s="64"/>
+      <c r="O12" s="65">
+        <v>13</v>
+      </c>
+      <c r="P12" s="66"/>
+      <c r="Q12" s="66">
+        <v>20</v>
+      </c>
+      <c r="R12" s="67">
+        <v>12</v>
+      </c>
+      <c r="S12" s="62"/>
+      <c r="T12" s="69">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="U12" s="69">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>66444</v>
+      </c>
+      <c r="V12" s="69">
+        <f>U12/24</f>
+        <v>2768.5</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
+      <c r="I13" s="70"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="55"/>
+      <c r="T13" s="76">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="U13" s="76">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>64</v>
+      </c>
+      <c r="V13" s="76">
+        <f>U13/24</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="70">
+        <v>4</v>
+      </c>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="55"/>
+      <c r="T14" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="75">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>96</v>
+      </c>
+      <c r="V14" s="75">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>4</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="55"/>
+      <c r="T15" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="55"/>
+      <c r="T16" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I17" s="70"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U17" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V17" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="55"/>
+      <c r="T18" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="70">
+        <v>2</v>
+      </c>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70">
+        <f>20+24</f>
+        <v>44</v>
+      </c>
+      <c r="I19" s="70"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="55"/>
+      <c r="T19" s="58">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="U19" s="75">
+        <f t="shared" si="4"/>
+        <v>92</v>
+      </c>
+      <c r="V19" s="75">
+        <f t="shared" si="5"/>
+        <v>3.8333333333333335</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="74"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="55"/>
+      <c r="T20" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V20" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70">
+        <f>2*24</f>
+        <v>48</v>
+      </c>
+      <c r="I21" s="70"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="58">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="U21" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V21" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="70"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
+      <c r="J22" s="71"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="55"/>
+      <c r="T22" s="58">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U22" s="75">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="V22" s="75">
+        <f t="shared" si="5"/>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
+      <c r="I23" s="70"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="74"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="55"/>
+      <c r="T23" s="58">
+        <f t="shared" si="0"/>
+        <v>907</v>
+      </c>
+      <c r="U23" s="75">
+        <f t="shared" si="4"/>
+        <v>907</v>
+      </c>
+      <c r="V23" s="75">
+        <f t="shared" si="5"/>
+        <v>37.791666666666664</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="70">
+        <v>5</v>
+      </c>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I24" s="70"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="55"/>
+      <c r="T24" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U24" s="75">
+        <f t="shared" si="4"/>
+        <v>192</v>
+      </c>
+      <c r="V24" s="75">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="70">
+        <f>63+9</f>
+        <v>72</v>
+      </c>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70">
+        <v>1</v>
+      </c>
+      <c r="J25" s="71"/>
+      <c r="K25" s="72"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="73">
+        <v>10</v>
+      </c>
+      <c r="N25" s="74"/>
+      <c r="O25" s="70">
+        <v>1</v>
+      </c>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71">
+        <v>12</v>
+      </c>
+      <c r="R25" s="72"/>
+      <c r="S25" s="55"/>
+      <c r="T25" s="58">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="U25" s="75">
+        <f t="shared" si="4"/>
+        <v>2281</v>
+      </c>
+      <c r="V25" s="75">
+        <f t="shared" si="5"/>
+        <v>95.041666666666671</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="70">
+        <v>2</v>
+      </c>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="74"/>
+      <c r="O26" s="70"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="71"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="55"/>
+      <c r="T26" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V26" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="70"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="70"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="55"/>
+      <c r="T27" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="70"/>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="73"/>
+      <c r="N28" s="74"/>
+      <c r="O28" s="70"/>
+      <c r="P28" s="71"/>
+      <c r="Q28" s="71"/>
+      <c r="R28" s="72"/>
+      <c r="S28" s="55"/>
+      <c r="T28" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="70">
+        <v>37</v>
+      </c>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70">
+        <v>5</v>
+      </c>
+      <c r="J29" s="71"/>
+      <c r="K29" s="72"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="73"/>
+      <c r="N29" s="74"/>
+      <c r="O29" s="70"/>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71">
+        <v>4</v>
+      </c>
+      <c r="R29" s="72"/>
+      <c r="S29" s="55"/>
+      <c r="T29" s="58">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U29" s="75">
+        <f t="shared" si="4"/>
+        <v>989</v>
+      </c>
+      <c r="V29" s="75">
+        <f t="shared" si="5"/>
+        <v>41.208333333333336</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="70">
+        <v>8</v>
+      </c>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="74"/>
+      <c r="O30" s="70"/>
+      <c r="P30" s="71"/>
+      <c r="Q30" s="71">
+        <v>1</v>
+      </c>
+      <c r="R30" s="72"/>
+      <c r="S30" s="55"/>
+      <c r="T30" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="75">
+        <f t="shared" si="4"/>
+        <v>216</v>
+      </c>
+      <c r="V30" s="75">
+        <f t="shared" si="5"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="70"/>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="70">
+        <v>1</v>
+      </c>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="74"/>
+      <c r="O32" s="70"/>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="55"/>
+      <c r="T32" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="75">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="V32" s="75">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="70"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="73"/>
+      <c r="N33" s="74"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="55"/>
+      <c r="T33" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="70">
+        <v>36</v>
+      </c>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
+      <c r="J34" s="71"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
+      <c r="L34" s="55"/>
+      <c r="M34" s="73">
+        <v>1</v>
+      </c>
+      <c r="N34" s="74"/>
+      <c r="O34" s="70">
+        <v>1</v>
+      </c>
+      <c r="P34" s="71">
+        <v>12</v>
+      </c>
+      <c r="Q34" s="71">
+        <v>5</v>
+      </c>
+      <c r="R34" s="72"/>
+      <c r="S34" s="55"/>
+      <c r="T34" s="58">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="U34" s="75">
+        <f t="shared" si="4"/>
+        <v>1046</v>
+      </c>
+      <c r="V34" s="75">
+        <f t="shared" si="5"/>
+        <v>43.583333333333336</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="72"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="74"/>
+      <c r="O35" s="70"/>
+      <c r="P35" s="71"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="72"/>
+      <c r="S35" s="55"/>
+      <c r="T35" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="73"/>
+      <c r="N36" s="74"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="71"/>
+      <c r="Q36" s="71"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="55"/>
+      <c r="T36" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="59">
+        <f>864+1728+48</f>
+        <v>2640</v>
+      </c>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59">
+        <v>4</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>4</v>
+      </c>
+      <c r="K37" s="61">
+        <v>3</v>
+      </c>
+      <c r="L37" s="62"/>
+      <c r="M37" s="63">
+        <v>7</v>
+      </c>
+      <c r="N37" s="64"/>
+      <c r="O37" s="65">
+        <v>20</v>
+      </c>
+      <c r="P37" s="66"/>
+      <c r="Q37" s="66">
+        <v>109</v>
+      </c>
+      <c r="R37" s="67"/>
+      <c r="S37" s="62"/>
+      <c r="T37" s="77">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="U37" s="77">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>16669</v>
+      </c>
+      <c r="V37" s="77">
+        <f>U37/6</f>
+        <v>2778.1666666666665</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="70">
+        <v>2</v>
+      </c>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="73"/>
+      <c r="N38" s="74"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="71"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="55"/>
+      <c r="T38" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="75">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>48</v>
+      </c>
+      <c r="V38" s="75">
+        <f>U38/24</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="74"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="71"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="95"/>
+      <c r="T39" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U39" s="75">
+        <f>C39*24+M39*24+O39*24+Q39*24+T39</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="75">
+        <f>U39/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="59">
+        <f>126+38</f>
+        <v>164</v>
+      </c>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
+      <c r="L40" s="62"/>
+      <c r="M40" s="63"/>
+      <c r="N40" s="64"/>
+      <c r="O40" s="65"/>
+      <c r="P40" s="66"/>
+      <c r="Q40" s="66">
+        <v>10</v>
+      </c>
+      <c r="R40" s="67"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="77">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U40" s="77">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>4196</v>
+      </c>
+      <c r="V40" s="77">
+        <f>U40/24</f>
+        <v>174.83333333333334</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="82">
+        <f>192+44</f>
+        <v>236</v>
+      </c>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="85"/>
+      <c r="M41" s="86"/>
+      <c r="N41" s="87"/>
+      <c r="O41" s="82">
+        <v>4</v>
+      </c>
+      <c r="P41" s="83"/>
+      <c r="Q41" s="83">
+        <v>52</v>
+      </c>
+      <c r="R41" s="84"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="88">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>3504</v>
+      </c>
+      <c r="V41" s="88">
+        <f>U41/12</f>
+        <v>292</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="71"/>
+      <c r="K42" s="72"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="73"/>
+      <c r="N42" s="74"/>
+      <c r="O42" s="70"/>
+      <c r="P42" s="71"/>
+      <c r="Q42" s="71"/>
+      <c r="R42" s="72"/>
+      <c r="S42" s="55"/>
+      <c r="T42" s="75"/>
+      <c r="U42" s="75"/>
+      <c r="V42" s="75"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="65">
+        <f>7776+3024+8424+4320+4644</f>
+        <v>28188</v>
+      </c>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65">
+        <v>3</v>
+      </c>
+      <c r="I43" s="65">
+        <v>7</v>
+      </c>
+      <c r="J43" s="66">
+        <f>3*6+2</f>
+        <v>20</v>
+      </c>
+      <c r="K43" s="67">
+        <f>64*6+2</f>
+        <v>386</v>
+      </c>
+      <c r="L43" s="62"/>
+      <c r="M43" s="63">
+        <v>463</v>
+      </c>
+      <c r="N43" s="64"/>
+      <c r="O43" s="65">
+        <v>405</v>
+      </c>
+      <c r="P43" s="66"/>
+      <c r="Q43" s="66">
+        <v>542</v>
+      </c>
+      <c r="R43" s="67"/>
+      <c r="S43" s="62"/>
+      <c r="T43" s="77">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>416</v>
+      </c>
+      <c r="U43" s="77">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>178004</v>
+      </c>
+      <c r="V43" s="77">
+        <f>U43/6</f>
+        <v>29667.333333333332</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="70"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="71"/>
+      <c r="K44" s="72"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="73"/>
+      <c r="N44" s="74"/>
+      <c r="O44" s="70"/>
+      <c r="P44" s="71"/>
+      <c r="Q44" s="71"/>
+      <c r="R44" s="72"/>
+      <c r="S44" s="55"/>
+      <c r="T44" s="75"/>
+      <c r="U44" s="75"/>
+      <c r="V44" s="75"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="70">
+        <v>7</v>
+      </c>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="70"/>
+      <c r="I45" s="70"/>
+      <c r="J45" s="71"/>
+      <c r="K45" s="72"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="73"/>
+      <c r="N45" s="74"/>
+      <c r="O45" s="70">
+        <v>1</v>
+      </c>
+      <c r="P45" s="71"/>
+      <c r="Q45" s="71"/>
+      <c r="R45" s="72"/>
+      <c r="S45" s="55"/>
+      <c r="T45" s="75">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="75">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>192</v>
+      </c>
+      <c r="V45" s="75">
+        <f>U45/24</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="73"/>
+      <c r="N46" s="74"/>
+      <c r="O46" s="70"/>
+      <c r="P46" s="71"/>
+      <c r="Q46" s="71"/>
+      <c r="R46" s="72"/>
+      <c r="S46" s="55"/>
+      <c r="T46" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="75">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="75">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="65">
+        <f>432+106+2160+64</f>
+        <v>2762</v>
+      </c>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
+      <c r="I47" s="65"/>
+      <c r="J47" s="66">
+        <v>1</v>
+      </c>
+      <c r="K47" s="67">
+        <v>4</v>
+      </c>
+      <c r="L47" s="62"/>
+      <c r="M47" s="63">
+        <v>8</v>
+      </c>
+      <c r="N47" s="64"/>
+      <c r="O47" s="65">
+        <v>9</v>
+      </c>
+      <c r="P47" s="66">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="66">
+        <v>6</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
+      <c r="S47" s="62"/>
+      <c r="T47" s="77">
+        <f t="shared" si="7"/>
+        <v>13</v>
+      </c>
+      <c r="U47" s="77">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>16723</v>
+      </c>
+      <c r="V47" s="77">
+        <f>U47/6</f>
+        <v>2787.1666666666665</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
+      <c r="I48" s="70"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="72"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="73"/>
+      <c r="N48" s="74"/>
+      <c r="O48" s="70"/>
+      <c r="P48" s="71"/>
+      <c r="Q48" s="71"/>
+      <c r="R48" s="72"/>
+      <c r="S48" s="55"/>
+      <c r="T48" s="75">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="U48" s="75">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="V48" s="75">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="70"/>
+      <c r="I49" s="70"/>
+      <c r="J49" s="71"/>
+      <c r="K49" s="72"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="74"/>
+      <c r="O49" s="70"/>
+      <c r="P49" s="71"/>
+      <c r="Q49" s="71"/>
+      <c r="R49" s="72"/>
+      <c r="S49" s="55"/>
+      <c r="T49" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="70"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="70"/>
+      <c r="F50" s="70"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
+      <c r="J50" s="71"/>
+      <c r="K50" s="72"/>
+      <c r="L50" s="55"/>
+      <c r="M50" s="73"/>
+      <c r="N50" s="74"/>
+      <c r="O50" s="70"/>
+      <c r="P50" s="71"/>
+      <c r="Q50" s="71"/>
+      <c r="R50" s="72"/>
+      <c r="S50" s="55"/>
+      <c r="T50" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="65"/>
+      <c r="I51" s="65"/>
+      <c r="J51" s="66"/>
+      <c r="K51" s="67"/>
+      <c r="L51" s="62"/>
+      <c r="M51" s="63"/>
+      <c r="N51" s="64"/>
+      <c r="O51" s="65"/>
+      <c r="P51" s="66"/>
+      <c r="Q51" s="66"/>
+      <c r="R51" s="67"/>
+      <c r="S51" s="62"/>
+      <c r="T51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="77">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>204</v>
+      </c>
+      <c r="V51" s="77">
+        <f>U51/6</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="70"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="70"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="71"/>
+      <c r="K52" s="72"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="73"/>
+      <c r="N52" s="74"/>
+      <c r="O52" s="70"/>
+      <c r="P52" s="71"/>
+      <c r="Q52" s="71"/>
+      <c r="R52" s="72"/>
+      <c r="S52" s="55"/>
+      <c r="T52" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="75">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="70">
+        <v>9</v>
+      </c>
+      <c r="D53" s="70"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="70"/>
+      <c r="H53" s="70"/>
+      <c r="I53" s="70"/>
+      <c r="J53" s="71"/>
+      <c r="K53" s="72"/>
+      <c r="L53" s="55"/>
+      <c r="M53" s="73"/>
+      <c r="N53" s="74"/>
+      <c r="O53" s="70"/>
+      <c r="P53" s="71"/>
+      <c r="Q53" s="71"/>
+      <c r="R53" s="72"/>
+      <c r="S53" s="55"/>
+      <c r="T53" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="75">
+        <f t="shared" si="10"/>
+        <v>216</v>
+      </c>
+      <c r="V53" s="75">
+        <f t="shared" si="9"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="71"/>
+      <c r="K54" s="72"/>
+      <c r="L54" s="55"/>
+      <c r="M54" s="73"/>
+      <c r="N54" s="74"/>
+      <c r="O54" s="70"/>
+      <c r="P54" s="71"/>
+      <c r="Q54" s="71"/>
+      <c r="R54" s="72"/>
+      <c r="S54" s="55"/>
+      <c r="T54" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="70"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="70"/>
+      <c r="I55" s="70"/>
+      <c r="J55" s="71"/>
+      <c r="K55" s="72"/>
+      <c r="L55" s="55"/>
+      <c r="M55" s="73"/>
+      <c r="N55" s="74"/>
+      <c r="O55" s="70"/>
+      <c r="P55" s="71"/>
+      <c r="Q55" s="71"/>
+      <c r="R55" s="72"/>
+      <c r="S55" s="55"/>
+      <c r="T55" s="75"/>
+      <c r="U55" s="75"/>
+      <c r="V55" s="75"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="70"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="70"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="71"/>
+      <c r="K56" s="72"/>
+      <c r="L56" s="55"/>
+      <c r="M56" s="73"/>
+      <c r="N56" s="74"/>
+      <c r="O56" s="70"/>
+      <c r="P56" s="71"/>
+      <c r="Q56" s="71"/>
+      <c r="R56" s="72"/>
+      <c r="S56" s="55"/>
+      <c r="T56" s="75"/>
+      <c r="U56" s="75"/>
+      <c r="V56" s="75"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="70"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="70"/>
+      <c r="I57" s="70"/>
+      <c r="J57" s="71"/>
+      <c r="K57" s="72"/>
+      <c r="L57" s="55"/>
+      <c r="M57" s="73"/>
+      <c r="N57" s="74"/>
+      <c r="O57" s="70"/>
+      <c r="P57" s="71"/>
+      <c r="Q57" s="71"/>
+      <c r="R57" s="72"/>
+      <c r="S57" s="55"/>
+      <c r="T57" s="75"/>
+      <c r="U57" s="75"/>
+      <c r="V57" s="75"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>37126</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>1191</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>39</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>25</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>422</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>509</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>457</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>16</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>764</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>15</v>
+      </c>
+      <c r="S58" s="55"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>1708</v>
+      </c>
+      <c r="U58" s="90">
+        <f>SUM(U7:U57)</f>
+        <v>297274</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>38982.416666666664</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="113" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -29998,21 +33131,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -30024,17 +33157,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -30054,13 +33187,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -30100,10 +33233,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -30111,9 +33244,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -32825,17 +35958,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -33144,21 +36277,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -33170,17 +36303,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -33200,13 +36333,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -33246,10 +36379,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -33257,9 +36390,9 @@
       <c r="Q5" s="96"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -35994,17 +39127,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -36313,21 +39446,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -36339,17 +39472,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -36369,13 +39502,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -36415,10 +39548,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -36426,9 +39559,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -39123,17 +42256,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -39442,21 +42575,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -39468,17 +42601,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -39498,13 +42631,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -39544,10 +42677,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -39555,9 +42688,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -42257,17 +45390,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -42576,21 +45709,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -42602,17 +45735,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -42632,13 +45765,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -42678,10 +45811,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -42689,9 +45822,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -45385,17 +48518,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -45704,21 +48837,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -45730,17 +48863,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -45760,13 +48893,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -45806,10 +48939,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -45817,9 +48950,9 @@
       <c r="Q5" s="100"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -48515,17 +51648,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -48834,21 +51967,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -48860,17 +51993,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -48890,13 +52023,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -48936,10 +52069,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -48947,9 +52080,9 @@
       <c r="Q5" s="101"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -51650,17 +54783,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -51969,21 +55102,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -51995,17 +55128,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -52025,13 +55158,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -52071,10 +55204,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -52082,9 +55215,9 @@
       <c r="Q5" s="102"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -54780,17 +57913,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>

--- a/GBDS JUNE FILES 2026/INVENTORY COUNT SHEET - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/INVENTORY COUNT SHEET - JUNE 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B475FC0-A242-4053-9406-1BC00D932AA4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{427DA506-DA77-4450-9095-085887FAF3F4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="8" activeTab="17" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="9" activeTab="18" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -31,6 +31,7 @@
     <sheet name="06-19-2026 " sheetId="69" r:id="rId16"/>
     <sheet name="06-22-2026" sheetId="70" r:id="rId17"/>
     <sheet name="06-23-2026" sheetId="71" r:id="rId18"/>
+    <sheet name="06-24-2026" sheetId="72" r:id="rId19"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'06-01-2026'!$A$1:$W$59</definedName>
@@ -50,6 +51,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="15">'06-19-2026 '!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="16">'06-22-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="17">'06-23-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="18">'06-24-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -68,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1512" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1596" uniqueCount="74">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -1277,7 +1279,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1563,6 +1565,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2015,21 +2020,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -2041,17 +2046,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="119"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -2071,13 +2076,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="122" t="s">
+      <c r="U4" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="109" t="s">
+      <c r="V4" s="110" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2117,10 +2122,10 @@
       <c r="I5" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="111" t="s">
+      <c r="J5" s="112" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="112"/>
+      <c r="K5" s="113"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2128,9 +2133,9 @@
       <c r="Q5" s="89"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="123"/>
-      <c r="V5" s="110"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="111"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -4661,17 +4666,17 @@
       <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="113" t="s">
+      <c r="C62" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="114"/>
-      <c r="E62" s="114"/>
-      <c r="F62" s="114"/>
-      <c r="G62" s="114"/>
-      <c r="H62" s="114"/>
-      <c r="I62" s="114"/>
-      <c r="J62" s="114"/>
-      <c r="K62" s="115"/>
+      <c r="D62" s="115"/>
+      <c r="E62" s="115"/>
+      <c r="F62" s="115"/>
+      <c r="G62" s="115"/>
+      <c r="H62" s="115"/>
+      <c r="I62" s="115"/>
+      <c r="J62" s="115"/>
+      <c r="K62" s="116"/>
       <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
@@ -4980,21 +4985,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -5006,17 +5011,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="119"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -5036,13 +5041,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="126" t="s">
+      <c r="U4" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="109" t="s">
+      <c r="V4" s="110" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -5082,10 +5087,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="124" t="s">
+      <c r="J5" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="125"/>
+      <c r="K5" s="126"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -5093,9 +5098,9 @@
       <c r="Q5" s="103"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="127"/>
-      <c r="V5" s="110"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="111"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -7780,17 +7785,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="113" t="s">
+      <c r="C60" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="114"/>
-      <c r="E60" s="114"/>
-      <c r="F60" s="114"/>
-      <c r="G60" s="114"/>
-      <c r="H60" s="114"/>
-      <c r="I60" s="114"/>
-      <c r="J60" s="114"/>
-      <c r="K60" s="115"/>
+      <c r="D60" s="115"/>
+      <c r="E60" s="115"/>
+      <c r="F60" s="115"/>
+      <c r="G60" s="115"/>
+      <c r="H60" s="115"/>
+      <c r="I60" s="115"/>
+      <c r="J60" s="115"/>
+      <c r="K60" s="116"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -8099,21 +8104,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -8125,17 +8130,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="119"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -8155,13 +8160,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="126" t="s">
+      <c r="U4" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="109" t="s">
+      <c r="V4" s="110" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -8201,10 +8206,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="124" t="s">
+      <c r="J5" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="125"/>
+      <c r="K5" s="126"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -8212,9 +8217,9 @@
       <c r="Q5" s="104"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="127"/>
-      <c r="V5" s="110"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="111"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -10908,17 +10913,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="113" t="s">
+      <c r="C60" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="114"/>
-      <c r="E60" s="114"/>
-      <c r="F60" s="114"/>
-      <c r="G60" s="114"/>
-      <c r="H60" s="114"/>
-      <c r="I60" s="114"/>
-      <c r="J60" s="114"/>
-      <c r="K60" s="115"/>
+      <c r="D60" s="115"/>
+      <c r="E60" s="115"/>
+      <c r="F60" s="115"/>
+      <c r="G60" s="115"/>
+      <c r="H60" s="115"/>
+      <c r="I60" s="115"/>
+      <c r="J60" s="115"/>
+      <c r="K60" s="116"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -11227,21 +11232,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -11253,17 +11258,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="119"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -11283,13 +11288,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="126" t="s">
+      <c r="U4" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="109" t="s">
+      <c r="V4" s="110" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -11329,10 +11334,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="124" t="s">
+      <c r="J5" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="125"/>
+      <c r="K5" s="126"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -11340,9 +11345,9 @@
       <c r="Q5" s="105"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="127"/>
-      <c r="V5" s="110"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="111"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -14037,17 +14042,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="113" t="s">
+      <c r="C60" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="114"/>
-      <c r="E60" s="114"/>
-      <c r="F60" s="114"/>
-      <c r="G60" s="114"/>
-      <c r="H60" s="114"/>
-      <c r="I60" s="114"/>
-      <c r="J60" s="114"/>
-      <c r="K60" s="115"/>
+      <c r="D60" s="115"/>
+      <c r="E60" s="115"/>
+      <c r="F60" s="115"/>
+      <c r="G60" s="115"/>
+      <c r="H60" s="115"/>
+      <c r="I60" s="115"/>
+      <c r="J60" s="115"/>
+      <c r="K60" s="116"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -14356,21 +14361,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -14382,17 +14387,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="119"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -14412,13 +14417,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="126" t="s">
+      <c r="U4" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="109" t="s">
+      <c r="V4" s="110" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -14458,10 +14463,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="124" t="s">
+      <c r="J5" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="125"/>
+      <c r="K5" s="126"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -14469,9 +14474,9 @@
       <c r="Q5" s="106"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="127"/>
-      <c r="V5" s="110"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="111"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -17164,17 +17169,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="113" t="s">
+      <c r="C60" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="114"/>
-      <c r="E60" s="114"/>
-      <c r="F60" s="114"/>
-      <c r="G60" s="114"/>
-      <c r="H60" s="114"/>
-      <c r="I60" s="114"/>
-      <c r="J60" s="114"/>
-      <c r="K60" s="115"/>
+      <c r="D60" s="115"/>
+      <c r="E60" s="115"/>
+      <c r="F60" s="115"/>
+      <c r="G60" s="115"/>
+      <c r="H60" s="115"/>
+      <c r="I60" s="115"/>
+      <c r="J60" s="115"/>
+      <c r="K60" s="116"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -17483,21 +17488,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -17509,17 +17514,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="119"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -17539,13 +17544,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="126" t="s">
+      <c r="U4" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="109" t="s">
+      <c r="V4" s="110" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -17585,10 +17590,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="124" t="s">
+      <c r="J5" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="125"/>
+      <c r="K5" s="126"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -17596,9 +17601,9 @@
       <c r="Q5" s="107"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="127"/>
-      <c r="V5" s="110"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="111"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -20287,17 +20292,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="113" t="s">
+      <c r="C60" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="114"/>
-      <c r="E60" s="114"/>
-      <c r="F60" s="114"/>
-      <c r="G60" s="114"/>
-      <c r="H60" s="114"/>
-      <c r="I60" s="114"/>
-      <c r="J60" s="114"/>
-      <c r="K60" s="115"/>
+      <c r="D60" s="115"/>
+      <c r="E60" s="115"/>
+      <c r="F60" s="115"/>
+      <c r="G60" s="115"/>
+      <c r="H60" s="115"/>
+      <c r="I60" s="115"/>
+      <c r="J60" s="115"/>
+      <c r="K60" s="116"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -20606,21 +20611,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -20632,17 +20637,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="119"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -20662,13 +20667,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="126" t="s">
+      <c r="U4" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="109" t="s">
+      <c r="V4" s="110" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -20708,10 +20713,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="124" t="s">
+      <c r="J5" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="125"/>
+      <c r="K5" s="126"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -20719,9 +20724,9 @@
       <c r="Q5" s="107"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="127"/>
-      <c r="V5" s="110"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="111"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -23410,17 +23415,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="113" t="s">
+      <c r="C60" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="114"/>
-      <c r="E60" s="114"/>
-      <c r="F60" s="114"/>
-      <c r="G60" s="114"/>
-      <c r="H60" s="114"/>
-      <c r="I60" s="114"/>
-      <c r="J60" s="114"/>
-      <c r="K60" s="115"/>
+      <c r="D60" s="115"/>
+      <c r="E60" s="115"/>
+      <c r="F60" s="115"/>
+      <c r="G60" s="115"/>
+      <c r="H60" s="115"/>
+      <c r="I60" s="115"/>
+      <c r="J60" s="115"/>
+      <c r="K60" s="116"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -23729,21 +23734,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -23755,17 +23760,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="119"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -23785,13 +23790,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="126" t="s">
+      <c r="U4" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="109" t="s">
+      <c r="V4" s="110" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -23831,10 +23836,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="124" t="s">
+      <c r="J5" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="125"/>
+      <c r="K5" s="126"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -23842,9 +23847,9 @@
       <c r="Q5" s="107"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="127"/>
-      <c r="V5" s="110"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="111"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -26542,17 +26547,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="113" t="s">
+      <c r="C60" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="114"/>
-      <c r="E60" s="114"/>
-      <c r="F60" s="114"/>
-      <c r="G60" s="114"/>
-      <c r="H60" s="114"/>
-      <c r="I60" s="114"/>
-      <c r="J60" s="114"/>
-      <c r="K60" s="115"/>
+      <c r="D60" s="115"/>
+      <c r="E60" s="115"/>
+      <c r="F60" s="115"/>
+      <c r="G60" s="115"/>
+      <c r="H60" s="115"/>
+      <c r="I60" s="115"/>
+      <c r="J60" s="115"/>
+      <c r="K60" s="116"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -26861,21 +26866,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -26887,17 +26892,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="119"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -26917,13 +26922,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="126" t="s">
+      <c r="U4" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="109" t="s">
+      <c r="V4" s="110" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -26963,10 +26968,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="124" t="s">
+      <c r="J5" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="125"/>
+      <c r="K5" s="126"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -26974,9 +26979,9 @@
       <c r="Q5" s="107"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="127"/>
-      <c r="V5" s="110"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="111"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -29684,17 +29689,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="113" t="s">
+      <c r="C60" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="114"/>
-      <c r="E60" s="114"/>
-      <c r="F60" s="114"/>
-      <c r="G60" s="114"/>
-      <c r="H60" s="114"/>
-      <c r="I60" s="114"/>
-      <c r="J60" s="114"/>
-      <c r="K60" s="115"/>
+      <c r="D60" s="115"/>
+      <c r="E60" s="115"/>
+      <c r="F60" s="115"/>
+      <c r="G60" s="115"/>
+      <c r="H60" s="115"/>
+      <c r="I60" s="115"/>
+      <c r="J60" s="115"/>
+      <c r="K60" s="116"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -30003,21 +30008,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -30029,17 +30034,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="119"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -30059,13 +30064,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="126" t="s">
+      <c r="U4" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="109" t="s">
+      <c r="V4" s="110" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -30105,10 +30110,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="124" t="s">
+      <c r="J5" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="125"/>
+      <c r="K5" s="126"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -30116,9 +30121,9 @@
       <c r="Q5" s="108"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="127"/>
-      <c r="V5" s="110"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="111"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -32812,17 +32817,3165 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="113" t="s">
+      <c r="C60" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="114"/>
-      <c r="E60" s="114"/>
-      <c r="F60" s="114"/>
-      <c r="G60" s="114"/>
-      <c r="H60" s="114"/>
-      <c r="I60" s="114"/>
-      <c r="J60" s="114"/>
-      <c r="K60" s="115"/>
+      <c r="D60" s="115"/>
+      <c r="E60" s="115"/>
+      <c r="F60" s="115"/>
+      <c r="G60" s="115"/>
+      <c r="H60" s="115"/>
+      <c r="I60" s="115"/>
+      <c r="J60" s="115"/>
+      <c r="K60" s="116"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9E77CA5-5417-4708-A976-C4AC15747B86}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="9" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="117" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="118" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="121" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="127" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="110" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="125" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="126"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="109"/>
+      <c r="Q5" s="109"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="111"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="109"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="109"/>
+      <c r="Q6" s="109"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="52">
+        <v>14</v>
+      </c>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
+      <c r="J7" s="53"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
+      <c r="L7" s="55"/>
+      <c r="M7" s="56">
+        <v>1</v>
+      </c>
+      <c r="N7" s="57"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="53">
+        <v>1</v>
+      </c>
+      <c r="R7" s="54"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="58">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>9</v>
+      </c>
+      <c r="U7" s="58">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>417</v>
+      </c>
+      <c r="V7" s="58">
+        <f>U7/24</f>
+        <v>17.375</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="59">
+        <f>55+33</f>
+        <v>88</v>
+      </c>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="63">
+        <v>2</v>
+      </c>
+      <c r="N8" s="64"/>
+      <c r="O8" s="65">
+        <v>1</v>
+      </c>
+      <c r="P8" s="66"/>
+      <c r="Q8" s="66">
+        <v>2</v>
+      </c>
+      <c r="R8" s="67"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="68">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="69">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>2232</v>
+      </c>
+      <c r="V8" s="69">
+        <f>U8/24</f>
+        <v>93</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="70">
+        <v>78</v>
+      </c>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="73">
+        <v>5</v>
+      </c>
+      <c r="N9" s="74"/>
+      <c r="O9" s="70">
+        <v>1</v>
+      </c>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71"/>
+      <c r="R9" s="72"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="76">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>2016</v>
+      </c>
+      <c r="V9" s="76">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>84</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="70"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="74"/>
+      <c r="O10" s="70"/>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71"/>
+      <c r="R10" s="72"/>
+      <c r="S10" s="55"/>
+      <c r="T10" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V10" s="58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="70">
+        <v>5</v>
+      </c>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
+      <c r="L11" s="55"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="55"/>
+      <c r="T11" s="58">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U11" s="58">
+        <f t="shared" si="2"/>
+        <v>122</v>
+      </c>
+      <c r="V11" s="58">
+        <f t="shared" si="3"/>
+        <v>5.083333333333333</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="59">
+        <f>720+11+1440+432+19+64</f>
+        <v>2686</v>
+      </c>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="63">
+        <v>14</v>
+      </c>
+      <c r="N12" s="64"/>
+      <c r="O12" s="65">
+        <v>14</v>
+      </c>
+      <c r="P12" s="66"/>
+      <c r="Q12" s="66">
+        <v>20</v>
+      </c>
+      <c r="R12" s="67">
+        <v>12</v>
+      </c>
+      <c r="S12" s="62"/>
+      <c r="T12" s="69">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="U12" s="69">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>65628</v>
+      </c>
+      <c r="V12" s="69">
+        <f>U12/24</f>
+        <v>2734.5</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
+      <c r="I13" s="70"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="55"/>
+      <c r="T13" s="76">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="U13" s="76">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>64</v>
+      </c>
+      <c r="V13" s="76">
+        <f>U13/24</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="70">
+        <v>4</v>
+      </c>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="55"/>
+      <c r="T14" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="75">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>96</v>
+      </c>
+      <c r="V14" s="75">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>4</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="55"/>
+      <c r="T15" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="55"/>
+      <c r="T16" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I17" s="70"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U17" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V17" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="55"/>
+      <c r="T18" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="70">
+        <v>2</v>
+      </c>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70">
+        <f>20+24</f>
+        <v>44</v>
+      </c>
+      <c r="I19" s="70"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="55"/>
+      <c r="T19" s="58">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="U19" s="75">
+        <f t="shared" si="4"/>
+        <v>92</v>
+      </c>
+      <c r="V19" s="75">
+        <f t="shared" si="5"/>
+        <v>3.8333333333333335</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="74"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="55"/>
+      <c r="T20" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V20" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70">
+        <f>2*24</f>
+        <v>48</v>
+      </c>
+      <c r="I21" s="70"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="58">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="U21" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V21" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="70"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
+      <c r="J22" s="71"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="55"/>
+      <c r="T22" s="58">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U22" s="75">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="V22" s="75">
+        <f t="shared" si="5"/>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
+      <c r="I23" s="70"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="74"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="55"/>
+      <c r="T23" s="58">
+        <f t="shared" si="0"/>
+        <v>907</v>
+      </c>
+      <c r="U23" s="75">
+        <f t="shared" si="4"/>
+        <v>907</v>
+      </c>
+      <c r="V23" s="75">
+        <f t="shared" si="5"/>
+        <v>37.791666666666664</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="70">
+        <v>5</v>
+      </c>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I24" s="70"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="55"/>
+      <c r="T24" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U24" s="75">
+        <f t="shared" si="4"/>
+        <v>192</v>
+      </c>
+      <c r="V24" s="75">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="70">
+        <f>63+3</f>
+        <v>66</v>
+      </c>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70"/>
+      <c r="J25" s="71">
+        <v>1</v>
+      </c>
+      <c r="K25" s="72"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="73">
+        <v>2</v>
+      </c>
+      <c r="N25" s="74"/>
+      <c r="O25" s="70">
+        <v>1</v>
+      </c>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71">
+        <v>2</v>
+      </c>
+      <c r="R25" s="72"/>
+      <c r="S25" s="55"/>
+      <c r="T25" s="58">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="U25" s="75">
+        <f t="shared" si="4"/>
+        <v>1705</v>
+      </c>
+      <c r="V25" s="75">
+        <f t="shared" si="5"/>
+        <v>71.041666666666671</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="73">
+        <v>2</v>
+      </c>
+      <c r="N26" s="74"/>
+      <c r="O26" s="70"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="71"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="55"/>
+      <c r="T26" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V26" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="70"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="70"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="55"/>
+      <c r="T27" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="70">
+        <v>192</v>
+      </c>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="73"/>
+      <c r="N28" s="74"/>
+      <c r="O28" s="70"/>
+      <c r="P28" s="71"/>
+      <c r="Q28" s="71"/>
+      <c r="R28" s="72"/>
+      <c r="S28" s="55"/>
+      <c r="T28" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="75">
+        <f t="shared" si="4"/>
+        <v>4608</v>
+      </c>
+      <c r="V28" s="75">
+        <f t="shared" si="5"/>
+        <v>192</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="70">
+        <v>32</v>
+      </c>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70"/>
+      <c r="J29" s="71">
+        <v>5</v>
+      </c>
+      <c r="K29" s="72"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="73">
+        <v>1</v>
+      </c>
+      <c r="N29" s="74"/>
+      <c r="O29" s="70">
+        <v>1</v>
+      </c>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71">
+        <v>2</v>
+      </c>
+      <c r="R29" s="72"/>
+      <c r="S29" s="55"/>
+      <c r="T29" s="58">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U29" s="75">
+        <f t="shared" si="4"/>
+        <v>869</v>
+      </c>
+      <c r="V29" s="75">
+        <f t="shared" si="5"/>
+        <v>36.208333333333336</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="70">
+        <v>5</v>
+      </c>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="73">
+        <v>1</v>
+      </c>
+      <c r="N30" s="74"/>
+      <c r="O30" s="70"/>
+      <c r="P30" s="71"/>
+      <c r="Q30" s="71">
+        <v>2</v>
+      </c>
+      <c r="R30" s="72"/>
+      <c r="S30" s="55"/>
+      <c r="T30" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="75">
+        <f t="shared" si="4"/>
+        <v>192</v>
+      </c>
+      <c r="V30" s="75">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="70">
+        <v>5</v>
+      </c>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="70"/>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V31" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="70"/>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="73">
+        <v>1</v>
+      </c>
+      <c r="N32" s="74"/>
+      <c r="O32" s="70"/>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="55"/>
+      <c r="T32" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="75">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="V32" s="75">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="70"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="73"/>
+      <c r="N33" s="74"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="55"/>
+      <c r="T33" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="70">
+        <v>32</v>
+      </c>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
+      <c r="J34" s="71"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
+      <c r="L34" s="55"/>
+      <c r="M34" s="73">
+        <v>1</v>
+      </c>
+      <c r="N34" s="74"/>
+      <c r="O34" s="70">
+        <v>1</v>
+      </c>
+      <c r="P34" s="71">
+        <v>12</v>
+      </c>
+      <c r="Q34" s="71">
+        <v>2</v>
+      </c>
+      <c r="R34" s="72"/>
+      <c r="S34" s="55"/>
+      <c r="T34" s="58">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="U34" s="75">
+        <f t="shared" si="4"/>
+        <v>878</v>
+      </c>
+      <c r="V34" s="75">
+        <f t="shared" si="5"/>
+        <v>36.583333333333336</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="72"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="74"/>
+      <c r="O35" s="70"/>
+      <c r="P35" s="71"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="72"/>
+      <c r="S35" s="55"/>
+      <c r="T35" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="73"/>
+      <c r="N36" s="74"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="71"/>
+      <c r="Q36" s="71"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="55"/>
+      <c r="T36" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="59">
+        <f>864+1620+42</f>
+        <v>2526</v>
+      </c>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59">
+        <v>4</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>4</v>
+      </c>
+      <c r="K37" s="61">
+        <v>3</v>
+      </c>
+      <c r="L37" s="62"/>
+      <c r="M37" s="63">
+        <v>43</v>
+      </c>
+      <c r="N37" s="64"/>
+      <c r="O37" s="65">
+        <v>30</v>
+      </c>
+      <c r="P37" s="66"/>
+      <c r="Q37" s="66">
+        <v>43</v>
+      </c>
+      <c r="R37" s="67"/>
+      <c r="S37" s="62"/>
+      <c r="T37" s="77">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="U37" s="77">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>15865</v>
+      </c>
+      <c r="V37" s="77">
+        <f>U37/6</f>
+        <v>2644.1666666666665</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="73">
+        <v>2</v>
+      </c>
+      <c r="N38" s="74"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="71"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="55"/>
+      <c r="T38" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="75">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>48</v>
+      </c>
+      <c r="V38" s="75">
+        <f>U38/24</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="74"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="71"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="95"/>
+      <c r="T39" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U39" s="75">
+        <f>C39*24+M39*24+O39*24+Q39*24+T39</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="75">
+        <f>U39/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="59">
+        <f>126+33</f>
+        <v>159</v>
+      </c>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
+      <c r="L40" s="62"/>
+      <c r="M40" s="63">
+        <v>2</v>
+      </c>
+      <c r="N40" s="64"/>
+      <c r="O40" s="65">
+        <v>1</v>
+      </c>
+      <c r="P40" s="66"/>
+      <c r="Q40" s="66">
+        <v>2</v>
+      </c>
+      <c r="R40" s="67"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="77">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U40" s="77">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>3956</v>
+      </c>
+      <c r="V40" s="77">
+        <f>U40/24</f>
+        <v>164.83333333333334</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="82">
+        <f>96+94</f>
+        <v>190</v>
+      </c>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="85"/>
+      <c r="M41" s="86">
+        <v>10</v>
+      </c>
+      <c r="N41" s="87"/>
+      <c r="O41" s="82">
+        <v>6</v>
+      </c>
+      <c r="P41" s="83"/>
+      <c r="Q41" s="83">
+        <v>26</v>
+      </c>
+      <c r="R41" s="84"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="88">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>2784</v>
+      </c>
+      <c r="V41" s="88">
+        <f>U41/12</f>
+        <v>232</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="71"/>
+      <c r="K42" s="72"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="73"/>
+      <c r="N42" s="74"/>
+      <c r="O42" s="70"/>
+      <c r="P42" s="71"/>
+      <c r="Q42" s="71"/>
+      <c r="R42" s="72"/>
+      <c r="S42" s="55"/>
+      <c r="T42" s="75"/>
+      <c r="U42" s="75"/>
+      <c r="V42" s="75"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="65">
+        <f>1512+7776+3024+8424+3024+4644+72</f>
+        <v>28476</v>
+      </c>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65">
+        <v>1</v>
+      </c>
+      <c r="I43" s="65">
+        <v>7</v>
+      </c>
+      <c r="J43" s="66">
+        <f>4*6+3</f>
+        <v>27</v>
+      </c>
+      <c r="K43" s="67">
+        <f>64*6+2</f>
+        <v>386</v>
+      </c>
+      <c r="L43" s="62"/>
+      <c r="M43" s="63">
+        <v>364</v>
+      </c>
+      <c r="N43" s="64"/>
+      <c r="O43" s="65">
+        <v>416</v>
+      </c>
+      <c r="P43" s="66"/>
+      <c r="Q43" s="66">
+        <v>581</v>
+      </c>
+      <c r="R43" s="67"/>
+      <c r="S43" s="62"/>
+      <c r="T43" s="77">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>421</v>
+      </c>
+      <c r="U43" s="77">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>179443</v>
+      </c>
+      <c r="V43" s="77">
+        <f>U43/6</f>
+        <v>29907.166666666668</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="70"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="71"/>
+      <c r="K44" s="72"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="73"/>
+      <c r="N44" s="74"/>
+      <c r="O44" s="70"/>
+      <c r="P44" s="71"/>
+      <c r="Q44" s="71"/>
+      <c r="R44" s="72"/>
+      <c r="S44" s="55"/>
+      <c r="T44" s="75"/>
+      <c r="U44" s="75"/>
+      <c r="V44" s="75"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="70">
+        <v>5</v>
+      </c>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="70"/>
+      <c r="I45" s="70"/>
+      <c r="J45" s="71"/>
+      <c r="K45" s="72"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="73">
+        <v>2</v>
+      </c>
+      <c r="N45" s="74"/>
+      <c r="O45" s="70">
+        <v>1</v>
+      </c>
+      <c r="P45" s="71"/>
+      <c r="Q45" s="71"/>
+      <c r="R45" s="72"/>
+      <c r="S45" s="55"/>
+      <c r="T45" s="75">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="75">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>192</v>
+      </c>
+      <c r="V45" s="75">
+        <f>U45/24</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="73"/>
+      <c r="N46" s="74"/>
+      <c r="O46" s="70"/>
+      <c r="P46" s="71"/>
+      <c r="Q46" s="71"/>
+      <c r="R46" s="72"/>
+      <c r="S46" s="55"/>
+      <c r="T46" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="75">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="75">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="65">
+        <f>432+106+2160+64</f>
+        <v>2762</v>
+      </c>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
+      <c r="I47" s="65"/>
+      <c r="J47" s="66">
+        <v>1</v>
+      </c>
+      <c r="K47" s="67">
+        <v>4</v>
+      </c>
+      <c r="L47" s="62"/>
+      <c r="M47" s="63">
+        <v>6</v>
+      </c>
+      <c r="N47" s="64"/>
+      <c r="O47" s="65">
+        <v>9</v>
+      </c>
+      <c r="P47" s="66">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="66">
+        <v>3</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
+      <c r="S47" s="62"/>
+      <c r="T47" s="77">
+        <f t="shared" si="7"/>
+        <v>13</v>
+      </c>
+      <c r="U47" s="77">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>16693</v>
+      </c>
+      <c r="V47" s="77">
+        <f>U47/6</f>
+        <v>2782.1666666666665</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
+      <c r="I48" s="70"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="72"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="73"/>
+      <c r="N48" s="74"/>
+      <c r="O48" s="70"/>
+      <c r="P48" s="71"/>
+      <c r="Q48" s="71"/>
+      <c r="R48" s="72"/>
+      <c r="S48" s="55"/>
+      <c r="T48" s="75">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="U48" s="75">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="V48" s="75">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="70"/>
+      <c r="I49" s="70"/>
+      <c r="J49" s="71"/>
+      <c r="K49" s="72"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="74"/>
+      <c r="O49" s="70"/>
+      <c r="P49" s="71"/>
+      <c r="Q49" s="71"/>
+      <c r="R49" s="72"/>
+      <c r="S49" s="55"/>
+      <c r="T49" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="70"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="70"/>
+      <c r="F50" s="70"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
+      <c r="J50" s="71"/>
+      <c r="K50" s="72"/>
+      <c r="L50" s="55"/>
+      <c r="M50" s="73"/>
+      <c r="N50" s="74"/>
+      <c r="O50" s="70"/>
+      <c r="P50" s="71"/>
+      <c r="Q50" s="71"/>
+      <c r="R50" s="72"/>
+      <c r="S50" s="55"/>
+      <c r="T50" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="65"/>
+      <c r="I51" s="65"/>
+      <c r="J51" s="66"/>
+      <c r="K51" s="67"/>
+      <c r="L51" s="62"/>
+      <c r="M51" s="63"/>
+      <c r="N51" s="64"/>
+      <c r="O51" s="65"/>
+      <c r="P51" s="66"/>
+      <c r="Q51" s="66"/>
+      <c r="R51" s="67"/>
+      <c r="S51" s="62"/>
+      <c r="T51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="77">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>204</v>
+      </c>
+      <c r="V51" s="77">
+        <f>U51/6</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="70"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="70"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="71"/>
+      <c r="K52" s="72"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="73"/>
+      <c r="N52" s="74"/>
+      <c r="O52" s="70"/>
+      <c r="P52" s="71"/>
+      <c r="Q52" s="71"/>
+      <c r="R52" s="72"/>
+      <c r="S52" s="55"/>
+      <c r="T52" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="75">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="70">
+        <v>9</v>
+      </c>
+      <c r="D53" s="70"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="70"/>
+      <c r="H53" s="70"/>
+      <c r="I53" s="70"/>
+      <c r="J53" s="71"/>
+      <c r="K53" s="72"/>
+      <c r="L53" s="55"/>
+      <c r="M53" s="73"/>
+      <c r="N53" s="74"/>
+      <c r="O53" s="70"/>
+      <c r="P53" s="71"/>
+      <c r="Q53" s="71"/>
+      <c r="R53" s="72"/>
+      <c r="S53" s="55"/>
+      <c r="T53" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="75">
+        <f t="shared" si="10"/>
+        <v>216</v>
+      </c>
+      <c r="V53" s="75">
+        <f t="shared" si="9"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="71"/>
+      <c r="K54" s="72"/>
+      <c r="L54" s="55"/>
+      <c r="M54" s="73"/>
+      <c r="N54" s="74"/>
+      <c r="O54" s="70"/>
+      <c r="P54" s="71"/>
+      <c r="Q54" s="71"/>
+      <c r="R54" s="72"/>
+      <c r="S54" s="55"/>
+      <c r="T54" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="70"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="70"/>
+      <c r="I55" s="70"/>
+      <c r="J55" s="71"/>
+      <c r="K55" s="72"/>
+      <c r="L55" s="55"/>
+      <c r="M55" s="73"/>
+      <c r="N55" s="74"/>
+      <c r="O55" s="70"/>
+      <c r="P55" s="71"/>
+      <c r="Q55" s="71"/>
+      <c r="R55" s="72"/>
+      <c r="S55" s="55"/>
+      <c r="T55" s="75"/>
+      <c r="U55" s="75"/>
+      <c r="V55" s="75"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="70"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="70"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="71"/>
+      <c r="K56" s="72"/>
+      <c r="L56" s="55"/>
+      <c r="M56" s="73"/>
+      <c r="N56" s="74"/>
+      <c r="O56" s="70"/>
+      <c r="P56" s="71"/>
+      <c r="Q56" s="71"/>
+      <c r="R56" s="72"/>
+      <c r="S56" s="55"/>
+      <c r="T56" s="75"/>
+      <c r="U56" s="75"/>
+      <c r="V56" s="75"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="70"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="70"/>
+      <c r="I57" s="70"/>
+      <c r="J57" s="71"/>
+      <c r="K57" s="72"/>
+      <c r="L57" s="55"/>
+      <c r="M57" s="73"/>
+      <c r="N57" s="74"/>
+      <c r="O57" s="70"/>
+      <c r="P57" s="71"/>
+      <c r="Q57" s="71"/>
+      <c r="R57" s="72"/>
+      <c r="S57" s="55"/>
+      <c r="T57" s="75"/>
+      <c r="U57" s="75"/>
+      <c r="V57" s="75"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>37382</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>1189</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>33</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>38</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>422</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>459</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>483</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>16</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>686</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>15</v>
+      </c>
+      <c r="S58" s="55"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>1713</v>
+      </c>
+      <c r="U58" s="90">
+        <f>SUM(U7:U57)</f>
+        <v>299895</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>39137.25</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="114" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="115"/>
+      <c r="E60" s="115"/>
+      <c r="F60" s="115"/>
+      <c r="G60" s="115"/>
+      <c r="H60" s="115"/>
+      <c r="I60" s="115"/>
+      <c r="J60" s="115"/>
+      <c r="K60" s="116"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -33131,21 +36284,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -33157,17 +36310,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="119"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -33187,13 +36340,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="126" t="s">
+      <c r="U4" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="109" t="s">
+      <c r="V4" s="110" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -33233,10 +36386,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="124" t="s">
+      <c r="J5" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="125"/>
+      <c r="K5" s="126"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -33244,9 +36397,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="127"/>
-      <c r="V5" s="110"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="111"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -35958,17 +39111,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="113" t="s">
+      <c r="C60" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="114"/>
-      <c r="E60" s="114"/>
-      <c r="F60" s="114"/>
-      <c r="G60" s="114"/>
-      <c r="H60" s="114"/>
-      <c r="I60" s="114"/>
-      <c r="J60" s="114"/>
-      <c r="K60" s="115"/>
+      <c r="D60" s="115"/>
+      <c r="E60" s="115"/>
+      <c r="F60" s="115"/>
+      <c r="G60" s="115"/>
+      <c r="H60" s="115"/>
+      <c r="I60" s="115"/>
+      <c r="J60" s="115"/>
+      <c r="K60" s="116"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -36277,21 +39430,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -36303,17 +39456,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="119"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -36333,13 +39486,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="126" t="s">
+      <c r="U4" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="109" t="s">
+      <c r="V4" s="110" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -36379,10 +39532,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="124" t="s">
+      <c r="J5" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="125"/>
+      <c r="K5" s="126"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -36390,9 +39543,9 @@
       <c r="Q5" s="96"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="127"/>
-      <c r="V5" s="110"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="111"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -39127,17 +42280,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="113" t="s">
+      <c r="C60" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="114"/>
-      <c r="E60" s="114"/>
-      <c r="F60" s="114"/>
-      <c r="G60" s="114"/>
-      <c r="H60" s="114"/>
-      <c r="I60" s="114"/>
-      <c r="J60" s="114"/>
-      <c r="K60" s="115"/>
+      <c r="D60" s="115"/>
+      <c r="E60" s="115"/>
+      <c r="F60" s="115"/>
+      <c r="G60" s="115"/>
+      <c r="H60" s="115"/>
+      <c r="I60" s="115"/>
+      <c r="J60" s="115"/>
+      <c r="K60" s="116"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -39446,21 +42599,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -39472,17 +42625,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="119"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -39502,13 +42655,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="126" t="s">
+      <c r="U4" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="109" t="s">
+      <c r="V4" s="110" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -39548,10 +42701,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="124" t="s">
+      <c r="J5" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="125"/>
+      <c r="K5" s="126"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -39559,9 +42712,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="127"/>
-      <c r="V5" s="110"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="111"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -42256,17 +45409,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="113" t="s">
+      <c r="C60" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="114"/>
-      <c r="E60" s="114"/>
-      <c r="F60" s="114"/>
-      <c r="G60" s="114"/>
-      <c r="H60" s="114"/>
-      <c r="I60" s="114"/>
-      <c r="J60" s="114"/>
-      <c r="K60" s="115"/>
+      <c r="D60" s="115"/>
+      <c r="E60" s="115"/>
+      <c r="F60" s="115"/>
+      <c r="G60" s="115"/>
+      <c r="H60" s="115"/>
+      <c r="I60" s="115"/>
+      <c r="J60" s="115"/>
+      <c r="K60" s="116"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -42575,21 +45728,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -42601,17 +45754,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="119"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -42631,13 +45784,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="126" t="s">
+      <c r="U4" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="109" t="s">
+      <c r="V4" s="110" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -42677,10 +45830,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="124" t="s">
+      <c r="J5" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="125"/>
+      <c r="K5" s="126"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -42688,9 +45841,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="127"/>
-      <c r="V5" s="110"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="111"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -45390,17 +48543,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="113" t="s">
+      <c r="C60" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="114"/>
-      <c r="E60" s="114"/>
-      <c r="F60" s="114"/>
-      <c r="G60" s="114"/>
-      <c r="H60" s="114"/>
-      <c r="I60" s="114"/>
-      <c r="J60" s="114"/>
-      <c r="K60" s="115"/>
+      <c r="D60" s="115"/>
+      <c r="E60" s="115"/>
+      <c r="F60" s="115"/>
+      <c r="G60" s="115"/>
+      <c r="H60" s="115"/>
+      <c r="I60" s="115"/>
+      <c r="J60" s="115"/>
+      <c r="K60" s="116"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -45709,21 +48862,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -45735,17 +48888,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="119"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -45765,13 +48918,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="126" t="s">
+      <c r="U4" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="109" t="s">
+      <c r="V4" s="110" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -45811,10 +48964,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="124" t="s">
+      <c r="J5" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="125"/>
+      <c r="K5" s="126"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -45822,9 +48975,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="127"/>
-      <c r="V5" s="110"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="111"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -48518,17 +51671,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="113" t="s">
+      <c r="C60" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="114"/>
-      <c r="E60" s="114"/>
-      <c r="F60" s="114"/>
-      <c r="G60" s="114"/>
-      <c r="H60" s="114"/>
-      <c r="I60" s="114"/>
-      <c r="J60" s="114"/>
-      <c r="K60" s="115"/>
+      <c r="D60" s="115"/>
+      <c r="E60" s="115"/>
+      <c r="F60" s="115"/>
+      <c r="G60" s="115"/>
+      <c r="H60" s="115"/>
+      <c r="I60" s="115"/>
+      <c r="J60" s="115"/>
+      <c r="K60" s="116"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -48837,21 +51990,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -48863,17 +52016,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="119"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -48893,13 +52046,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="126" t="s">
+      <c r="U4" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="109" t="s">
+      <c r="V4" s="110" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -48939,10 +52092,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="124" t="s">
+      <c r="J5" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="125"/>
+      <c r="K5" s="126"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -48950,9 +52103,9 @@
       <c r="Q5" s="100"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="127"/>
-      <c r="V5" s="110"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="111"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -51648,17 +54801,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="113" t="s">
+      <c r="C60" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="114"/>
-      <c r="E60" s="114"/>
-      <c r="F60" s="114"/>
-      <c r="G60" s="114"/>
-      <c r="H60" s="114"/>
-      <c r="I60" s="114"/>
-      <c r="J60" s="114"/>
-      <c r="K60" s="115"/>
+      <c r="D60" s="115"/>
+      <c r="E60" s="115"/>
+      <c r="F60" s="115"/>
+      <c r="G60" s="115"/>
+      <c r="H60" s="115"/>
+      <c r="I60" s="115"/>
+      <c r="J60" s="115"/>
+      <c r="K60" s="116"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -51967,21 +55120,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -51993,17 +55146,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="119"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -52023,13 +55176,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="126" t="s">
+      <c r="U4" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="109" t="s">
+      <c r="V4" s="110" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -52069,10 +55222,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="124" t="s">
+      <c r="J5" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="125"/>
+      <c r="K5" s="126"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -52080,9 +55233,9 @@
       <c r="Q5" s="101"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="127"/>
-      <c r="V5" s="110"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="111"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -54783,17 +57936,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="113" t="s">
+      <c r="C60" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="114"/>
-      <c r="E60" s="114"/>
-      <c r="F60" s="114"/>
-      <c r="G60" s="114"/>
-      <c r="H60" s="114"/>
-      <c r="I60" s="114"/>
-      <c r="J60" s="114"/>
-      <c r="K60" s="115"/>
+      <c r="D60" s="115"/>
+      <c r="E60" s="115"/>
+      <c r="F60" s="115"/>
+      <c r="G60" s="115"/>
+      <c r="H60" s="115"/>
+      <c r="I60" s="115"/>
+      <c r="J60" s="115"/>
+      <c r="K60" s="116"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -55102,21 +58255,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -55128,17 +58281,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="119"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -55158,13 +58311,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="126" t="s">
+      <c r="U4" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="109" t="s">
+      <c r="V4" s="110" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -55204,10 +58357,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="124" t="s">
+      <c r="J5" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="125"/>
+      <c r="K5" s="126"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -55215,9 +58368,9 @@
       <c r="Q5" s="102"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="127"/>
-      <c r="V5" s="110"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="111"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -57913,17 +61066,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="113" t="s">
+      <c r="C60" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="114"/>
-      <c r="E60" s="114"/>
-      <c r="F60" s="114"/>
-      <c r="G60" s="114"/>
-      <c r="H60" s="114"/>
-      <c r="I60" s="114"/>
-      <c r="J60" s="114"/>
-      <c r="K60" s="115"/>
+      <c r="D60" s="115"/>
+      <c r="E60" s="115"/>
+      <c r="F60" s="115"/>
+      <c r="G60" s="115"/>
+      <c r="H60" s="115"/>
+      <c r="I60" s="115"/>
+      <c r="J60" s="115"/>
+      <c r="K60" s="116"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>

--- a/GBDS JUNE FILES 2026/INVENTORY COUNT SHEET - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/INVENTORY COUNT SHEET - JUNE 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{427DA506-DA77-4450-9095-085887FAF3F4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4672245-16B3-4EF1-AE42-B2E27812F726}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="9" activeTab="18" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="10" activeTab="18" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -32,6 +32,7 @@
     <sheet name="06-22-2026" sheetId="70" r:id="rId17"/>
     <sheet name="06-23-2026" sheetId="71" r:id="rId18"/>
     <sheet name="06-24-2026" sheetId="72" r:id="rId19"/>
+    <sheet name="06-25-2026" sheetId="73" r:id="rId20"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'06-01-2026'!$A$1:$W$59</definedName>
@@ -52,6 +53,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="16">'06-22-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="17">'06-23-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="18">'06-24-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="19">'06-25-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -70,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1596" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1680" uniqueCount="74">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -1279,7 +1281,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1565,6 +1567,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2020,21 +2025,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="I1" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -2046,17 +2051,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="120"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="121"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -2076,13 +2081,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="121" t="s">
+      <c r="T4" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="123" t="s">
+      <c r="U4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="110" t="s">
+      <c r="V4" s="111" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2122,10 +2127,10 @@
       <c r="I5" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="112" t="s">
+      <c r="J5" s="113" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="113"/>
+      <c r="K5" s="114"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2133,9 +2138,9 @@
       <c r="Q5" s="89"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="122"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="111"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="112"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -4666,17 +4671,17 @@
       <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="114" t="s">
+      <c r="C62" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="115"/>
-      <c r="E62" s="115"/>
-      <c r="F62" s="115"/>
-      <c r="G62" s="115"/>
-      <c r="H62" s="115"/>
-      <c r="I62" s="115"/>
-      <c r="J62" s="115"/>
-      <c r="K62" s="116"/>
+      <c r="D62" s="116"/>
+      <c r="E62" s="116"/>
+      <c r="F62" s="116"/>
+      <c r="G62" s="116"/>
+      <c r="H62" s="116"/>
+      <c r="I62" s="116"/>
+      <c r="J62" s="116"/>
+      <c r="K62" s="117"/>
       <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
@@ -4985,21 +4990,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="I1" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -5011,17 +5016,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="120"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="121"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -5041,13 +5046,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="121" t="s">
+      <c r="T4" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="127" t="s">
+      <c r="U4" s="128" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="110" t="s">
+      <c r="V4" s="111" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -5087,10 +5092,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="125" t="s">
+      <c r="J5" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="126"/>
+      <c r="K5" s="127"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -5098,9 +5103,9 @@
       <c r="Q5" s="103"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="122"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="111"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="112"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -7785,17 +7790,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="114" t="s">
+      <c r="C60" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="115"/>
-      <c r="E60" s="115"/>
-      <c r="F60" s="115"/>
-      <c r="G60" s="115"/>
-      <c r="H60" s="115"/>
-      <c r="I60" s="115"/>
-      <c r="J60" s="115"/>
-      <c r="K60" s="116"/>
+      <c r="D60" s="116"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="116"/>
+      <c r="G60" s="116"/>
+      <c r="H60" s="116"/>
+      <c r="I60" s="116"/>
+      <c r="J60" s="116"/>
+      <c r="K60" s="117"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -8104,21 +8109,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="I1" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -8130,17 +8135,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="120"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="121"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -8160,13 +8165,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="121" t="s">
+      <c r="T4" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="127" t="s">
+      <c r="U4" s="128" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="110" t="s">
+      <c r="V4" s="111" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -8206,10 +8211,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="125" t="s">
+      <c r="J5" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="126"/>
+      <c r="K5" s="127"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -8217,9 +8222,9 @@
       <c r="Q5" s="104"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="122"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="111"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="112"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -10913,17 +10918,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="114" t="s">
+      <c r="C60" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="115"/>
-      <c r="E60" s="115"/>
-      <c r="F60" s="115"/>
-      <c r="G60" s="115"/>
-      <c r="H60" s="115"/>
-      <c r="I60" s="115"/>
-      <c r="J60" s="115"/>
-      <c r="K60" s="116"/>
+      <c r="D60" s="116"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="116"/>
+      <c r="G60" s="116"/>
+      <c r="H60" s="116"/>
+      <c r="I60" s="116"/>
+      <c r="J60" s="116"/>
+      <c r="K60" s="117"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -11232,21 +11237,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="I1" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -11258,17 +11263,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="120"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="121"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -11288,13 +11293,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="121" t="s">
+      <c r="T4" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="127" t="s">
+      <c r="U4" s="128" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="110" t="s">
+      <c r="V4" s="111" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -11334,10 +11339,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="125" t="s">
+      <c r="J5" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="126"/>
+      <c r="K5" s="127"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -11345,9 +11350,9 @@
       <c r="Q5" s="105"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="122"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="111"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="112"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -14042,17 +14047,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="114" t="s">
+      <c r="C60" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="115"/>
-      <c r="E60" s="115"/>
-      <c r="F60" s="115"/>
-      <c r="G60" s="115"/>
-      <c r="H60" s="115"/>
-      <c r="I60" s="115"/>
-      <c r="J60" s="115"/>
-      <c r="K60" s="116"/>
+      <c r="D60" s="116"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="116"/>
+      <c r="G60" s="116"/>
+      <c r="H60" s="116"/>
+      <c r="I60" s="116"/>
+      <c r="J60" s="116"/>
+      <c r="K60" s="117"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -14361,21 +14366,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="I1" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -14387,17 +14392,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="120"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="121"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -14417,13 +14422,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="121" t="s">
+      <c r="T4" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="127" t="s">
+      <c r="U4" s="128" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="110" t="s">
+      <c r="V4" s="111" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -14463,10 +14468,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="125" t="s">
+      <c r="J5" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="126"/>
+      <c r="K5" s="127"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -14474,9 +14479,9 @@
       <c r="Q5" s="106"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="122"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="111"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="112"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -17169,17 +17174,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="114" t="s">
+      <c r="C60" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="115"/>
-      <c r="E60" s="115"/>
-      <c r="F60" s="115"/>
-      <c r="G60" s="115"/>
-      <c r="H60" s="115"/>
-      <c r="I60" s="115"/>
-      <c r="J60" s="115"/>
-      <c r="K60" s="116"/>
+      <c r="D60" s="116"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="116"/>
+      <c r="G60" s="116"/>
+      <c r="H60" s="116"/>
+      <c r="I60" s="116"/>
+      <c r="J60" s="116"/>
+      <c r="K60" s="117"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -17488,21 +17493,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="I1" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -17514,17 +17519,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="120"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="121"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -17544,13 +17549,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="121" t="s">
+      <c r="T4" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="127" t="s">
+      <c r="U4" s="128" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="110" t="s">
+      <c r="V4" s="111" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -17590,10 +17595,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="125" t="s">
+      <c r="J5" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="126"/>
+      <c r="K5" s="127"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -17601,9 +17606,9 @@
       <c r="Q5" s="107"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="122"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="111"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="112"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -20292,17 +20297,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="114" t="s">
+      <c r="C60" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="115"/>
-      <c r="E60" s="115"/>
-      <c r="F60" s="115"/>
-      <c r="G60" s="115"/>
-      <c r="H60" s="115"/>
-      <c r="I60" s="115"/>
-      <c r="J60" s="115"/>
-      <c r="K60" s="116"/>
+      <c r="D60" s="116"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="116"/>
+      <c r="G60" s="116"/>
+      <c r="H60" s="116"/>
+      <c r="I60" s="116"/>
+      <c r="J60" s="116"/>
+      <c r="K60" s="117"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -20611,21 +20616,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="I1" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -20637,17 +20642,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="120"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="121"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -20667,13 +20672,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="121" t="s">
+      <c r="T4" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="127" t="s">
+      <c r="U4" s="128" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="110" t="s">
+      <c r="V4" s="111" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -20713,10 +20718,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="125" t="s">
+      <c r="J5" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="126"/>
+      <c r="K5" s="127"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -20724,9 +20729,9 @@
       <c r="Q5" s="107"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="122"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="111"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="112"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -23415,17 +23420,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="114" t="s">
+      <c r="C60" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="115"/>
-      <c r="E60" s="115"/>
-      <c r="F60" s="115"/>
-      <c r="G60" s="115"/>
-      <c r="H60" s="115"/>
-      <c r="I60" s="115"/>
-      <c r="J60" s="115"/>
-      <c r="K60" s="116"/>
+      <c r="D60" s="116"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="116"/>
+      <c r="G60" s="116"/>
+      <c r="H60" s="116"/>
+      <c r="I60" s="116"/>
+      <c r="J60" s="116"/>
+      <c r="K60" s="117"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -23734,21 +23739,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="I1" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -23760,17 +23765,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="120"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="121"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -23790,13 +23795,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="121" t="s">
+      <c r="T4" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="127" t="s">
+      <c r="U4" s="128" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="110" t="s">
+      <c r="V4" s="111" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -23836,10 +23841,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="125" t="s">
+      <c r="J5" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="126"/>
+      <c r="K5" s="127"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -23847,9 +23852,9 @@
       <c r="Q5" s="107"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="122"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="111"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="112"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -26547,17 +26552,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="114" t="s">
+      <c r="C60" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="115"/>
-      <c r="E60" s="115"/>
-      <c r="F60" s="115"/>
-      <c r="G60" s="115"/>
-      <c r="H60" s="115"/>
-      <c r="I60" s="115"/>
-      <c r="J60" s="115"/>
-      <c r="K60" s="116"/>
+      <c r="D60" s="116"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="116"/>
+      <c r="G60" s="116"/>
+      <c r="H60" s="116"/>
+      <c r="I60" s="116"/>
+      <c r="J60" s="116"/>
+      <c r="K60" s="117"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -26866,21 +26871,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="I1" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -26892,17 +26897,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="120"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="121"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -26922,13 +26927,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="121" t="s">
+      <c r="T4" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="127" t="s">
+      <c r="U4" s="128" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="110" t="s">
+      <c r="V4" s="111" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -26968,10 +26973,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="125" t="s">
+      <c r="J5" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="126"/>
+      <c r="K5" s="127"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -26979,9 +26984,9 @@
       <c r="Q5" s="107"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="122"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="111"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="112"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -29689,17 +29694,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="114" t="s">
+      <c r="C60" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="115"/>
-      <c r="E60" s="115"/>
-      <c r="F60" s="115"/>
-      <c r="G60" s="115"/>
-      <c r="H60" s="115"/>
-      <c r="I60" s="115"/>
-      <c r="J60" s="115"/>
-      <c r="K60" s="116"/>
+      <c r="D60" s="116"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="116"/>
+      <c r="G60" s="116"/>
+      <c r="H60" s="116"/>
+      <c r="I60" s="116"/>
+      <c r="J60" s="116"/>
+      <c r="K60" s="117"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -30008,21 +30013,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="I1" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -30034,17 +30039,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="120"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="121"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -30064,13 +30069,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="121" t="s">
+      <c r="T4" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="127" t="s">
+      <c r="U4" s="128" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="110" t="s">
+      <c r="V4" s="111" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -30110,10 +30115,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="125" t="s">
+      <c r="J5" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="126"/>
+      <c r="K5" s="127"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -30121,9 +30126,9 @@
       <c r="Q5" s="108"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="122"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="111"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="112"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -32817,17 +32822,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="114" t="s">
+      <c r="C60" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="115"/>
-      <c r="E60" s="115"/>
-      <c r="F60" s="115"/>
-      <c r="G60" s="115"/>
-      <c r="H60" s="115"/>
-      <c r="I60" s="115"/>
-      <c r="J60" s="115"/>
-      <c r="K60" s="116"/>
+      <c r="D60" s="116"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="116"/>
+      <c r="G60" s="116"/>
+      <c r="H60" s="116"/>
+      <c r="I60" s="116"/>
+      <c r="J60" s="116"/>
+      <c r="K60" s="117"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -33136,21 +33141,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="I1" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -33162,17 +33167,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="120"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="121"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -33192,13 +33197,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="121" t="s">
+      <c r="T4" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="127" t="s">
+      <c r="U4" s="128" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="110" t="s">
+      <c r="V4" s="111" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -33238,10 +33243,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="125" t="s">
+      <c r="J5" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="126"/>
+      <c r="K5" s="127"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -33249,9 +33254,9 @@
       <c r="Q5" s="109"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="122"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="111"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="112"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -35965,17 +35970,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="114" t="s">
+      <c r="C60" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="115"/>
-      <c r="E60" s="115"/>
-      <c r="F60" s="115"/>
-      <c r="G60" s="115"/>
-      <c r="H60" s="115"/>
-      <c r="I60" s="115"/>
-      <c r="J60" s="115"/>
-      <c r="K60" s="116"/>
+      <c r="D60" s="116"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="116"/>
+      <c r="G60" s="116"/>
+      <c r="H60" s="116"/>
+      <c r="I60" s="116"/>
+      <c r="J60" s="116"/>
+      <c r="K60" s="117"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -36227,13 +36232,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -36284,21 +36289,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="I1" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -36310,17 +36315,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="120"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="121"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -36340,13 +36345,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="121" t="s">
+      <c r="T4" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="127" t="s">
+      <c r="U4" s="128" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="110" t="s">
+      <c r="V4" s="111" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -36386,10 +36391,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="125" t="s">
+      <c r="J5" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="126"/>
+      <c r="K5" s="127"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -36397,9 +36402,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="122"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="111"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="112"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -39111,17 +39116,3162 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="114" t="s">
+      <c r="C60" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="115"/>
-      <c r="E60" s="115"/>
-      <c r="F60" s="115"/>
-      <c r="G60" s="115"/>
-      <c r="H60" s="115"/>
-      <c r="I60" s="115"/>
-      <c r="J60" s="115"/>
-      <c r="K60" s="116"/>
+      <c r="D60" s="116"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="116"/>
+      <c r="G60" s="116"/>
+      <c r="H60" s="116"/>
+      <c r="I60" s="116"/>
+      <c r="J60" s="116"/>
+      <c r="K60" s="117"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDBD1730-828B-43C2-9C11-0B41A0D9103D}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="9" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="118" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="119" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="121"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="122" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="128" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="111" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="126" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="127"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="110"/>
+      <c r="Q5" s="110"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="112"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="110"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="110"/>
+      <c r="Q6" s="110"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="52">
+        <v>14</v>
+      </c>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
+      <c r="J7" s="53"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
+      <c r="L7" s="55"/>
+      <c r="M7" s="56">
+        <v>1</v>
+      </c>
+      <c r="N7" s="57"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="53">
+        <v>1</v>
+      </c>
+      <c r="R7" s="54"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="58">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>9</v>
+      </c>
+      <c r="U7" s="58">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>417</v>
+      </c>
+      <c r="V7" s="58">
+        <f>U7/24</f>
+        <v>17.375</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="59">
+        <f>33+55</f>
+        <v>88</v>
+      </c>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="63">
+        <v>2</v>
+      </c>
+      <c r="N8" s="64"/>
+      <c r="O8" s="65">
+        <v>1</v>
+      </c>
+      <c r="P8" s="66"/>
+      <c r="Q8" s="66">
+        <v>2</v>
+      </c>
+      <c r="R8" s="67"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="68">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="69">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>2232</v>
+      </c>
+      <c r="V8" s="69">
+        <f>U8/24</f>
+        <v>93</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="70">
+        <v>71</v>
+      </c>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="73">
+        <v>5</v>
+      </c>
+      <c r="N9" s="74"/>
+      <c r="O9" s="70">
+        <v>2</v>
+      </c>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71"/>
+      <c r="R9" s="72"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="76">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>1872</v>
+      </c>
+      <c r="V9" s="76">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>78</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="70"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="74"/>
+      <c r="O10" s="70"/>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71"/>
+      <c r="R10" s="72"/>
+      <c r="S10" s="55"/>
+      <c r="T10" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V10" s="58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="70"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
+      <c r="L11" s="55">
+        <v>5</v>
+      </c>
+      <c r="M11" s="73">
+        <v>5</v>
+      </c>
+      <c r="N11" s="74"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="55"/>
+      <c r="T11" s="58">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U11" s="58">
+        <f t="shared" si="2"/>
+        <v>122</v>
+      </c>
+      <c r="V11" s="58">
+        <f t="shared" si="3"/>
+        <v>5.083333333333333</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="59">
+        <f>720+11+1440+432+57</f>
+        <v>2660</v>
+      </c>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="63">
+        <v>12</v>
+      </c>
+      <c r="N12" s="64"/>
+      <c r="O12" s="65">
+        <v>9</v>
+      </c>
+      <c r="P12" s="66"/>
+      <c r="Q12" s="66">
+        <v>24</v>
+      </c>
+      <c r="R12" s="67"/>
+      <c r="S12" s="62"/>
+      <c r="T12" s="69">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U12" s="69">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>64920</v>
+      </c>
+      <c r="V12" s="69">
+        <f>U12/24</f>
+        <v>2705</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
+      <c r="I13" s="70"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="55"/>
+      <c r="T13" s="76">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="U13" s="76">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>64</v>
+      </c>
+      <c r="V13" s="76">
+        <f>U13/24</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="70">
+        <v>4</v>
+      </c>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="55"/>
+      <c r="T14" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="75">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>96</v>
+      </c>
+      <c r="V14" s="75">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>4</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="55"/>
+      <c r="T15" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="55"/>
+      <c r="T16" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I17" s="70"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U17" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V17" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="55"/>
+      <c r="T18" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="70">
+        <v>2</v>
+      </c>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70">
+        <f>20+24</f>
+        <v>44</v>
+      </c>
+      <c r="I19" s="70"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="55"/>
+      <c r="T19" s="58">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="U19" s="75">
+        <f t="shared" si="4"/>
+        <v>92</v>
+      </c>
+      <c r="V19" s="75">
+        <f t="shared" si="5"/>
+        <v>3.8333333333333335</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="74"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="55"/>
+      <c r="T20" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V20" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70">
+        <f>2*24</f>
+        <v>48</v>
+      </c>
+      <c r="I21" s="70"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="58">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="U21" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V21" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="70"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
+      <c r="J22" s="71"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="55"/>
+      <c r="T22" s="58">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U22" s="75">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="V22" s="75">
+        <f t="shared" si="5"/>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
+      <c r="I23" s="70"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="74"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="55"/>
+      <c r="T23" s="58">
+        <f t="shared" si="0"/>
+        <v>907</v>
+      </c>
+      <c r="U23" s="75">
+        <f t="shared" si="4"/>
+        <v>907</v>
+      </c>
+      <c r="V23" s="75">
+        <f t="shared" si="5"/>
+        <v>37.791666666666664</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="70">
+        <v>5</v>
+      </c>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I24" s="70"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="55"/>
+      <c r="T24" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U24" s="75">
+        <f t="shared" si="4"/>
+        <v>192</v>
+      </c>
+      <c r="V24" s="75">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="70">
+        <f>63+3</f>
+        <v>66</v>
+      </c>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70"/>
+      <c r="J25" s="71">
+        <v>1</v>
+      </c>
+      <c r="K25" s="72"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="73">
+        <v>1</v>
+      </c>
+      <c r="N25" s="74"/>
+      <c r="O25" s="70">
+        <v>1</v>
+      </c>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71">
+        <v>2</v>
+      </c>
+      <c r="R25" s="72"/>
+      <c r="S25" s="55"/>
+      <c r="T25" s="58">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="U25" s="75">
+        <f t="shared" si="4"/>
+        <v>1681</v>
+      </c>
+      <c r="V25" s="75">
+        <f t="shared" si="5"/>
+        <v>70.041666666666671</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="73">
+        <v>1</v>
+      </c>
+      <c r="N26" s="74"/>
+      <c r="O26" s="70"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="71"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="55"/>
+      <c r="T26" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="75">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="V26" s="75">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="70"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="70"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="55"/>
+      <c r="T27" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="70">
+        <f>126+48+2</f>
+        <v>176</v>
+      </c>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="73"/>
+      <c r="N28" s="74"/>
+      <c r="O28" s="70">
+        <v>1</v>
+      </c>
+      <c r="P28" s="71"/>
+      <c r="Q28" s="71">
+        <v>15</v>
+      </c>
+      <c r="R28" s="72"/>
+      <c r="S28" s="55"/>
+      <c r="T28" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="75">
+        <f t="shared" si="4"/>
+        <v>4608</v>
+      </c>
+      <c r="V28" s="75">
+        <f t="shared" si="5"/>
+        <v>192</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="70">
+        <v>32</v>
+      </c>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70"/>
+      <c r="J29" s="71">
+        <v>5</v>
+      </c>
+      <c r="K29" s="72"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="73"/>
+      <c r="N29" s="74"/>
+      <c r="O29" s="70"/>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71">
+        <v>1</v>
+      </c>
+      <c r="R29" s="72"/>
+      <c r="S29" s="55"/>
+      <c r="T29" s="58">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U29" s="75">
+        <f t="shared" si="4"/>
+        <v>797</v>
+      </c>
+      <c r="V29" s="75">
+        <f t="shared" si="5"/>
+        <v>33.208333333333336</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="70">
+        <v>5</v>
+      </c>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="74"/>
+      <c r="O30" s="70"/>
+      <c r="P30" s="71"/>
+      <c r="Q30" s="71">
+        <v>1</v>
+      </c>
+      <c r="R30" s="72"/>
+      <c r="S30" s="55"/>
+      <c r="T30" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="75">
+        <f t="shared" si="4"/>
+        <v>144</v>
+      </c>
+      <c r="V30" s="75">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="70">
+        <v>2</v>
+      </c>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="73">
+        <v>2</v>
+      </c>
+      <c r="N31" s="74"/>
+      <c r="O31" s="70">
+        <v>1</v>
+      </c>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V31" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="70"/>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="74"/>
+      <c r="O32" s="70"/>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="55"/>
+      <c r="T32" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="70"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="73"/>
+      <c r="N33" s="74"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="55"/>
+      <c r="T33" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="70">
+        <v>32</v>
+      </c>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
+      <c r="J34" s="71"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
+      <c r="L34" s="55"/>
+      <c r="M34" s="73"/>
+      <c r="N34" s="74"/>
+      <c r="O34" s="70">
+        <v>1</v>
+      </c>
+      <c r="P34" s="71">
+        <v>12</v>
+      </c>
+      <c r="Q34" s="71">
+        <v>2</v>
+      </c>
+      <c r="R34" s="72"/>
+      <c r="S34" s="55"/>
+      <c r="T34" s="58">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="U34" s="75">
+        <f t="shared" si="4"/>
+        <v>854</v>
+      </c>
+      <c r="V34" s="75">
+        <f t="shared" si="5"/>
+        <v>35.583333333333336</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="72"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="74"/>
+      <c r="O35" s="70"/>
+      <c r="P35" s="71"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="72"/>
+      <c r="S35" s="55"/>
+      <c r="T35" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="73"/>
+      <c r="N36" s="74"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="71"/>
+      <c r="Q36" s="71"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="55"/>
+      <c r="T36" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="59">
+        <f>864+1620+42</f>
+        <v>2526</v>
+      </c>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59">
+        <v>4</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>4</v>
+      </c>
+      <c r="K37" s="61">
+        <v>3</v>
+      </c>
+      <c r="L37" s="62"/>
+      <c r="M37" s="63"/>
+      <c r="N37" s="64"/>
+      <c r="O37" s="65">
+        <v>25</v>
+      </c>
+      <c r="P37" s="66"/>
+      <c r="Q37" s="66">
+        <v>23</v>
+      </c>
+      <c r="R37" s="67"/>
+      <c r="S37" s="62"/>
+      <c r="T37" s="77">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="U37" s="77">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>15457</v>
+      </c>
+      <c r="V37" s="77">
+        <f>U37/6</f>
+        <v>2576.1666666666665</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="73">
+        <v>1</v>
+      </c>
+      <c r="N38" s="74"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="71"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="55"/>
+      <c r="T38" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="75">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>24</v>
+      </c>
+      <c r="V38" s="75">
+        <f>U38/24</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="74"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="71"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="95"/>
+      <c r="T39" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U39" s="75">
+        <f>C39*24+M39*24+O39*24+Q39*24+T39</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="75">
+        <f>U39/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="59">
+        <f>126+33</f>
+        <v>159</v>
+      </c>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
+      <c r="L40" s="62"/>
+      <c r="M40" s="63">
+        <v>2</v>
+      </c>
+      <c r="N40" s="64"/>
+      <c r="O40" s="65">
+        <v>1</v>
+      </c>
+      <c r="P40" s="66"/>
+      <c r="Q40" s="66">
+        <v>2</v>
+      </c>
+      <c r="R40" s="67"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="77">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U40" s="77">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>3956</v>
+      </c>
+      <c r="V40" s="77">
+        <f>U40/24</f>
+        <v>164.83333333333334</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="82">
+        <f>96+57</f>
+        <v>153</v>
+      </c>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="85"/>
+      <c r="M41" s="86">
+        <v>25</v>
+      </c>
+      <c r="N41" s="87"/>
+      <c r="O41" s="82">
+        <v>6</v>
+      </c>
+      <c r="P41" s="83"/>
+      <c r="Q41" s="83">
+        <v>18</v>
+      </c>
+      <c r="R41" s="84"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="88">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>2424</v>
+      </c>
+      <c r="V41" s="88">
+        <f>U41/12</f>
+        <v>202</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="71"/>
+      <c r="K42" s="72"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="73"/>
+      <c r="N42" s="74"/>
+      <c r="O42" s="70"/>
+      <c r="P42" s="71"/>
+      <c r="Q42" s="71"/>
+      <c r="R42" s="72"/>
+      <c r="S42" s="55"/>
+      <c r="T42" s="75"/>
+      <c r="U42" s="75"/>
+      <c r="V42" s="75"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="65">
+        <f>7776+3024+8424+1944+54+3348+6480</f>
+        <v>31050</v>
+      </c>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65">
+        <v>1</v>
+      </c>
+      <c r="I43" s="65">
+        <v>7</v>
+      </c>
+      <c r="J43" s="66">
+        <f>4*6+3</f>
+        <v>27</v>
+      </c>
+      <c r="K43" s="67">
+        <f>64*6+2</f>
+        <v>386</v>
+      </c>
+      <c r="L43" s="62"/>
+      <c r="M43" s="63">
+        <v>211</v>
+      </c>
+      <c r="N43" s="64"/>
+      <c r="O43" s="65">
+        <v>377</v>
+      </c>
+      <c r="P43" s="66"/>
+      <c r="Q43" s="66">
+        <v>656</v>
+      </c>
+      <c r="R43" s="67"/>
+      <c r="S43" s="62"/>
+      <c r="T43" s="77">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>421</v>
+      </c>
+      <c r="U43" s="77">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>194185</v>
+      </c>
+      <c r="V43" s="77">
+        <f>U43/6</f>
+        <v>32364.166666666668</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="70"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="71"/>
+      <c r="K44" s="72"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="73"/>
+      <c r="N44" s="74"/>
+      <c r="O44" s="70"/>
+      <c r="P44" s="71"/>
+      <c r="Q44" s="71"/>
+      <c r="R44" s="72"/>
+      <c r="S44" s="55"/>
+      <c r="T44" s="75"/>
+      <c r="U44" s="75"/>
+      <c r="V44" s="75"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="70">
+        <v>5</v>
+      </c>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="70"/>
+      <c r="I45" s="70"/>
+      <c r="J45" s="71"/>
+      <c r="K45" s="72"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="73">
+        <v>1</v>
+      </c>
+      <c r="N45" s="74"/>
+      <c r="O45" s="70">
+        <v>1</v>
+      </c>
+      <c r="P45" s="71"/>
+      <c r="Q45" s="71"/>
+      <c r="R45" s="72"/>
+      <c r="S45" s="55"/>
+      <c r="T45" s="75">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="75">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>168</v>
+      </c>
+      <c r="V45" s="75">
+        <f>U45/24</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="73"/>
+      <c r="N46" s="74"/>
+      <c r="O46" s="70"/>
+      <c r="P46" s="71"/>
+      <c r="Q46" s="71"/>
+      <c r="R46" s="72"/>
+      <c r="S46" s="55"/>
+      <c r="T46" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="75">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="75">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="65">
+        <f>432+106+2160+64</f>
+        <v>2762</v>
+      </c>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
+      <c r="I47" s="65"/>
+      <c r="J47" s="66">
+        <v>1</v>
+      </c>
+      <c r="K47" s="67">
+        <v>4</v>
+      </c>
+      <c r="L47" s="62"/>
+      <c r="M47" s="63">
+        <v>6</v>
+      </c>
+      <c r="N47" s="64"/>
+      <c r="O47" s="65">
+        <v>9</v>
+      </c>
+      <c r="P47" s="66">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="66">
+        <v>3</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
+      <c r="S47" s="62"/>
+      <c r="T47" s="77">
+        <f t="shared" si="7"/>
+        <v>13</v>
+      </c>
+      <c r="U47" s="77">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>16693</v>
+      </c>
+      <c r="V47" s="77">
+        <f>U47/6</f>
+        <v>2782.1666666666665</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
+      <c r="I48" s="70"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="72"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="73"/>
+      <c r="N48" s="74"/>
+      <c r="O48" s="70"/>
+      <c r="P48" s="71"/>
+      <c r="Q48" s="71"/>
+      <c r="R48" s="72"/>
+      <c r="S48" s="55"/>
+      <c r="T48" s="75">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="U48" s="75">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="V48" s="75">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="70"/>
+      <c r="I49" s="70"/>
+      <c r="J49" s="71"/>
+      <c r="K49" s="72"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="74"/>
+      <c r="O49" s="70"/>
+      <c r="P49" s="71"/>
+      <c r="Q49" s="71"/>
+      <c r="R49" s="72"/>
+      <c r="S49" s="55"/>
+      <c r="T49" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="70"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="70"/>
+      <c r="F50" s="70"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
+      <c r="J50" s="71"/>
+      <c r="K50" s="72"/>
+      <c r="L50" s="55"/>
+      <c r="M50" s="73"/>
+      <c r="N50" s="74"/>
+      <c r="O50" s="70"/>
+      <c r="P50" s="71"/>
+      <c r="Q50" s="71"/>
+      <c r="R50" s="72"/>
+      <c r="S50" s="55"/>
+      <c r="T50" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="65"/>
+      <c r="I51" s="65"/>
+      <c r="J51" s="66"/>
+      <c r="K51" s="67"/>
+      <c r="L51" s="62"/>
+      <c r="M51" s="63"/>
+      <c r="N51" s="64"/>
+      <c r="O51" s="65"/>
+      <c r="P51" s="66"/>
+      <c r="Q51" s="66"/>
+      <c r="R51" s="67"/>
+      <c r="S51" s="62"/>
+      <c r="T51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="77">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>204</v>
+      </c>
+      <c r="V51" s="77">
+        <f>U51/6</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="70"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="70"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="71"/>
+      <c r="K52" s="72"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="73"/>
+      <c r="N52" s="74"/>
+      <c r="O52" s="70"/>
+      <c r="P52" s="71"/>
+      <c r="Q52" s="71"/>
+      <c r="R52" s="72"/>
+      <c r="S52" s="55"/>
+      <c r="T52" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="75">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="70">
+        <v>9</v>
+      </c>
+      <c r="D53" s="70"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="70"/>
+      <c r="H53" s="70"/>
+      <c r="I53" s="70"/>
+      <c r="J53" s="71"/>
+      <c r="K53" s="72"/>
+      <c r="L53" s="55"/>
+      <c r="M53" s="73"/>
+      <c r="N53" s="74"/>
+      <c r="O53" s="70"/>
+      <c r="P53" s="71"/>
+      <c r="Q53" s="71"/>
+      <c r="R53" s="72"/>
+      <c r="S53" s="55"/>
+      <c r="T53" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="75">
+        <f t="shared" si="10"/>
+        <v>216</v>
+      </c>
+      <c r="V53" s="75">
+        <f t="shared" si="9"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="71"/>
+      <c r="K54" s="72"/>
+      <c r="L54" s="55"/>
+      <c r="M54" s="73"/>
+      <c r="N54" s="74"/>
+      <c r="O54" s="70"/>
+      <c r="P54" s="71"/>
+      <c r="Q54" s="71"/>
+      <c r="R54" s="72"/>
+      <c r="S54" s="55"/>
+      <c r="T54" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="70"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="70"/>
+      <c r="I55" s="70"/>
+      <c r="J55" s="71"/>
+      <c r="K55" s="72"/>
+      <c r="L55" s="55"/>
+      <c r="M55" s="73"/>
+      <c r="N55" s="74"/>
+      <c r="O55" s="70"/>
+      <c r="P55" s="71"/>
+      <c r="Q55" s="71"/>
+      <c r="R55" s="72"/>
+      <c r="S55" s="55"/>
+      <c r="T55" s="75"/>
+      <c r="U55" s="75"/>
+      <c r="V55" s="75"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="70"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="70"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="71"/>
+      <c r="K56" s="72"/>
+      <c r="L56" s="55"/>
+      <c r="M56" s="73"/>
+      <c r="N56" s="74"/>
+      <c r="O56" s="70"/>
+      <c r="P56" s="71"/>
+      <c r="Q56" s="71"/>
+      <c r="R56" s="72"/>
+      <c r="S56" s="55"/>
+      <c r="T56" s="75"/>
+      <c r="U56" s="75"/>
+      <c r="V56" s="75"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="70"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="70"/>
+      <c r="I57" s="70"/>
+      <c r="J57" s="71"/>
+      <c r="K57" s="72"/>
+      <c r="L57" s="55"/>
+      <c r="M57" s="73"/>
+      <c r="N57" s="74"/>
+      <c r="O57" s="70"/>
+      <c r="P57" s="71"/>
+      <c r="Q57" s="71"/>
+      <c r="R57" s="72"/>
+      <c r="S57" s="55"/>
+      <c r="T57" s="75"/>
+      <c r="U57" s="75"/>
+      <c r="V57" s="75"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>39862</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>1189</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>33</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>38</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>422</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>275</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>436</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>16</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>750</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>3</v>
+      </c>
+      <c r="S58" s="55"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>1701</v>
+      </c>
+      <c r="U58" s="90">
+        <f>SUM(U7:U57)</f>
+        <v>312753</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>41449.75</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="115" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="116"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="116"/>
+      <c r="G60" s="116"/>
+      <c r="H60" s="116"/>
+      <c r="I60" s="116"/>
+      <c r="J60" s="116"/>
+      <c r="K60" s="117"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -39430,21 +42580,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="I1" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -39456,17 +42606,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="120"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="121"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -39486,13 +42636,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="121" t="s">
+      <c r="T4" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="127" t="s">
+      <c r="U4" s="128" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="110" t="s">
+      <c r="V4" s="111" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -39532,10 +42682,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="125" t="s">
+      <c r="J5" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="126"/>
+      <c r="K5" s="127"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -39543,9 +42693,9 @@
       <c r="Q5" s="96"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="122"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="111"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="112"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -42280,17 +45430,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="114" t="s">
+      <c r="C60" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="115"/>
-      <c r="E60" s="115"/>
-      <c r="F60" s="115"/>
-      <c r="G60" s="115"/>
-      <c r="H60" s="115"/>
-      <c r="I60" s="115"/>
-      <c r="J60" s="115"/>
-      <c r="K60" s="116"/>
+      <c r="D60" s="116"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="116"/>
+      <c r="G60" s="116"/>
+      <c r="H60" s="116"/>
+      <c r="I60" s="116"/>
+      <c r="J60" s="116"/>
+      <c r="K60" s="117"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -42599,21 +45749,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="I1" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -42625,17 +45775,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="120"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="121"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -42655,13 +45805,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="121" t="s">
+      <c r="T4" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="127" t="s">
+      <c r="U4" s="128" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="110" t="s">
+      <c r="V4" s="111" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -42701,10 +45851,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="125" t="s">
+      <c r="J5" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="126"/>
+      <c r="K5" s="127"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -42712,9 +45862,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="122"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="111"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="112"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -45409,17 +48559,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="114" t="s">
+      <c r="C60" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="115"/>
-      <c r="E60" s="115"/>
-      <c r="F60" s="115"/>
-      <c r="G60" s="115"/>
-      <c r="H60" s="115"/>
-      <c r="I60" s="115"/>
-      <c r="J60" s="115"/>
-      <c r="K60" s="116"/>
+      <c r="D60" s="116"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="116"/>
+      <c r="G60" s="116"/>
+      <c r="H60" s="116"/>
+      <c r="I60" s="116"/>
+      <c r="J60" s="116"/>
+      <c r="K60" s="117"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -45728,21 +48878,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="I1" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -45754,17 +48904,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="120"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="121"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -45784,13 +48934,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="121" t="s">
+      <c r="T4" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="127" t="s">
+      <c r="U4" s="128" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="110" t="s">
+      <c r="V4" s="111" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -45830,10 +48980,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="125" t="s">
+      <c r="J5" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="126"/>
+      <c r="K5" s="127"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -45841,9 +48991,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="122"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="111"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="112"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -48543,17 +51693,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="114" t="s">
+      <c r="C60" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="115"/>
-      <c r="E60" s="115"/>
-      <c r="F60" s="115"/>
-      <c r="G60" s="115"/>
-      <c r="H60" s="115"/>
-      <c r="I60" s="115"/>
-      <c r="J60" s="115"/>
-      <c r="K60" s="116"/>
+      <c r="D60" s="116"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="116"/>
+      <c r="G60" s="116"/>
+      <c r="H60" s="116"/>
+      <c r="I60" s="116"/>
+      <c r="J60" s="116"/>
+      <c r="K60" s="117"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -48862,21 +52012,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="I1" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -48888,17 +52038,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="120"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="121"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -48918,13 +52068,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="121" t="s">
+      <c r="T4" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="127" t="s">
+      <c r="U4" s="128" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="110" t="s">
+      <c r="V4" s="111" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -48964,10 +52114,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="125" t="s">
+      <c r="J5" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="126"/>
+      <c r="K5" s="127"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -48975,9 +52125,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="122"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="111"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="112"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -51671,17 +54821,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="114" t="s">
+      <c r="C60" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="115"/>
-      <c r="E60" s="115"/>
-      <c r="F60" s="115"/>
-      <c r="G60" s="115"/>
-      <c r="H60" s="115"/>
-      <c r="I60" s="115"/>
-      <c r="J60" s="115"/>
-      <c r="K60" s="116"/>
+      <c r="D60" s="116"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="116"/>
+      <c r="G60" s="116"/>
+      <c r="H60" s="116"/>
+      <c r="I60" s="116"/>
+      <c r="J60" s="116"/>
+      <c r="K60" s="117"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -51990,21 +55140,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="I1" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -52016,17 +55166,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="120"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="121"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -52046,13 +55196,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="121" t="s">
+      <c r="T4" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="127" t="s">
+      <c r="U4" s="128" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="110" t="s">
+      <c r="V4" s="111" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -52092,10 +55242,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="125" t="s">
+      <c r="J5" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="126"/>
+      <c r="K5" s="127"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -52103,9 +55253,9 @@
       <c r="Q5" s="100"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="122"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="111"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="112"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -54801,17 +57951,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="114" t="s">
+      <c r="C60" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="115"/>
-      <c r="E60" s="115"/>
-      <c r="F60" s="115"/>
-      <c r="G60" s="115"/>
-      <c r="H60" s="115"/>
-      <c r="I60" s="115"/>
-      <c r="J60" s="115"/>
-      <c r="K60" s="116"/>
+      <c r="D60" s="116"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="116"/>
+      <c r="G60" s="116"/>
+      <c r="H60" s="116"/>
+      <c r="I60" s="116"/>
+      <c r="J60" s="116"/>
+      <c r="K60" s="117"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -55120,21 +58270,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="I1" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -55146,17 +58296,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="120"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="121"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -55176,13 +58326,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="121" t="s">
+      <c r="T4" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="127" t="s">
+      <c r="U4" s="128" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="110" t="s">
+      <c r="V4" s="111" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -55222,10 +58372,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="125" t="s">
+      <c r="J5" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="126"/>
+      <c r="K5" s="127"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -55233,9 +58383,9 @@
       <c r="Q5" s="101"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="122"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="111"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="112"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -57936,17 +61086,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="114" t="s">
+      <c r="C60" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="115"/>
-      <c r="E60" s="115"/>
-      <c r="F60" s="115"/>
-      <c r="G60" s="115"/>
-      <c r="H60" s="115"/>
-      <c r="I60" s="115"/>
-      <c r="J60" s="115"/>
-      <c r="K60" s="116"/>
+      <c r="D60" s="116"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="116"/>
+      <c r="G60" s="116"/>
+      <c r="H60" s="116"/>
+      <c r="I60" s="116"/>
+      <c r="J60" s="116"/>
+      <c r="K60" s="117"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -58255,21 +61405,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="I1" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -58281,17 +61431,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="120"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="121"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -58311,13 +61461,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="121" t="s">
+      <c r="T4" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="127" t="s">
+      <c r="U4" s="128" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="110" t="s">
+      <c r="V4" s="111" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -58357,10 +61507,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="125" t="s">
+      <c r="J5" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="126"/>
+      <c r="K5" s="127"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -58368,9 +61518,9 @@
       <c r="Q5" s="102"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="122"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="111"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="112"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -61066,17 +64216,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="114" t="s">
+      <c r="C60" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="115"/>
-      <c r="E60" s="115"/>
-      <c r="F60" s="115"/>
-      <c r="G60" s="115"/>
-      <c r="H60" s="115"/>
-      <c r="I60" s="115"/>
-      <c r="J60" s="115"/>
-      <c r="K60" s="116"/>
+      <c r="D60" s="116"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="116"/>
+      <c r="G60" s="116"/>
+      <c r="H60" s="116"/>
+      <c r="I60" s="116"/>
+      <c r="J60" s="116"/>
+      <c r="K60" s="117"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>

--- a/GBDS JUNE FILES 2026/INVENTORY COUNT SHEET - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/INVENTORY COUNT SHEET - JUNE 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4672245-16B3-4EF1-AE42-B2E27812F726}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48539C7C-50F5-4C0A-BF43-8BBBDF357F5E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="10" activeTab="18" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="11" activeTab="20" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -33,6 +33,7 @@
     <sheet name="06-23-2026" sheetId="71" r:id="rId18"/>
     <sheet name="06-24-2026" sheetId="72" r:id="rId19"/>
     <sheet name="06-25-2026" sheetId="73" r:id="rId20"/>
+    <sheet name="06-26-2026" sheetId="74" r:id="rId21"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'06-01-2026'!$A$1:$W$59</definedName>
@@ -54,6 +55,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="17">'06-23-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="18">'06-24-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="19">'06-25-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="20">'06-26-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -72,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1680" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="74">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -1281,7 +1283,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1567,6 +1569,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2025,21 +2030,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="118" t="s">
+      <c r="I1" s="119" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="118"/>
-      <c r="K1" s="118"/>
-      <c r="L1" s="118"/>
-      <c r="M1" s="118"/>
-      <c r="N1" s="118"/>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="118"/>
-      <c r="T1" s="118"/>
-      <c r="U1" s="118"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -2051,17 +2056,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="119" t="s">
+      <c r="C4" s="120" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
-      <c r="H4" s="119"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="121"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120"/>
+      <c r="I4" s="120"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="122"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -2081,13 +2086,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="122" t="s">
+      <c r="T4" s="123" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="124" t="s">
+      <c r="U4" s="125" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="111" t="s">
+      <c r="V4" s="112" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2127,10 +2132,10 @@
       <c r="I5" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="113" t="s">
+      <c r="J5" s="114" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="114"/>
+      <c r="K5" s="115"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2138,9 +2143,9 @@
       <c r="Q5" s="89"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="123"/>
-      <c r="U5" s="125"/>
-      <c r="V5" s="112"/>
+      <c r="T5" s="124"/>
+      <c r="U5" s="126"/>
+      <c r="V5" s="113"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -4671,17 +4676,17 @@
       <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="115" t="s">
+      <c r="C62" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="116"/>
-      <c r="E62" s="116"/>
-      <c r="F62" s="116"/>
-      <c r="G62" s="116"/>
-      <c r="H62" s="116"/>
-      <c r="I62" s="116"/>
-      <c r="J62" s="116"/>
-      <c r="K62" s="117"/>
+      <c r="D62" s="117"/>
+      <c r="E62" s="117"/>
+      <c r="F62" s="117"/>
+      <c r="G62" s="117"/>
+      <c r="H62" s="117"/>
+      <c r="I62" s="117"/>
+      <c r="J62" s="117"/>
+      <c r="K62" s="118"/>
       <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
@@ -4990,21 +4995,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="118" t="s">
+      <c r="I1" s="119" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="118"/>
-      <c r="K1" s="118"/>
-      <c r="L1" s="118"/>
-      <c r="M1" s="118"/>
-      <c r="N1" s="118"/>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="118"/>
-      <c r="T1" s="118"/>
-      <c r="U1" s="118"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -5016,17 +5021,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="119" t="s">
+      <c r="C4" s="120" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
-      <c r="H4" s="119"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="121"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120"/>
+      <c r="I4" s="120"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="122"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -5046,13 +5051,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="122" t="s">
+      <c r="T4" s="123" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="128" t="s">
+      <c r="U4" s="129" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="111" t="s">
+      <c r="V4" s="112" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -5092,10 +5097,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="126" t="s">
+      <c r="J5" s="127" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="127"/>
+      <c r="K5" s="128"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -5103,9 +5108,9 @@
       <c r="Q5" s="103"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="123"/>
-      <c r="U5" s="129"/>
-      <c r="V5" s="112"/>
+      <c r="T5" s="124"/>
+      <c r="U5" s="130"/>
+      <c r="V5" s="113"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -7790,17 +7795,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="115" t="s">
+      <c r="C60" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="116"/>
-      <c r="E60" s="116"/>
-      <c r="F60" s="116"/>
-      <c r="G60" s="116"/>
-      <c r="H60" s="116"/>
-      <c r="I60" s="116"/>
-      <c r="J60" s="116"/>
-      <c r="K60" s="117"/>
+      <c r="D60" s="117"/>
+      <c r="E60" s="117"/>
+      <c r="F60" s="117"/>
+      <c r="G60" s="117"/>
+      <c r="H60" s="117"/>
+      <c r="I60" s="117"/>
+      <c r="J60" s="117"/>
+      <c r="K60" s="118"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -8109,21 +8114,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="118" t="s">
+      <c r="I1" s="119" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="118"/>
-      <c r="K1" s="118"/>
-      <c r="L1" s="118"/>
-      <c r="M1" s="118"/>
-      <c r="N1" s="118"/>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="118"/>
-      <c r="T1" s="118"/>
-      <c r="U1" s="118"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -8135,17 +8140,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="119" t="s">
+      <c r="C4" s="120" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
-      <c r="H4" s="119"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="121"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120"/>
+      <c r="I4" s="120"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="122"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -8165,13 +8170,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="122" t="s">
+      <c r="T4" s="123" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="128" t="s">
+      <c r="U4" s="129" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="111" t="s">
+      <c r="V4" s="112" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -8211,10 +8216,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="126" t="s">
+      <c r="J5" s="127" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="127"/>
+      <c r="K5" s="128"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -8222,9 +8227,9 @@
       <c r="Q5" s="104"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="123"/>
-      <c r="U5" s="129"/>
-      <c r="V5" s="112"/>
+      <c r="T5" s="124"/>
+      <c r="U5" s="130"/>
+      <c r="V5" s="113"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -10918,17 +10923,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="115" t="s">
+      <c r="C60" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="116"/>
-      <c r="E60" s="116"/>
-      <c r="F60" s="116"/>
-      <c r="G60" s="116"/>
-      <c r="H60" s="116"/>
-      <c r="I60" s="116"/>
-      <c r="J60" s="116"/>
-      <c r="K60" s="117"/>
+      <c r="D60" s="117"/>
+      <c r="E60" s="117"/>
+      <c r="F60" s="117"/>
+      <c r="G60" s="117"/>
+      <c r="H60" s="117"/>
+      <c r="I60" s="117"/>
+      <c r="J60" s="117"/>
+      <c r="K60" s="118"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -11237,21 +11242,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="118" t="s">
+      <c r="I1" s="119" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="118"/>
-      <c r="K1" s="118"/>
-      <c r="L1" s="118"/>
-      <c r="M1" s="118"/>
-      <c r="N1" s="118"/>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="118"/>
-      <c r="T1" s="118"/>
-      <c r="U1" s="118"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -11263,17 +11268,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="119" t="s">
+      <c r="C4" s="120" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
-      <c r="H4" s="119"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="121"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120"/>
+      <c r="I4" s="120"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="122"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -11293,13 +11298,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="122" t="s">
+      <c r="T4" s="123" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="128" t="s">
+      <c r="U4" s="129" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="111" t="s">
+      <c r="V4" s="112" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -11339,10 +11344,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="126" t="s">
+      <c r="J5" s="127" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="127"/>
+      <c r="K5" s="128"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -11350,9 +11355,9 @@
       <c r="Q5" s="105"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="123"/>
-      <c r="U5" s="129"/>
-      <c r="V5" s="112"/>
+      <c r="T5" s="124"/>
+      <c r="U5" s="130"/>
+      <c r="V5" s="113"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -14047,17 +14052,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="115" t="s">
+      <c r="C60" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="116"/>
-      <c r="E60" s="116"/>
-      <c r="F60" s="116"/>
-      <c r="G60" s="116"/>
-      <c r="H60" s="116"/>
-      <c r="I60" s="116"/>
-      <c r="J60" s="116"/>
-      <c r="K60" s="117"/>
+      <c r="D60" s="117"/>
+      <c r="E60" s="117"/>
+      <c r="F60" s="117"/>
+      <c r="G60" s="117"/>
+      <c r="H60" s="117"/>
+      <c r="I60" s="117"/>
+      <c r="J60" s="117"/>
+      <c r="K60" s="118"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -14366,21 +14371,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="118" t="s">
+      <c r="I1" s="119" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="118"/>
-      <c r="K1" s="118"/>
-      <c r="L1" s="118"/>
-      <c r="M1" s="118"/>
-      <c r="N1" s="118"/>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="118"/>
-      <c r="T1" s="118"/>
-      <c r="U1" s="118"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -14392,17 +14397,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="119" t="s">
+      <c r="C4" s="120" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
-      <c r="H4" s="119"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="121"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120"/>
+      <c r="I4" s="120"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="122"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -14422,13 +14427,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="122" t="s">
+      <c r="T4" s="123" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="128" t="s">
+      <c r="U4" s="129" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="111" t="s">
+      <c r="V4" s="112" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -14468,10 +14473,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="126" t="s">
+      <c r="J5" s="127" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="127"/>
+      <c r="K5" s="128"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -14479,9 +14484,9 @@
       <c r="Q5" s="106"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="123"/>
-      <c r="U5" s="129"/>
-      <c r="V5" s="112"/>
+      <c r="T5" s="124"/>
+      <c r="U5" s="130"/>
+      <c r="V5" s="113"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -17174,17 +17179,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="115" t="s">
+      <c r="C60" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="116"/>
-      <c r="E60" s="116"/>
-      <c r="F60" s="116"/>
-      <c r="G60" s="116"/>
-      <c r="H60" s="116"/>
-      <c r="I60" s="116"/>
-      <c r="J60" s="116"/>
-      <c r="K60" s="117"/>
+      <c r="D60" s="117"/>
+      <c r="E60" s="117"/>
+      <c r="F60" s="117"/>
+      <c r="G60" s="117"/>
+      <c r="H60" s="117"/>
+      <c r="I60" s="117"/>
+      <c r="J60" s="117"/>
+      <c r="K60" s="118"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -17493,21 +17498,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="118" t="s">
+      <c r="I1" s="119" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="118"/>
-      <c r="K1" s="118"/>
-      <c r="L1" s="118"/>
-      <c r="M1" s="118"/>
-      <c r="N1" s="118"/>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="118"/>
-      <c r="T1" s="118"/>
-      <c r="U1" s="118"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -17519,17 +17524,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="119" t="s">
+      <c r="C4" s="120" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
-      <c r="H4" s="119"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="121"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120"/>
+      <c r="I4" s="120"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="122"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -17549,13 +17554,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="122" t="s">
+      <c r="T4" s="123" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="128" t="s">
+      <c r="U4" s="129" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="111" t="s">
+      <c r="V4" s="112" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -17595,10 +17600,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="126" t="s">
+      <c r="J5" s="127" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="127"/>
+      <c r="K5" s="128"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -17606,9 +17611,9 @@
       <c r="Q5" s="107"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="123"/>
-      <c r="U5" s="129"/>
-      <c r="V5" s="112"/>
+      <c r="T5" s="124"/>
+      <c r="U5" s="130"/>
+      <c r="V5" s="113"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -20297,17 +20302,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="115" t="s">
+      <c r="C60" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="116"/>
-      <c r="E60" s="116"/>
-      <c r="F60" s="116"/>
-      <c r="G60" s="116"/>
-      <c r="H60" s="116"/>
-      <c r="I60" s="116"/>
-      <c r="J60" s="116"/>
-      <c r="K60" s="117"/>
+      <c r="D60" s="117"/>
+      <c r="E60" s="117"/>
+      <c r="F60" s="117"/>
+      <c r="G60" s="117"/>
+      <c r="H60" s="117"/>
+      <c r="I60" s="117"/>
+      <c r="J60" s="117"/>
+      <c r="K60" s="118"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -20616,21 +20621,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="118" t="s">
+      <c r="I1" s="119" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="118"/>
-      <c r="K1" s="118"/>
-      <c r="L1" s="118"/>
-      <c r="M1" s="118"/>
-      <c r="N1" s="118"/>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="118"/>
-      <c r="T1" s="118"/>
-      <c r="U1" s="118"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -20642,17 +20647,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="119" t="s">
+      <c r="C4" s="120" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
-      <c r="H4" s="119"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="121"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120"/>
+      <c r="I4" s="120"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="122"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -20672,13 +20677,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="122" t="s">
+      <c r="T4" s="123" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="128" t="s">
+      <c r="U4" s="129" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="111" t="s">
+      <c r="V4" s="112" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -20718,10 +20723,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="126" t="s">
+      <c r="J5" s="127" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="127"/>
+      <c r="K5" s="128"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -20729,9 +20734,9 @@
       <c r="Q5" s="107"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="123"/>
-      <c r="U5" s="129"/>
-      <c r="V5" s="112"/>
+      <c r="T5" s="124"/>
+      <c r="U5" s="130"/>
+      <c r="V5" s="113"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -23420,17 +23425,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="115" t="s">
+      <c r="C60" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="116"/>
-      <c r="E60" s="116"/>
-      <c r="F60" s="116"/>
-      <c r="G60" s="116"/>
-      <c r="H60" s="116"/>
-      <c r="I60" s="116"/>
-      <c r="J60" s="116"/>
-      <c r="K60" s="117"/>
+      <c r="D60" s="117"/>
+      <c r="E60" s="117"/>
+      <c r="F60" s="117"/>
+      <c r="G60" s="117"/>
+      <c r="H60" s="117"/>
+      <c r="I60" s="117"/>
+      <c r="J60" s="117"/>
+      <c r="K60" s="118"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -23739,21 +23744,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="118" t="s">
+      <c r="I1" s="119" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="118"/>
-      <c r="K1" s="118"/>
-      <c r="L1" s="118"/>
-      <c r="M1" s="118"/>
-      <c r="N1" s="118"/>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="118"/>
-      <c r="T1" s="118"/>
-      <c r="U1" s="118"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -23765,17 +23770,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="119" t="s">
+      <c r="C4" s="120" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
-      <c r="H4" s="119"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="121"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120"/>
+      <c r="I4" s="120"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="122"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -23795,13 +23800,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="122" t="s">
+      <c r="T4" s="123" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="128" t="s">
+      <c r="U4" s="129" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="111" t="s">
+      <c r="V4" s="112" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -23841,10 +23846,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="126" t="s">
+      <c r="J5" s="127" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="127"/>
+      <c r="K5" s="128"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -23852,9 +23857,9 @@
       <c r="Q5" s="107"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="123"/>
-      <c r="U5" s="129"/>
-      <c r="V5" s="112"/>
+      <c r="T5" s="124"/>
+      <c r="U5" s="130"/>
+      <c r="V5" s="113"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -26552,17 +26557,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="115" t="s">
+      <c r="C60" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="116"/>
-      <c r="E60" s="116"/>
-      <c r="F60" s="116"/>
-      <c r="G60" s="116"/>
-      <c r="H60" s="116"/>
-      <c r="I60" s="116"/>
-      <c r="J60" s="116"/>
-      <c r="K60" s="117"/>
+      <c r="D60" s="117"/>
+      <c r="E60" s="117"/>
+      <c r="F60" s="117"/>
+      <c r="G60" s="117"/>
+      <c r="H60" s="117"/>
+      <c r="I60" s="117"/>
+      <c r="J60" s="117"/>
+      <c r="K60" s="118"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -26871,21 +26876,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="118" t="s">
+      <c r="I1" s="119" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="118"/>
-      <c r="K1" s="118"/>
-      <c r="L1" s="118"/>
-      <c r="M1" s="118"/>
-      <c r="N1" s="118"/>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="118"/>
-      <c r="T1" s="118"/>
-      <c r="U1" s="118"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -26897,17 +26902,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="119" t="s">
+      <c r="C4" s="120" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
-      <c r="H4" s="119"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="121"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120"/>
+      <c r="I4" s="120"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="122"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -26927,13 +26932,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="122" t="s">
+      <c r="T4" s="123" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="128" t="s">
+      <c r="U4" s="129" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="111" t="s">
+      <c r="V4" s="112" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -26973,10 +26978,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="126" t="s">
+      <c r="J5" s="127" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="127"/>
+      <c r="K5" s="128"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -26984,9 +26989,9 @@
       <c r="Q5" s="107"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="123"/>
-      <c r="U5" s="129"/>
-      <c r="V5" s="112"/>
+      <c r="T5" s="124"/>
+      <c r="U5" s="130"/>
+      <c r="V5" s="113"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -29694,17 +29699,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="115" t="s">
+      <c r="C60" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="116"/>
-      <c r="E60" s="116"/>
-      <c r="F60" s="116"/>
-      <c r="G60" s="116"/>
-      <c r="H60" s="116"/>
-      <c r="I60" s="116"/>
-      <c r="J60" s="116"/>
-      <c r="K60" s="117"/>
+      <c r="D60" s="117"/>
+      <c r="E60" s="117"/>
+      <c r="F60" s="117"/>
+      <c r="G60" s="117"/>
+      <c r="H60" s="117"/>
+      <c r="I60" s="117"/>
+      <c r="J60" s="117"/>
+      <c r="K60" s="118"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -30013,21 +30018,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="118" t="s">
+      <c r="I1" s="119" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="118"/>
-      <c r="K1" s="118"/>
-      <c r="L1" s="118"/>
-      <c r="M1" s="118"/>
-      <c r="N1" s="118"/>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="118"/>
-      <c r="T1" s="118"/>
-      <c r="U1" s="118"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -30039,17 +30044,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="119" t="s">
+      <c r="C4" s="120" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
-      <c r="H4" s="119"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="121"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120"/>
+      <c r="I4" s="120"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="122"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -30069,13 +30074,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="122" t="s">
+      <c r="T4" s="123" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="128" t="s">
+      <c r="U4" s="129" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="111" t="s">
+      <c r="V4" s="112" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -30115,10 +30120,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="126" t="s">
+      <c r="J5" s="127" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="127"/>
+      <c r="K5" s="128"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -30126,9 +30131,9 @@
       <c r="Q5" s="108"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="123"/>
-      <c r="U5" s="129"/>
-      <c r="V5" s="112"/>
+      <c r="T5" s="124"/>
+      <c r="U5" s="130"/>
+      <c r="V5" s="113"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -32822,17 +32827,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="115" t="s">
+      <c r="C60" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="116"/>
-      <c r="E60" s="116"/>
-      <c r="F60" s="116"/>
-      <c r="G60" s="116"/>
-      <c r="H60" s="116"/>
-      <c r="I60" s="116"/>
-      <c r="J60" s="116"/>
-      <c r="K60" s="117"/>
+      <c r="D60" s="117"/>
+      <c r="E60" s="117"/>
+      <c r="F60" s="117"/>
+      <c r="G60" s="117"/>
+      <c r="H60" s="117"/>
+      <c r="I60" s="117"/>
+      <c r="J60" s="117"/>
+      <c r="K60" s="118"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -33141,21 +33146,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="118" t="s">
+      <c r="I1" s="119" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="118"/>
-      <c r="K1" s="118"/>
-      <c r="L1" s="118"/>
-      <c r="M1" s="118"/>
-      <c r="N1" s="118"/>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="118"/>
-      <c r="T1" s="118"/>
-      <c r="U1" s="118"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -33167,17 +33172,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="119" t="s">
+      <c r="C4" s="120" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
-      <c r="H4" s="119"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="121"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120"/>
+      <c r="I4" s="120"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="122"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -33197,13 +33202,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="122" t="s">
+      <c r="T4" s="123" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="128" t="s">
+      <c r="U4" s="129" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="111" t="s">
+      <c r="V4" s="112" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -33243,10 +33248,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="126" t="s">
+      <c r="J5" s="127" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="127"/>
+      <c r="K5" s="128"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -33254,9 +33259,9 @@
       <c r="Q5" s="109"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="123"/>
-      <c r="U5" s="129"/>
-      <c r="V5" s="112"/>
+      <c r="T5" s="124"/>
+      <c r="U5" s="130"/>
+      <c r="V5" s="113"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -35970,17 +35975,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="115" t="s">
+      <c r="C60" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="116"/>
-      <c r="E60" s="116"/>
-      <c r="F60" s="116"/>
-      <c r="G60" s="116"/>
-      <c r="H60" s="116"/>
-      <c r="I60" s="116"/>
-      <c r="J60" s="116"/>
-      <c r="K60" s="117"/>
+      <c r="D60" s="117"/>
+      <c r="E60" s="117"/>
+      <c r="F60" s="117"/>
+      <c r="G60" s="117"/>
+      <c r="H60" s="117"/>
+      <c r="I60" s="117"/>
+      <c r="J60" s="117"/>
+      <c r="K60" s="118"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -36289,21 +36294,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="118" t="s">
+      <c r="I1" s="119" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="118"/>
-      <c r="K1" s="118"/>
-      <c r="L1" s="118"/>
-      <c r="M1" s="118"/>
-      <c r="N1" s="118"/>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="118"/>
-      <c r="T1" s="118"/>
-      <c r="U1" s="118"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -36315,17 +36320,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="119" t="s">
+      <c r="C4" s="120" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
-      <c r="H4" s="119"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="121"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120"/>
+      <c r="I4" s="120"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="122"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -36345,13 +36350,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="122" t="s">
+      <c r="T4" s="123" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="128" t="s">
+      <c r="U4" s="129" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="111" t="s">
+      <c r="V4" s="112" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -36391,10 +36396,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="126" t="s">
+      <c r="J5" s="127" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="127"/>
+      <c r="K5" s="128"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -36402,9 +36407,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="123"/>
-      <c r="U5" s="129"/>
-      <c r="V5" s="112"/>
+      <c r="T5" s="124"/>
+      <c r="U5" s="130"/>
+      <c r="V5" s="113"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -39116,17 +39121,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="115" t="s">
+      <c r="C60" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="116"/>
-      <c r="E60" s="116"/>
-      <c r="F60" s="116"/>
-      <c r="G60" s="116"/>
-      <c r="H60" s="116"/>
-      <c r="I60" s="116"/>
-      <c r="J60" s="116"/>
-      <c r="K60" s="117"/>
+      <c r="D60" s="117"/>
+      <c r="E60" s="117"/>
+      <c r="F60" s="117"/>
+      <c r="G60" s="117"/>
+      <c r="H60" s="117"/>
+      <c r="I60" s="117"/>
+      <c r="J60" s="117"/>
+      <c r="K60" s="118"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -39435,21 +39440,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="118" t="s">
+      <c r="I1" s="119" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="118"/>
-      <c r="K1" s="118"/>
-      <c r="L1" s="118"/>
-      <c r="M1" s="118"/>
-      <c r="N1" s="118"/>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="118"/>
-      <c r="T1" s="118"/>
-      <c r="U1" s="118"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -39461,17 +39466,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="119" t="s">
+      <c r="C4" s="120" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
-      <c r="H4" s="119"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="121"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120"/>
+      <c r="I4" s="120"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="122"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -39491,13 +39496,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="122" t="s">
+      <c r="T4" s="123" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="128" t="s">
+      <c r="U4" s="129" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="111" t="s">
+      <c r="V4" s="112" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -39537,10 +39542,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="126" t="s">
+      <c r="J5" s="127" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="127"/>
+      <c r="K5" s="128"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -39548,9 +39553,9 @@
       <c r="Q5" s="110"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="123"/>
-      <c r="U5" s="129"/>
-      <c r="V5" s="112"/>
+      <c r="T5" s="124"/>
+      <c r="U5" s="130"/>
+      <c r="V5" s="113"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -42261,17 +42266,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="115" t="s">
+      <c r="C60" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="116"/>
-      <c r="E60" s="116"/>
-      <c r="F60" s="116"/>
-      <c r="G60" s="116"/>
-      <c r="H60" s="116"/>
-      <c r="I60" s="116"/>
-      <c r="J60" s="116"/>
-      <c r="K60" s="117"/>
+      <c r="D60" s="117"/>
+      <c r="E60" s="117"/>
+      <c r="F60" s="117"/>
+      <c r="G60" s="117"/>
+      <c r="H60" s="117"/>
+      <c r="I60" s="117"/>
+      <c r="J60" s="117"/>
+      <c r="K60" s="118"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -42530,6 +42535,3134 @@
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F95391F2-1BB6-4CCB-8EC4-EBABD0A49A8C}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="9" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="119" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="120" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="120"/>
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120"/>
+      <c r="I4" s="120"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="122"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="123" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="129" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="112" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="127" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="128"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="111"/>
+      <c r="Q5" s="111"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="124"/>
+      <c r="U5" s="130"/>
+      <c r="V5" s="113"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="111"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="111"/>
+      <c r="Q6" s="111"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="52">
+        <v>9</v>
+      </c>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
+      <c r="J7" s="53"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
+      <c r="L7" s="55"/>
+      <c r="M7" s="56">
+        <v>1</v>
+      </c>
+      <c r="N7" s="57"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="53">
+        <v>5</v>
+      </c>
+      <c r="R7" s="54"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="58">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>9</v>
+      </c>
+      <c r="U7" s="58">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>393</v>
+      </c>
+      <c r="V7" s="58">
+        <f>U7/24</f>
+        <v>16.375</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="59">
+        <f>55+23</f>
+        <v>78</v>
+      </c>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="63">
+        <v>1</v>
+      </c>
+      <c r="N8" s="64"/>
+      <c r="O8" s="65">
+        <v>1</v>
+      </c>
+      <c r="P8" s="66"/>
+      <c r="Q8" s="66">
+        <v>10</v>
+      </c>
+      <c r="R8" s="67"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="68">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="69">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>2160</v>
+      </c>
+      <c r="V8" s="69">
+        <f>U8/24</f>
+        <v>90</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="70">
+        <v>64</v>
+      </c>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="73"/>
+      <c r="N9" s="74"/>
+      <c r="O9" s="70"/>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71">
+        <v>5</v>
+      </c>
+      <c r="R9" s="72"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="76">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>1656</v>
+      </c>
+      <c r="V9" s="76">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>69</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="70"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="74"/>
+      <c r="O10" s="70"/>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71"/>
+      <c r="R10" s="72"/>
+      <c r="S10" s="55"/>
+      <c r="T10" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V10" s="58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="70"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
+      <c r="L11" s="55"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="55"/>
+      <c r="T11" s="58">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U11" s="58">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="V11" s="58">
+        <f t="shared" si="3"/>
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="59">
+        <f>720+11+1440+432+42</f>
+        <v>2645</v>
+      </c>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="63">
+        <v>11</v>
+      </c>
+      <c r="N12" s="64"/>
+      <c r="O12" s="65">
+        <v>15</v>
+      </c>
+      <c r="P12" s="66"/>
+      <c r="Q12" s="66">
+        <v>7</v>
+      </c>
+      <c r="R12" s="67"/>
+      <c r="S12" s="62"/>
+      <c r="T12" s="69">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U12" s="69">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>64272</v>
+      </c>
+      <c r="V12" s="69">
+        <f>U12/24</f>
+        <v>2678</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
+      <c r="I13" s="70"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="55"/>
+      <c r="T13" s="76">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="U13" s="76">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>64</v>
+      </c>
+      <c r="V13" s="76">
+        <f>U13/24</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="70">
+        <v>4</v>
+      </c>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="55"/>
+      <c r="T14" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="75">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>96</v>
+      </c>
+      <c r="V14" s="75">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>4</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="55"/>
+      <c r="T15" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="55"/>
+      <c r="T16" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70">
+        <f>24*3</f>
+        <v>72</v>
+      </c>
+      <c r="I17" s="70"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U17" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V17" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="55"/>
+      <c r="T18" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="70">
+        <v>2</v>
+      </c>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70">
+        <f>24+20</f>
+        <v>44</v>
+      </c>
+      <c r="I19" s="70"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="55"/>
+      <c r="T19" s="58">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="U19" s="75">
+        <f t="shared" si="4"/>
+        <v>92</v>
+      </c>
+      <c r="V19" s="75">
+        <f t="shared" si="5"/>
+        <v>3.8333333333333335</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="74"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="55"/>
+      <c r="T20" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V20" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70">
+        <f>2*24</f>
+        <v>48</v>
+      </c>
+      <c r="I21" s="70"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="58">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="U21" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V21" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="70"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
+      <c r="J22" s="71"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="55"/>
+      <c r="T22" s="58">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U22" s="75">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="V22" s="75">
+        <f t="shared" si="5"/>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
+      <c r="I23" s="70"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="74"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="55"/>
+      <c r="T23" s="58">
+        <f t="shared" si="0"/>
+        <v>907</v>
+      </c>
+      <c r="U23" s="75">
+        <f t="shared" si="4"/>
+        <v>907</v>
+      </c>
+      <c r="V23" s="75">
+        <f t="shared" si="5"/>
+        <v>37.791666666666664</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="70">
+        <v>5</v>
+      </c>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I24" s="70"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="55"/>
+      <c r="T24" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U24" s="75">
+        <f t="shared" si="4"/>
+        <v>192</v>
+      </c>
+      <c r="V24" s="75">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="70">
+        <v>51</v>
+      </c>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70">
+        <v>1</v>
+      </c>
+      <c r="J25" s="71"/>
+      <c r="K25" s="72"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="73">
+        <v>1</v>
+      </c>
+      <c r="N25" s="74"/>
+      <c r="O25" s="70"/>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71">
+        <v>10</v>
+      </c>
+      <c r="R25" s="72"/>
+      <c r="S25" s="55"/>
+      <c r="T25" s="58">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="U25" s="75">
+        <f t="shared" si="4"/>
+        <v>1489</v>
+      </c>
+      <c r="V25" s="75">
+        <f t="shared" si="5"/>
+        <v>62.041666666666664</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="74"/>
+      <c r="O26" s="70"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="71">
+        <v>1</v>
+      </c>
+      <c r="R26" s="72"/>
+      <c r="S26" s="55"/>
+      <c r="T26" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="75">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="V26" s="75">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="70"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="70"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="55"/>
+      <c r="T27" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="70">
+        <f>126+28</f>
+        <v>154</v>
+      </c>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="73"/>
+      <c r="N28" s="74"/>
+      <c r="O28" s="70">
+        <v>1</v>
+      </c>
+      <c r="P28" s="71"/>
+      <c r="Q28" s="71">
+        <v>20</v>
+      </c>
+      <c r="R28" s="72"/>
+      <c r="S28" s="55"/>
+      <c r="T28" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="75">
+        <f t="shared" si="4"/>
+        <v>4200</v>
+      </c>
+      <c r="V28" s="75">
+        <f t="shared" si="5"/>
+        <v>175</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="70">
+        <v>26</v>
+      </c>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70">
+        <v>5</v>
+      </c>
+      <c r="J29" s="71"/>
+      <c r="K29" s="72"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="73"/>
+      <c r="N29" s="74"/>
+      <c r="O29" s="70"/>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71">
+        <v>5</v>
+      </c>
+      <c r="R29" s="72"/>
+      <c r="S29" s="55"/>
+      <c r="T29" s="58">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U29" s="75">
+        <f t="shared" si="4"/>
+        <v>749</v>
+      </c>
+      <c r="V29" s="75">
+        <f t="shared" si="5"/>
+        <v>31.208333333333332</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="70">
+        <v>4</v>
+      </c>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="74"/>
+      <c r="O30" s="70"/>
+      <c r="P30" s="71"/>
+      <c r="Q30" s="71"/>
+      <c r="R30" s="72"/>
+      <c r="S30" s="55"/>
+      <c r="T30" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="75">
+        <f t="shared" si="4"/>
+        <v>96</v>
+      </c>
+      <c r="V30" s="75">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="70">
+        <v>1</v>
+      </c>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71">
+        <v>1</v>
+      </c>
+      <c r="R31" s="72"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V31" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="70"/>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="74"/>
+      <c r="O32" s="70"/>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="55"/>
+      <c r="T32" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="70"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="73"/>
+      <c r="N33" s="74"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="55"/>
+      <c r="T33" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="70">
+        <v>17</v>
+      </c>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
+      <c r="J34" s="71"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
+      <c r="L34" s="55"/>
+      <c r="M34" s="73"/>
+      <c r="N34" s="74"/>
+      <c r="O34" s="70">
+        <v>1</v>
+      </c>
+      <c r="P34" s="71">
+        <v>12</v>
+      </c>
+      <c r="Q34" s="71">
+        <v>10</v>
+      </c>
+      <c r="R34" s="72"/>
+      <c r="S34" s="55"/>
+      <c r="T34" s="58">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="U34" s="75">
+        <f t="shared" si="4"/>
+        <v>686</v>
+      </c>
+      <c r="V34" s="75">
+        <f t="shared" si="5"/>
+        <v>28.583333333333332</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="72"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="74"/>
+      <c r="O35" s="70"/>
+      <c r="P35" s="71"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="72"/>
+      <c r="S35" s="55"/>
+      <c r="T35" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="73"/>
+      <c r="N36" s="74"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="71"/>
+      <c r="Q36" s="71"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="55"/>
+      <c r="T36" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="59">
+        <f>864+1512+32</f>
+        <v>2408</v>
+      </c>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59">
+        <v>4</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>4</v>
+      </c>
+      <c r="K37" s="61">
+        <v>3</v>
+      </c>
+      <c r="L37" s="62"/>
+      <c r="M37" s="63"/>
+      <c r="N37" s="64"/>
+      <c r="O37" s="65">
+        <v>63</v>
+      </c>
+      <c r="P37" s="66"/>
+      <c r="Q37" s="66">
+        <v>53</v>
+      </c>
+      <c r="R37" s="67"/>
+      <c r="S37" s="62"/>
+      <c r="T37" s="77">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="U37" s="77">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>15157</v>
+      </c>
+      <c r="V37" s="77">
+        <f>U37/6</f>
+        <v>2526.1666666666665</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="73"/>
+      <c r="N38" s="74"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="71">
+        <v>1</v>
+      </c>
+      <c r="R38" s="72"/>
+      <c r="S38" s="55"/>
+      <c r="T38" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="75">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>24</v>
+      </c>
+      <c r="V38" s="75">
+        <f>U38/24</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="74"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="71"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="95"/>
+      <c r="T39" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U39" s="75">
+        <f>C39*24+M39*24+O39*24+Q39*24+T39</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="75">
+        <f>U39/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="59">
+        <f>63+36</f>
+        <v>99</v>
+      </c>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
+      <c r="L40" s="62"/>
+      <c r="M40" s="63">
+        <v>2</v>
+      </c>
+      <c r="N40" s="64"/>
+      <c r="O40" s="65">
+        <v>1</v>
+      </c>
+      <c r="P40" s="66"/>
+      <c r="Q40" s="66">
+        <v>10</v>
+      </c>
+      <c r="R40" s="67"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="77">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U40" s="77">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>2708</v>
+      </c>
+      <c r="V40" s="77">
+        <f>U40/24</f>
+        <v>112.83333333333333</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="82">
+        <f>96+34</f>
+        <v>130</v>
+      </c>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="85"/>
+      <c r="M41" s="86"/>
+      <c r="N41" s="87"/>
+      <c r="O41" s="82">
+        <v>3</v>
+      </c>
+      <c r="P41" s="83"/>
+      <c r="Q41" s="83">
+        <v>21</v>
+      </c>
+      <c r="R41" s="84"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="88">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>1848</v>
+      </c>
+      <c r="V41" s="88">
+        <f>U41/12</f>
+        <v>154</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="71"/>
+      <c r="K42" s="72"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="73"/>
+      <c r="N42" s="74"/>
+      <c r="O42" s="70"/>
+      <c r="P42" s="71"/>
+      <c r="Q42" s="71"/>
+      <c r="R42" s="72"/>
+      <c r="S42" s="55"/>
+      <c r="T42" s="75"/>
+      <c r="U42" s="75"/>
+      <c r="V42" s="75"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="65">
+        <f>7776+1836+3024+8424+1404+3348+6480</f>
+        <v>32292</v>
+      </c>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65">
+        <v>5</v>
+      </c>
+      <c r="I43" s="65">
+        <v>7</v>
+      </c>
+      <c r="J43" s="66">
+        <f>4*6+3</f>
+        <v>27</v>
+      </c>
+      <c r="K43" s="67">
+        <f>64*6+2</f>
+        <v>386</v>
+      </c>
+      <c r="L43" s="62"/>
+      <c r="M43" s="63">
+        <v>1</v>
+      </c>
+      <c r="N43" s="64"/>
+      <c r="O43" s="65">
+        <v>458</v>
+      </c>
+      <c r="P43" s="66"/>
+      <c r="Q43" s="66">
+        <v>209</v>
+      </c>
+      <c r="R43" s="67"/>
+      <c r="S43" s="62"/>
+      <c r="T43" s="77">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>425</v>
+      </c>
+      <c r="U43" s="77">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>198185</v>
+      </c>
+      <c r="V43" s="77">
+        <f>U43/6</f>
+        <v>33030.833333333336</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="70"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="71"/>
+      <c r="K44" s="72"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="73"/>
+      <c r="N44" s="74"/>
+      <c r="O44" s="70"/>
+      <c r="P44" s="71"/>
+      <c r="Q44" s="71"/>
+      <c r="R44" s="72"/>
+      <c r="S44" s="55"/>
+      <c r="T44" s="75"/>
+      <c r="U44" s="75"/>
+      <c r="V44" s="75"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="70"/>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="70"/>
+      <c r="I45" s="70"/>
+      <c r="J45" s="71"/>
+      <c r="K45" s="72"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="73"/>
+      <c r="N45" s="74"/>
+      <c r="O45" s="70">
+        <v>1</v>
+      </c>
+      <c r="P45" s="71"/>
+      <c r="Q45" s="71">
+        <v>4</v>
+      </c>
+      <c r="R45" s="72"/>
+      <c r="S45" s="55"/>
+      <c r="T45" s="75">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="75">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>120</v>
+      </c>
+      <c r="V45" s="75">
+        <f>U45/24</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="73"/>
+      <c r="N46" s="74"/>
+      <c r="O46" s="70"/>
+      <c r="P46" s="71"/>
+      <c r="Q46" s="71"/>
+      <c r="R46" s="72"/>
+      <c r="S46" s="55"/>
+      <c r="T46" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="75">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="75">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="65">
+        <f>756+64+324+98+540+432+432+106</f>
+        <v>2752</v>
+      </c>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
+      <c r="I47" s="65"/>
+      <c r="J47" s="66">
+        <v>1</v>
+      </c>
+      <c r="K47" s="67">
+        <v>4</v>
+      </c>
+      <c r="L47" s="62"/>
+      <c r="M47" s="63">
+        <v>3</v>
+      </c>
+      <c r="N47" s="64"/>
+      <c r="O47" s="65">
+        <v>9</v>
+      </c>
+      <c r="P47" s="66">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="66">
+        <v>13</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
+      <c r="S47" s="62"/>
+      <c r="T47" s="77">
+        <f t="shared" si="7"/>
+        <v>13</v>
+      </c>
+      <c r="U47" s="77">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>16675</v>
+      </c>
+      <c r="V47" s="77">
+        <f>U47/6</f>
+        <v>2779.1666666666665</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
+      <c r="I48" s="70"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="72"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="73"/>
+      <c r="N48" s="74"/>
+      <c r="O48" s="70"/>
+      <c r="P48" s="71"/>
+      <c r="Q48" s="71"/>
+      <c r="R48" s="72"/>
+      <c r="S48" s="55"/>
+      <c r="T48" s="75">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="U48" s="75">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="V48" s="75">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="70"/>
+      <c r="I49" s="70"/>
+      <c r="J49" s="71"/>
+      <c r="K49" s="72"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="74"/>
+      <c r="O49" s="70"/>
+      <c r="P49" s="71"/>
+      <c r="Q49" s="71"/>
+      <c r="R49" s="72"/>
+      <c r="S49" s="55"/>
+      <c r="T49" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="70"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="70"/>
+      <c r="F50" s="70"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
+      <c r="J50" s="71"/>
+      <c r="K50" s="72"/>
+      <c r="L50" s="55"/>
+      <c r="M50" s="73"/>
+      <c r="N50" s="74"/>
+      <c r="O50" s="70"/>
+      <c r="P50" s="71"/>
+      <c r="Q50" s="71"/>
+      <c r="R50" s="72"/>
+      <c r="S50" s="55"/>
+      <c r="T50" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="65"/>
+      <c r="I51" s="65"/>
+      <c r="J51" s="66"/>
+      <c r="K51" s="67"/>
+      <c r="L51" s="62"/>
+      <c r="M51" s="63"/>
+      <c r="N51" s="64"/>
+      <c r="O51" s="65"/>
+      <c r="P51" s="66"/>
+      <c r="Q51" s="66"/>
+      <c r="R51" s="67"/>
+      <c r="S51" s="62"/>
+      <c r="T51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="77">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>204</v>
+      </c>
+      <c r="V51" s="77">
+        <f>U51/6</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="70"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="70"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="71"/>
+      <c r="K52" s="72"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="73"/>
+      <c r="N52" s="74"/>
+      <c r="O52" s="70"/>
+      <c r="P52" s="71"/>
+      <c r="Q52" s="71"/>
+      <c r="R52" s="72"/>
+      <c r="S52" s="55"/>
+      <c r="T52" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="75">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="70">
+        <v>9</v>
+      </c>
+      <c r="D53" s="70"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="70"/>
+      <c r="H53" s="70"/>
+      <c r="I53" s="70"/>
+      <c r="J53" s="71"/>
+      <c r="K53" s="72"/>
+      <c r="L53" s="55"/>
+      <c r="M53" s="73"/>
+      <c r="N53" s="74"/>
+      <c r="O53" s="70"/>
+      <c r="P53" s="71"/>
+      <c r="Q53" s="71"/>
+      <c r="R53" s="72"/>
+      <c r="S53" s="55"/>
+      <c r="T53" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="75">
+        <f t="shared" si="10"/>
+        <v>216</v>
+      </c>
+      <c r="V53" s="75">
+        <f t="shared" si="9"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="71"/>
+      <c r="K54" s="72"/>
+      <c r="L54" s="55"/>
+      <c r="M54" s="73"/>
+      <c r="N54" s="74"/>
+      <c r="O54" s="70"/>
+      <c r="P54" s="71"/>
+      <c r="Q54" s="71"/>
+      <c r="R54" s="72"/>
+      <c r="S54" s="55"/>
+      <c r="T54" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="70"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="70"/>
+      <c r="I55" s="70"/>
+      <c r="J55" s="71"/>
+      <c r="K55" s="72"/>
+      <c r="L55" s="55"/>
+      <c r="M55" s="73"/>
+      <c r="N55" s="74"/>
+      <c r="O55" s="70"/>
+      <c r="P55" s="71"/>
+      <c r="Q55" s="71"/>
+      <c r="R55" s="72"/>
+      <c r="S55" s="55"/>
+      <c r="T55" s="75"/>
+      <c r="U55" s="75"/>
+      <c r="V55" s="75"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="70"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="70"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="71"/>
+      <c r="K56" s="72"/>
+      <c r="L56" s="55"/>
+      <c r="M56" s="73"/>
+      <c r="N56" s="74"/>
+      <c r="O56" s="70"/>
+      <c r="P56" s="71"/>
+      <c r="Q56" s="71"/>
+      <c r="R56" s="72"/>
+      <c r="S56" s="55"/>
+      <c r="T56" s="75"/>
+      <c r="U56" s="75"/>
+      <c r="V56" s="75"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="70"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="70"/>
+      <c r="I57" s="70"/>
+      <c r="J57" s="71"/>
+      <c r="K57" s="72"/>
+      <c r="L57" s="55"/>
+      <c r="M57" s="73"/>
+      <c r="N57" s="74"/>
+      <c r="O57" s="70"/>
+      <c r="P57" s="71"/>
+      <c r="Q57" s="71"/>
+      <c r="R57" s="72"/>
+      <c r="S57" s="55"/>
+      <c r="T57" s="75"/>
+      <c r="U57" s="75"/>
+      <c r="V57" s="75"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>40790</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>1193</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>39</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>32</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>422</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>20</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>555</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>16</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>385</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>3</v>
+      </c>
+      <c r="S58" s="55"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>1705</v>
+      </c>
+      <c r="U58" s="90">
+        <f>SUM(U7:U57)</f>
+        <v>312547</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>41877.416666666664</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="116" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="117"/>
+      <c r="E60" s="117"/>
+      <c r="F60" s="117"/>
+      <c r="G60" s="117"/>
+      <c r="H60" s="117"/>
+      <c r="I60" s="117"/>
+      <c r="J60" s="117"/>
+      <c r="K60" s="118"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -42580,21 +45713,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="118" t="s">
+      <c r="I1" s="119" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="118"/>
-      <c r="K1" s="118"/>
-      <c r="L1" s="118"/>
-      <c r="M1" s="118"/>
-      <c r="N1" s="118"/>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="118"/>
-      <c r="T1" s="118"/>
-      <c r="U1" s="118"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -42606,17 +45739,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="119" t="s">
+      <c r="C4" s="120" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
-      <c r="H4" s="119"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="121"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120"/>
+      <c r="I4" s="120"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="122"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -42636,13 +45769,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="122" t="s">
+      <c r="T4" s="123" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="128" t="s">
+      <c r="U4" s="129" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="111" t="s">
+      <c r="V4" s="112" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -42682,10 +45815,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="126" t="s">
+      <c r="J5" s="127" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="127"/>
+      <c r="K5" s="128"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -42693,9 +45826,9 @@
       <c r="Q5" s="96"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="123"/>
-      <c r="U5" s="129"/>
-      <c r="V5" s="112"/>
+      <c r="T5" s="124"/>
+      <c r="U5" s="130"/>
+      <c r="V5" s="113"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -45430,17 +48563,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="115" t="s">
+      <c r="C60" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="116"/>
-      <c r="E60" s="116"/>
-      <c r="F60" s="116"/>
-      <c r="G60" s="116"/>
-      <c r="H60" s="116"/>
-      <c r="I60" s="116"/>
-      <c r="J60" s="116"/>
-      <c r="K60" s="117"/>
+      <c r="D60" s="117"/>
+      <c r="E60" s="117"/>
+      <c r="F60" s="117"/>
+      <c r="G60" s="117"/>
+      <c r="H60" s="117"/>
+      <c r="I60" s="117"/>
+      <c r="J60" s="117"/>
+      <c r="K60" s="118"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -45749,21 +48882,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="118" t="s">
+      <c r="I1" s="119" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="118"/>
-      <c r="K1" s="118"/>
-      <c r="L1" s="118"/>
-      <c r="M1" s="118"/>
-      <c r="N1" s="118"/>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="118"/>
-      <c r="T1" s="118"/>
-      <c r="U1" s="118"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -45775,17 +48908,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="119" t="s">
+      <c r="C4" s="120" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
-      <c r="H4" s="119"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="121"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120"/>
+      <c r="I4" s="120"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="122"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -45805,13 +48938,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="122" t="s">
+      <c r="T4" s="123" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="128" t="s">
+      <c r="U4" s="129" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="111" t="s">
+      <c r="V4" s="112" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -45851,10 +48984,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="126" t="s">
+      <c r="J5" s="127" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="127"/>
+      <c r="K5" s="128"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -45862,9 +48995,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="123"/>
-      <c r="U5" s="129"/>
-      <c r="V5" s="112"/>
+      <c r="T5" s="124"/>
+      <c r="U5" s="130"/>
+      <c r="V5" s="113"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -48559,17 +51692,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="115" t="s">
+      <c r="C60" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="116"/>
-      <c r="E60" s="116"/>
-      <c r="F60" s="116"/>
-      <c r="G60" s="116"/>
-      <c r="H60" s="116"/>
-      <c r="I60" s="116"/>
-      <c r="J60" s="116"/>
-      <c r="K60" s="117"/>
+      <c r="D60" s="117"/>
+      <c r="E60" s="117"/>
+      <c r="F60" s="117"/>
+      <c r="G60" s="117"/>
+      <c r="H60" s="117"/>
+      <c r="I60" s="117"/>
+      <c r="J60" s="117"/>
+      <c r="K60" s="118"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -48878,21 +52011,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="118" t="s">
+      <c r="I1" s="119" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="118"/>
-      <c r="K1" s="118"/>
-      <c r="L1" s="118"/>
-      <c r="M1" s="118"/>
-      <c r="N1" s="118"/>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="118"/>
-      <c r="T1" s="118"/>
-      <c r="U1" s="118"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -48904,17 +52037,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="119" t="s">
+      <c r="C4" s="120" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
-      <c r="H4" s="119"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="121"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120"/>
+      <c r="I4" s="120"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="122"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -48934,13 +52067,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="122" t="s">
+      <c r="T4" s="123" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="128" t="s">
+      <c r="U4" s="129" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="111" t="s">
+      <c r="V4" s="112" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -48980,10 +52113,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="126" t="s">
+      <c r="J5" s="127" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="127"/>
+      <c r="K5" s="128"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -48991,9 +52124,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="123"/>
-      <c r="U5" s="129"/>
-      <c r="V5" s="112"/>
+      <c r="T5" s="124"/>
+      <c r="U5" s="130"/>
+      <c r="V5" s="113"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -51693,17 +54826,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="115" t="s">
+      <c r="C60" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="116"/>
-      <c r="E60" s="116"/>
-      <c r="F60" s="116"/>
-      <c r="G60" s="116"/>
-      <c r="H60" s="116"/>
-      <c r="I60" s="116"/>
-      <c r="J60" s="116"/>
-      <c r="K60" s="117"/>
+      <c r="D60" s="117"/>
+      <c r="E60" s="117"/>
+      <c r="F60" s="117"/>
+      <c r="G60" s="117"/>
+      <c r="H60" s="117"/>
+      <c r="I60" s="117"/>
+      <c r="J60" s="117"/>
+      <c r="K60" s="118"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -52012,21 +55145,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="118" t="s">
+      <c r="I1" s="119" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="118"/>
-      <c r="K1" s="118"/>
-      <c r="L1" s="118"/>
-      <c r="M1" s="118"/>
-      <c r="N1" s="118"/>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="118"/>
-      <c r="T1" s="118"/>
-      <c r="U1" s="118"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -52038,17 +55171,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="119" t="s">
+      <c r="C4" s="120" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
-      <c r="H4" s="119"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="121"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120"/>
+      <c r="I4" s="120"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="122"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -52068,13 +55201,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="122" t="s">
+      <c r="T4" s="123" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="128" t="s">
+      <c r="U4" s="129" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="111" t="s">
+      <c r="V4" s="112" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -52114,10 +55247,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="126" t="s">
+      <c r="J5" s="127" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="127"/>
+      <c r="K5" s="128"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -52125,9 +55258,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="123"/>
-      <c r="U5" s="129"/>
-      <c r="V5" s="112"/>
+      <c r="T5" s="124"/>
+      <c r="U5" s="130"/>
+      <c r="V5" s="113"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -54821,17 +57954,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="115" t="s">
+      <c r="C60" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="116"/>
-      <c r="E60" s="116"/>
-      <c r="F60" s="116"/>
-      <c r="G60" s="116"/>
-      <c r="H60" s="116"/>
-      <c r="I60" s="116"/>
-      <c r="J60" s="116"/>
-      <c r="K60" s="117"/>
+      <c r="D60" s="117"/>
+      <c r="E60" s="117"/>
+      <c r="F60" s="117"/>
+      <c r="G60" s="117"/>
+      <c r="H60" s="117"/>
+      <c r="I60" s="117"/>
+      <c r="J60" s="117"/>
+      <c r="K60" s="118"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -55140,21 +58273,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="118" t="s">
+      <c r="I1" s="119" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="118"/>
-      <c r="K1" s="118"/>
-      <c r="L1" s="118"/>
-      <c r="M1" s="118"/>
-      <c r="N1" s="118"/>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="118"/>
-      <c r="T1" s="118"/>
-      <c r="U1" s="118"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -55166,17 +58299,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="119" t="s">
+      <c r="C4" s="120" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
-      <c r="H4" s="119"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="121"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120"/>
+      <c r="I4" s="120"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="122"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -55196,13 +58329,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="122" t="s">
+      <c r="T4" s="123" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="128" t="s">
+      <c r="U4" s="129" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="111" t="s">
+      <c r="V4" s="112" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -55242,10 +58375,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="126" t="s">
+      <c r="J5" s="127" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="127"/>
+      <c r="K5" s="128"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -55253,9 +58386,9 @@
       <c r="Q5" s="100"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="123"/>
-      <c r="U5" s="129"/>
-      <c r="V5" s="112"/>
+      <c r="T5" s="124"/>
+      <c r="U5" s="130"/>
+      <c r="V5" s="113"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -57951,17 +61084,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="115" t="s">
+      <c r="C60" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="116"/>
-      <c r="E60" s="116"/>
-      <c r="F60" s="116"/>
-      <c r="G60" s="116"/>
-      <c r="H60" s="116"/>
-      <c r="I60" s="116"/>
-      <c r="J60" s="116"/>
-      <c r="K60" s="117"/>
+      <c r="D60" s="117"/>
+      <c r="E60" s="117"/>
+      <c r="F60" s="117"/>
+      <c r="G60" s="117"/>
+      <c r="H60" s="117"/>
+      <c r="I60" s="117"/>
+      <c r="J60" s="117"/>
+      <c r="K60" s="118"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -58270,21 +61403,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="118" t="s">
+      <c r="I1" s="119" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="118"/>
-      <c r="K1" s="118"/>
-      <c r="L1" s="118"/>
-      <c r="M1" s="118"/>
-      <c r="N1" s="118"/>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="118"/>
-      <c r="T1" s="118"/>
-      <c r="U1" s="118"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -58296,17 +61429,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="119" t="s">
+      <c r="C4" s="120" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
-      <c r="H4" s="119"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="121"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120"/>
+      <c r="I4" s="120"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="122"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -58326,13 +61459,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="122" t="s">
+      <c r="T4" s="123" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="128" t="s">
+      <c r="U4" s="129" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="111" t="s">
+      <c r="V4" s="112" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -58372,10 +61505,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="126" t="s">
+      <c r="J5" s="127" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="127"/>
+      <c r="K5" s="128"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -58383,9 +61516,9 @@
       <c r="Q5" s="101"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="123"/>
-      <c r="U5" s="129"/>
-      <c r="V5" s="112"/>
+      <c r="T5" s="124"/>
+      <c r="U5" s="130"/>
+      <c r="V5" s="113"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -61086,17 +64219,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="115" t="s">
+      <c r="C60" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="116"/>
-      <c r="E60" s="116"/>
-      <c r="F60" s="116"/>
-      <c r="G60" s="116"/>
-      <c r="H60" s="116"/>
-      <c r="I60" s="116"/>
-      <c r="J60" s="116"/>
-      <c r="K60" s="117"/>
+      <c r="D60" s="117"/>
+      <c r="E60" s="117"/>
+      <c r="F60" s="117"/>
+      <c r="G60" s="117"/>
+      <c r="H60" s="117"/>
+      <c r="I60" s="117"/>
+      <c r="J60" s="117"/>
+      <c r="K60" s="118"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -61405,21 +64538,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="118" t="s">
+      <c r="I1" s="119" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="118"/>
-      <c r="K1" s="118"/>
-      <c r="L1" s="118"/>
-      <c r="M1" s="118"/>
-      <c r="N1" s="118"/>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="118"/>
-      <c r="T1" s="118"/>
-      <c r="U1" s="118"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -61431,17 +64564,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="119" t="s">
+      <c r="C4" s="120" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
-      <c r="H4" s="119"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="121"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120"/>
+      <c r="I4" s="120"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="122"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -61461,13 +64594,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="122" t="s">
+      <c r="T4" s="123" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="128" t="s">
+      <c r="U4" s="129" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="111" t="s">
+      <c r="V4" s="112" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -61507,10 +64640,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="126" t="s">
+      <c r="J5" s="127" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="127"/>
+      <c r="K5" s="128"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -61518,9 +64651,9 @@
       <c r="Q5" s="102"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="123"/>
-      <c r="U5" s="129"/>
-      <c r="V5" s="112"/>
+      <c r="T5" s="124"/>
+      <c r="U5" s="130"/>
+      <c r="V5" s="113"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -64216,17 +67349,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="115" t="s">
+      <c r="C60" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="116"/>
-      <c r="E60" s="116"/>
-      <c r="F60" s="116"/>
-      <c r="G60" s="116"/>
-      <c r="H60" s="116"/>
-      <c r="I60" s="116"/>
-      <c r="J60" s="116"/>
-      <c r="K60" s="117"/>
+      <c r="D60" s="117"/>
+      <c r="E60" s="117"/>
+      <c r="F60" s="117"/>
+      <c r="G60" s="117"/>
+      <c r="H60" s="117"/>
+      <c r="I60" s="117"/>
+      <c r="J60" s="117"/>
+      <c r="K60" s="118"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>

--- a/GBDS JUNE FILES 2026/INVENTORY COUNT SHEET - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/INVENTORY COUNT SHEET - JUNE 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48539C7C-50F5-4C0A-BF43-8BBBDF357F5E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9680BA10-488A-4A82-8887-3A327AFF5632}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="11" activeTab="20" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="12" activeTab="21" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -34,6 +34,7 @@
     <sheet name="06-24-2026" sheetId="72" r:id="rId19"/>
     <sheet name="06-25-2026" sheetId="73" r:id="rId20"/>
     <sheet name="06-26-2026" sheetId="74" r:id="rId21"/>
+    <sheet name="06-29-2026" sheetId="75" r:id="rId22"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'06-01-2026'!$A$1:$W$59</definedName>
@@ -56,6 +57,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="18">'06-24-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="19">'06-25-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="20">'06-26-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="21">'06-29-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -74,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1848" uniqueCount="74">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -1283,7 +1285,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1569,6 +1571,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2030,21 +2035,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -2056,17 +2061,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -2086,13 +2091,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2132,10 +2137,10 @@
       <c r="I5" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="114" t="s">
+      <c r="J5" s="115" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="115"/>
+      <c r="K5" s="116"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2143,9 +2148,9 @@
       <c r="Q5" s="89"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -4676,17 +4681,17 @@
       <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="116" t="s">
+      <c r="C62" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="117"/>
-      <c r="E62" s="117"/>
-      <c r="F62" s="117"/>
-      <c r="G62" s="117"/>
-      <c r="H62" s="117"/>
-      <c r="I62" s="117"/>
-      <c r="J62" s="117"/>
-      <c r="K62" s="118"/>
+      <c r="D62" s="118"/>
+      <c r="E62" s="118"/>
+      <c r="F62" s="118"/>
+      <c r="G62" s="118"/>
+      <c r="H62" s="118"/>
+      <c r="I62" s="118"/>
+      <c r="J62" s="118"/>
+      <c r="K62" s="119"/>
       <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
@@ -4995,21 +5000,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -5021,17 +5026,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -5051,13 +5056,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="129" t="s">
+      <c r="U4" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -5097,10 +5102,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="128"/>
+      <c r="K5" s="129"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -5108,9 +5113,9 @@
       <c r="Q5" s="103"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -7795,17 +7800,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="116" t="s">
+      <c r="C60" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -8114,21 +8119,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -8140,17 +8145,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -8170,13 +8175,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="129" t="s">
+      <c r="U4" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -8216,10 +8221,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="128"/>
+      <c r="K5" s="129"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -8227,9 +8232,9 @@
       <c r="Q5" s="104"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -10923,17 +10928,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="116" t="s">
+      <c r="C60" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -11242,21 +11247,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -11268,17 +11273,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -11298,13 +11303,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="129" t="s">
+      <c r="U4" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -11344,10 +11349,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="128"/>
+      <c r="K5" s="129"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -11355,9 +11360,9 @@
       <c r="Q5" s="105"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -14052,17 +14057,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="116" t="s">
+      <c r="C60" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -14371,21 +14376,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -14397,17 +14402,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -14427,13 +14432,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="129" t="s">
+      <c r="U4" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -14473,10 +14478,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="128"/>
+      <c r="K5" s="129"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -14484,9 +14489,9 @@
       <c r="Q5" s="106"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -17179,17 +17184,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="116" t="s">
+      <c r="C60" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -17498,21 +17503,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -17524,17 +17529,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -17554,13 +17559,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="129" t="s">
+      <c r="U4" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -17600,10 +17605,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="128"/>
+      <c r="K5" s="129"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -17611,9 +17616,9 @@
       <c r="Q5" s="107"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -20302,17 +20307,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="116" t="s">
+      <c r="C60" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -20621,21 +20626,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -20647,17 +20652,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -20677,13 +20682,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="129" t="s">
+      <c r="U4" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -20723,10 +20728,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="128"/>
+      <c r="K5" s="129"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -20734,9 +20739,9 @@
       <c r="Q5" s="107"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -23425,17 +23430,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="116" t="s">
+      <c r="C60" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -23744,21 +23749,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -23770,17 +23775,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -23800,13 +23805,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="129" t="s">
+      <c r="U4" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -23846,10 +23851,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="128"/>
+      <c r="K5" s="129"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -23857,9 +23862,9 @@
       <c r="Q5" s="107"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -26557,17 +26562,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="116" t="s">
+      <c r="C60" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -26876,21 +26881,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -26902,17 +26907,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -26932,13 +26937,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="129" t="s">
+      <c r="U4" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -26978,10 +26983,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="128"/>
+      <c r="K5" s="129"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -26989,9 +26994,9 @@
       <c r="Q5" s="107"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -29699,17 +29704,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="116" t="s">
+      <c r="C60" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -30018,21 +30023,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -30044,17 +30049,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -30074,13 +30079,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="129" t="s">
+      <c r="U4" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -30120,10 +30125,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="128"/>
+      <c r="K5" s="129"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -30131,9 +30136,9 @@
       <c r="Q5" s="108"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -32827,17 +32832,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="116" t="s">
+      <c r="C60" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -33146,21 +33151,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -33172,17 +33177,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -33202,13 +33207,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="129" t="s">
+      <c r="U4" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -33248,10 +33253,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="128"/>
+      <c r="K5" s="129"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -33259,9 +33264,9 @@
       <c r="Q5" s="109"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -35975,17 +35980,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="116" t="s">
+      <c r="C60" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -36294,21 +36299,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -36320,17 +36325,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -36350,13 +36355,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="129" t="s">
+      <c r="U4" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -36396,10 +36401,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="128"/>
+      <c r="K5" s="129"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -36407,9 +36412,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -39121,17 +39126,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="116" t="s">
+      <c r="C60" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -39440,21 +39445,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -39466,17 +39471,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -39496,13 +39501,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="129" t="s">
+      <c r="U4" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -39542,10 +39547,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="128"/>
+      <c r="K5" s="129"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -39553,9 +39558,9 @@
       <c r="Q5" s="110"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -42266,17 +42271,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="116" t="s">
+      <c r="C60" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -42585,21 +42590,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -42611,17 +42616,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -42641,13 +42646,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="129" t="s">
+      <c r="U4" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -42687,10 +42692,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="128"/>
+      <c r="K5" s="129"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -42698,9 +42703,9 @@
       <c r="Q5" s="111"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -45394,17 +45399,3138 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="116" t="s">
+      <c r="C60" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE477C78-D4ED-4464-8D13-B759C682AFFE}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="9" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="120" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="121" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="124" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="130" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="113" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="128" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="129"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="112"/>
+      <c r="Q5" s="112"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="112"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="112"/>
+      <c r="Q6" s="112"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="52">
+        <v>9</v>
+      </c>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
+      <c r="J7" s="53"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
+      <c r="L7" s="55"/>
+      <c r="M7" s="56">
+        <v>1</v>
+      </c>
+      <c r="N7" s="57"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="53"/>
+      <c r="R7" s="54"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="58">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>9</v>
+      </c>
+      <c r="U7" s="58">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>273</v>
+      </c>
+      <c r="V7" s="58">
+        <f>U7/24</f>
+        <v>11.375</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="59">
+        <f>53+23</f>
+        <v>76</v>
+      </c>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="63">
+        <v>1</v>
+      </c>
+      <c r="N8" s="64"/>
+      <c r="O8" s="65">
+        <v>1</v>
+      </c>
+      <c r="P8" s="66"/>
+      <c r="Q8" s="66">
+        <v>2</v>
+      </c>
+      <c r="R8" s="67"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="68">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="69">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>1920</v>
+      </c>
+      <c r="V8" s="69">
+        <f>U8/24</f>
+        <v>80</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="70">
+        <v>58</v>
+      </c>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="73"/>
+      <c r="N9" s="74"/>
+      <c r="O9" s="70">
+        <v>1</v>
+      </c>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71">
+        <v>5</v>
+      </c>
+      <c r="R9" s="72"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="76">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>1536</v>
+      </c>
+      <c r="V9" s="76">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>64</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="70"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="74"/>
+      <c r="O10" s="70"/>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71"/>
+      <c r="R10" s="72"/>
+      <c r="S10" s="55"/>
+      <c r="T10" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V10" s="58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="70"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
+      <c r="L11" s="55"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="55"/>
+      <c r="T11" s="58">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U11" s="58">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="V11" s="58">
+        <f t="shared" si="3"/>
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="59">
+        <f>720+11+1440+432</f>
+        <v>2603</v>
+      </c>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="63">
+        <v>26</v>
+      </c>
+      <c r="N12" s="64"/>
+      <c r="O12" s="65">
+        <v>12</v>
+      </c>
+      <c r="P12" s="66"/>
+      <c r="Q12" s="66">
+        <v>22</v>
+      </c>
+      <c r="R12" s="67"/>
+      <c r="S12" s="62"/>
+      <c r="T12" s="69">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U12" s="69">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>63912</v>
+      </c>
+      <c r="V12" s="69">
+        <f>U12/24</f>
+        <v>2663</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
+      <c r="I13" s="70"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="55"/>
+      <c r="T13" s="76">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="U13" s="76">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>64</v>
+      </c>
+      <c r="V13" s="76">
+        <f>U13/24</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="70">
+        <v>4</v>
+      </c>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="55"/>
+      <c r="T14" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="75">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>96</v>
+      </c>
+      <c r="V14" s="75">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>4</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="55"/>
+      <c r="T15" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="55"/>
+      <c r="T16" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I17" s="70"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U17" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V17" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="55"/>
+      <c r="T18" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="70">
+        <v>2</v>
+      </c>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70">
+        <f>20+24</f>
+        <v>44</v>
+      </c>
+      <c r="I19" s="70"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="55"/>
+      <c r="T19" s="58">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="U19" s="75">
+        <f t="shared" si="4"/>
+        <v>92</v>
+      </c>
+      <c r="V19" s="75">
+        <f t="shared" si="5"/>
+        <v>3.8333333333333335</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="74"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="55"/>
+      <c r="T20" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V20" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70">
+        <f>2*24</f>
+        <v>48</v>
+      </c>
+      <c r="I21" s="70"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="58">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="U21" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V21" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="70"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
+      <c r="J22" s="71"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="55"/>
+      <c r="T22" s="58">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U22" s="75">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="V22" s="75">
+        <f t="shared" si="5"/>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70">
+        <f>24*37+19</f>
+        <v>907</v>
+      </c>
+      <c r="I23" s="70"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="74"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="55"/>
+      <c r="T23" s="58">
+        <f t="shared" si="0"/>
+        <v>907</v>
+      </c>
+      <c r="U23" s="75">
+        <f t="shared" si="4"/>
+        <v>907</v>
+      </c>
+      <c r="V23" s="75">
+        <f t="shared" si="5"/>
+        <v>37.791666666666664</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="70">
+        <v>5</v>
+      </c>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I24" s="70"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="55"/>
+      <c r="T24" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U24" s="75">
+        <f t="shared" si="4"/>
+        <v>192</v>
+      </c>
+      <c r="V24" s="75">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="70">
+        <v>49</v>
+      </c>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70"/>
+      <c r="J25" s="71">
+        <v>1</v>
+      </c>
+      <c r="K25" s="72"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="73">
+        <v>1</v>
+      </c>
+      <c r="N25" s="74"/>
+      <c r="O25" s="70"/>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71">
+        <v>2</v>
+      </c>
+      <c r="R25" s="72"/>
+      <c r="S25" s="55"/>
+      <c r="T25" s="58">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="U25" s="75">
+        <f t="shared" si="4"/>
+        <v>1249</v>
+      </c>
+      <c r="V25" s="75">
+        <f t="shared" si="5"/>
+        <v>52.041666666666664</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="74"/>
+      <c r="O26" s="70"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="71"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="55"/>
+      <c r="T26" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="70"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="70"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="55"/>
+      <c r="T27" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="70">
+        <f>26+126</f>
+        <v>152</v>
+      </c>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="73"/>
+      <c r="N28" s="74"/>
+      <c r="O28" s="70">
+        <v>1</v>
+      </c>
+      <c r="P28" s="71"/>
+      <c r="Q28" s="71">
+        <v>2</v>
+      </c>
+      <c r="R28" s="72"/>
+      <c r="S28" s="55"/>
+      <c r="T28" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="75">
+        <f t="shared" si="4"/>
+        <v>3720</v>
+      </c>
+      <c r="V28" s="75">
+        <f t="shared" si="5"/>
+        <v>155</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="70">
+        <v>24</v>
+      </c>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70"/>
+      <c r="J29" s="71">
+        <v>5</v>
+      </c>
+      <c r="K29" s="72"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="73"/>
+      <c r="N29" s="74"/>
+      <c r="O29" s="70"/>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71">
+        <v>2</v>
+      </c>
+      <c r="R29" s="72"/>
+      <c r="S29" s="55"/>
+      <c r="T29" s="58">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U29" s="75">
+        <f t="shared" si="4"/>
+        <v>629</v>
+      </c>
+      <c r="V29" s="75">
+        <f t="shared" si="5"/>
+        <v>26.208333333333332</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="70">
+        <v>2</v>
+      </c>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="74"/>
+      <c r="O30" s="70"/>
+      <c r="P30" s="71"/>
+      <c r="Q30" s="71">
+        <v>2</v>
+      </c>
+      <c r="R30" s="72"/>
+      <c r="S30" s="55"/>
+      <c r="T30" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="75">
+        <f t="shared" si="4"/>
+        <v>96</v>
+      </c>
+      <c r="V30" s="75">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="70">
+        <v>1</v>
+      </c>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="75">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="V31" s="75">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="70"/>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="74"/>
+      <c r="O32" s="70"/>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="55"/>
+      <c r="T32" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="70"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="73"/>
+      <c r="N33" s="74"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="55"/>
+      <c r="T33" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="70">
+        <v>17</v>
+      </c>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
+      <c r="J34" s="71"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
+      <c r="L34" s="55"/>
+      <c r="M34" s="73"/>
+      <c r="N34" s="74"/>
+      <c r="O34" s="70">
+        <v>1</v>
+      </c>
+      <c r="P34" s="71">
+        <v>12</v>
+      </c>
+      <c r="Q34" s="71"/>
+      <c r="R34" s="72"/>
+      <c r="S34" s="55"/>
+      <c r="T34" s="58">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="U34" s="75">
+        <f t="shared" si="4"/>
+        <v>446</v>
+      </c>
+      <c r="V34" s="75">
+        <f t="shared" si="5"/>
+        <v>18.583333333333332</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="72"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="74"/>
+      <c r="O35" s="70"/>
+      <c r="P35" s="71"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="72"/>
+      <c r="S35" s="55"/>
+      <c r="T35" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="73"/>
+      <c r="N36" s="74"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="71"/>
+      <c r="Q36" s="71"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="55"/>
+      <c r="T36" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="59">
+        <f>864+1296+53</f>
+        <v>2213</v>
+      </c>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59">
+        <v>4</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>4</v>
+      </c>
+      <c r="K37" s="61">
+        <v>3</v>
+      </c>
+      <c r="L37" s="62"/>
+      <c r="M37" s="63">
+        <v>54</v>
+      </c>
+      <c r="N37" s="64"/>
+      <c r="O37" s="65">
+        <v>30</v>
+      </c>
+      <c r="P37" s="66"/>
+      <c r="Q37" s="66">
+        <v>109</v>
+      </c>
+      <c r="R37" s="67"/>
+      <c r="S37" s="62"/>
+      <c r="T37" s="77">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="U37" s="77">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>14449</v>
+      </c>
+      <c r="V37" s="77">
+        <f>U37/6</f>
+        <v>2408.1666666666665</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="73"/>
+      <c r="N38" s="74"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="71"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="55"/>
+      <c r="T38" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="75">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="75">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="74"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="71"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="95"/>
+      <c r="T39" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U39" s="75">
+        <f>C39*24+M39*24+O39*24+Q39*24+T39</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="75">
+        <f>U39/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="59">
+        <f>63+36</f>
+        <v>99</v>
+      </c>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
+      <c r="L40" s="62"/>
+      <c r="M40" s="63">
+        <v>2</v>
+      </c>
+      <c r="N40" s="64"/>
+      <c r="O40" s="65">
+        <v>1</v>
+      </c>
+      <c r="P40" s="66"/>
+      <c r="Q40" s="66"/>
+      <c r="R40" s="67"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="77">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U40" s="77">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>2468</v>
+      </c>
+      <c r="V40" s="77">
+        <f>U40/24</f>
+        <v>102.83333333333333</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="82">
+        <f>8+96</f>
+        <v>104</v>
+      </c>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="85"/>
+      <c r="M41" s="86"/>
+      <c r="N41" s="87"/>
+      <c r="O41" s="82">
+        <v>6</v>
+      </c>
+      <c r="P41" s="83"/>
+      <c r="Q41" s="83">
+        <v>21</v>
+      </c>
+      <c r="R41" s="84"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="88">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>1572</v>
+      </c>
+      <c r="V41" s="88">
+        <f>U41/12</f>
+        <v>131</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="71"/>
+      <c r="K42" s="72"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="73"/>
+      <c r="N42" s="74"/>
+      <c r="O42" s="70"/>
+      <c r="P42" s="71"/>
+      <c r="Q42" s="71"/>
+      <c r="R42" s="72"/>
+      <c r="S42" s="55"/>
+      <c r="T42" s="75"/>
+      <c r="U42" s="75"/>
+      <c r="V42" s="75"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="65">
+        <f>7776+7776+972+3024+8208+54+3780+6480</f>
+        <v>38070</v>
+      </c>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65">
+        <f>4+6</f>
+        <v>10</v>
+      </c>
+      <c r="I43" s="65">
+        <v>7</v>
+      </c>
+      <c r="J43" s="66">
+        <f>5*6+4</f>
+        <v>34</v>
+      </c>
+      <c r="K43" s="67">
+        <f>64*6+2</f>
+        <v>386</v>
+      </c>
+      <c r="L43" s="62"/>
+      <c r="M43" s="63">
+        <v>595</v>
+      </c>
+      <c r="N43" s="64"/>
+      <c r="O43" s="65">
+        <v>456</v>
+      </c>
+      <c r="P43" s="66"/>
+      <c r="Q43" s="66">
+        <v>542</v>
+      </c>
+      <c r="R43" s="67"/>
+      <c r="S43" s="62"/>
+      <c r="T43" s="77">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>437</v>
+      </c>
+      <c r="U43" s="77">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>238415</v>
+      </c>
+      <c r="V43" s="77">
+        <f>U43/6</f>
+        <v>39735.833333333336</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="70"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="71"/>
+      <c r="K44" s="72"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="73"/>
+      <c r="N44" s="74"/>
+      <c r="O44" s="70"/>
+      <c r="P44" s="71"/>
+      <c r="Q44" s="71"/>
+      <c r="R44" s="72"/>
+      <c r="S44" s="55"/>
+      <c r="T44" s="75"/>
+      <c r="U44" s="75"/>
+      <c r="V44" s="75"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="70"/>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="70"/>
+      <c r="I45" s="70"/>
+      <c r="J45" s="71"/>
+      <c r="K45" s="72"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="73"/>
+      <c r="N45" s="74"/>
+      <c r="O45" s="70">
+        <v>1</v>
+      </c>
+      <c r="P45" s="71"/>
+      <c r="Q45" s="71"/>
+      <c r="R45" s="72"/>
+      <c r="S45" s="55"/>
+      <c r="T45" s="75">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="75">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>24</v>
+      </c>
+      <c r="V45" s="75">
+        <f>U45/24</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="73"/>
+      <c r="N46" s="74"/>
+      <c r="O46" s="70"/>
+      <c r="P46" s="71"/>
+      <c r="Q46" s="71"/>
+      <c r="R46" s="72"/>
+      <c r="S46" s="55"/>
+      <c r="T46" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="75">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="75">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="65">
+        <f>756+64+324+98+540+432+432+106</f>
+        <v>2752</v>
+      </c>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
+      <c r="I47" s="65"/>
+      <c r="J47" s="66">
+        <v>1</v>
+      </c>
+      <c r="K47" s="67">
+        <v>4</v>
+      </c>
+      <c r="L47" s="62"/>
+      <c r="M47" s="63">
+        <v>3</v>
+      </c>
+      <c r="N47" s="64"/>
+      <c r="O47" s="65">
+        <v>9</v>
+      </c>
+      <c r="P47" s="66">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="66">
+        <v>3</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
+      <c r="S47" s="62"/>
+      <c r="T47" s="77">
+        <f t="shared" si="7"/>
+        <v>13</v>
+      </c>
+      <c r="U47" s="77">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>16615</v>
+      </c>
+      <c r="V47" s="77">
+        <f>U47/6</f>
+        <v>2769.1666666666665</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
+      <c r="I48" s="70"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="72"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="73"/>
+      <c r="N48" s="74"/>
+      <c r="O48" s="70"/>
+      <c r="P48" s="71"/>
+      <c r="Q48" s="71"/>
+      <c r="R48" s="72"/>
+      <c r="S48" s="55"/>
+      <c r="T48" s="75">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="U48" s="75">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="V48" s="75">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="70"/>
+      <c r="I49" s="70"/>
+      <c r="J49" s="71"/>
+      <c r="K49" s="72"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="74"/>
+      <c r="O49" s="70"/>
+      <c r="P49" s="71"/>
+      <c r="Q49" s="71"/>
+      <c r="R49" s="72"/>
+      <c r="S49" s="55"/>
+      <c r="T49" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="70"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="70"/>
+      <c r="F50" s="70"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
+      <c r="J50" s="71"/>
+      <c r="K50" s="72"/>
+      <c r="L50" s="55"/>
+      <c r="M50" s="73"/>
+      <c r="N50" s="74"/>
+      <c r="O50" s="70"/>
+      <c r="P50" s="71"/>
+      <c r="Q50" s="71"/>
+      <c r="R50" s="72"/>
+      <c r="S50" s="55"/>
+      <c r="T50" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="65"/>
+      <c r="I51" s="65"/>
+      <c r="J51" s="66"/>
+      <c r="K51" s="67"/>
+      <c r="L51" s="62"/>
+      <c r="M51" s="63"/>
+      <c r="N51" s="64"/>
+      <c r="O51" s="65"/>
+      <c r="P51" s="66"/>
+      <c r="Q51" s="66"/>
+      <c r="R51" s="67"/>
+      <c r="S51" s="62"/>
+      <c r="T51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="77">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>204</v>
+      </c>
+      <c r="V51" s="77">
+        <f>U51/6</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="70"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="70"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="71"/>
+      <c r="K52" s="72"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="73"/>
+      <c r="N52" s="74"/>
+      <c r="O52" s="70"/>
+      <c r="P52" s="71"/>
+      <c r="Q52" s="71"/>
+      <c r="R52" s="72"/>
+      <c r="S52" s="55"/>
+      <c r="T52" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="75">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="70">
+        <v>9</v>
+      </c>
+      <c r="D53" s="70"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="70"/>
+      <c r="H53" s="70"/>
+      <c r="I53" s="70"/>
+      <c r="J53" s="71"/>
+      <c r="K53" s="72"/>
+      <c r="L53" s="55"/>
+      <c r="M53" s="73"/>
+      <c r="N53" s="74"/>
+      <c r="O53" s="70"/>
+      <c r="P53" s="71"/>
+      <c r="Q53" s="71"/>
+      <c r="R53" s="72"/>
+      <c r="S53" s="55"/>
+      <c r="T53" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="75">
+        <f t="shared" si="10"/>
+        <v>216</v>
+      </c>
+      <c r="V53" s="75">
+        <f t="shared" si="9"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="71"/>
+      <c r="K54" s="72"/>
+      <c r="L54" s="55"/>
+      <c r="M54" s="73"/>
+      <c r="N54" s="74"/>
+      <c r="O54" s="70"/>
+      <c r="P54" s="71"/>
+      <c r="Q54" s="71"/>
+      <c r="R54" s="72"/>
+      <c r="S54" s="55"/>
+      <c r="T54" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="70"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="70"/>
+      <c r="I55" s="70"/>
+      <c r="J55" s="71"/>
+      <c r="K55" s="72"/>
+      <c r="L55" s="55"/>
+      <c r="M55" s="73"/>
+      <c r="N55" s="74"/>
+      <c r="O55" s="70"/>
+      <c r="P55" s="71"/>
+      <c r="Q55" s="71"/>
+      <c r="R55" s="72"/>
+      <c r="S55" s="55"/>
+      <c r="T55" s="75"/>
+      <c r="U55" s="75"/>
+      <c r="V55" s="75"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="70"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="70"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="71"/>
+      <c r="K56" s="72"/>
+      <c r="L56" s="55"/>
+      <c r="M56" s="73"/>
+      <c r="N56" s="74"/>
+      <c r="O56" s="70"/>
+      <c r="P56" s="71"/>
+      <c r="Q56" s="71"/>
+      <c r="R56" s="72"/>
+      <c r="S56" s="55"/>
+      <c r="T56" s="75"/>
+      <c r="U56" s="75"/>
+      <c r="V56" s="75"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="70"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="70"/>
+      <c r="I57" s="70"/>
+      <c r="J57" s="71"/>
+      <c r="K57" s="72"/>
+      <c r="L57" s="55"/>
+      <c r="M57" s="73"/>
+      <c r="N57" s="74"/>
+      <c r="O57" s="70"/>
+      <c r="P57" s="71"/>
+      <c r="Q57" s="71"/>
+      <c r="R57" s="72"/>
+      <c r="S57" s="55"/>
+      <c r="T57" s="75"/>
+      <c r="U57" s="75"/>
+      <c r="V57" s="75"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>46289</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>1198</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>33</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>45</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>422</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>683</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>521</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>16</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>712</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>3</v>
+      </c>
+      <c r="S58" s="55"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>1717</v>
+      </c>
+      <c r="U58" s="90">
+        <f>SUM(U7:U57)</f>
+        <v>349405</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>48334.416666666664</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="117" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -45713,21 +48839,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -45739,17 +48865,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -45769,13 +48895,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="129" t="s">
+      <c r="U4" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -45815,10 +48941,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="128"/>
+      <c r="K5" s="129"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -45826,9 +48952,9 @@
       <c r="Q5" s="96"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -48563,17 +51689,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="116" t="s">
+      <c r="C60" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -48882,21 +52008,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -48908,17 +52034,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -48938,13 +52064,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="129" t="s">
+      <c r="U4" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -48984,10 +52110,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="128"/>
+      <c r="K5" s="129"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -48995,9 +52121,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -51692,17 +54818,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="116" t="s">
+      <c r="C60" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -52011,21 +55137,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -52037,17 +55163,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -52067,13 +55193,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="129" t="s">
+      <c r="U4" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -52113,10 +55239,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="128"/>
+      <c r="K5" s="129"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -52124,9 +55250,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -54826,17 +57952,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="116" t="s">
+      <c r="C60" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -55145,21 +58271,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -55171,17 +58297,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -55201,13 +58327,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="129" t="s">
+      <c r="U4" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -55247,10 +58373,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="128"/>
+      <c r="K5" s="129"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -55258,9 +58384,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -57954,17 +61080,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="116" t="s">
+      <c r="C60" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -58273,21 +61399,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -58299,17 +61425,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -58329,13 +61455,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="129" t="s">
+      <c r="U4" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -58375,10 +61501,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="128"/>
+      <c r="K5" s="129"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -58386,9 +61512,9 @@
       <c r="Q5" s="100"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -61084,17 +64210,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="116" t="s">
+      <c r="C60" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -61403,21 +64529,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -61429,17 +64555,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -61459,13 +64585,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="129" t="s">
+      <c r="U4" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -61505,10 +64631,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="128"/>
+      <c r="K5" s="129"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -61516,9 +64642,9 @@
       <c r="Q5" s="101"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -64219,17 +67345,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="116" t="s">
+      <c r="C60" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -64538,21 +67664,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -64564,17 +67690,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -64594,13 +67720,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="129" t="s">
+      <c r="U4" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -64640,10 +67766,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="128"/>
+      <c r="K5" s="129"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -64651,9 +67777,9 @@
       <c r="Q5" s="102"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -67349,17 +70475,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="116" t="s">
+      <c r="C60" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>

--- a/GBDS JUNE FILES 2026/INVENTORY COUNT SHEET - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/INVENTORY COUNT SHEET - JUNE 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9680BA10-488A-4A82-8887-3A327AFF5632}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2329EF36-1266-4418-AF0E-59C34A2252C4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="12" activeTab="21" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="13" activeTab="22" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -35,6 +35,7 @@
     <sheet name="06-25-2026" sheetId="73" r:id="rId20"/>
     <sheet name="06-26-2026" sheetId="74" r:id="rId21"/>
     <sheet name="06-29-2026" sheetId="75" r:id="rId22"/>
+    <sheet name="06-30-2026" sheetId="76" r:id="rId23"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'06-01-2026'!$A$1:$W$59</definedName>
@@ -58,6 +59,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="19">'06-25-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="20">'06-26-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="21">'06-29-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="22">'06-30-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -76,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1848" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1932" uniqueCount="93">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -299,6 +301,63 @@
   </si>
   <si>
     <t>DATE: 06/03/2026</t>
+  </si>
+  <si>
+    <t>DATE: 06/29/2026</t>
+  </si>
+  <si>
+    <t>DATE: 06/30/2026</t>
+  </si>
+  <si>
+    <t>DATE: 06/26/2026</t>
+  </si>
+  <si>
+    <t>DATE: 06/25/2026</t>
+  </si>
+  <si>
+    <t>DATE: 06/24/2026</t>
+  </si>
+  <si>
+    <t>DATE: 06/23/2026</t>
+  </si>
+  <si>
+    <t>DATE: 06/22/2026</t>
+  </si>
+  <si>
+    <t>DATE: 06/19/2026</t>
+  </si>
+  <si>
+    <t>DATE: 06/18/2026</t>
+  </si>
+  <si>
+    <t>DATE: 06/17/2026</t>
+  </si>
+  <si>
+    <t>DATE: 06/16/2026</t>
+  </si>
+  <si>
+    <t>DATE: 06/15/2026</t>
+  </si>
+  <si>
+    <t>DATE: 06/12/2026</t>
+  </si>
+  <si>
+    <t>DATE: 06/11/2026</t>
+  </si>
+  <si>
+    <t>DATE: 06/10/2026</t>
+  </si>
+  <si>
+    <t>DATE: 06/09/2026</t>
+  </si>
+  <si>
+    <t>DATE: 06/08/2026</t>
+  </si>
+  <si>
+    <t>DATE: 06/05/2026</t>
+  </si>
+  <si>
+    <t>DATE: 06/04/2026</t>
   </si>
 </sst>
 </file>
@@ -1285,7 +1344,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1571,6 +1630,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2035,21 +2097,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="120" t="s">
+      <c r="I1" s="121" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="120"/>
-      <c r="S1" s="120"/>
-      <c r="T1" s="120"/>
-      <c r="U1" s="120"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -2061,17 +2123,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="121" t="s">
+      <c r="C4" s="122" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="121"/>
-      <c r="E4" s="121"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="121"/>
-      <c r="I4" s="121"/>
-      <c r="J4" s="122"/>
-      <c r="K4" s="123"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="122"/>
+      <c r="G4" s="122"/>
+      <c r="H4" s="122"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="123"/>
+      <c r="K4" s="124"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -2091,13 +2153,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="124" t="s">
+      <c r="T4" s="125" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="126" t="s">
+      <c r="U4" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="113" t="s">
+      <c r="V4" s="114" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2137,10 +2199,10 @@
       <c r="I5" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="115" t="s">
+      <c r="J5" s="116" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="116"/>
+      <c r="K5" s="117"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2148,9 +2210,9 @@
       <c r="Q5" s="89"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="125"/>
-      <c r="U5" s="127"/>
-      <c r="V5" s="114"/>
+      <c r="T5" s="126"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="115"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -4681,17 +4743,17 @@
       <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="117" t="s">
+      <c r="C62" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="118"/>
-      <c r="E62" s="118"/>
-      <c r="F62" s="118"/>
-      <c r="G62" s="118"/>
-      <c r="H62" s="118"/>
-      <c r="I62" s="118"/>
-      <c r="J62" s="118"/>
-      <c r="K62" s="119"/>
+      <c r="D62" s="119"/>
+      <c r="E62" s="119"/>
+      <c r="F62" s="119"/>
+      <c r="G62" s="119"/>
+      <c r="H62" s="119"/>
+      <c r="I62" s="119"/>
+      <c r="J62" s="119"/>
+      <c r="K62" s="120"/>
       <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
@@ -5000,25 +5062,25 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="120" t="s">
+      <c r="I1" s="121" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="120"/>
-      <c r="S1" s="120"/>
-      <c r="T1" s="120"/>
-      <c r="U1" s="120"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -5026,17 +5088,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="121" t="s">
+      <c r="C4" s="122" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="121"/>
-      <c r="E4" s="121"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="121"/>
-      <c r="I4" s="121"/>
-      <c r="J4" s="122"/>
-      <c r="K4" s="123"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="122"/>
+      <c r="G4" s="122"/>
+      <c r="H4" s="122"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="123"/>
+      <c r="K4" s="124"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -5056,13 +5118,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="124" t="s">
+      <c r="T4" s="125" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="130" t="s">
+      <c r="U4" s="131" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="113" t="s">
+      <c r="V4" s="114" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -5102,10 +5164,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="128" t="s">
+      <c r="J5" s="129" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="129"/>
+      <c r="K5" s="130"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -5113,9 +5175,9 @@
       <c r="Q5" s="103"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="125"/>
-      <c r="U5" s="131"/>
-      <c r="V5" s="114"/>
+      <c r="T5" s="126"/>
+      <c r="U5" s="132"/>
+      <c r="V5" s="115"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -7800,17 +7862,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="117" t="s">
+      <c r="C60" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="118"/>
-      <c r="E60" s="118"/>
-      <c r="F60" s="118"/>
-      <c r="G60" s="118"/>
-      <c r="H60" s="118"/>
-      <c r="I60" s="118"/>
-      <c r="J60" s="118"/>
-      <c r="K60" s="119"/>
+      <c r="D60" s="119"/>
+      <c r="E60" s="119"/>
+      <c r="F60" s="119"/>
+      <c r="G60" s="119"/>
+      <c r="H60" s="119"/>
+      <c r="I60" s="119"/>
+      <c r="J60" s="119"/>
+      <c r="K60" s="120"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -8119,25 +8181,25 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="120" t="s">
+      <c r="I1" s="121" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="120"/>
-      <c r="S1" s="120"/>
-      <c r="T1" s="120"/>
-      <c r="U1" s="120"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -8145,17 +8207,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="121" t="s">
+      <c r="C4" s="122" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="121"/>
-      <c r="E4" s="121"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="121"/>
-      <c r="I4" s="121"/>
-      <c r="J4" s="122"/>
-      <c r="K4" s="123"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="122"/>
+      <c r="G4" s="122"/>
+      <c r="H4" s="122"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="123"/>
+      <c r="K4" s="124"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -8175,13 +8237,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="124" t="s">
+      <c r="T4" s="125" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="130" t="s">
+      <c r="U4" s="131" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="113" t="s">
+      <c r="V4" s="114" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -8221,10 +8283,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="128" t="s">
+      <c r="J5" s="129" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="129"/>
+      <c r="K5" s="130"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -8232,9 +8294,9 @@
       <c r="Q5" s="104"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="125"/>
-      <c r="U5" s="131"/>
-      <c r="V5" s="114"/>
+      <c r="T5" s="126"/>
+      <c r="U5" s="132"/>
+      <c r="V5" s="115"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -10928,17 +10990,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="117" t="s">
+      <c r="C60" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="118"/>
-      <c r="E60" s="118"/>
-      <c r="F60" s="118"/>
-      <c r="G60" s="118"/>
-      <c r="H60" s="118"/>
-      <c r="I60" s="118"/>
-      <c r="J60" s="118"/>
-      <c r="K60" s="119"/>
+      <c r="D60" s="119"/>
+      <c r="E60" s="119"/>
+      <c r="F60" s="119"/>
+      <c r="G60" s="119"/>
+      <c r="H60" s="119"/>
+      <c r="I60" s="119"/>
+      <c r="J60" s="119"/>
+      <c r="K60" s="120"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -11247,25 +11309,25 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="120" t="s">
+      <c r="I1" s="121" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="120"/>
-      <c r="S1" s="120"/>
-      <c r="T1" s="120"/>
-      <c r="U1" s="120"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -11273,17 +11335,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="121" t="s">
+      <c r="C4" s="122" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="121"/>
-      <c r="E4" s="121"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="121"/>
-      <c r="I4" s="121"/>
-      <c r="J4" s="122"/>
-      <c r="K4" s="123"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="122"/>
+      <c r="G4" s="122"/>
+      <c r="H4" s="122"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="123"/>
+      <c r="K4" s="124"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -11303,13 +11365,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="124" t="s">
+      <c r="T4" s="125" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="130" t="s">
+      <c r="U4" s="131" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="113" t="s">
+      <c r="V4" s="114" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -11349,10 +11411,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="128" t="s">
+      <c r="J5" s="129" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="129"/>
+      <c r="K5" s="130"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -11360,9 +11422,9 @@
       <c r="Q5" s="105"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="125"/>
-      <c r="U5" s="131"/>
-      <c r="V5" s="114"/>
+      <c r="T5" s="126"/>
+      <c r="U5" s="132"/>
+      <c r="V5" s="115"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -14057,17 +14119,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="117" t="s">
+      <c r="C60" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="118"/>
-      <c r="E60" s="118"/>
-      <c r="F60" s="118"/>
-      <c r="G60" s="118"/>
-      <c r="H60" s="118"/>
-      <c r="I60" s="118"/>
-      <c r="J60" s="118"/>
-      <c r="K60" s="119"/>
+      <c r="D60" s="119"/>
+      <c r="E60" s="119"/>
+      <c r="F60" s="119"/>
+      <c r="G60" s="119"/>
+      <c r="H60" s="119"/>
+      <c r="I60" s="119"/>
+      <c r="J60" s="119"/>
+      <c r="K60" s="120"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -14376,25 +14438,25 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="120" t="s">
+      <c r="I1" s="121" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="120"/>
-      <c r="S1" s="120"/>
-      <c r="T1" s="120"/>
-      <c r="U1" s="120"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -14402,17 +14464,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="121" t="s">
+      <c r="C4" s="122" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="121"/>
-      <c r="E4" s="121"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="121"/>
-      <c r="I4" s="121"/>
-      <c r="J4" s="122"/>
-      <c r="K4" s="123"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="122"/>
+      <c r="G4" s="122"/>
+      <c r="H4" s="122"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="123"/>
+      <c r="K4" s="124"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -14432,13 +14494,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="124" t="s">
+      <c r="T4" s="125" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="130" t="s">
+      <c r="U4" s="131" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="113" t="s">
+      <c r="V4" s="114" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -14478,10 +14540,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="128" t="s">
+      <c r="J5" s="129" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="129"/>
+      <c r="K5" s="130"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -14489,9 +14551,9 @@
       <c r="Q5" s="106"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="125"/>
-      <c r="U5" s="131"/>
-      <c r="V5" s="114"/>
+      <c r="T5" s="126"/>
+      <c r="U5" s="132"/>
+      <c r="V5" s="115"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -17184,17 +17246,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="117" t="s">
+      <c r="C60" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="118"/>
-      <c r="E60" s="118"/>
-      <c r="F60" s="118"/>
-      <c r="G60" s="118"/>
-      <c r="H60" s="118"/>
-      <c r="I60" s="118"/>
-      <c r="J60" s="118"/>
-      <c r="K60" s="119"/>
+      <c r="D60" s="119"/>
+      <c r="E60" s="119"/>
+      <c r="F60" s="119"/>
+      <c r="G60" s="119"/>
+      <c r="H60" s="119"/>
+      <c r="I60" s="119"/>
+      <c r="J60" s="119"/>
+      <c r="K60" s="120"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -17503,25 +17565,25 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="120" t="s">
+      <c r="I1" s="121" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="120"/>
-      <c r="S1" s="120"/>
-      <c r="T1" s="120"/>
-      <c r="U1" s="120"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -17529,17 +17591,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="121" t="s">
+      <c r="C4" s="122" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="121"/>
-      <c r="E4" s="121"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="121"/>
-      <c r="I4" s="121"/>
-      <c r="J4" s="122"/>
-      <c r="K4" s="123"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="122"/>
+      <c r="G4" s="122"/>
+      <c r="H4" s="122"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="123"/>
+      <c r="K4" s="124"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -17559,13 +17621,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="124" t="s">
+      <c r="T4" s="125" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="130" t="s">
+      <c r="U4" s="131" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="113" t="s">
+      <c r="V4" s="114" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -17605,10 +17667,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="128" t="s">
+      <c r="J5" s="129" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="129"/>
+      <c r="K5" s="130"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -17616,9 +17678,9 @@
       <c r="Q5" s="107"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="125"/>
-      <c r="U5" s="131"/>
-      <c r="V5" s="114"/>
+      <c r="T5" s="126"/>
+      <c r="U5" s="132"/>
+      <c r="V5" s="115"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -20307,17 +20369,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="117" t="s">
+      <c r="C60" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="118"/>
-      <c r="E60" s="118"/>
-      <c r="F60" s="118"/>
-      <c r="G60" s="118"/>
-      <c r="H60" s="118"/>
-      <c r="I60" s="118"/>
-      <c r="J60" s="118"/>
-      <c r="K60" s="119"/>
+      <c r="D60" s="119"/>
+      <c r="E60" s="119"/>
+      <c r="F60" s="119"/>
+      <c r="G60" s="119"/>
+      <c r="H60" s="119"/>
+      <c r="I60" s="119"/>
+      <c r="J60" s="119"/>
+      <c r="K60" s="120"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -20626,25 +20688,25 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="120" t="s">
+      <c r="I1" s="121" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="120"/>
-      <c r="S1" s="120"/>
-      <c r="T1" s="120"/>
-      <c r="U1" s="120"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -20652,17 +20714,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="121" t="s">
+      <c r="C4" s="122" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="121"/>
-      <c r="E4" s="121"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="121"/>
-      <c r="I4" s="121"/>
-      <c r="J4" s="122"/>
-      <c r="K4" s="123"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="122"/>
+      <c r="G4" s="122"/>
+      <c r="H4" s="122"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="123"/>
+      <c r="K4" s="124"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -20682,13 +20744,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="124" t="s">
+      <c r="T4" s="125" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="130" t="s">
+      <c r="U4" s="131" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="113" t="s">
+      <c r="V4" s="114" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -20728,10 +20790,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="128" t="s">
+      <c r="J5" s="129" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="129"/>
+      <c r="K5" s="130"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -20739,9 +20801,9 @@
       <c r="Q5" s="107"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="125"/>
-      <c r="U5" s="131"/>
-      <c r="V5" s="114"/>
+      <c r="T5" s="126"/>
+      <c r="U5" s="132"/>
+      <c r="V5" s="115"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -23430,17 +23492,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="117" t="s">
+      <c r="C60" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="118"/>
-      <c r="E60" s="118"/>
-      <c r="F60" s="118"/>
-      <c r="G60" s="118"/>
-      <c r="H60" s="118"/>
-      <c r="I60" s="118"/>
-      <c r="J60" s="118"/>
-      <c r="K60" s="119"/>
+      <c r="D60" s="119"/>
+      <c r="E60" s="119"/>
+      <c r="F60" s="119"/>
+      <c r="G60" s="119"/>
+      <c r="H60" s="119"/>
+      <c r="I60" s="119"/>
+      <c r="J60" s="119"/>
+      <c r="K60" s="120"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -23749,25 +23811,25 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="120" t="s">
+      <c r="I1" s="121" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="120"/>
-      <c r="S1" s="120"/>
-      <c r="T1" s="120"/>
-      <c r="U1" s="120"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -23775,17 +23837,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="121" t="s">
+      <c r="C4" s="122" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="121"/>
-      <c r="E4" s="121"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="121"/>
-      <c r="I4" s="121"/>
-      <c r="J4" s="122"/>
-      <c r="K4" s="123"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="122"/>
+      <c r="G4" s="122"/>
+      <c r="H4" s="122"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="123"/>
+      <c r="K4" s="124"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -23805,13 +23867,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="124" t="s">
+      <c r="T4" s="125" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="130" t="s">
+      <c r="U4" s="131" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="113" t="s">
+      <c r="V4" s="114" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -23851,10 +23913,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="128" t="s">
+      <c r="J5" s="129" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="129"/>
+      <c r="K5" s="130"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -23862,9 +23924,9 @@
       <c r="Q5" s="107"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="125"/>
-      <c r="U5" s="131"/>
-      <c r="V5" s="114"/>
+      <c r="T5" s="126"/>
+      <c r="U5" s="132"/>
+      <c r="V5" s="115"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -26562,17 +26624,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="117" t="s">
+      <c r="C60" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="118"/>
-      <c r="E60" s="118"/>
-      <c r="F60" s="118"/>
-      <c r="G60" s="118"/>
-      <c r="H60" s="118"/>
-      <c r="I60" s="118"/>
-      <c r="J60" s="118"/>
-      <c r="K60" s="119"/>
+      <c r="D60" s="119"/>
+      <c r="E60" s="119"/>
+      <c r="F60" s="119"/>
+      <c r="G60" s="119"/>
+      <c r="H60" s="119"/>
+      <c r="I60" s="119"/>
+      <c r="J60" s="119"/>
+      <c r="K60" s="120"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -26881,25 +26943,25 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="120" t="s">
+      <c r="I1" s="121" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="120"/>
-      <c r="S1" s="120"/>
-      <c r="T1" s="120"/>
-      <c r="U1" s="120"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -26907,17 +26969,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="121" t="s">
+      <c r="C4" s="122" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="121"/>
-      <c r="E4" s="121"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="121"/>
-      <c r="I4" s="121"/>
-      <c r="J4" s="122"/>
-      <c r="K4" s="123"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="122"/>
+      <c r="G4" s="122"/>
+      <c r="H4" s="122"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="123"/>
+      <c r="K4" s="124"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -26937,13 +26999,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="124" t="s">
+      <c r="T4" s="125" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="130" t="s">
+      <c r="U4" s="131" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="113" t="s">
+      <c r="V4" s="114" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -26983,10 +27045,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="128" t="s">
+      <c r="J5" s="129" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="129"/>
+      <c r="K5" s="130"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -26994,9 +27056,9 @@
       <c r="Q5" s="107"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="125"/>
-      <c r="U5" s="131"/>
-      <c r="V5" s="114"/>
+      <c r="T5" s="126"/>
+      <c r="U5" s="132"/>
+      <c r="V5" s="115"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -29704,17 +29766,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="117" t="s">
+      <c r="C60" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="118"/>
-      <c r="E60" s="118"/>
-      <c r="F60" s="118"/>
-      <c r="G60" s="118"/>
-      <c r="H60" s="118"/>
-      <c r="I60" s="118"/>
-      <c r="J60" s="118"/>
-      <c r="K60" s="119"/>
+      <c r="D60" s="119"/>
+      <c r="E60" s="119"/>
+      <c r="F60" s="119"/>
+      <c r="G60" s="119"/>
+      <c r="H60" s="119"/>
+      <c r="I60" s="119"/>
+      <c r="J60" s="119"/>
+      <c r="K60" s="120"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -30023,25 +30085,25 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="120" t="s">
+      <c r="I1" s="121" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="120"/>
-      <c r="S1" s="120"/>
-      <c r="T1" s="120"/>
-      <c r="U1" s="120"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -30049,17 +30111,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="121" t="s">
+      <c r="C4" s="122" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="121"/>
-      <c r="E4" s="121"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="121"/>
-      <c r="I4" s="121"/>
-      <c r="J4" s="122"/>
-      <c r="K4" s="123"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="122"/>
+      <c r="G4" s="122"/>
+      <c r="H4" s="122"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="123"/>
+      <c r="K4" s="124"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -30079,13 +30141,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="124" t="s">
+      <c r="T4" s="125" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="130" t="s">
+      <c r="U4" s="131" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="113" t="s">
+      <c r="V4" s="114" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -30125,10 +30187,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="128" t="s">
+      <c r="J5" s="129" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="129"/>
+      <c r="K5" s="130"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -30136,9 +30198,9 @@
       <c r="Q5" s="108"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="125"/>
-      <c r="U5" s="131"/>
-      <c r="V5" s="114"/>
+      <c r="T5" s="126"/>
+      <c r="U5" s="132"/>
+      <c r="V5" s="115"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -32832,17 +32894,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="117" t="s">
+      <c r="C60" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="118"/>
-      <c r="E60" s="118"/>
-      <c r="F60" s="118"/>
-      <c r="G60" s="118"/>
-      <c r="H60" s="118"/>
-      <c r="I60" s="118"/>
-      <c r="J60" s="118"/>
-      <c r="K60" s="119"/>
+      <c r="D60" s="119"/>
+      <c r="E60" s="119"/>
+      <c r="F60" s="119"/>
+      <c r="G60" s="119"/>
+      <c r="H60" s="119"/>
+      <c r="I60" s="119"/>
+      <c r="J60" s="119"/>
+      <c r="K60" s="120"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -33151,25 +33213,25 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="120" t="s">
+      <c r="I1" s="121" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="120"/>
-      <c r="S1" s="120"/>
-      <c r="T1" s="120"/>
-      <c r="U1" s="120"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -33177,17 +33239,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="121" t="s">
+      <c r="C4" s="122" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="121"/>
-      <c r="E4" s="121"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="121"/>
-      <c r="I4" s="121"/>
-      <c r="J4" s="122"/>
-      <c r="K4" s="123"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="122"/>
+      <c r="G4" s="122"/>
+      <c r="H4" s="122"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="123"/>
+      <c r="K4" s="124"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -33207,13 +33269,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="124" t="s">
+      <c r="T4" s="125" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="130" t="s">
+      <c r="U4" s="131" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="113" t="s">
+      <c r="V4" s="114" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -33253,10 +33315,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="128" t="s">
+      <c r="J5" s="129" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="129"/>
+      <c r="K5" s="130"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -33264,9 +33326,9 @@
       <c r="Q5" s="109"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="125"/>
-      <c r="U5" s="131"/>
-      <c r="V5" s="114"/>
+      <c r="T5" s="126"/>
+      <c r="U5" s="132"/>
+      <c r="V5" s="115"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -35980,17 +36042,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="117" t="s">
+      <c r="C60" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="118"/>
-      <c r="E60" s="118"/>
-      <c r="F60" s="118"/>
-      <c r="G60" s="118"/>
-      <c r="H60" s="118"/>
-      <c r="I60" s="118"/>
-      <c r="J60" s="118"/>
-      <c r="K60" s="119"/>
+      <c r="D60" s="119"/>
+      <c r="E60" s="119"/>
+      <c r="F60" s="119"/>
+      <c r="G60" s="119"/>
+      <c r="H60" s="119"/>
+      <c r="I60" s="119"/>
+      <c r="J60" s="119"/>
+      <c r="K60" s="120"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -36299,21 +36361,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="120" t="s">
+      <c r="I1" s="121" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="120"/>
-      <c r="S1" s="120"/>
-      <c r="T1" s="120"/>
-      <c r="U1" s="120"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -36325,17 +36387,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="121" t="s">
+      <c r="C4" s="122" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="121"/>
-      <c r="E4" s="121"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="121"/>
-      <c r="I4" s="121"/>
-      <c r="J4" s="122"/>
-      <c r="K4" s="123"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="122"/>
+      <c r="G4" s="122"/>
+      <c r="H4" s="122"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="123"/>
+      <c r="K4" s="124"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -36355,13 +36417,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="124" t="s">
+      <c r="T4" s="125" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="130" t="s">
+      <c r="U4" s="131" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="113" t="s">
+      <c r="V4" s="114" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -36401,10 +36463,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="128" t="s">
+      <c r="J5" s="129" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="129"/>
+      <c r="K5" s="130"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -36412,9 +36474,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="125"/>
-      <c r="U5" s="131"/>
-      <c r="V5" s="114"/>
+      <c r="T5" s="126"/>
+      <c r="U5" s="132"/>
+      <c r="V5" s="115"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -39126,17 +39188,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="117" t="s">
+      <c r="C60" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="118"/>
-      <c r="E60" s="118"/>
-      <c r="F60" s="118"/>
-      <c r="G60" s="118"/>
-      <c r="H60" s="118"/>
-      <c r="I60" s="118"/>
-      <c r="J60" s="118"/>
-      <c r="K60" s="119"/>
+      <c r="D60" s="119"/>
+      <c r="E60" s="119"/>
+      <c r="F60" s="119"/>
+      <c r="G60" s="119"/>
+      <c r="H60" s="119"/>
+      <c r="I60" s="119"/>
+      <c r="J60" s="119"/>
+      <c r="K60" s="120"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -39445,25 +39507,25 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="120" t="s">
+      <c r="I1" s="121" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="120"/>
-      <c r="S1" s="120"/>
-      <c r="T1" s="120"/>
-      <c r="U1" s="120"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -39471,17 +39533,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="121" t="s">
+      <c r="C4" s="122" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="121"/>
-      <c r="E4" s="121"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="121"/>
-      <c r="I4" s="121"/>
-      <c r="J4" s="122"/>
-      <c r="K4" s="123"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="122"/>
+      <c r="G4" s="122"/>
+      <c r="H4" s="122"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="123"/>
+      <c r="K4" s="124"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -39501,13 +39563,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="124" t="s">
+      <c r="T4" s="125" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="130" t="s">
+      <c r="U4" s="131" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="113" t="s">
+      <c r="V4" s="114" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -39547,10 +39609,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="128" t="s">
+      <c r="J5" s="129" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="129"/>
+      <c r="K5" s="130"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -39558,9 +39620,9 @@
       <c r="Q5" s="110"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="125"/>
-      <c r="U5" s="131"/>
-      <c r="V5" s="114"/>
+      <c r="T5" s="126"/>
+      <c r="U5" s="132"/>
+      <c r="V5" s="115"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -42271,17 +42333,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="117" t="s">
+      <c r="C60" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="118"/>
-      <c r="E60" s="118"/>
-      <c r="F60" s="118"/>
-      <c r="G60" s="118"/>
-      <c r="H60" s="118"/>
-      <c r="I60" s="118"/>
-      <c r="J60" s="118"/>
-      <c r="K60" s="119"/>
+      <c r="D60" s="119"/>
+      <c r="E60" s="119"/>
+      <c r="F60" s="119"/>
+      <c r="G60" s="119"/>
+      <c r="H60" s="119"/>
+      <c r="I60" s="119"/>
+      <c r="J60" s="119"/>
+      <c r="K60" s="120"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -42590,25 +42652,25 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="120" t="s">
+      <c r="I1" s="121" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="120"/>
-      <c r="S1" s="120"/>
-      <c r="T1" s="120"/>
-      <c r="U1" s="120"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -42616,17 +42678,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="121" t="s">
+      <c r="C4" s="122" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="121"/>
-      <c r="E4" s="121"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="121"/>
-      <c r="I4" s="121"/>
-      <c r="J4" s="122"/>
-      <c r="K4" s="123"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="122"/>
+      <c r="G4" s="122"/>
+      <c r="H4" s="122"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="123"/>
+      <c r="K4" s="124"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -42646,13 +42708,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="124" t="s">
+      <c r="T4" s="125" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="130" t="s">
+      <c r="U4" s="131" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="113" t="s">
+      <c r="V4" s="114" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -42692,10 +42754,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="128" t="s">
+      <c r="J5" s="129" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="129"/>
+      <c r="K5" s="130"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -42703,9 +42765,9 @@
       <c r="Q5" s="111"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="125"/>
-      <c r="U5" s="131"/>
-      <c r="V5" s="114"/>
+      <c r="T5" s="126"/>
+      <c r="U5" s="132"/>
+      <c r="V5" s="115"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -45399,17 +45461,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="117" t="s">
+      <c r="C60" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="118"/>
-      <c r="E60" s="118"/>
-      <c r="F60" s="118"/>
-      <c r="G60" s="118"/>
-      <c r="H60" s="118"/>
-      <c r="I60" s="118"/>
-      <c r="J60" s="118"/>
-      <c r="K60" s="119"/>
+      <c r="D60" s="119"/>
+      <c r="E60" s="119"/>
+      <c r="F60" s="119"/>
+      <c r="G60" s="119"/>
+      <c r="H60" s="119"/>
+      <c r="I60" s="119"/>
+      <c r="J60" s="119"/>
+      <c r="K60" s="120"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -45718,25 +45780,25 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="120" t="s">
+      <c r="I1" s="121" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="120"/>
-      <c r="S1" s="120"/>
-      <c r="T1" s="120"/>
-      <c r="U1" s="120"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -45744,17 +45806,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="121" t="s">
+      <c r="C4" s="122" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="121"/>
-      <c r="E4" s="121"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="121"/>
-      <c r="I4" s="121"/>
-      <c r="J4" s="122"/>
-      <c r="K4" s="123"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="122"/>
+      <c r="G4" s="122"/>
+      <c r="H4" s="122"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="123"/>
+      <c r="K4" s="124"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -45774,13 +45836,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="124" t="s">
+      <c r="T4" s="125" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="130" t="s">
+      <c r="U4" s="131" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="113" t="s">
+      <c r="V4" s="114" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -45820,10 +45882,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="128" t="s">
+      <c r="J5" s="129" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="129"/>
+      <c r="K5" s="130"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -45831,9 +45893,9 @@
       <c r="Q5" s="112"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="125"/>
-      <c r="U5" s="131"/>
-      <c r="V5" s="114"/>
+      <c r="T5" s="126"/>
+      <c r="U5" s="132"/>
+      <c r="V5" s="115"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -48520,17 +48582,3142 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="117" t="s">
+      <c r="C60" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="118"/>
-      <c r="E60" s="118"/>
-      <c r="F60" s="118"/>
-      <c r="G60" s="118"/>
-      <c r="H60" s="118"/>
-      <c r="I60" s="118"/>
-      <c r="J60" s="118"/>
-      <c r="K60" s="119"/>
+      <c r="D60" s="119"/>
+      <c r="E60" s="119"/>
+      <c r="F60" s="119"/>
+      <c r="G60" s="119"/>
+      <c r="H60" s="119"/>
+      <c r="I60" s="119"/>
+      <c r="J60" s="119"/>
+      <c r="K60" s="120"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r=